--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -340,10 +340,10 @@
     <t>DEF_C</t>
   </si>
   <si>
+    <t>STG</t>
+  </si>
+  <si>
     <t>*HPS*</t>
-  </si>
-  <si>
-    <t>STG</t>
   </si>
   <si>
     <t>AuxStoOUT</t>
@@ -1565,6 +1565,12 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1576,12 +1582,6 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="40">
@@ -5023,7 +5023,7 @@
   <cols>
     <col min="2" max="2" width="25.5272727272727" customWidth="1"/>
     <col min="3" max="3" width="16.4636363636364" customWidth="1"/>
-    <col min="4" max="4" width="4.8" customWidth="1"/>
+    <col min="4" max="4" width="28.5454545454545" customWidth="1"/>
     <col min="5" max="5" width="43.7272727272727" customWidth="1"/>
     <col min="8" max="8" width="10.1818181818182" customWidth="1"/>
   </cols>
@@ -5193,10 +5193,10 @@
       </c>
     </row>
     <row r="24" spans="2:13">
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>72</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>73</v>
       </c>
       <c r="F24" t="s">
@@ -5207,11 +5207,11 @@
       </c>
     </row>
     <row r="25" spans="2:13">
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
         <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>73</v>
       </c>
       <c r="F25" t="str">
         <f>F24</f>

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="2"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="C35" authorId="0">
+    <comment ref="C34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1565,15 +1565,15 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -1581,7 +1581,7 @@
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="40">
@@ -1594,6 +1594,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1618,12 +1624,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1977,7 +1977,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2072,7 +2072,7 @@
     <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2081,14 +2081,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2099,23 +2103,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="13"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="14"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2138,7 +2141,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="54"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="16" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="16" applyFont="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="54" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="53" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="24"/>
@@ -2508,2385 +2511,2385 @@
   <dimension ref="B2:AE92"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.13636363636364" style="32" customWidth="1"/>
-    <col min="2" max="2" width="9.86363636363636" style="32" customWidth="1"/>
-    <col min="3" max="3" width="8.46363636363636" style="32" customWidth="1"/>
-    <col min="4" max="4" width="12.8" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5" style="32" customWidth="1"/>
-    <col min="6" max="6" width="14.2" style="32" customWidth="1"/>
-    <col min="7" max="7" width="6.86363636363636" style="32" customWidth="1"/>
-    <col min="8" max="8" width="10.4636363636364" style="32" customWidth="1"/>
-    <col min="9" max="9" width="8.46363636363636" style="32" customWidth="1"/>
-    <col min="10" max="10" width="5.13636363636364" style="32" customWidth="1"/>
-    <col min="11" max="12" width="5" style="32" customWidth="1"/>
-    <col min="13" max="256" width="11.4636363636364" style="32" customWidth="1"/>
-    <col min="257" max="16384" width="9.13636363636364" style="32"/>
+    <col min="1" max="1" width="9.13636363636364" style="33" customWidth="1"/>
+    <col min="2" max="2" width="9.86363636363636" style="33" customWidth="1"/>
+    <col min="3" max="3" width="8.46363636363636" style="33" customWidth="1"/>
+    <col min="4" max="4" width="12.8" style="33" customWidth="1"/>
+    <col min="5" max="5" width="5" style="33" customWidth="1"/>
+    <col min="6" max="6" width="14.2" style="33" customWidth="1"/>
+    <col min="7" max="7" width="6.86363636363636" style="33" customWidth="1"/>
+    <col min="8" max="8" width="10.4636363636364" style="33" customWidth="1"/>
+    <col min="9" max="9" width="8.46363636363636" style="33" customWidth="1"/>
+    <col min="10" max="10" width="5.13636363636364" style="33" customWidth="1"/>
+    <col min="11" max="12" width="5" style="33" customWidth="1"/>
+    <col min="13" max="256" width="11.4636363636364" style="33" customWidth="1"/>
+    <col min="257" max="16384" width="9.13636363636364" style="33"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:31">
-      <c r="B2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="32" t="s">
+      <c r="B2" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="14.5" spans="2:31">
-      <c r="B3" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="33" t="s">
+      <c r="B3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="34" t="s">
         <v>8</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
-      <c r="Y3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="32" t="s">
+      <c r="Y3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AB3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="32" t="s">
+      <c r="AC3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="32" t="s">
+      <c r="AD3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="AE3" s="32" t="s">
+      <c r="AE3" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="14.5" spans="2:31">
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="33" t="s">
         <v>9</v>
       </c>
       <c r="H4">
         <v>0.1</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="33" t="s">
         <v>10</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
-      <c r="T4" s="35" t="s">
+      <c r="T4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="U4" s="35" t="s">
+      <c r="U4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="35" t="s">
+      <c r="V4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="35" t="s">
+      <c r="W4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AD4" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="AE4" s="32">
+      <c r="AE4" s="33">
         <f>1.10926234054354*H39</f>
         <v>1.20144204104271</v>
       </c>
     </row>
     <row r="5" ht="14.5" spans="2:31">
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="33">
         <v>2020</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
-      <c r="T5" s="35" t="s">
+      <c r="T5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U5" s="35" t="s">
+      <c r="U5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V5" s="35">
+      <c r="V5" s="36">
         <v>2001</v>
       </c>
-      <c r="W5" s="35">
+      <c r="W5" s="36">
         <v>0.762827515602112</v>
       </c>
-      <c r="AA5" s="32" t="s">
+      <c r="AA5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AD5" s="32" t="s">
+      <c r="AD5" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="AE5" s="32">
+      <c r="AE5" s="33">
         <f>O6</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="2:31">
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="33">
         <v>1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="O6" s="36">
+      <c r="O6" s="37">
         <v>0.07</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="P6" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="35" t="s">
+      <c r="T6" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="36">
         <v>2002</v>
       </c>
-      <c r="W6" s="35">
+      <c r="W6" s="36">
         <v>0.774460315704346</v>
       </c>
-      <c r="AA6" s="35" t="s">
+      <c r="AA6" s="36" t="s">
         <v>15</v>
       </c>
       <c r="AB6"/>
-      <c r="AC6" s="35" t="s">
+      <c r="AC6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="AD6" s="35" t="s">
+      <c r="AD6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="AE6" s="37">
+      <c r="AE6" s="38">
         <f>H45</f>
         <v>0.9896</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:31">
-      <c r="D7" s="32" t="str">
+      <c r="D7" s="33" t="str">
         <f>IF(F7=G7,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="32" t="str">
+      <c r="G7" s="33" t="str">
         <f>"USD"&amp;RIGHT(O9,2)</f>
         <v>USD83</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="39">
         <f>ROUND($P$46/P9,4)</f>
         <v>2.2201</v>
       </c>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U7" s="35" t="s">
+      <c r="U7" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V7" s="35">
+      <c r="V7" s="36">
         <v>2003</v>
       </c>
-      <c r="W7" s="35">
+      <c r="W7" s="36">
         <v>0.789065361022949</v>
       </c>
-      <c r="AA7" s="35" t="s">
+      <c r="AA7" s="36" t="s">
         <v>21</v>
       </c>
       <c r="AB7"/>
       <c r="AC7"/>
-      <c r="AD7" s="35" t="s">
+      <c r="AD7" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="AE7" s="35">
+      <c r="AE7" s="36">
         <f>AE5</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:31">
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="33" t="str">
         <f t="shared" ref="D8:D42" si="0">IF(F8=G8,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="33" t="str">
         <f t="shared" ref="G8:G42" si="1">"USD"&amp;RIGHT(O10,2)</f>
         <v>USD84</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="39">
         <f t="shared" ref="H8:H49" si="2">ROUND($P$46/P10,4)</f>
         <v>2.1427</v>
       </c>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39" t="s">
+      <c r="O8" s="40"/>
+      <c r="P8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U8" s="35" t="s">
+      <c r="U8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V8" s="35">
+      <c r="V8" s="36">
         <v>2004</v>
       </c>
-      <c r="W8" s="35">
+      <c r="W8" s="36">
         <v>0.810197472572327</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:31">
-      <c r="D9" s="32" t="str">
+      <c r="D9" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="32" t="str">
+      <c r="G9" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD85</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="39">
         <f t="shared" si="2"/>
         <v>2.077</v>
       </c>
-      <c r="O9" s="39">
+      <c r="O9" s="40">
         <v>1983</v>
       </c>
-      <c r="P9" s="40">
+      <c r="P9" s="41">
         <f>VLOOKUP(O9,$V$5:$W$99,2,FALSE)</f>
         <v>0.487872630357742</v>
       </c>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U9" s="35" t="s">
+      <c r="U9" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V9" s="35">
+      <c r="V9" s="36">
         <v>2005</v>
       </c>
-      <c r="W9" s="35">
+      <c r="W9" s="36">
         <v>0.835319578647614</v>
       </c>
     </row>
     <row r="10" ht="14.5" spans="2:31">
-      <c r="D10" s="32" t="str">
+      <c r="D10" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="32" t="str">
+      <c r="G10" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD86</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="39">
         <f t="shared" si="2"/>
         <v>2.0358</v>
       </c>
-      <c r="O10" s="39">
+      <c r="O10" s="40">
         <v>1984</v>
       </c>
-      <c r="P10" s="40">
+      <c r="P10" s="41">
         <f t="shared" ref="P10:P51" si="3">VLOOKUP(O10,$V$5:$W$99,2,FALSE)</f>
         <v>0.505495131015778</v>
       </c>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U10" s="35" t="s">
+      <c r="U10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V10" s="35">
+      <c r="V10" s="36">
         <v>2006</v>
       </c>
-      <c r="W10" s="35">
+      <c r="W10" s="36">
         <v>0.860807240009308</v>
       </c>
     </row>
     <row r="11" ht="14.5" spans="2:31">
-      <c r="D11" s="32" t="str">
+      <c r="D11" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="32" t="str">
+      <c r="G11" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD87</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="39">
         <f t="shared" si="2"/>
         <v>1.987</v>
       </c>
-      <c r="O11" s="39">
+      <c r="O11" s="40">
         <v>1985</v>
       </c>
-      <c r="P11" s="40">
+      <c r="P11" s="41">
         <f t="shared" si="3"/>
         <v>0.521485805511475</v>
       </c>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U11" s="35" t="s">
+      <c r="U11" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V11" s="35">
+      <c r="V11" s="36">
         <v>2007</v>
       </c>
-      <c r="W11" s="35">
+      <c r="W11" s="36">
         <v>0.883970141410828</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="2:31">
-      <c r="D12" s="32" t="str">
+      <c r="D12" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="32" t="str">
+      <c r="G12" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD88</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="39">
         <f t="shared" si="2"/>
         <v>1.9192</v>
       </c>
-      <c r="O12" s="39">
+      <c r="O12" s="40">
         <v>1986</v>
       </c>
-      <c r="P12" s="40">
+      <c r="P12" s="41">
         <f t="shared" si="3"/>
         <v>0.532050728797913</v>
       </c>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U12" s="35" t="s">
+      <c r="U12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V12" s="35">
+      <c r="V12" s="36">
         <v>2008</v>
       </c>
-      <c r="W12" s="35">
+      <c r="W12" s="36">
         <v>0.900844812393188</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="2:31">
-      <c r="D13" s="32" t="str">
+      <c r="D13" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="32" t="str">
+      <c r="G13" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD89</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="39">
         <f t="shared" si="2"/>
         <v>1.8468</v>
       </c>
-      <c r="O13" s="39">
+      <c r="O13" s="40">
         <v>1987</v>
       </c>
-      <c r="P13" s="40">
+      <c r="P13" s="41">
         <f t="shared" si="3"/>
         <v>0.54511946439743</v>
       </c>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U13" s="35" t="s">
+      <c r="U13" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V13" s="35">
+      <c r="V13" s="36">
         <v>2009</v>
       </c>
-      <c r="W13" s="35">
+      <c r="W13" s="36">
         <v>0.907873749732971</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="2:31">
-      <c r="D14" s="32" t="str">
+      <c r="D14" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="32" t="str">
+      <c r="G14" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD90</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="39">
         <f t="shared" si="2"/>
         <v>1.7799</v>
       </c>
-      <c r="O14" s="39">
+      <c r="O14" s="40">
         <v>1988</v>
       </c>
-      <c r="P14" s="40">
+      <c r="P14" s="41">
         <f t="shared" si="3"/>
         <v>0.564371347427368</v>
       </c>
-      <c r="T14" s="35" t="s">
+      <c r="T14" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="35" t="s">
+      <c r="U14" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V14" s="35">
+      <c r="V14" s="36">
         <v>2010</v>
       </c>
-      <c r="W14" s="35">
+      <c r="W14" s="36">
         <v>0.918479204177856</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="2:31">
-      <c r="D15" s="32" t="str">
+      <c r="D15" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="32" t="str">
+      <c r="G15" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD91</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="39">
         <f t="shared" si="2"/>
         <v>1.722</v>
       </c>
-      <c r="O15" s="39">
+      <c r="O15" s="40">
         <v>1989</v>
       </c>
-      <c r="P15" s="40">
+      <c r="P15" s="41">
         <f t="shared" si="3"/>
         <v>0.58649742603302</v>
       </c>
-      <c r="T15" s="35" t="s">
+      <c r="T15" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U15" s="35" t="s">
+      <c r="U15" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V15" s="35">
+      <c r="V15" s="36">
         <v>2011</v>
       </c>
-      <c r="W15" s="35">
+      <c r="W15" s="36">
         <v>0.937618970870972</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:31">
-      <c r="D16" s="32" t="str">
+      <c r="D16" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="32" t="str">
+      <c r="G16" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD92</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <f t="shared" si="2"/>
         <v>1.6836</v>
       </c>
-      <c r="O16" s="39">
+      <c r="O16" s="40">
         <v>1990</v>
       </c>
-      <c r="P16" s="40">
+      <c r="P16" s="41">
         <f t="shared" si="3"/>
         <v>0.608532726764679</v>
       </c>
-      <c r="T16" s="35" t="s">
+      <c r="T16" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="35" t="s">
+      <c r="U16" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="35">
+      <c r="V16" s="36">
         <v>2012</v>
       </c>
-      <c r="W16" s="35">
+      <c r="W16" s="36">
         <v>0.955666601657867</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="4:23">
-      <c r="D17" s="32" t="str">
+      <c r="D17" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="32" t="str">
+      <c r="G17" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD93</v>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="39">
         <f t="shared" si="2"/>
         <v>1.6446</v>
       </c>
-      <c r="O17" s="39">
+      <c r="O17" s="40">
         <v>1991</v>
       </c>
-      <c r="P17" s="40">
+      <c r="P17" s="41">
         <f t="shared" si="3"/>
         <v>0.629012584686279</v>
       </c>
-      <c r="T17" s="35" t="s">
+      <c r="T17" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="35" t="s">
+      <c r="U17" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="35">
+      <c r="V17" s="36">
         <v>2013</v>
       </c>
-      <c r="W17" s="35">
+      <c r="W17" s="36">
         <v>0.972605764865875</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="4:23">
-      <c r="D18" s="32" t="str">
+      <c r="D18" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="32" t="str">
+      <c r="G18" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD94</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="39">
         <f t="shared" si="2"/>
         <v>1.6102</v>
       </c>
-      <c r="O18" s="39">
+      <c r="O18" s="40">
         <v>1992</v>
       </c>
-      <c r="P18" s="40">
+      <c r="P18" s="41">
         <f t="shared" si="3"/>
         <v>0.643362104892731</v>
       </c>
-      <c r="T18" s="35" t="s">
+      <c r="T18" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U18" s="35" t="s">
+      <c r="U18" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="35">
+      <c r="V18" s="36">
         <v>2014</v>
       </c>
-      <c r="W18" s="35">
+      <c r="W18" s="36">
         <v>0.990517318248749</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="4:23">
-      <c r="D19" s="32" t="str">
+      <c r="D19" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="32" t="str">
+      <c r="G19" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD95</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="39">
         <f t="shared" si="2"/>
         <v>1.5771</v>
       </c>
-      <c r="O19" s="39">
+      <c r="O19" s="40">
         <v>1993</v>
       </c>
-      <c r="P19" s="40">
+      <c r="P19" s="41">
         <f t="shared" si="3"/>
         <v>0.658619225025177</v>
       </c>
-      <c r="T19" s="35" t="s">
+      <c r="T19" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="35" t="s">
+      <c r="U19" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="35">
+      <c r="V19" s="36">
         <v>2015</v>
       </c>
-      <c r="W19" s="35">
+      <c r="W19" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="4:23">
-      <c r="D20" s="32" t="str">
+      <c r="D20" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="str">
+      <c r="G20" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD96</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="39">
         <f t="shared" si="2"/>
         <v>1.5488</v>
       </c>
-      <c r="O20" s="39">
+      <c r="O20" s="40">
         <v>1994</v>
       </c>
-      <c r="P20" s="40">
+      <c r="P20" s="41">
         <f t="shared" si="3"/>
         <v>0.67265796661377</v>
       </c>
-      <c r="T20" s="35" t="s">
+      <c r="T20" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U20" s="35" t="s">
+      <c r="U20" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V20" s="35">
+      <c r="V20" s="36">
         <v>2016</v>
       </c>
-      <c r="W20" s="35">
+      <c r="W20" s="36">
         <v>1.01048374176025</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="4:23">
-      <c r="D21" s="32" t="str">
+      <c r="D21" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="F21" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="32" t="str">
+      <c r="G21" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD97</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="39">
         <f t="shared" si="2"/>
         <v>1.5224</v>
       </c>
-      <c r="O21" s="39">
+      <c r="O21" s="40">
         <v>1995</v>
       </c>
-      <c r="P21" s="40">
+      <c r="P21" s="41">
         <f t="shared" si="3"/>
         <v>0.686780393123627</v>
       </c>
-      <c r="T21" s="35" t="s">
+      <c r="T21" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U21" s="35" t="s">
+      <c r="U21" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V21" s="35">
+      <c r="V21" s="36">
         <v>2017</v>
       </c>
-      <c r="W21" s="35">
+      <c r="W21" s="36">
         <v>1.02974033355713</v>
       </c>
     </row>
     <row r="22" ht="14.5" spans="4:23">
-      <c r="D22" s="32" t="str">
+      <c r="D22" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="32" t="str">
+      <c r="G22" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD98</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="39">
         <f t="shared" si="2"/>
         <v>1.5058</v>
       </c>
-      <c r="O22" s="39">
+      <c r="O22" s="40">
         <v>1996</v>
       </c>
-      <c r="P22" s="40">
+      <c r="P22" s="41">
         <f t="shared" si="3"/>
         <v>0.699335396289825</v>
       </c>
-      <c r="T22" s="35" t="s">
+      <c r="T22" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U22" s="35" t="s">
+      <c r="U22" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V22" s="35">
+      <c r="V22" s="36">
         <v>2018</v>
       </c>
-      <c r="W22" s="35">
+      <c r="W22" s="36">
         <v>1.05430805683136</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="4:23">
-      <c r="D23" s="32" t="str">
+      <c r="D23" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="32" t="str">
+      <c r="G23" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD99</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="39">
         <f t="shared" si="2"/>
         <v>1.4845</v>
       </c>
-      <c r="O23" s="39">
+      <c r="O23" s="40">
         <v>1997</v>
       </c>
-      <c r="P23" s="40">
+      <c r="P23" s="41">
         <f t="shared" si="3"/>
         <v>0.71145087480545</v>
       </c>
-      <c r="T23" s="35" t="s">
+      <c r="T23" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U23" s="35" t="s">
+      <c r="U23" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V23" s="35">
+      <c r="V23" s="36">
         <v>2019</v>
       </c>
-      <c r="W23" s="35">
+      <c r="W23" s="36">
         <v>1.07337832450867</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="4:23">
-      <c r="D24" s="32" t="str">
+      <c r="D24" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="32" t="str">
+      <c r="G24" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD00</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="39">
         <f t="shared" si="2"/>
         <v>1.4518</v>
       </c>
-      <c r="O24" s="39">
+      <c r="O24" s="40">
         <v>1998</v>
       </c>
-      <c r="P24" s="40">
+      <c r="P24" s="41">
         <f t="shared" si="3"/>
         <v>0.719296872615814</v>
       </c>
-      <c r="T24" s="35" t="s">
+      <c r="T24" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U24" s="35" t="s">
+      <c r="U24" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="35">
+      <c r="V24" s="36">
         <v>2020</v>
       </c>
-      <c r="W24" s="35">
+      <c r="W24" s="36">
         <v>1.08314538002014</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="4:23">
-      <c r="D25" s="32" t="str">
+      <c r="D25" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="32" t="str">
+      <c r="G25" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD01</v>
       </c>
-      <c r="H25" s="38">
+      <c r="H25" s="39">
         <f t="shared" si="2"/>
         <v>1.4199</v>
       </c>
-      <c r="O25" s="39">
+      <c r="O25" s="40">
         <v>1999</v>
       </c>
-      <c r="P25" s="40">
+      <c r="P25" s="41">
         <f t="shared" si="3"/>
         <v>0.729613304138184</v>
       </c>
-      <c r="T25" s="35" t="s">
+      <c r="T25" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U25" s="35" t="s">
+      <c r="U25" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V25" s="35">
+      <c r="V25" s="36">
         <v>2021</v>
       </c>
-      <c r="W25" s="35">
+      <c r="W25" s="36">
         <v>1.09456992149353</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="4:23">
-      <c r="D26" s="32" t="str">
+      <c r="D26" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="32" t="str">
+      <c r="G26" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD02</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="39">
         <f t="shared" si="2"/>
         <v>1.3986</v>
       </c>
-      <c r="O26" s="39">
+      <c r="O26" s="40">
         <v>2000</v>
       </c>
-      <c r="P26" s="40">
+      <c r="P26" s="41">
         <f t="shared" si="3"/>
         <v>0.746074616909027</v>
       </c>
-      <c r="T26" s="35" t="s">
+      <c r="T26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U26" s="35" t="s">
+      <c r="U26" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V26" s="35">
+      <c r="V26" s="36">
         <v>2022</v>
       </c>
-      <c r="W26" s="35">
+      <c r="W26" s="36">
         <v>1.1073887348175</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="4:23">
-      <c r="D27" s="32" t="str">
+      <c r="D27" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="str">
+      <c r="G27" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD03</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27" s="39">
         <f t="shared" si="2"/>
         <v>1.3727</v>
       </c>
-      <c r="O27" s="39">
+      <c r="O27" s="40">
         <v>2001</v>
       </c>
-      <c r="P27" s="40">
+      <c r="P27" s="41">
         <f t="shared" si="3"/>
         <v>0.762827515602112</v>
       </c>
-      <c r="T27" s="35" t="s">
+      <c r="T27" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="35" t="s">
+      <c r="U27" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V27" s="35">
+      <c r="V27" s="36">
         <v>2023</v>
       </c>
-      <c r="W27" s="35">
+      <c r="W27" s="36">
         <v>1.1224308013916</v>
       </c>
     </row>
     <row r="28" ht="14.5" spans="4:23">
-      <c r="D28" s="32" t="str">
+      <c r="D28" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="32" t="str">
+      <c r="G28" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD04</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="39">
         <f t="shared" si="2"/>
         <v>1.3369</v>
       </c>
-      <c r="O28" s="39">
+      <c r="O28" s="40">
         <v>2002</v>
       </c>
-      <c r="P28" s="40">
+      <c r="P28" s="41">
         <f t="shared" si="3"/>
         <v>0.774460315704346</v>
       </c>
-      <c r="T28" s="35" t="s">
+      <c r="T28" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U28" s="35" t="s">
+      <c r="U28" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V28" s="35">
+      <c r="V28" s="36">
         <v>2024</v>
       </c>
-      <c r="W28" s="35">
+      <c r="W28" s="36">
         <v>1.14128732681274</v>
       </c>
     </row>
     <row r="29" ht="14.5" spans="4:23">
-      <c r="D29" s="32" t="str">
+      <c r="D29" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="32" t="str">
+      <c r="G29" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD05</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29" s="39">
         <f t="shared" si="2"/>
         <v>1.2967</v>
       </c>
-      <c r="O29" s="39">
+      <c r="O29" s="40">
         <v>2003</v>
       </c>
-      <c r="P29" s="40">
+      <c r="P29" s="41">
         <f t="shared" si="3"/>
         <v>0.789065361022949</v>
       </c>
-      <c r="T29" s="35" t="s">
+      <c r="T29" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U29" s="35" t="s">
+      <c r="U29" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V29" s="35">
+      <c r="V29" s="36">
         <v>2025</v>
       </c>
-      <c r="W29" s="35">
+      <c r="W29" s="36">
         <v>1.16506481170654</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="4:23">
-      <c r="D30" s="32" t="str">
+      <c r="D30" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="32" t="str">
+      <c r="G30" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD06</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="39">
         <f t="shared" si="2"/>
         <v>1.2583</v>
       </c>
-      <c r="O30" s="39">
+      <c r="O30" s="40">
         <v>2004</v>
       </c>
-      <c r="P30" s="40">
+      <c r="P30" s="41">
         <f t="shared" si="3"/>
         <v>0.810197472572327</v>
       </c>
-      <c r="T30" s="35" t="s">
+      <c r="T30" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U30" s="35" t="s">
+      <c r="U30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="36">
         <v>2026</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="36">
         <v>1.19280254840851</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="4:23">
-      <c r="D31" s="32" t="str">
+      <c r="D31" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="32" t="str">
+      <c r="G31" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD07</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31" s="39">
         <f t="shared" si="2"/>
         <v>1.2253</v>
       </c>
-      <c r="O31" s="39">
+      <c r="O31" s="40">
         <v>2005</v>
       </c>
-      <c r="P31" s="40">
+      <c r="P31" s="41">
         <f t="shared" si="3"/>
         <v>0.835319578647614</v>
       </c>
-      <c r="T31" s="35" t="s">
+      <c r="T31" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U31" s="35" t="s">
+      <c r="U31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V31" s="35">
+      <c r="V31" s="36">
         <v>2027</v>
       </c>
-      <c r="W31" s="35">
+      <c r="W31" s="36">
         <v>1.22309768199921</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="4:23">
-      <c r="D32" s="32" t="str">
+      <c r="D32" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="32" t="str">
+      <c r="G32" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD08</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="39">
         <f t="shared" si="2"/>
         <v>1.2024</v>
       </c>
-      <c r="O32" s="39">
+      <c r="O32" s="40">
         <v>2006</v>
       </c>
-      <c r="P32" s="40">
+      <c r="P32" s="41">
         <f t="shared" si="3"/>
         <v>0.860807240009308</v>
       </c>
-      <c r="T32" s="35" t="s">
+      <c r="T32" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U32" s="35" t="s">
+      <c r="U32" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V32" s="35">
+      <c r="V32" s="36">
         <v>2028</v>
       </c>
-      <c r="W32" s="35">
+      <c r="W32" s="36">
         <v>1.25531399250031</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="4:23">
-      <c r="D33" s="32" t="str">
+      <c r="D33" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="F33" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="32" t="str">
+      <c r="G33" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD09</v>
       </c>
-      <c r="H33" s="38">
+      <c r="H33" s="39">
         <f t="shared" si="2"/>
         <v>1.1931</v>
       </c>
-      <c r="O33" s="39">
+      <c r="O33" s="40">
         <v>2007</v>
       </c>
-      <c r="P33" s="40">
+      <c r="P33" s="41">
         <f t="shared" si="3"/>
         <v>0.883970141410828</v>
       </c>
-      <c r="T33" s="35" t="s">
+      <c r="T33" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="U33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="36">
         <v>2029</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>1.28839552402496</v>
       </c>
     </row>
     <row r="34" ht="14.5" spans="4:23">
-      <c r="D34" s="32" t="str">
+      <c r="D34" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="F34" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="32" t="str">
+      <c r="G34" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD10</v>
       </c>
-      <c r="H34" s="38">
+      <c r="H34" s="39">
         <f t="shared" si="2"/>
         <v>1.1793</v>
       </c>
-      <c r="O34" s="39">
+      <c r="O34" s="40">
         <v>2008</v>
       </c>
-      <c r="P34" s="40">
+      <c r="P34" s="41">
         <f t="shared" si="3"/>
         <v>0.900844812393188</v>
       </c>
-      <c r="T34" s="35" t="s">
+      <c r="T34" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U34" s="35" t="s">
+      <c r="U34" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="36">
         <v>2030</v>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="36">
         <v>1.32175171375275</v>
       </c>
     </row>
     <row r="35" ht="14.5" spans="4:23">
-      <c r="D35" s="32" t="str">
+      <c r="D35" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F35" s="32" t="s">
+      <c r="F35" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="32" t="str">
+      <c r="G35" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD11</v>
       </c>
-      <c r="H35" s="38">
+      <c r="H35" s="39">
         <f t="shared" si="2"/>
         <v>1.1552</v>
       </c>
-      <c r="O35" s="39">
+      <c r="O35" s="40">
         <v>2009</v>
       </c>
-      <c r="P35" s="40">
+      <c r="P35" s="41">
         <f t="shared" si="3"/>
         <v>0.907873749732971</v>
       </c>
-      <c r="T35" s="35" t="s">
+      <c r="T35" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U35" s="35" t="s">
+      <c r="U35" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>1980</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>0.404039144515991</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="4:23">
-      <c r="D36" s="32" t="str">
+      <c r="D36" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F36" s="32" t="s">
+      <c r="F36" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="32" t="str">
+      <c r="G36" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD12</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="39">
         <f t="shared" si="2"/>
         <v>1.1334</v>
       </c>
-      <c r="O36" s="39">
+      <c r="O36" s="40">
         <v>2010</v>
       </c>
-      <c r="P36" s="40">
+      <c r="P36" s="41">
         <f t="shared" si="3"/>
         <v>0.918479204177856</v>
       </c>
-      <c r="T36" s="35" t="s">
+      <c r="T36" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U36" s="35" t="s">
+      <c r="U36" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="36">
         <v>1981</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="36">
         <v>0.442179799079895</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="4:23">
-      <c r="D37" s="32" t="str">
+      <c r="D37" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F37" s="32" t="s">
+      <c r="F37" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="32" t="str">
+      <c r="G37" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD13</v>
       </c>
-      <c r="H37" s="38">
+      <c r="H37" s="39">
         <f t="shared" si="2"/>
         <v>1.1137</v>
       </c>
-      <c r="O37" s="39">
+      <c r="O37" s="40">
         <v>2011</v>
       </c>
-      <c r="P37" s="40">
+      <c r="P37" s="41">
         <f t="shared" si="3"/>
         <v>0.937618970870972</v>
       </c>
-      <c r="T37" s="35" t="s">
+      <c r="T37" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U37" s="35" t="s">
+      <c r="U37" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V37" s="35">
+      <c r="V37" s="36">
         <v>1982</v>
       </c>
-      <c r="W37" s="35">
+      <c r="W37" s="36">
         <v>0.469521433115005</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="4:23">
-      <c r="D38" s="32" t="str">
+      <c r="D38" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="F38" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="32" t="str">
+      <c r="G38" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD14</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="39">
         <f t="shared" si="2"/>
         <v>1.0935</v>
       </c>
-      <c r="O38" s="39">
+      <c r="O38" s="40">
         <v>2012</v>
       </c>
-      <c r="P38" s="40">
+      <c r="P38" s="41">
         <f t="shared" si="3"/>
         <v>0.955666601657867</v>
       </c>
-      <c r="T38" s="35" t="s">
+      <c r="T38" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U38" s="35" t="s">
+      <c r="U38" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V38" s="35">
+      <c r="V38" s="36">
         <v>1983</v>
       </c>
-      <c r="W38" s="35">
+      <c r="W38" s="36">
         <v>0.487872630357742</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="4:23">
-      <c r="D39" s="32" t="str">
+      <c r="D39" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F39" s="32" t="s">
+      <c r="F39" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="32" t="str">
+      <c r="G39" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD15</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="39">
         <f t="shared" si="2"/>
         <v>1.0831</v>
       </c>
-      <c r="O39" s="39">
+      <c r="O39" s="40">
         <v>2013</v>
       </c>
-      <c r="P39" s="40">
+      <c r="P39" s="41">
         <f t="shared" si="3"/>
         <v>0.972605764865875</v>
       </c>
-      <c r="T39" s="35" t="s">
+      <c r="T39" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U39" s="35" t="s">
+      <c r="U39" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V39" s="35">
+      <c r="V39" s="36">
         <v>1984</v>
       </c>
-      <c r="W39" s="35">
+      <c r="W39" s="36">
         <v>0.505495131015778</v>
       </c>
     </row>
     <row r="40" ht="14.5" spans="4:23">
-      <c r="D40" s="32" t="str">
+      <c r="D40" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="32" t="str">
+      <c r="G40" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD16</v>
       </c>
-      <c r="H40" s="38">
+      <c r="H40" s="39">
         <f t="shared" si="2"/>
         <v>1.0719</v>
       </c>
-      <c r="O40" s="39">
+      <c r="O40" s="40">
         <v>2014</v>
       </c>
-      <c r="P40" s="40">
+      <c r="P40" s="41">
         <f t="shared" si="3"/>
         <v>0.990517318248749</v>
       </c>
-      <c r="T40" s="35" t="s">
+      <c r="T40" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U40" s="35" t="s">
+      <c r="U40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V40" s="35">
+      <c r="V40" s="36">
         <v>1985</v>
       </c>
-      <c r="W40" s="35">
+      <c r="W40" s="36">
         <v>0.521485805511475</v>
       </c>
     </row>
     <row r="41" ht="14.5" spans="4:23">
-      <c r="D41" s="32" t="str">
+      <c r="D41" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="F41" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G41" s="32" t="str">
+      <c r="G41" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD17</v>
       </c>
-      <c r="H41" s="38">
+      <c r="H41" s="39">
         <f t="shared" si="2"/>
         <v>1.0519</v>
       </c>
-      <c r="O41" s="39">
+      <c r="O41" s="40">
         <v>2015</v>
       </c>
-      <c r="P41" s="40">
+      <c r="P41" s="41">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T41" s="35" t="s">
+      <c r="T41" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U41" s="35" t="s">
+      <c r="U41" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="36">
         <v>1986</v>
       </c>
-      <c r="W41" s="35">
+      <c r="W41" s="36">
         <v>0.532050728797913</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="4:23">
-      <c r="D42" s="32" t="str">
+      <c r="D42" s="33" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="F42" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="32" t="str">
+      <c r="G42" s="33" t="str">
         <f t="shared" si="1"/>
         <v>USD18</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="39">
         <f t="shared" si="2"/>
         <v>1.0274</v>
       </c>
-      <c r="O42" s="39">
+      <c r="O42" s="40">
         <v>2016</v>
       </c>
-      <c r="P42" s="40">
+      <c r="P42" s="41">
         <f t="shared" si="3"/>
         <v>1.01048374176025</v>
       </c>
-      <c r="T42" s="35" t="s">
+      <c r="T42" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U42" s="35" t="s">
+      <c r="U42" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V42" s="35">
+      <c r="V42" s="36">
         <v>1987</v>
       </c>
-      <c r="W42" s="35">
+      <c r="W42" s="36">
         <v>0.54511946439743</v>
       </c>
     </row>
     <row r="43" ht="14.5" spans="4:23">
-      <c r="D43" s="32" t="str">
+      <c r="D43" s="33" t="str">
         <f t="shared" ref="D43:D49" si="4">IF(F43=G43,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F43" s="32" t="s">
+      <c r="F43" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="32" t="str">
+      <c r="G43" s="33" t="str">
         <f t="shared" ref="G43:G49" si="5">"USD"&amp;RIGHT(O45,2)</f>
         <v>USD19</v>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="39">
         <f t="shared" si="2"/>
         <v>1.0091</v>
       </c>
-      <c r="O43" s="39">
+      <c r="O43" s="40">
         <v>2017</v>
       </c>
-      <c r="P43" s="40">
+      <c r="P43" s="41">
         <f t="shared" si="3"/>
         <v>1.02974033355713</v>
       </c>
-      <c r="T43" s="35" t="s">
+      <c r="T43" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U43" s="35" t="s">
+      <c r="U43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V43" s="35">
+      <c r="V43" s="36">
         <v>1988</v>
       </c>
-      <c r="W43" s="35">
+      <c r="W43" s="36">
         <v>0.564371347427368</v>
       </c>
     </row>
     <row r="44" ht="14.5" spans="4:23">
-      <c r="D44" s="32" t="str">
+      <c r="D44" s="33" t="str">
         <f t="shared" si="4"/>
         <v>*G_CUREX</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F44" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="32" t="str">
+      <c r="G44" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD20</v>
       </c>
-      <c r="H44" s="38">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O44" s="39">
+      <c r="H44" s="39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O44" s="40">
         <v>2018</v>
       </c>
-      <c r="P44" s="40">
+      <c r="P44" s="41">
         <f t="shared" si="3"/>
         <v>1.05430805683136</v>
       </c>
-      <c r="T44" s="35" t="s">
+      <c r="T44" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U44" s="35" t="s">
+      <c r="U44" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V44" s="35">
+      <c r="V44" s="36">
         <v>1989</v>
       </c>
-      <c r="W44" s="35">
+      <c r="W44" s="36">
         <v>0.58649742603302</v>
       </c>
     </row>
     <row r="45" ht="14.5" spans="4:23">
-      <c r="D45" s="32" t="str">
+      <c r="D45" s="33" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F45" s="32" t="s">
+      <c r="F45" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="32" t="str">
+      <c r="G45" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD21</v>
       </c>
-      <c r="H45" s="38">
+      <c r="H45" s="39">
         <f t="shared" si="2"/>
         <v>0.9896</v>
       </c>
-      <c r="O45" s="39">
+      <c r="O45" s="40">
         <v>2019</v>
       </c>
-      <c r="P45" s="40">
+      <c r="P45" s="41">
         <f t="shared" si="3"/>
         <v>1.07337832450867</v>
       </c>
-      <c r="T45" s="35" t="s">
+      <c r="T45" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U45" s="35" t="s">
+      <c r="U45" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V45" s="35">
+      <c r="V45" s="36">
         <v>1990</v>
       </c>
-      <c r="W45" s="35">
+      <c r="W45" s="36">
         <v>0.608532726764679</v>
       </c>
     </row>
     <row r="46" ht="14.5" spans="4:23">
-      <c r="D46" s="32" t="str">
+      <c r="D46" s="33" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F46" s="32" t="s">
+      <c r="F46" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="32" t="str">
+      <c r="G46" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD22</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="39">
         <f t="shared" si="2"/>
         <v>0.9781</v>
       </c>
-      <c r="O46" s="39">
+      <c r="O46" s="40">
         <v>2020</v>
       </c>
-      <c r="P46" s="40">
+      <c r="P46" s="41">
         <f t="shared" si="3"/>
         <v>1.08314538002014</v>
       </c>
-      <c r="T46" s="35" t="s">
+      <c r="T46" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U46" s="35" t="s">
+      <c r="U46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V46" s="35">
+      <c r="V46" s="36">
         <v>1991</v>
       </c>
-      <c r="W46" s="35">
+      <c r="W46" s="36">
         <v>0.629012584686279</v>
       </c>
     </row>
     <row r="47" ht="14.5" spans="4:23">
-      <c r="D47" s="32" t="str">
+      <c r="D47" s="33" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F47" s="32" t="s">
+      <c r="F47" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="32" t="str">
+      <c r="G47" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD23</v>
       </c>
-      <c r="H47" s="38">
+      <c r="H47" s="39">
         <f t="shared" si="2"/>
         <v>0.965</v>
       </c>
-      <c r="O47" s="39">
+      <c r="O47" s="40">
         <v>2021</v>
       </c>
-      <c r="P47" s="40">
+      <c r="P47" s="41">
         <f t="shared" si="3"/>
         <v>1.09456992149353</v>
       </c>
-      <c r="T47" s="35" t="s">
+      <c r="T47" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U47" s="35" t="s">
+      <c r="U47" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V47" s="35">
+      <c r="V47" s="36">
         <v>1992</v>
       </c>
-      <c r="W47" s="35">
+      <c r="W47" s="36">
         <v>0.643362104892731</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="4:23">
-      <c r="D48" s="32" t="str">
+      <c r="D48" s="33" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F48" s="32" t="s">
+      <c r="F48" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="32" t="str">
+      <c r="G48" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD24</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="39">
         <f t="shared" si="2"/>
         <v>0.9491</v>
       </c>
-      <c r="O48" s="39">
+      <c r="O48" s="40">
         <v>2022</v>
       </c>
-      <c r="P48" s="40">
+      <c r="P48" s="41">
         <f t="shared" si="3"/>
         <v>1.1073887348175</v>
       </c>
-      <c r="T48" s="35" t="s">
+      <c r="T48" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U48" s="35" t="s">
+      <c r="U48" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V48" s="35">
+      <c r="V48" s="36">
         <v>1993</v>
       </c>
-      <c r="W48" s="35">
+      <c r="W48" s="36">
         <v>0.658619225025177</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="4:23">
-      <c r="D49" s="32" t="str">
+      <c r="D49" s="33" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F49" s="32" t="s">
+      <c r="F49" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="32" t="str">
+      <c r="G49" s="33" t="str">
         <f t="shared" si="5"/>
         <v>USD25</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="39">
         <f t="shared" si="2"/>
         <v>0.9297</v>
       </c>
-      <c r="O49" s="39">
+      <c r="O49" s="40">
         <v>2023</v>
       </c>
-      <c r="P49" s="40">
+      <c r="P49" s="41">
         <f t="shared" si="3"/>
         <v>1.1224308013916</v>
       </c>
-      <c r="T49" s="35" t="s">
+      <c r="T49" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U49" s="35" t="s">
+      <c r="U49" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V49" s="35">
+      <c r="V49" s="36">
         <v>1994</v>
       </c>
-      <c r="W49" s="35">
+      <c r="W49" s="36">
         <v>0.67265796661377</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="4:23">
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="32" t="str">
+      <c r="G50" s="33" t="str">
         <f t="shared" ref="G50:G85" si="6">G7</f>
         <v>USD83</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="39">
         <f>$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O50" s="39">
+      <c r="O50" s="40">
         <v>2024</v>
       </c>
-      <c r="P50" s="40">
+      <c r="P50" s="41">
         <f t="shared" si="3"/>
         <v>1.14128732681274</v>
       </c>
-      <c r="T50" s="35" t="s">
+      <c r="T50" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U50" s="35" t="s">
+      <c r="U50" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V50" s="35">
+      <c r="V50" s="36">
         <v>1995</v>
       </c>
-      <c r="W50" s="35">
+      <c r="W50" s="36">
         <v>0.686780393123627</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="4:23">
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="32" t="str">
+      <c r="G51" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD84</v>
       </c>
-      <c r="H51" s="38">
+      <c r="H51" s="39">
         <f t="shared" ref="H51:H92" si="7">$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O51" s="39">
+      <c r="O51" s="40">
         <v>2025</v>
       </c>
-      <c r="P51" s="40">
+      <c r="P51" s="41">
         <f t="shared" si="3"/>
         <v>1.16506481170654</v>
       </c>
-      <c r="T51" s="35" t="s">
+      <c r="T51" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U51" s="35" t="s">
+      <c r="U51" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V51" s="35">
+      <c r="V51" s="36">
         <v>1996</v>
       </c>
-      <c r="W51" s="35">
+      <c r="W51" s="36">
         <v>0.699335396289825</v>
       </c>
     </row>
     <row r="52" spans="4:23">
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="32" t="str">
+      <c r="G52" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD85</v>
       </c>
-      <c r="H52" s="38">
+      <c r="H52" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T52" s="35" t="s">
+      <c r="T52" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U52" s="35" t="s">
+      <c r="U52" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V52" s="35">
+      <c r="V52" s="36">
         <v>1997</v>
       </c>
-      <c r="W52" s="35">
+      <c r="W52" s="36">
         <v>0.71145087480545</v>
       </c>
     </row>
     <row r="53" spans="4:23">
-      <c r="D53" s="32" t="s">
+      <c r="D53" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="32" t="str">
+      <c r="G53" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD86</v>
       </c>
-      <c r="H53" s="38">
+      <c r="H53" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T53" s="35" t="s">
+      <c r="T53" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U53" s="35" t="s">
+      <c r="U53" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V53" s="35">
+      <c r="V53" s="36">
         <v>1998</v>
       </c>
-      <c r="W53" s="35">
+      <c r="W53" s="36">
         <v>0.719296872615814</v>
       </c>
     </row>
     <row r="54" spans="4:23">
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="32" t="str">
+      <c r="G54" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD87</v>
       </c>
-      <c r="H54" s="38">
+      <c r="H54" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T54" s="35" t="s">
+      <c r="T54" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U54" s="35" t="s">
+      <c r="U54" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V54" s="35">
+      <c r="V54" s="36">
         <v>1999</v>
       </c>
-      <c r="W54" s="35">
+      <c r="W54" s="36">
         <v>0.729613304138184</v>
       </c>
     </row>
     <row r="55" spans="4:23">
-      <c r="D55" s="32" t="s">
+      <c r="D55" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="32" t="str">
+      <c r="G55" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD88</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T55" s="35" t="s">
+      <c r="T55" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="U55" s="35" t="s">
+      <c r="U55" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V55" s="35">
+      <c r="V55" s="36">
         <v>2000</v>
       </c>
-      <c r="W55" s="35">
+      <c r="W55" s="36">
         <v>0.746074616909027</v>
       </c>
     </row>
     <row r="56" spans="4:23">
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="32" t="str">
+      <c r="G56" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD89</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="57" spans="4:23">
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="32" t="str">
+      <c r="G57" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD90</v>
       </c>
-      <c r="H57" s="38">
+      <c r="H57" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="58" spans="4:23">
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="32" t="str">
+      <c r="G58" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD91</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="59" spans="4:23">
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="32" t="str">
+      <c r="G59" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD92</v>
       </c>
-      <c r="H59" s="38">
+      <c r="H59" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="60" spans="4:23">
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="32" t="str">
+      <c r="G60" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD93</v>
       </c>
-      <c r="H60" s="38">
+      <c r="H60" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="61" spans="4:23">
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G61" s="32" t="str">
+      <c r="G61" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD94</v>
       </c>
-      <c r="H61" s="38">
+      <c r="H61" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="62" spans="4:23">
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G62" s="32" t="str">
+      <c r="G62" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD95</v>
       </c>
-      <c r="H62" s="38">
+      <c r="H62" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="63" spans="4:23">
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="32" t="str">
+      <c r="G63" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD96</v>
       </c>
-      <c r="H63" s="38">
+      <c r="H63" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="64" spans="4:23">
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="32" t="str">
+      <c r="G64" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD97</v>
       </c>
-      <c r="H64" s="38">
+      <c r="H64" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="65" spans="4:8">
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="32" t="str">
+      <c r="G65" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD98</v>
       </c>
-      <c r="H65" s="38">
+      <c r="H65" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="66" spans="4:8">
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G66" s="32" t="str">
+      <c r="G66" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD99</v>
       </c>
-      <c r="H66" s="38">
+      <c r="H66" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="67" spans="4:8">
-      <c r="D67" s="32" t="s">
+      <c r="D67" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="32" t="str">
+      <c r="G67" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD00</v>
       </c>
-      <c r="H67" s="38">
+      <c r="H67" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="68" spans="4:8">
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="32" t="str">
+      <c r="G68" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD01</v>
       </c>
-      <c r="H68" s="38">
+      <c r="H68" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="69" spans="4:8">
-      <c r="D69" s="32" t="s">
+      <c r="D69" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="32" t="str">
+      <c r="G69" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD02</v>
       </c>
-      <c r="H69" s="38">
+      <c r="H69" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="70" spans="4:8">
-      <c r="D70" s="32" t="s">
+      <c r="D70" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="32" t="str">
+      <c r="G70" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD03</v>
       </c>
-      <c r="H70" s="38">
+      <c r="H70" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="71" spans="4:8">
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G71" s="32" t="str">
+      <c r="G71" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD04</v>
       </c>
-      <c r="H71" s="38">
+      <c r="H71" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="72" spans="4:8">
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="32" t="str">
+      <c r="G72" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD05</v>
       </c>
-      <c r="H72" s="38">
+      <c r="H72" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="73" spans="4:8">
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G73" s="32" t="str">
+      <c r="G73" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD06</v>
       </c>
-      <c r="H73" s="38">
+      <c r="H73" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="74" spans="4:8">
-      <c r="D74" s="32" t="s">
+      <c r="D74" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="32" t="str">
+      <c r="G74" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD07</v>
       </c>
-      <c r="H74" s="38">
+      <c r="H74" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="75" spans="4:8">
-      <c r="D75" s="32" t="s">
+      <c r="D75" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G75" s="32" t="str">
+      <c r="G75" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD08</v>
       </c>
-      <c r="H75" s="38">
+      <c r="H75" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="76" spans="4:8">
-      <c r="D76" s="32" t="s">
+      <c r="D76" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G76" s="32" t="str">
+      <c r="G76" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD09</v>
       </c>
-      <c r="H76" s="38">
+      <c r="H76" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="77" spans="4:8">
-      <c r="D77" s="32" t="s">
+      <c r="D77" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G77" s="32" t="str">
+      <c r="G77" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD10</v>
       </c>
-      <c r="H77" s="38">
+      <c r="H77" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="78" spans="4:8">
-      <c r="D78" s="32" t="s">
+      <c r="D78" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G78" s="32" t="str">
+      <c r="G78" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD11</v>
       </c>
-      <c r="H78" s="38">
+      <c r="H78" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="79" spans="4:8">
-      <c r="D79" s="32" t="s">
+      <c r="D79" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="32" t="str">
+      <c r="G79" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD12</v>
       </c>
-      <c r="H79" s="38">
+      <c r="H79" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="80" spans="4:8">
-      <c r="D80" s="32" t="s">
+      <c r="D80" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G80" s="32" t="str">
+      <c r="G80" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD13</v>
       </c>
-      <c r="H80" s="38">
+      <c r="H80" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="81" spans="4:8">
-      <c r="D81" s="32" t="s">
+      <c r="D81" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="32" t="str">
+      <c r="G81" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD14</v>
       </c>
-      <c r="H81" s="38">
+      <c r="H81" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="82" spans="4:8">
-      <c r="D82" s="32" t="s">
+      <c r="D82" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G82" s="32" t="str">
+      <c r="G82" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD15</v>
       </c>
-      <c r="H82" s="38">
+      <c r="H82" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="83" spans="4:8">
-      <c r="D83" s="32" t="s">
+      <c r="D83" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G83" s="32" t="str">
+      <c r="G83" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD16</v>
       </c>
-      <c r="H83" s="38">
+      <c r="H83" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="84" spans="4:8">
-      <c r="D84" s="32" t="s">
+      <c r="D84" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="32" t="str">
+      <c r="G84" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD17</v>
       </c>
-      <c r="H84" s="38">
+      <c r="H84" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="85" spans="4:8">
-      <c r="D85" s="32" t="s">
+      <c r="D85" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G85" s="32" t="str">
+      <c r="G85" s="33" t="str">
         <f t="shared" si="6"/>
         <v>USD18</v>
       </c>
-      <c r="H85" s="38">
+      <c r="H85" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="86" spans="4:8">
-      <c r="D86" s="32" t="s">
+      <c r="D86" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G86" s="32" t="str">
+      <c r="G86" s="33" t="str">
         <f t="shared" ref="G86:G92" si="8">G43</f>
         <v>USD19</v>
       </c>
-      <c r="H86" s="38">
+      <c r="H86" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="87" spans="4:8">
-      <c r="D87" s="32" t="s">
+      <c r="D87" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G87" s="32" t="str">
+      <c r="G87" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD20</v>
       </c>
-      <c r="H87" s="38">
+      <c r="H87" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="88" spans="4:8">
-      <c r="D88" s="32" t="s">
+      <c r="D88" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G88" s="32" t="str">
+      <c r="G88" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD21</v>
       </c>
-      <c r="H88" s="38">
+      <c r="H88" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="89" spans="4:8">
-      <c r="D89" s="32" t="s">
+      <c r="D89" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="32" t="str">
+      <c r="G89" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD22</v>
       </c>
-      <c r="H89" s="38">
+      <c r="H89" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="90" spans="4:8">
-      <c r="D90" s="32" t="s">
+      <c r="D90" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G90" s="32" t="str">
+      <c r="G90" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD23</v>
       </c>
-      <c r="H90" s="38">
+      <c r="H90" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="91" spans="4:8">
-      <c r="D91" s="32" t="s">
+      <c r="D91" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G91" s="32" t="str">
+      <c r="G91" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD24</v>
       </c>
-      <c r="H91" s="38">
+      <c r="H91" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="92" spans="4:8">
-      <c r="D92" s="32" t="s">
+      <c r="D92" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G92" s="32" t="str">
+      <c r="G92" s="33" t="str">
         <f t="shared" si="8"/>
         <v>USD25</v>
       </c>
-      <c r="H92" s="38">
+      <c r="H92" s="39">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
@@ -4945,7 +4948,7 @@
       <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="12">
         <v>0.1</v>
       </c>
     </row>
@@ -4963,7 +4966,7 @@
       <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="12">
         <f>H9</f>
         <v>0.1</v>
       </c>
@@ -4975,39 +4978,39 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="24" t="str">
+      <c r="F11" s="25" t="str">
         <f>F10</f>
         <v>Trd*</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="12">
         <f>H10</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="4:8">
-      <c r="G12" s="25"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="4:8">
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="4:8">
-      <c r="G14" s="28"/>
+      <c r="G14" s="29"/>
     </row>
     <row r="17" spans="6:10">
-      <c r="H17" s="29"/>
+      <c r="H17" s="30"/>
     </row>
     <row r="18" spans="6:10">
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5029,7 +5032,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5078,7 +5081,7 @@
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="24" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5097,10 +5100,10 @@
       <c r="B13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="23">
         <v>2150</v>
       </c>
     </row>
@@ -5110,7 +5113,7 @@
       </c>
     </row>
     <row r="20" spans="2:13">
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="24" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5202,7 +5205,7 @@
       <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="2">
         <v>0.5</v>
       </c>
     </row>
@@ -5217,7 +5220,7 @@
         <f>F24</f>
         <v>AuxStoOUT</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="2">
         <f>I24/4</f>
         <v>0.125</v>
       </c>
@@ -17782,13 +17785,13 @@
       <c r="E3" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="12">
         <v>0.5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="12">
         <v>0.25</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="12">
         <v>0.1</v>
       </c>
       <c r="L3" t="s">
@@ -17928,11 +17931,11 @@
         <f>IF(A4="","\I:",A4)</f>
         <v>Africa_North</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="16">
         <f>B4*1.1</f>
         <v>0</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="16">
         <f>MAX(VLOOKUP(L6,$E$4:$G$40,3,FALSE),M6*1.5)</f>
         <v>41.3</v>
       </c>
@@ -17947,7 +17950,7 @@
         <f t="shared" ref="U6:U28" si="0">L6</f>
         <v>Africa_North</v>
       </c>
-      <c r="V6" s="21"/>
+      <c r="V6" s="23"/>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
@@ -17975,11 +17978,11 @@
         <f t="shared" ref="L7:L27" si="1">IF(A5="","\I:",A5)</f>
         <v>BeNeLux</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="16">
         <f t="shared" ref="M7:M27" si="2">B5*1.1</f>
         <v>5.885</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="16">
         <f t="shared" ref="N7:N27" si="3">MAX(VLOOKUP(L7,$E$4:$G$40,3,FALSE),M7*1.5)</f>
         <v>8.8275</v>
       </c>
@@ -17994,7 +17997,7 @@
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="V7" s="21"/>
+      <c r="V7" s="23"/>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
@@ -18022,11 +18025,11 @@
         <f t="shared" si="1"/>
         <v>Brazil</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="16">
         <f t="shared" si="2"/>
         <v>2.189</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="16">
         <f t="shared" si="3"/>
         <v>29.2</v>
       </c>
@@ -18041,7 +18044,7 @@
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="V8" s="21"/>
+      <c r="V8" s="23"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
@@ -18069,11 +18072,11 @@
         <f t="shared" si="1"/>
         <v>China</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="16">
         <f t="shared" si="2"/>
         <v>61.083</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="16">
         <f t="shared" si="3"/>
         <v>628.9</v>
       </c>
@@ -18088,7 +18091,7 @@
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="V9" s="21"/>
+      <c r="V9" s="23"/>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
@@ -18116,11 +18119,11 @@
         <f t="shared" si="1"/>
         <v>CroSloven</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="16">
         <f t="shared" si="2"/>
         <v>0.759</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="16">
         <f t="shared" si="3"/>
         <v>1.1385</v>
       </c>
@@ -18135,7 +18138,7 @@
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="V10" s="21"/>
+      <c r="V10" s="23"/>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
@@ -18163,11 +18166,11 @@
         <f t="shared" si="1"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="16">
         <f t="shared" si="2"/>
         <v>6.919</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="16">
         <f t="shared" si="3"/>
         <v>10.3785</v>
       </c>
@@ -18182,7 +18185,7 @@
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="V11" s="21"/>
+      <c r="V11" s="23"/>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
@@ -18210,11 +18213,11 @@
         <f t="shared" si="1"/>
         <v>France</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="16">
         <f t="shared" si="2"/>
         <v>67.54</v>
       </c>
-      <c r="N12" s="14">
+      <c r="N12" s="16">
         <f t="shared" si="3"/>
         <v>101.31</v>
       </c>
@@ -18229,7 +18232,7 @@
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="V12" s="21"/>
+      <c r="V12" s="23"/>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
@@ -18257,11 +18260,11 @@
         <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="16">
         <f t="shared" si="2"/>
         <v>4.62</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="16">
         <f t="shared" si="3"/>
         <v>19.3</v>
       </c>
@@ -18276,7 +18279,7 @@
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="V13" s="21"/>
+      <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
@@ -18304,11 +18307,11 @@
         <f t="shared" si="1"/>
         <v>HunRomBul</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="16">
         <f t="shared" si="2"/>
         <v>5.874</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="16">
         <f t="shared" si="3"/>
         <v>8.811</v>
       </c>
@@ -18323,7 +18326,7 @@
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="V14" s="21"/>
+      <c r="V14" s="23"/>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
@@ -18351,11 +18354,11 @@
         <f t="shared" si="1"/>
         <v>India</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="16">
         <f t="shared" si="2"/>
         <v>7.458</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="16">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
@@ -18370,7 +18373,7 @@
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="V15" s="21"/>
+      <c r="V15" s="23"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
@@ -18398,11 +18401,11 @@
         <f t="shared" si="1"/>
         <v>Japan</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="16">
         <f t="shared" si="2"/>
         <v>36.388</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="16">
         <f t="shared" si="3"/>
         <v>54.582</v>
       </c>
@@ -18417,7 +18420,7 @@
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V16" s="21"/>
+      <c r="V16" s="23"/>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
@@ -18445,11 +18448,11 @@
         <f t="shared" si="1"/>
         <v>LatAm</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="16">
         <f t="shared" si="2"/>
         <v>1.925</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="16">
         <f t="shared" si="3"/>
         <v>46.1</v>
       </c>
@@ -18464,7 +18467,7 @@
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="V17" s="21"/>
+      <c r="V17" s="23"/>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
@@ -18492,11 +18495,11 @@
         <f t="shared" si="1"/>
         <v>MidEast</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="16">
         <f t="shared" si="2"/>
         <v>4.18</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="16">
         <f t="shared" si="3"/>
         <v>51.6</v>
       </c>
@@ -18511,7 +18514,7 @@
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="V18" s="21"/>
+      <c r="V18" s="23"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
@@ -18539,11 +18542,11 @@
         <f t="shared" si="1"/>
         <v>NorthAm</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="16">
         <f t="shared" si="2"/>
         <v>120.571</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="16">
         <f t="shared" si="3"/>
         <v>201.3</v>
       </c>
@@ -18558,7 +18561,7 @@
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="V19" s="21"/>
+      <c r="V19" s="23"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
@@ -18586,11 +18589,11 @@
         <f t="shared" si="1"/>
         <v>ROW</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="16">
         <f t="shared" si="2"/>
         <v>34.771</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="16">
         <f t="shared" si="3"/>
         <v>160.1</v>
       </c>
@@ -18605,7 +18608,7 @@
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="V20" s="21"/>
+      <c r="V20" s="23"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
@@ -18633,11 +18636,11 @@
         <f t="shared" si="1"/>
         <v>Russia</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="16">
         <f t="shared" si="2"/>
         <v>33.781</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="16">
         <f t="shared" si="3"/>
         <v>50.6715</v>
       </c>
@@ -18652,7 +18655,7 @@
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="V21" s="21"/>
+      <c r="V21" s="23"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
@@ -18680,11 +18683,11 @@
         <f t="shared" si="1"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="16">
         <f t="shared" si="2"/>
         <v>2.134</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="16">
         <f t="shared" si="3"/>
         <v>10.3</v>
       </c>
@@ -18699,7 +18702,7 @@
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="V22" s="21"/>
+      <c r="V22" s="23"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
@@ -18727,11 +18730,11 @@
         <f t="shared" si="1"/>
         <v>SpainPor</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="16">
         <f t="shared" si="2"/>
         <v>7.832</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="16">
         <f t="shared" si="3"/>
         <v>11.748</v>
       </c>
@@ -18746,7 +18749,7 @@
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="V23" s="21"/>
+      <c r="V23" s="23"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
@@ -18774,11 +18777,11 @@
         <f t="shared" si="1"/>
         <v>SweFinDen</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="16">
         <f t="shared" si="2"/>
         <v>10.659</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="16">
         <f t="shared" si="3"/>
         <v>15.9885</v>
       </c>
@@ -18793,7 +18796,7 @@
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="V24" s="21"/>
+      <c r="V24" s="23"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
@@ -18821,11 +18824,11 @@
         <f t="shared" si="1"/>
         <v>Switzerland</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M25" s="16">
         <f t="shared" si="2"/>
         <v>3.256</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25" s="16">
         <f t="shared" si="3"/>
         <v>4.884</v>
       </c>
@@ -18840,7 +18843,7 @@
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="V25" s="21"/>
+      <c r="V25" s="23"/>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
@@ -18868,11 +18871,11 @@
         <f t="shared" si="1"/>
         <v>Turkey</v>
       </c>
-      <c r="M26" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="14">
+      <c r="M26" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="16">
         <f t="shared" si="3"/>
         <v>16.4</v>
       </c>
@@ -18887,7 +18890,7 @@
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="V26" s="21"/>
+      <c r="V26" s="23"/>
     </row>
     <row r="27" spans="1:22">
       <c r="E27" t="s">
@@ -18906,11 +18909,11 @@
         <f t="shared" si="1"/>
         <v>UK</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M27" s="16">
         <f t="shared" si="2"/>
         <v>8.613</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="16">
         <f t="shared" si="3"/>
         <v>13.2</v>
       </c>
@@ -18925,7 +18928,7 @@
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="V27" s="21"/>
+      <c r="V27" s="23"/>
     </row>
     <row r="28" spans="1:22">
       <c r="E28" t="s">
@@ -18944,11 +18947,11 @@
         <f t="shared" ref="L28" si="5">IF(A26="","\I:",A26)</f>
         <v>Ukraine</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M28" s="16">
         <f t="shared" ref="M28" si="6">B26*1.1</f>
         <v>15.224</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="16">
         <f t="shared" ref="N28" si="7">MAX(VLOOKUP(L28,$E$4:$G$40,3,FALSE),M28*1.5)</f>
         <v>22.836</v>
       </c>
@@ -18963,7 +18966,7 @@
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="V28" s="21"/>
+      <c r="V28" s="23"/>
     </row>
     <row r="29" spans="1:22">
       <c r="E29" t="s">
@@ -18978,8 +18981,8 @@
       <c r="H29">
         <v>9.3</v>
       </c>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
       <c r="S29" t="s">
         <v>287</v>
       </c>
@@ -18989,7 +18992,7 @@
       <c r="U29" t="s">
         <v>251</v>
       </c>
-      <c r="V29" s="21">
+      <c r="V29" s="23">
         <v>0.33</v>
       </c>
     </row>
@@ -19015,7 +19018,7 @@
       <c r="U30" t="s">
         <v>253</v>
       </c>
-      <c r="V30" s="21">
+      <c r="V30" s="23">
         <v>0.33</v>
       </c>
     </row>
@@ -19058,11 +19061,11 @@
       <c r="H32">
         <v>3.8</v>
       </c>
-      <c r="M32" s="14">
+      <c r="M32" s="16">
         <f>SUM(M6:M29)</f>
         <v>441.661</v>
       </c>
-      <c r="N32" s="14">
+      <c r="N32" s="16">
         <f>SUM(N6:N29)</f>
         <v>1704.8755</v>
       </c>
@@ -21765,164 +21768,164 @@
       </c>
     </row>
     <row r="36" ht="17.75" spans="1:40">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="20" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="37" ht="16" spans="1:40">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="19" t="str">
+      <c r="C37" s="21" t="str">
         <f t="shared" ref="C37:AK37" si="0">B18</f>
         <v>Africa_North</v>
       </c>
-      <c r="D37" s="19" t="str">
+      <c r="D37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Africa_Other</v>
       </c>
-      <c r="E37" s="19" t="str">
+      <c r="E37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Australia</v>
       </c>
-      <c r="F37" s="19" t="str">
+      <c r="F37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Austria</v>
       </c>
-      <c r="G37" s="19" t="str">
+      <c r="G37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Baltics</v>
       </c>
-      <c r="H37" s="19" t="str">
+      <c r="H37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="I37" s="19" t="str">
+      <c r="I37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="J37" s="19" t="str">
+      <c r="J37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="K37" s="19" t="str">
+      <c r="K37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="L37" s="19" t="str">
+      <c r="L37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="M37" s="19" t="str">
+      <c r="M37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="N37" s="19" t="str">
+      <c r="N37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="O37" s="19" t="str">
+      <c r="O37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>GreeceCyp</v>
       </c>
-      <c r="P37" s="19" t="str">
+      <c r="P37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="Q37" s="19" t="str">
+      <c r="Q37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Iceland</v>
       </c>
-      <c r="R37" s="19" t="str">
+      <c r="R37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="S37" s="19" t="str">
+      <c r="S37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Ireland</v>
       </c>
-      <c r="T37" s="19" t="str">
+      <c r="T37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ItalyMal</v>
       </c>
-      <c r="U37" s="19" t="str">
+      <c r="U37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V37" s="19" t="str">
+      <c r="V37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="W37" s="19" t="str">
+      <c r="W37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="X37" s="19" t="str">
+      <c r="X37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="Y37" s="19" t="str">
+      <c r="Y37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Norway</v>
       </c>
-      <c r="Z37" s="19" t="str">
+      <c r="Z37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Poland</v>
       </c>
-      <c r="AA37" s="19" t="str">
+      <c r="AA37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="AB37" s="19" t="str">
+      <c r="AB37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="AC37" s="19" t="str">
+      <c r="AC37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>SaudiArabia</v>
       </c>
-      <c r="AD37" s="19" t="str">
+      <c r="AD37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="AE37" s="19" t="str">
+      <c r="AE37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="AF37" s="19" t="str">
+      <c r="AF37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="AG37" s="19" t="str">
+      <c r="AG37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="AH37" s="19" t="str">
+      <c r="AH37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="AI37" s="19" t="str">
+      <c r="AI37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="AJ37" s="19" t="str">
+      <c r="AJ37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="AK37" s="19" t="str">
+      <c r="AK37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>WestBalkans</v>
       </c>
-      <c r="AL37" s="19" t="s">
+      <c r="AL37" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AM37" s="19" t="s">
+      <c r="AM37" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="AN37" s="19" t="s">
+      <c r="AN37" s="21" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22234,143 +22237,143 @@
       <c r="A41" t="s">
         <v>318</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="22">
         <f>1-B25/100</f>
         <v>0.781</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="22">
         <f t="shared" ref="D41:AK41" si="4">1-C25/100</f>
         <v>0.8018</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="22">
         <f t="shared" si="4"/>
         <v>0.9012</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="22">
         <f t="shared" si="4"/>
         <v>0.9157</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="22">
         <f t="shared" si="4"/>
         <v>0.7593</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="22">
         <f t="shared" si="4"/>
         <v>0.9248</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="22">
         <f t="shared" si="4"/>
         <v>0.8378</v>
       </c>
-      <c r="J41" s="20">
+      <c r="J41" s="22">
         <f t="shared" si="4"/>
         <v>0.9004</v>
       </c>
-      <c r="K41" s="20">
+      <c r="K41" s="22">
         <f t="shared" si="4"/>
         <v>0.8597</v>
       </c>
-      <c r="L41" s="20">
+      <c r="L41" s="22">
         <f t="shared" si="4"/>
         <v>0.8738</v>
       </c>
-      <c r="M41" s="20">
+      <c r="M41" s="22">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="N41" s="20">
+      <c r="N41" s="22">
         <f t="shared" si="4"/>
         <v>0.9038</v>
       </c>
-      <c r="O41" s="20">
+      <c r="O41" s="22">
         <f t="shared" si="4"/>
         <v>0.8756</v>
       </c>
-      <c r="P41" s="20">
+      <c r="P41" s="22">
         <f t="shared" si="4"/>
         <v>0.8429</v>
       </c>
-      <c r="Q41" s="20">
+      <c r="Q41" s="22">
         <f t="shared" si="4"/>
         <v>0.9532</v>
       </c>
-      <c r="R41" s="20">
+      <c r="R41" s="22">
         <f t="shared" si="4"/>
         <v>0.7732</v>
       </c>
-      <c r="S41" s="20">
+      <c r="S41" s="22">
         <f t="shared" si="4"/>
         <v>0.8973</v>
       </c>
-      <c r="T41" s="20">
+      <c r="T41" s="22">
         <f t="shared" si="4"/>
         <v>0.899</v>
       </c>
-      <c r="U41" s="20">
+      <c r="U41" s="22">
         <f t="shared" si="4"/>
         <v>0.9173</v>
       </c>
-      <c r="V41" s="20">
+      <c r="V41" s="22">
         <f t="shared" si="4"/>
         <v>0.8421</v>
       </c>
-      <c r="W41" s="20">
+      <c r="W41" s="22">
         <f t="shared" si="4"/>
         <v>0.8113</v>
       </c>
-      <c r="X41" s="20">
+      <c r="X41" s="22">
         <f t="shared" si="4"/>
         <v>0.9117</v>
       </c>
-      <c r="Y41" s="20">
+      <c r="Y41" s="22">
         <f t="shared" si="4"/>
         <v>0.9496</v>
       </c>
-      <c r="Z41" s="20">
+      <c r="Z41" s="22">
         <f t="shared" si="4"/>
         <v>0.8708</v>
       </c>
-      <c r="AA41" s="20">
+      <c r="AA41" s="22">
         <f t="shared" si="4"/>
         <v>0.895</v>
       </c>
-      <c r="AB41" s="20">
+      <c r="AB41" s="22">
         <f t="shared" si="4"/>
         <v>0.8521</v>
       </c>
-      <c r="AC41" s="20">
+      <c r="AC41" s="22">
         <f t="shared" si="4"/>
         <v>0.8649</v>
       </c>
-      <c r="AD41" s="20">
+      <c r="AD41" s="22">
         <f t="shared" si="4"/>
         <v>0.844</v>
       </c>
-      <c r="AE41" s="20">
+      <c r="AE41" s="22">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="AF41" s="20">
+      <c r="AF41" s="22">
         <f t="shared" si="4"/>
         <v>0.9225</v>
       </c>
-      <c r="AG41" s="20">
+      <c r="AG41" s="22">
         <f t="shared" si="4"/>
         <v>0.8956</v>
       </c>
-      <c r="AH41" s="20">
+      <c r="AH41" s="22">
         <f t="shared" si="4"/>
         <v>0.8644</v>
       </c>
-      <c r="AI41" s="20">
+      <c r="AI41" s="22">
         <f t="shared" si="4"/>
         <v>0.8994</v>
       </c>
-      <c r="AJ41" s="20">
+      <c r="AJ41" s="22">
         <f t="shared" si="4"/>
         <v>0.827</v>
       </c>
-      <c r="AK41" s="20">
+      <c r="AK41" s="22">
         <f t="shared" si="4"/>
         <v>0.8198</v>
       </c>
@@ -22385,143 +22388,143 @@
       <c r="A42" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="12">
         <f t="shared" ref="C42:AK42" si="5">MAX($C$41:$AL$41)</f>
         <v>0.9532</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="O42" s="10">
+      <c r="O42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="P42" s="10">
+      <c r="P42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Q42" s="10">
+      <c r="Q42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="R42" s="10">
+      <c r="R42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="S42" s="10">
+      <c r="S42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="T42" s="10">
+      <c r="T42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="U42" s="10">
+      <c r="U42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="W42" s="10">
+      <c r="W42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="X42" s="10">
+      <c r="X42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Y42" s="10">
+      <c r="Y42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Z42" s="10">
+      <c r="Z42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AA42" s="10">
+      <c r="AA42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AB42" s="10">
+      <c r="AB42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AC42" s="10">
+      <c r="AC42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AD42" s="10">
+      <c r="AD42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AE42" s="10">
+      <c r="AE42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AF42" s="10">
+      <c r="AF42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AG42" s="10">
+      <c r="AG42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AH42" s="10">
+      <c r="AH42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AI42" s="10">
+      <c r="AI42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AJ42" s="10">
+      <c r="AJ42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AK42" s="10">
+      <c r="AK42" s="12">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
@@ -24258,39 +24261,39 @@
       </c>
     </row>
     <row r="20" spans="1:46">
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AE20" s="12"/>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
     </row>
     <row r="21" spans="1:46">
       <c r="A21" t="s">
@@ -24302,150 +24305,150 @@
       <c r="C21" t="s">
         <v>335</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="10" t="str">
+      <c r="E21" s="12" t="str">
         <f>E1</f>
         <v>Africa_North</v>
       </c>
-      <c r="F21" s="10" t="str">
+      <c r="F21" s="12" t="str">
         <f t="shared" ref="F21:AM21" si="1">F1</f>
         <v>Africa_Other</v>
       </c>
-      <c r="G21" s="10" t="str">
+      <c r="G21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Australia</v>
       </c>
-      <c r="H21" s="10" t="str">
+      <c r="H21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Austria</v>
       </c>
-      <c r="I21" s="10" t="str">
+      <c r="I21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Baltics</v>
       </c>
-      <c r="J21" s="10" t="str">
+      <c r="J21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>BeNeLux</v>
       </c>
-      <c r="K21" s="10" t="str">
+      <c r="K21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Brazil</v>
       </c>
-      <c r="L21" s="10" t="str">
+      <c r="L21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>China</v>
       </c>
-      <c r="M21" s="10" t="str">
+      <c r="M21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>CroSloven</v>
       </c>
-      <c r="N21" s="10" t="str">
+      <c r="N21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="O21" s="10" t="str">
+      <c r="O21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>France</v>
       </c>
-      <c r="P21" s="10" t="str">
+      <c r="P21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
-      <c r="Q21" s="10" t="str">
+      <c r="Q21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GreeceCyp</v>
       </c>
-      <c r="R21" s="10" t="str">
+      <c r="R21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>HunRomBul</v>
       </c>
-      <c r="S21" s="10" t="str">
+      <c r="S21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Iceland</v>
       </c>
-      <c r="T21" s="10" t="str">
+      <c r="T21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>India</v>
       </c>
-      <c r="U21" s="10" t="str">
+      <c r="U21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Ireland</v>
       </c>
-      <c r="V21" s="10" t="str">
+      <c r="V21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>ItalyMal</v>
       </c>
-      <c r="W21" s="10" t="str">
+      <c r="W21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Japan</v>
       </c>
-      <c r="X21" s="10" t="str">
+      <c r="X21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>LatAm</v>
       </c>
-      <c r="Y21" s="10" t="str">
+      <c r="Y21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>MidEast</v>
       </c>
-      <c r="Z21" s="10" t="str">
+      <c r="Z21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>NorthAm</v>
       </c>
-      <c r="AA21" s="10" t="str">
+      <c r="AA21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Norway</v>
       </c>
-      <c r="AB21" s="10" t="str">
+      <c r="AB21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Poland</v>
       </c>
-      <c r="AC21" s="10" t="str">
+      <c r="AC21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>ROW</v>
       </c>
-      <c r="AD21" s="10" t="str">
+      <c r="AD21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Russia</v>
       </c>
-      <c r="AE21" s="10" t="str">
+      <c r="AE21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>SaudiArabia</v>
       </c>
-      <c r="AF21" s="10" t="str">
+      <c r="AF21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="AG21" s="10" t="str">
+      <c r="AG21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>SpainPor</v>
       </c>
-      <c r="AH21" s="10" t="str">
+      <c r="AH21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>SweFinDen</v>
       </c>
-      <c r="AI21" s="10" t="str">
+      <c r="AI21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Switzerland</v>
       </c>
-      <c r="AJ21" s="10" t="str">
+      <c r="AJ21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Turkey</v>
       </c>
-      <c r="AK21" s="10" t="str">
+      <c r="AK21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>UK</v>
       </c>
-      <c r="AL21" s="10" t="str">
+      <c r="AL21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Ukraine</v>
       </c>
-      <c r="AM21" s="10" t="str">
+      <c r="AM21" s="12" t="str">
         <f t="shared" si="1"/>
         <v>WestBalkans</v>
       </c>
-      <c r="AN21" s="10" t="s">
+      <c r="AN21" s="12" t="s">
         <v>336</v>
       </c>
       <c r="AO21" t="s">
@@ -24454,21 +24457,21 @@
       <c r="AP21" t="s">
         <v>337</v>
       </c>
-      <c r="AQ21" s="10" t="s">
+      <c r="AQ21" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="AR21" s="10" t="s">
+      <c r="AR21" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="AS21" s="10" t="s">
+      <c r="AS21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AT21" s="10" t="s">
+      <c r="AT21" s="12" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:46">
-      <c r="A22" s="12">
+      <c r="A22" s="14">
         <v>0.95</v>
       </c>
       <c r="B22" t="str">
@@ -24478,150 +24481,150 @@
       <c r="C22" t="s">
         <v>340</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="15">
         <v>2023</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="12">
         <f>IF(E2="","",-MIN(E2,0.8)*$A22)</f>
         <v>-0.03135</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <f t="shared" ref="F22:AM26" si="2">IF(F2="","",-MIN(F2,0.8)*$A22)</f>
         <v>-0.2527</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <f t="shared" si="2"/>
         <v>-0.3857</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <f t="shared" si="2"/>
         <v>-0.40755</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="12">
         <f t="shared" si="2"/>
         <v>-0.5282</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="12">
         <f t="shared" si="2"/>
         <v>-0.34485</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="12">
         <f t="shared" si="2"/>
         <v>-0.5586</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="12">
         <f t="shared" si="2"/>
         <v>-0.6669</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="12">
         <f t="shared" si="2"/>
         <v>-0.66025</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="12">
         <f t="shared" si="2"/>
         <v>-0.55955</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="12">
         <f t="shared" si="2"/>
         <v>-0.4883</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="12">
         <f t="shared" si="2"/>
         <v>-0.64315</v>
       </c>
-      <c r="S22" s="10" t="str">
+      <c r="S22" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T22" s="10">
+      <c r="T22" s="12">
         <f t="shared" si="2"/>
         <v>-0.38665</v>
       </c>
-      <c r="U22" s="10">
+      <c r="U22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="12">
         <f t="shared" si="2"/>
         <v>-0.5928</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="X22" s="10">
+      <c r="X22" s="12">
         <f t="shared" si="2"/>
         <v>-0.4389</v>
       </c>
-      <c r="Y22" s="10">
+      <c r="Y22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Z22" s="10">
+      <c r="Z22" s="12">
         <f t="shared" si="2"/>
         <v>-0.51965</v>
       </c>
-      <c r="AA22" s="10">
+      <c r="AA22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AB22" s="10">
+      <c r="AB22" s="12">
         <f t="shared" si="2"/>
         <v>-0.741</v>
       </c>
-      <c r="AC22" s="10">
+      <c r="AC22" s="12">
         <f t="shared" si="2"/>
         <v>-0.5358</v>
       </c>
-      <c r="AD22" s="10">
+      <c r="AD22" s="12">
         <f t="shared" si="2"/>
         <v>-0.06745</v>
       </c>
-      <c r="AE22" s="10" t="str">
+      <c r="AE22" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF22" s="10">
+      <c r="AF22" s="12">
         <f t="shared" si="2"/>
         <v>-0.171</v>
       </c>
-      <c r="AG22" s="10">
+      <c r="AG22" s="12">
         <f t="shared" si="2"/>
         <v>-0.5738</v>
       </c>
-      <c r="AH22" s="10">
+      <c r="AH22" s="12">
         <f t="shared" si="2"/>
         <v>-0.36575</v>
       </c>
-      <c r="AI22" s="10">
+      <c r="AI22" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AJ22" s="10">
+      <c r="AJ22" s="12">
         <f t="shared" si="2"/>
         <v>-0.45695</v>
       </c>
-      <c r="AK22" s="10">
+      <c r="AK22" s="12">
         <f t="shared" si="2"/>
         <v>-0.55005</v>
       </c>
-      <c r="AL22" s="10">
+      <c r="AL22" s="12">
         <f t="shared" si="2"/>
         <v>-0.16245</v>
       </c>
-      <c r="AM22" s="10">
+      <c r="AM22" s="12">
         <f t="shared" si="2"/>
         <v>-0.60705</v>
       </c>
-      <c r="AN22" s="14">
+      <c r="AN22" s="16">
         <f>1/31.536</f>
         <v>0.0317097919837646</v>
       </c>
@@ -24635,12 +24638,12 @@
       <c r="AQ22">
         <v>2</v>
       </c>
-      <c r="AR22" s="41" t="s">
+      <c r="AR22" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:46">
-      <c r="A23" s="15">
+      <c r="A23" s="17">
         <v>0.8</v>
       </c>
       <c r="B23" t="str">
@@ -24650,151 +24653,151 @@
       <c r="C23" t="s">
         <v>340</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="15">
         <f>D22</f>
         <v>2023</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="12">
         <f t="shared" ref="E23:T26" si="4">IF(E3="","",-MIN(E3,0.8)*$A23)</f>
         <v>-0.5864</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="12">
         <f t="shared" si="4"/>
         <v>-0.5016</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="12">
         <f t="shared" si="4"/>
         <v>-0.64</v>
       </c>
-      <c r="I23" s="10" t="str">
+      <c r="I23" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="12">
         <f t="shared" si="4"/>
         <v>-0.2224</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="12">
         <f t="shared" si="4"/>
         <v>-0.4072</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="12">
         <f t="shared" si="4"/>
         <v>-0.4608</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="12">
         <f t="shared" si="4"/>
         <v>-0.2944</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="12">
         <f t="shared" si="4"/>
         <v>-0.3656</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="12">
         <f t="shared" si="4"/>
         <v>-0.0784</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="12">
         <f t="shared" si="4"/>
         <v>-0.3056</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="12">
         <f t="shared" si="4"/>
         <v>-0.1496</v>
       </c>
-      <c r="R23" s="10">
+      <c r="R23" s="12">
         <f t="shared" si="4"/>
         <v>-0.2216</v>
       </c>
-      <c r="S23" s="10" t="str">
+      <c r="S23" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T23" s="10">
+      <c r="T23" s="12">
         <f t="shared" si="4"/>
         <v>-0.5656</v>
       </c>
-      <c r="U23" s="10">
+      <c r="U23" s="12">
         <f t="shared" si="2"/>
         <v>-0.1056</v>
       </c>
-      <c r="V23" s="10">
+      <c r="V23" s="12">
         <f t="shared" si="2"/>
         <v>-0.2056</v>
       </c>
-      <c r="W23" s="10">
+      <c r="W23" s="12">
         <f t="shared" si="2"/>
         <v>-0.5392</v>
       </c>
-      <c r="X23" s="10">
+      <c r="X23" s="12">
         <f t="shared" si="2"/>
         <v>-0.3984</v>
       </c>
-      <c r="Y23" s="10">
+      <c r="Y23" s="12">
         <f t="shared" si="2"/>
         <v>-0.64</v>
       </c>
-      <c r="Z23" s="10">
+      <c r="Z23" s="12">
         <f t="shared" si="2"/>
         <v>-0.316</v>
       </c>
-      <c r="AA23" s="10">
+      <c r="AA23" s="12">
         <f t="shared" si="2"/>
         <v>-0.64</v>
       </c>
-      <c r="AB23" s="10">
+      <c r="AB23" s="12">
         <f t="shared" si="2"/>
         <v>-0.3296</v>
       </c>
-      <c r="AC23" s="10">
+      <c r="AC23" s="12">
         <f t="shared" si="2"/>
         <v>-0.452</v>
       </c>
-      <c r="AD23" s="10">
+      <c r="AD23" s="12">
         <f t="shared" si="2"/>
         <v>-0.5096</v>
       </c>
-      <c r="AE23" s="10" t="str">
+      <c r="AE23" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF23" s="10">
+      <c r="AF23" s="12">
         <f t="shared" si="2"/>
         <v>-0.3792</v>
       </c>
-      <c r="AG23" s="10">
+      <c r="AG23" s="12">
         <f t="shared" si="2"/>
         <v>-0.1208</v>
       </c>
-      <c r="AH23" s="10">
+      <c r="AH23" s="12">
         <f t="shared" si="2"/>
         <v>-0.1328</v>
       </c>
-      <c r="AI23" s="10" t="str">
+      <c r="AI23" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AJ23" s="10">
+      <c r="AJ23" s="12">
         <f t="shared" si="2"/>
         <v>-0.5168</v>
       </c>
-      <c r="AK23" s="10">
+      <c r="AK23" s="12">
         <f t="shared" si="2"/>
         <v>-0.1472</v>
       </c>
-      <c r="AL23" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM23" s="10">
+      <c r="AL23" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="12">
         <f t="shared" si="2"/>
         <v>-0.472</v>
       </c>
-      <c r="AN23" s="14">
+      <c r="AN23" s="16">
         <f t="shared" ref="AN23:AN31" si="5">1/31.536</f>
         <v>0.0317097919837646</v>
       </c>
@@ -24808,12 +24811,12 @@
       <c r="AQ23">
         <v>2</v>
       </c>
-      <c r="AR23" s="41" t="s">
+      <c r="AR23" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:46">
-      <c r="A24" s="12">
+      <c r="A24" s="14">
         <v>0.95</v>
       </c>
       <c r="B24" t="str">
@@ -24823,151 +24826,151 @@
       <c r="C24" t="s">
         <v>340</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="15">
         <f t="shared" ref="D24:D31" si="6">D23</f>
         <v>2023</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="12">
         <f t="shared" si="4"/>
         <v>-0.36765</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="12">
         <f t="shared" si="2"/>
         <v>-0.31065</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="12">
         <f t="shared" si="2"/>
         <v>-0.18715</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="12">
         <f t="shared" si="2"/>
         <v>-0.1501</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="12">
         <f t="shared" si="2"/>
         <v>-0.07315</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="12">
         <f t="shared" si="2"/>
         <v>-0.2964</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="12">
         <f t="shared" si="2"/>
         <v>-0.2204</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="12">
         <f t="shared" si="2"/>
         <v>-0.24605</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="12">
         <f t="shared" si="2"/>
         <v>-0.6536</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="12">
         <f t="shared" si="2"/>
         <v>-0.13775</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="12">
         <f t="shared" si="2"/>
         <v>-0.1843</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="12">
         <f t="shared" si="2"/>
         <v>-0.24795</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="12">
         <f t="shared" si="2"/>
         <v>-0.26885</v>
       </c>
-      <c r="R24" s="10">
+      <c r="R24" s="12">
         <f t="shared" si="2"/>
         <v>-0.18905</v>
       </c>
-      <c r="S24" s="10" t="str">
+      <c r="S24" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T24" s="10">
+      <c r="T24" s="12">
         <f t="shared" si="2"/>
         <v>-0.17575</v>
       </c>
-      <c r="U24" s="10">
+      <c r="U24" s="12">
         <f t="shared" si="2"/>
         <v>-0.39045</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="12">
         <f t="shared" si="2"/>
         <v>-0.2261</v>
       </c>
-      <c r="W24" s="10">
+      <c r="W24" s="12">
         <f t="shared" si="2"/>
         <v>-0.44175</v>
       </c>
-      <c r="X24" s="10">
+      <c r="X24" s="12">
         <f t="shared" si="2"/>
         <v>-0.38</v>
       </c>
-      <c r="Y24" s="10">
+      <c r="Y24" s="12">
         <f t="shared" si="2"/>
         <v>-0.41515</v>
       </c>
-      <c r="Z24" s="10">
+      <c r="Z24" s="12">
         <f t="shared" si="2"/>
         <v>-0.37335</v>
       </c>
-      <c r="AA24" s="10">
+      <c r="AA24" s="12">
         <f t="shared" si="2"/>
         <v>-0.24985</v>
       </c>
-      <c r="AB24" s="10">
+      <c r="AB24" s="12">
         <f t="shared" si="2"/>
         <v>-0.4579</v>
       </c>
-      <c r="AC24" s="10">
+      <c r="AC24" s="12">
         <f t="shared" si="2"/>
         <v>-0.43415</v>
       </c>
-      <c r="AD24" s="10">
+      <c r="AD24" s="12">
         <f t="shared" si="2"/>
         <v>-0.51015</v>
       </c>
-      <c r="AE24" s="10">
+      <c r="AE24" s="12">
         <f t="shared" si="2"/>
         <v>-0.4104</v>
       </c>
-      <c r="AF24" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="10">
+      <c r="AF24" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="12">
         <f t="shared" si="2"/>
         <v>-0.25555</v>
       </c>
-      <c r="AH24" s="10">
+      <c r="AH24" s="12">
         <f t="shared" si="2"/>
         <v>-0.0456</v>
       </c>
-      <c r="AI24" s="10">
+      <c r="AI24" s="12">
         <f t="shared" si="2"/>
         <v>-0.2356</v>
       </c>
-      <c r="AJ24" s="10">
+      <c r="AJ24" s="12">
         <f t="shared" si="2"/>
         <v>-0.26125</v>
       </c>
-      <c r="AK24" s="10">
+      <c r="AK24" s="12">
         <f t="shared" si="2"/>
         <v>-0.28595</v>
       </c>
-      <c r="AL24" s="10">
+      <c r="AL24" s="12">
         <f t="shared" si="2"/>
         <v>-0.47025</v>
       </c>
-      <c r="AM24" s="10">
+      <c r="AM24" s="12">
         <f t="shared" si="2"/>
         <v>-0.2489</v>
       </c>
-      <c r="AN24" s="14">
+      <c r="AN24" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -24981,10 +24984,10 @@
       <c r="AQ24">
         <v>2</v>
       </c>
-      <c r="AR24" s="41" t="s">
+      <c r="AR24" s="42" t="s">
         <v>341</v>
       </c>
-      <c r="AS24" s="41" t="s">
+      <c r="AS24" s="42" t="s">
         <v>342</v>
       </c>
       <c r="AT24" t="s">
@@ -24992,7 +24995,7 @@
       </c>
     </row>
     <row r="25" spans="1:46">
-      <c r="A25" s="12">
+      <c r="A25" s="14">
         <v>0.95</v>
       </c>
       <c r="B25" t="str">
@@ -25002,151 +25005,151 @@
       <c r="C25" t="s">
         <v>340</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E25" s="10" t="str">
+      <c r="E25" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F25" s="10" t="str">
+      <c r="F25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G25" s="10" t="str">
+      <c r="G25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H25" s="10" t="str">
+      <c r="H25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I25" s="10" t="str">
+      <c r="I25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="12">
         <f t="shared" si="2"/>
         <v>-0.5928</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Q25" s="10" t="str">
+      <c r="Q25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R25" s="10">
+      <c r="R25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="S25" s="10" t="str">
+      <c r="S25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T25" s="10">
+      <c r="T25" s="12">
         <f t="shared" si="2"/>
         <v>-0.6992</v>
       </c>
-      <c r="U25" s="10" t="str">
+      <c r="U25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V25" s="10" t="str">
+      <c r="V25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="W25" s="10">
+      <c r="W25" s="12">
         <f t="shared" si="2"/>
         <v>-0.25365</v>
       </c>
-      <c r="X25" s="10">
+      <c r="X25" s="12">
         <f t="shared" si="2"/>
         <v>-0.5548</v>
       </c>
-      <c r="Y25" s="10">
+      <c r="Y25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Z25" s="10">
+      <c r="Z25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AA25" s="10" t="str">
+      <c r="AA25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB25" s="10" t="str">
+      <c r="AB25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AC25" s="10">
+      <c r="AC25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AD25" s="10">
+      <c r="AD25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AE25" s="10" t="str">
+      <c r="AE25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF25" s="10">
+      <c r="AF25" s="12">
         <f t="shared" si="2"/>
         <v>-0.4997</v>
       </c>
-      <c r="AG25" s="10">
+      <c r="AG25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AH25" s="10">
+      <c r="AH25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AI25" s="10">
+      <c r="AI25" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AJ25" s="10" t="str">
+      <c r="AJ25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AK25" s="10">
+      <c r="AK25" s="12">
         <f t="shared" si="2"/>
         <v>-0.75145</v>
       </c>
-      <c r="AL25" s="10" t="str">
+      <c r="AL25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AM25" s="10" t="str">
+      <c r="AM25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AN25" s="14">
+      <c r="AN25" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25160,12 +25163,12 @@
       <c r="AQ25">
         <v>2</v>
       </c>
-      <c r="AR25" s="41" t="s">
+      <c r="AR25" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:46">
-      <c r="A26" s="12">
+      <c r="A26" s="14">
         <v>0.95</v>
       </c>
       <c r="B26" t="str">
@@ -25175,151 +25178,151 @@
       <c r="C26" t="s">
         <v>344</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="12">
         <f t="shared" si="4"/>
         <v>-0.76</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="12">
         <f t="shared" si="2"/>
         <v>-0.1387</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="12">
         <f t="shared" si="2"/>
         <v>-0.2489</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="12">
         <f t="shared" si="2"/>
         <v>-0.54435</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="12">
         <f t="shared" si="2"/>
         <v>-0.35055</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="12">
         <f t="shared" si="2"/>
         <v>-0.1577</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="12">
         <f t="shared" si="2"/>
         <v>-0.5529</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="12">
         <f t="shared" si="2"/>
         <v>-0.01615</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="12">
         <f t="shared" si="2"/>
         <v>-0.54245</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="12">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="Q26" s="12">
         <f t="shared" si="2"/>
         <v>-0.2964</v>
       </c>
-      <c r="R26" s="10">
+      <c r="R26" s="12">
         <f t="shared" si="2"/>
         <v>-0.0836</v>
       </c>
-      <c r="S26" s="10" t="str">
+      <c r="S26" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T26" s="10">
+      <c r="T26" s="12">
         <f t="shared" ref="T26:AM26" si="7">IF(T6="","",-MIN(T6,0.8)*$A26)</f>
         <v>-0.0247</v>
       </c>
-      <c r="U26" s="10">
+      <c r="U26" s="12">
         <f t="shared" si="7"/>
         <v>-0.10545</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="W26" s="10">
+      <c r="W26" s="12">
         <f t="shared" si="7"/>
         <v>-0.1843</v>
       </c>
-      <c r="X26" s="10">
+      <c r="X26" s="12">
         <f t="shared" si="7"/>
         <v>-0.20995</v>
       </c>
-      <c r="Y26" s="10">
+      <c r="Y26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="Z26" s="10">
+      <c r="Z26" s="12">
         <f t="shared" si="7"/>
         <v>-0.12825</v>
       </c>
-      <c r="AA26" s="10">
+      <c r="AA26" s="12">
         <f t="shared" si="7"/>
         <v>-0.684</v>
       </c>
-      <c r="AB26" s="10">
+      <c r="AB26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AC26" s="10">
+      <c r="AC26" s="12">
         <f t="shared" si="7"/>
         <v>-0.19</v>
       </c>
-      <c r="AD26" s="10">
+      <c r="AD26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AE26" s="10">
+      <c r="AE26" s="12">
         <f t="shared" si="7"/>
         <v>-0.608</v>
       </c>
-      <c r="AF26" s="10">
+      <c r="AF26" s="12">
         <f t="shared" si="7"/>
         <v>-0.21945</v>
       </c>
-      <c r="AG26" s="10">
+      <c r="AG26" s="12">
         <f t="shared" si="7"/>
         <v>-0.3553</v>
       </c>
-      <c r="AH26" s="10">
+      <c r="AH26" s="12">
         <f t="shared" si="7"/>
         <v>-0.095</v>
       </c>
-      <c r="AI26" s="10">
+      <c r="AI26" s="12">
         <f t="shared" si="7"/>
         <v>-0.26505</v>
       </c>
-      <c r="AJ26" s="10">
+      <c r="AJ26" s="12">
         <f t="shared" si="7"/>
         <v>-0.15485</v>
       </c>
-      <c r="AK26" s="10">
+      <c r="AK26" s="12">
         <f t="shared" si="7"/>
         <v>-0.40375</v>
       </c>
-      <c r="AL26" s="10">
+      <c r="AL26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AM26" s="10">
+      <c r="AM26" s="12">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AN26" s="14">
+      <c r="AN26" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25333,12 +25336,12 @@
       <c r="AQ26">
         <v>2</v>
       </c>
-      <c r="AR26" s="41" t="s">
+      <c r="AR26" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:46">
-      <c r="A27" s="12">
+      <c r="A27" s="14">
         <v>1.05</v>
       </c>
       <c r="B27" t="str">
@@ -25348,151 +25351,151 @@
       <c r="C27" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="12">
         <f>IF(E2="","",-E2*$A27)</f>
         <v>-0.03465</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="12">
         <f>IF(F2="","",-F2*$A27)</f>
         <v>-0.2793</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="12">
         <f t="shared" ref="G27:AM30" si="8">IF(G2="","",-G2*$A27)</f>
         <v>-0.4263</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="12">
         <f t="shared" si="8"/>
         <v>-0.45045</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="12">
         <f t="shared" si="8"/>
         <v>-0.5838</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="12">
         <f t="shared" si="8"/>
         <v>-0.38115</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="12">
         <f t="shared" si="8"/>
         <v>-0.6174</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="12">
         <f t="shared" si="8"/>
         <v>-0.7371</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="12">
         <f t="shared" si="8"/>
         <v>-0.72975</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="12">
         <f t="shared" si="8"/>
         <v>-0.61845</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="12">
         <f t="shared" si="8"/>
         <v>-0.5397</v>
       </c>
-      <c r="R27" s="10">
+      <c r="R27" s="12">
         <f t="shared" si="8"/>
         <v>-0.71085</v>
       </c>
-      <c r="S27" s="10" t="str">
+      <c r="S27" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T27" s="10">
+      <c r="T27" s="12">
         <f t="shared" si="8"/>
         <v>-0.42735</v>
       </c>
-      <c r="U27" s="10">
+      <c r="U27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="V27" s="10">
+      <c r="V27" s="12">
         <f t="shared" si="8"/>
         <v>-0.6552</v>
       </c>
-      <c r="W27" s="10">
+      <c r="W27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9408</v>
       </c>
-      <c r="X27" s="10">
+      <c r="X27" s="12">
         <f t="shared" si="8"/>
         <v>-0.4851</v>
       </c>
-      <c r="Y27" s="10">
+      <c r="Y27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Z27" s="10">
+      <c r="Z27" s="12">
         <f t="shared" si="8"/>
         <v>-0.57435</v>
       </c>
-      <c r="AA27" s="10">
+      <c r="AA27" s="12">
         <f t="shared" si="8"/>
         <v>-0.95865</v>
       </c>
-      <c r="AB27" s="10">
+      <c r="AB27" s="12">
         <f t="shared" si="8"/>
         <v>-0.819</v>
       </c>
-      <c r="AC27" s="10">
+      <c r="AC27" s="12">
         <f t="shared" si="8"/>
         <v>-0.5922</v>
       </c>
-      <c r="AD27" s="10">
+      <c r="AD27" s="12">
         <f t="shared" si="8"/>
         <v>-0.07455</v>
       </c>
-      <c r="AE27" s="10" t="str">
+      <c r="AE27" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF27" s="10">
+      <c r="AF27" s="12">
         <f t="shared" si="8"/>
         <v>-0.189</v>
       </c>
-      <c r="AG27" s="10">
+      <c r="AG27" s="12">
         <f t="shared" si="8"/>
         <v>-0.6342</v>
       </c>
-      <c r="AH27" s="10">
+      <c r="AH27" s="12">
         <f t="shared" si="8"/>
         <v>-0.40425</v>
       </c>
-      <c r="AI27" s="10">
+      <c r="AI27" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="AJ27" s="10">
+      <c r="AJ27" s="12">
         <f t="shared" si="8"/>
         <v>-0.50505</v>
       </c>
-      <c r="AK27" s="10">
+      <c r="AK27" s="12">
         <f t="shared" si="8"/>
         <v>-0.60795</v>
       </c>
-      <c r="AL27" s="10">
+      <c r="AL27" s="12">
         <f t="shared" si="8"/>
         <v>-0.17955</v>
       </c>
-      <c r="AM27" s="10">
+      <c r="AM27" s="12">
         <f t="shared" si="8"/>
         <v>-0.67095</v>
       </c>
-      <c r="AN27" s="14">
+      <c r="AN27" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25506,12 +25509,12 @@
       <c r="AQ27">
         <v>2</v>
       </c>
-      <c r="AR27" s="41" t="s">
+      <c r="AR27" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:46">
-      <c r="A28" s="12">
+      <c r="A28" s="14">
         <v>1.05</v>
       </c>
       <c r="B28" t="str">
@@ -25521,151 +25524,151 @@
       <c r="C28" t="s">
         <v>345</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="12">
         <f t="shared" ref="E28:T31" si="10">IF(E3="","",-E3*$A28)</f>
         <v>-0.76965</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="12">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="12">
         <f t="shared" si="8"/>
         <v>-0.65835</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="I28" s="10" t="str">
+      <c r="I28" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="12">
         <f t="shared" si="8"/>
         <v>-0.2919</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="12">
         <f t="shared" si="8"/>
         <v>-0.53445</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="12">
         <f t="shared" si="8"/>
         <v>-0.6048</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="12">
         <f t="shared" si="8"/>
         <v>-0.3864</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="12">
         <f t="shared" si="8"/>
         <v>-0.47985</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="12">
         <f t="shared" si="8"/>
         <v>-0.1029</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="12">
         <f t="shared" si="8"/>
         <v>-0.4011</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q28" s="12">
         <f t="shared" si="8"/>
         <v>-0.19635</v>
       </c>
-      <c r="R28" s="10">
+      <c r="R28" s="12">
         <f t="shared" si="8"/>
         <v>-0.29085</v>
       </c>
-      <c r="S28" s="10" t="str">
+      <c r="S28" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T28" s="10">
+      <c r="T28" s="12">
         <f t="shared" si="8"/>
         <v>-0.74235</v>
       </c>
-      <c r="U28" s="10">
+      <c r="U28" s="12">
         <f t="shared" si="8"/>
         <v>-0.1386</v>
       </c>
-      <c r="V28" s="10">
+      <c r="V28" s="12">
         <f t="shared" si="8"/>
         <v>-0.26985</v>
       </c>
-      <c r="W28" s="10">
+      <c r="W28" s="12">
         <f t="shared" si="8"/>
         <v>-0.7077</v>
       </c>
-      <c r="X28" s="10">
+      <c r="X28" s="12">
         <f t="shared" si="8"/>
         <v>-0.5229</v>
       </c>
-      <c r="Y28" s="10">
+      <c r="Y28" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Z28" s="10">
+      <c r="Z28" s="12">
         <f t="shared" si="8"/>
         <v>-0.41475</v>
       </c>
-      <c r="AA28" s="10">
+      <c r="AA28" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="AB28" s="10">
+      <c r="AB28" s="12">
         <f t="shared" si="8"/>
         <v>-0.4326</v>
       </c>
-      <c r="AC28" s="10">
+      <c r="AC28" s="12">
         <f t="shared" si="8"/>
         <v>-0.59325</v>
       </c>
-      <c r="AD28" s="10">
+      <c r="AD28" s="12">
         <f t="shared" si="8"/>
         <v>-0.66885</v>
       </c>
-      <c r="AE28" s="10" t="str">
+      <c r="AE28" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF28" s="10">
+      <c r="AF28" s="12">
         <f t="shared" si="8"/>
         <v>-0.4977</v>
       </c>
-      <c r="AG28" s="10">
+      <c r="AG28" s="12">
         <f t="shared" si="8"/>
         <v>-0.15855</v>
       </c>
-      <c r="AH28" s="10">
+      <c r="AH28" s="12">
         <f t="shared" si="8"/>
         <v>-0.1743</v>
       </c>
-      <c r="AI28" s="10" t="str">
+      <c r="AI28" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AJ28" s="10">
+      <c r="AJ28" s="12">
         <f t="shared" si="8"/>
         <v>-0.6783</v>
       </c>
-      <c r="AK28" s="10">
+      <c r="AK28" s="12">
         <f t="shared" si="8"/>
         <v>-0.1932</v>
       </c>
-      <c r="AL28" s="10">
+      <c r="AL28" s="12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM28" s="10">
+      <c r="AM28" s="12">
         <f t="shared" si="8"/>
         <v>-0.6195</v>
       </c>
-      <c r="AN28" s="14">
+      <c r="AN28" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25679,12 +25682,12 @@
       <c r="AQ28">
         <v>2</v>
       </c>
-      <c r="AR28" s="41" t="s">
+      <c r="AR28" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:46">
-      <c r="A29" s="12">
+      <c r="A29" s="14">
         <v>1.05</v>
       </c>
       <c r="B29" t="str">
@@ -25694,151 +25697,151 @@
       <c r="C29" t="s">
         <v>345</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="12">
         <f t="shared" si="10"/>
         <v>-0.40635</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="12">
         <f t="shared" si="10"/>
         <v>-0.34335</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="12">
         <f t="shared" si="8"/>
         <v>-0.20685</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="12">
         <f t="shared" si="8"/>
         <v>-0.1659</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="12">
         <f t="shared" si="8"/>
         <v>-0.08085</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="12">
         <f t="shared" si="8"/>
         <v>-0.3276</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="12">
         <f t="shared" si="8"/>
         <v>-0.2436</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="12">
         <f t="shared" si="8"/>
         <v>-0.27195</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="12">
         <f t="shared" si="8"/>
         <v>-0.7224</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="12">
         <f t="shared" si="8"/>
         <v>-0.15225</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="12">
         <f t="shared" si="8"/>
         <v>-0.2037</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="12">
         <f t="shared" si="8"/>
         <v>-0.27405</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="12">
         <f t="shared" si="8"/>
         <v>-0.29715</v>
       </c>
-      <c r="R29" s="10">
+      <c r="R29" s="12">
         <f t="shared" si="8"/>
         <v>-0.20895</v>
       </c>
-      <c r="S29" s="10" t="str">
+      <c r="S29" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T29" s="10">
+      <c r="T29" s="12">
         <f t="shared" si="8"/>
         <v>-0.19425</v>
       </c>
-      <c r="U29" s="10">
+      <c r="U29" s="12">
         <f t="shared" si="8"/>
         <v>-0.43155</v>
       </c>
-      <c r="V29" s="10">
+      <c r="V29" s="12">
         <f t="shared" si="8"/>
         <v>-0.2499</v>
       </c>
-      <c r="W29" s="10">
+      <c r="W29" s="12">
         <f t="shared" si="8"/>
         <v>-0.48825</v>
       </c>
-      <c r="X29" s="10">
+      <c r="X29" s="12">
         <f t="shared" si="8"/>
         <v>-0.42</v>
       </c>
-      <c r="Y29" s="10">
+      <c r="Y29" s="12">
         <f t="shared" si="8"/>
         <v>-0.45885</v>
       </c>
-      <c r="Z29" s="10">
+      <c r="Z29" s="12">
         <f t="shared" si="8"/>
         <v>-0.41265</v>
       </c>
-      <c r="AA29" s="10">
+      <c r="AA29" s="12">
         <f t="shared" si="8"/>
         <v>-0.27615</v>
       </c>
-      <c r="AB29" s="10">
+      <c r="AB29" s="12">
         <f t="shared" si="8"/>
         <v>-0.5061</v>
       </c>
-      <c r="AC29" s="10">
+      <c r="AC29" s="12">
         <f t="shared" si="8"/>
         <v>-0.47985</v>
       </c>
-      <c r="AD29" s="10">
+      <c r="AD29" s="12">
         <f t="shared" si="8"/>
         <v>-0.56385</v>
       </c>
-      <c r="AE29" s="10">
+      <c r="AE29" s="12">
         <f t="shared" si="8"/>
         <v>-0.4536</v>
       </c>
-      <c r="AF29" s="10">
+      <c r="AF29" s="12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="10">
+      <c r="AG29" s="12">
         <f t="shared" si="8"/>
         <v>-0.28245</v>
       </c>
-      <c r="AH29" s="10">
+      <c r="AH29" s="12">
         <f t="shared" si="8"/>
         <v>-0.0504</v>
       </c>
-      <c r="AI29" s="10">
+      <c r="AI29" s="12">
         <f t="shared" si="8"/>
         <v>-0.2604</v>
       </c>
-      <c r="AJ29" s="10">
+      <c r="AJ29" s="12">
         <f t="shared" si="8"/>
         <v>-0.28875</v>
       </c>
-      <c r="AK29" s="10">
+      <c r="AK29" s="12">
         <f t="shared" si="8"/>
         <v>-0.31605</v>
       </c>
-      <c r="AL29" s="10">
+      <c r="AL29" s="12">
         <f t="shared" si="8"/>
         <v>-0.51975</v>
       </c>
-      <c r="AM29" s="10">
+      <c r="AM29" s="12">
         <f t="shared" si="8"/>
         <v>-0.2751</v>
       </c>
-      <c r="AN29" s="14">
+      <c r="AN29" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25852,12 +25855,12 @@
       <c r="AQ29">
         <v>2</v>
       </c>
-      <c r="AR29" s="41" t="s">
+      <c r="AR29" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:46">
-      <c r="A30" s="12">
+      <c r="A30" s="14">
         <v>1.05</v>
       </c>
       <c r="B30" t="str">
@@ -25867,151 +25870,151 @@
       <c r="C30" t="s">
         <v>345</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E30" s="10" t="str">
+      <c r="E30" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F30" s="10" t="str">
+      <c r="F30" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G30" s="10" t="str">
+      <c r="G30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H30" s="10" t="str">
+      <c r="H30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I30" s="10" t="str">
+      <c r="I30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="12">
         <f t="shared" si="8"/>
         <v>-0.8736</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="12">
         <f t="shared" si="8"/>
         <v>-0.9156</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="12">
         <f t="shared" si="8"/>
         <v>-0.97965</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="12">
         <f t="shared" si="8"/>
         <v>-0.92925</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="12">
         <f t="shared" si="8"/>
         <v>-0.6552</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="12">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Q30" s="10" t="str">
+      <c r="Q30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="12">
         <f t="shared" si="8"/>
         <v>-0.97125</v>
       </c>
-      <c r="S30" s="10" t="str">
+      <c r="S30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T30" s="10">
+      <c r="T30" s="12">
         <f t="shared" si="8"/>
         <v>-0.7728</v>
       </c>
-      <c r="U30" s="10" t="str">
+      <c r="U30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="V30" s="10" t="str">
+      <c r="V30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="W30" s="10">
+      <c r="W30" s="12">
         <f t="shared" si="8"/>
         <v>-0.28035</v>
       </c>
-      <c r="X30" s="10">
+      <c r="X30" s="12">
         <f t="shared" si="8"/>
         <v>-0.6132</v>
       </c>
-      <c r="Y30" s="10">
+      <c r="Y30" s="12">
         <f t="shared" si="8"/>
         <v>-0.8988</v>
       </c>
-      <c r="Z30" s="10">
+      <c r="Z30" s="12">
         <f t="shared" si="8"/>
         <v>-0.94815</v>
       </c>
-      <c r="AA30" s="10" t="str">
+      <c r="AA30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB30" s="10" t="str">
+      <c r="AB30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AC30" s="10">
+      <c r="AC30" s="12">
         <f t="shared" si="8"/>
         <v>-0.87675</v>
       </c>
-      <c r="AD30" s="10">
+      <c r="AD30" s="12">
         <f t="shared" si="8"/>
         <v>-0.882</v>
       </c>
-      <c r="AE30" s="10" t="str">
+      <c r="AE30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF30" s="10">
+      <c r="AF30" s="12">
         <f t="shared" si="8"/>
         <v>-0.5523</v>
       </c>
-      <c r="AG30" s="10">
+      <c r="AG30" s="12">
         <f t="shared" si="8"/>
         <v>-0.95655</v>
       </c>
-      <c r="AH30" s="10">
+      <c r="AH30" s="12">
         <f t="shared" si="8"/>
         <v>-0.8736</v>
       </c>
-      <c r="AI30" s="10">
+      <c r="AI30" s="12">
         <f t="shared" si="8"/>
         <v>-0.97965</v>
       </c>
-      <c r="AJ30" s="10" t="str">
+      <c r="AJ30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AK30" s="10">
+      <c r="AK30" s="12">
         <f t="shared" si="8"/>
         <v>-0.83055</v>
       </c>
-      <c r="AL30" s="10" t="str">
+      <c r="AL30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AM30" s="10" t="str">
+      <c r="AM30" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN30" s="14">
+      <c r="AN30" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -26025,12 +26028,12 @@
       <c r="AQ30">
         <v>2</v>
       </c>
-      <c r="AR30" s="41" t="s">
+      <c r="AR30" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:46">
-      <c r="A31" s="12">
+      <c r="A31" s="14">
         <v>1.05</v>
       </c>
       <c r="B31" t="str">
@@ -26040,151 +26043,151 @@
       <c r="C31" t="s">
         <v>345</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="15">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="12">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="12">
         <f t="shared" si="10"/>
         <v>-0.1533</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="12">
         <f t="shared" si="10"/>
         <v>-0.2751</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="12">
         <f t="shared" si="10"/>
         <v>-0.60165</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="12">
         <f t="shared" si="10"/>
         <v>-0.38745</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="12">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="12">
         <f t="shared" si="10"/>
         <v>-0.1743</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="12">
         <f t="shared" si="10"/>
         <v>-0.6111</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="12">
         <f t="shared" si="10"/>
         <v>-0.01785</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="12">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O31" s="12">
         <f t="shared" si="10"/>
         <v>-0.59955</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="12">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q31" s="12">
         <f t="shared" si="10"/>
         <v>-0.3276</v>
       </c>
-      <c r="R31" s="10">
+      <c r="R31" s="12">
         <f t="shared" si="10"/>
         <v>-0.0924</v>
       </c>
-      <c r="S31" s="10" t="str">
+      <c r="S31" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="T31" s="10">
+      <c r="T31" s="12">
         <f t="shared" si="10"/>
         <v>-0.0273</v>
       </c>
-      <c r="U31" s="10">
+      <c r="U31" s="12">
         <f t="shared" ref="U31:AM31" si="12">IF(U6="","",-U6*$A31)</f>
         <v>-0.11655</v>
       </c>
-      <c r="V31" s="10">
+      <c r="V31" s="12">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="W31" s="10">
+      <c r="W31" s="12">
         <f t="shared" si="12"/>
         <v>-0.2037</v>
       </c>
-      <c r="X31" s="10">
+      <c r="X31" s="12">
         <f t="shared" si="12"/>
         <v>-0.23205</v>
       </c>
-      <c r="Y31" s="10">
+      <c r="Y31" s="12">
         <f t="shared" si="12"/>
         <v>-0.93975</v>
       </c>
-      <c r="Z31" s="10">
+      <c r="Z31" s="12">
         <f t="shared" si="12"/>
         <v>-0.14175</v>
       </c>
-      <c r="AA31" s="10">
+      <c r="AA31" s="12">
         <f t="shared" si="12"/>
         <v>-0.756</v>
       </c>
-      <c r="AB31" s="10">
+      <c r="AB31" s="12">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AC31" s="10">
+      <c r="AC31" s="12">
         <f t="shared" si="12"/>
         <v>-0.21</v>
       </c>
-      <c r="AD31" s="10">
+      <c r="AD31" s="12">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AE31" s="10">
+      <c r="AE31" s="12">
         <f t="shared" si="12"/>
         <v>-0.672</v>
       </c>
-      <c r="AF31" s="10">
+      <c r="AF31" s="12">
         <f t="shared" si="12"/>
         <v>-0.24255</v>
       </c>
-      <c r="AG31" s="10">
+      <c r="AG31" s="12">
         <f t="shared" si="12"/>
         <v>-0.3927</v>
       </c>
-      <c r="AH31" s="10">
+      <c r="AH31" s="12">
         <f t="shared" si="12"/>
         <v>-0.105</v>
       </c>
-      <c r="AI31" s="10">
+      <c r="AI31" s="12">
         <f t="shared" si="12"/>
         <v>-0.29295</v>
       </c>
-      <c r="AJ31" s="10">
+      <c r="AJ31" s="12">
         <f t="shared" si="12"/>
         <v>-0.17115</v>
       </c>
-      <c r="AK31" s="10">
+      <c r="AK31" s="12">
         <f t="shared" si="12"/>
         <v>-0.44625</v>
       </c>
-      <c r="AL31" s="10">
+      <c r="AL31" s="12">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AM31" s="10">
+      <c r="AM31" s="12">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AN31" s="14">
+      <c r="AN31" s="16">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -26198,7 +26201,7 @@
       <c r="AQ31">
         <v>2</v>
       </c>
-      <c r="AR31" s="41" t="s">
+      <c r="AR31" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26208,7 +26211,7 @@
       </c>
     </row>
     <row r="33" spans="1:46">
-      <c r="A33" s="16">
+      <c r="A33" s="18">
         <v>0.3</v>
       </c>
       <c r="B33" t="str">
@@ -26223,160 +26226,160 @@
         <f>D22+7</f>
         <v>2030</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="16">
         <f>IF(E7="","",-MIN(E7,E2,0.8)*$A33)</f>
         <v>-0.0042</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="16">
         <f t="shared" ref="F33:AM37" si="13">IF(F7="","",-MIN(F7,F2,0.8)*$A33)</f>
         <v>-0.0525</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1218</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1287</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1668</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="16">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1089</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="16">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="M33" s="14">
+      <c r="M33" s="16">
         <f t="shared" si="13"/>
         <v>-0.165</v>
       </c>
-      <c r="N33" s="14">
+      <c r="N33" s="16">
         <f t="shared" si="13"/>
         <v>-0.2106</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O33" s="16">
         <f t="shared" si="13"/>
         <v>-0.2085</v>
       </c>
-      <c r="P33" s="14">
+      <c r="P33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1767</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="Q33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1407</v>
       </c>
-      <c r="R33" s="14">
+      <c r="R33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1467</v>
       </c>
-      <c r="S33" s="14" t="str">
+      <c r="S33" s="16" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="T33" s="14">
+      <c r="T33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0921</v>
       </c>
-      <c r="U33" s="14">
+      <c r="U33" s="16">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="V33" s="14">
+      <c r="V33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1872</v>
       </c>
-      <c r="W33" s="14">
+      <c r="W33" s="16">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="X33" s="14">
+      <c r="X33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1044</v>
       </c>
-      <c r="Y33" s="14">
+      <c r="Y33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0882</v>
       </c>
-      <c r="Z33" s="14">
+      <c r="Z33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1641</v>
       </c>
-      <c r="AA33" s="14">
+      <c r="AA33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0855</v>
       </c>
-      <c r="AB33" s="14">
+      <c r="AB33" s="16">
         <f t="shared" si="13"/>
         <v>-0.2232</v>
       </c>
-      <c r="AC33" s="14">
+      <c r="AC33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1248</v>
       </c>
-      <c r="AD33" s="14">
+      <c r="AD33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0153</v>
       </c>
-      <c r="AE33" s="14" t="str">
+      <c r="AE33" s="16" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AF33" s="14">
+      <c r="AF33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0435</v>
       </c>
-      <c r="AG33" s="14">
+      <c r="AG33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1812</v>
       </c>
-      <c r="AH33" s="14">
+      <c r="AH33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1155</v>
       </c>
-      <c r="AI33" s="14">
+      <c r="AI33" s="16">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="AJ33" s="14">
+      <c r="AJ33" s="16">
         <f t="shared" si="13"/>
         <v>-0.135</v>
       </c>
-      <c r="AK33" s="14">
+      <c r="AK33" s="16">
         <f t="shared" si="13"/>
         <v>-0.1737</v>
       </c>
-      <c r="AL33" s="14">
+      <c r="AL33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0513</v>
       </c>
-      <c r="AM33" s="14">
+      <c r="AM33" s="16">
         <f t="shared" si="13"/>
         <v>-0.0684</v>
       </c>
-      <c r="AO33" s="14" t="str">
+      <c r="AO33" s="16" t="str">
         <f>AO22</f>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP33" s="14" t="str">
+      <c r="AP33" s="16" t="str">
         <f t="shared" ref="AP33:AP42" si="14">AP22</f>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR33" s="41" t="s">
+      <c r="AR33" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:46">
-      <c r="A34" s="16">
+      <c r="A34" s="18">
         <v>0.3</v>
       </c>
       <c r="B34" t="str">
@@ -26391,160 +26394,160 @@
         <f t="shared" ref="D34:D42" si="16">D23+7</f>
         <v>2030</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="16">
         <f t="shared" ref="E34:AG37" si="17">IF(E8="","",-MIN(E8,E3,0.8)*$A34)</f>
         <v>-0.171</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1815</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0831</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="16">
         <f t="shared" si="17"/>
         <v>-0.24</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0753</v>
       </c>
-      <c r="K34" s="14">
+      <c r="K34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1527</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1545</v>
       </c>
-      <c r="M34" s="14">
+      <c r="M34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1104</v>
       </c>
-      <c r="N34" s="14">
+      <c r="N34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1284</v>
       </c>
-      <c r="O34" s="14">
+      <c r="O34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0282</v>
       </c>
-      <c r="P34" s="14">
+      <c r="P34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0984</v>
       </c>
-      <c r="Q34" s="14">
+      <c r="Q34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0561</v>
       </c>
-      <c r="R34" s="14">
+      <c r="R34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0804</v>
       </c>
-      <c r="S34" s="14" t="str">
+      <c r="S34" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T34" s="14">
+      <c r="T34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1734</v>
       </c>
-      <c r="U34" s="14">
+      <c r="U34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="V34" s="14">
+      <c r="V34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0591</v>
       </c>
-      <c r="W34" s="14">
+      <c r="W34" s="16">
         <f t="shared" si="17"/>
         <v>-0.2022</v>
       </c>
-      <c r="X34" s="14">
+      <c r="X34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1494</v>
       </c>
-      <c r="Y34" s="14">
+      <c r="Y34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1155</v>
       </c>
-      <c r="Z34" s="14">
+      <c r="Z34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1152</v>
       </c>
-      <c r="AA34" s="14">
+      <c r="AA34" s="16">
         <f t="shared" si="17"/>
         <v>-0.24</v>
       </c>
-      <c r="AB34" s="14">
+      <c r="AB34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1236</v>
       </c>
-      <c r="AC34" s="14">
+      <c r="AC34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1671</v>
       </c>
-      <c r="AD34" s="14">
+      <c r="AD34" s="16">
         <f t="shared" si="17"/>
         <v>-0.126</v>
       </c>
-      <c r="AE34" s="14" t="str">
+      <c r="AE34" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AF34" s="14">
+      <c r="AF34" s="16">
         <f t="shared" si="17"/>
         <v>-0.1422</v>
       </c>
-      <c r="AG34" s="14">
+      <c r="AG34" s="16">
         <f t="shared" si="17"/>
         <v>-0.0375</v>
       </c>
-      <c r="AH34" s="14">
+      <c r="AH34" s="16">
         <f t="shared" si="13"/>
         <v>-0.0498</v>
       </c>
-      <c r="AI34" s="14" t="str">
+      <c r="AI34" s="16" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AJ34" s="14">
+      <c r="AJ34" s="16">
         <f t="shared" si="13"/>
         <v>-0.1704</v>
       </c>
-      <c r="AK34" s="14">
+      <c r="AK34" s="16">
         <f t="shared" si="13"/>
         <v>-0.0246</v>
       </c>
-      <c r="AL34" s="14">
+      <c r="AL34" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM34" s="14">
+      <c r="AM34" s="16">
         <f t="shared" si="13"/>
         <v>-0.177</v>
       </c>
-      <c r="AO34" s="14" t="str">
+      <c r="AO34" s="16" t="str">
         <f t="shared" ref="AO34:AO42" si="18">AO23</f>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP34" s="14" t="str">
+      <c r="AP34" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR34" s="41" t="s">
+      <c r="AR34" s="42" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:46">
-      <c r="A35" s="16">
+      <c r="A35" s="18">
         <v>0.3</v>
       </c>
       <c r="B35" t="str">
@@ -26559,158 +26562,158 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1119</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0954</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0591</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0381</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0936</v>
       </c>
-      <c r="K35" s="14">
+      <c r="K35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0696</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0777</v>
       </c>
-      <c r="M35" s="14">
+      <c r="M35" s="16">
         <f t="shared" si="17"/>
         <v>-0.087</v>
       </c>
-      <c r="N35" s="14">
+      <c r="N35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0264</v>
       </c>
-      <c r="O35" s="14">
+      <c r="O35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="P35" s="14">
+      <c r="P35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0762</v>
       </c>
-      <c r="Q35" s="14">
+      <c r="Q35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0462</v>
       </c>
-      <c r="R35" s="14">
+      <c r="R35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0492</v>
       </c>
-      <c r="S35" s="14" t="str">
+      <c r="S35" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T35" s="14">
+      <c r="T35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0495</v>
       </c>
-      <c r="U35" s="14">
+      <c r="U35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0966</v>
       </c>
-      <c r="V35" s="14">
+      <c r="V35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0474</v>
       </c>
-      <c r="W35" s="14">
+      <c r="W35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1395</v>
       </c>
-      <c r="X35" s="14">
+      <c r="X35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1056</v>
       </c>
-      <c r="Y35" s="14">
+      <c r="Y35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1167</v>
       </c>
-      <c r="Z35" s="14">
+      <c r="Z35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0942</v>
       </c>
-      <c r="AA35" s="14">
+      <c r="AA35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0138</v>
       </c>
-      <c r="AB35" s="14">
+      <c r="AB35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1116</v>
       </c>
-      <c r="AC35" s="14">
+      <c r="AC35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1371</v>
       </c>
-      <c r="AD35" s="14">
+      <c r="AD35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1425</v>
       </c>
-      <c r="AE35" s="14">
+      <c r="AE35" s="16">
         <f t="shared" si="17"/>
         <v>-0.1158</v>
       </c>
-      <c r="AF35" s="14">
+      <c r="AF35" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="14">
+      <c r="AG35" s="16">
         <f t="shared" si="17"/>
         <v>-0.0585</v>
       </c>
-      <c r="AH35" s="14">
+      <c r="AH35" s="16">
         <f t="shared" si="13"/>
         <v>-0.0144</v>
       </c>
-      <c r="AI35" s="14">
+      <c r="AI35" s="16">
         <f t="shared" si="13"/>
         <v>-0.0714</v>
       </c>
-      <c r="AJ35" s="14">
+      <c r="AJ35" s="16">
         <f t="shared" si="13"/>
         <v>-0.0681</v>
       </c>
-      <c r="AK35" s="14">
+      <c r="AK35" s="16">
         <f t="shared" si="13"/>
         <v>-0.0903</v>
       </c>
-      <c r="AL35" s="14">
+      <c r="AL35" s="16">
         <f t="shared" si="13"/>
         <v>-0.042</v>
       </c>
-      <c r="AM35" s="14">
+      <c r="AM35" s="16">
         <f t="shared" si="13"/>
         <v>-0.0186</v>
       </c>
-      <c r="AO35" s="14" t="str">
+      <c r="AO35" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP35" s="14" t="str">
+      <c r="AP35" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR35" s="41" t="s">
+      <c r="AR35" s="42" t="s">
         <v>341</v>
       </c>
-      <c r="AS35" s="41" t="s">
+      <c r="AS35" s="42" t="s">
         <v>342</v>
       </c>
       <c r="AT35" t="s">
@@ -26730,155 +26733,155 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E36" s="14" t="str">
+      <c r="E36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F36" s="14" t="str">
+      <c r="F36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="G36" s="14" t="str">
+      <c r="G36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="H36" s="14" t="str">
+      <c r="H36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I36" s="14" t="str">
+      <c r="I36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J36" s="14">
+      <c r="J36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="M36" s="14">
+      <c r="M36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N36" s="14">
+      <c r="N36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P36" s="14">
+      <c r="P36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="14" t="str">
+      <c r="Q36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="R36" s="14">
+      <c r="R36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="S36" s="14" t="str">
+      <c r="S36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T36" s="14">
+      <c r="T36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="U36" s="14" t="str">
+      <c r="U36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="V36" s="14" t="str">
+      <c r="V36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="W36" s="14">
+      <c r="W36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X36" s="14">
+      <c r="X36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="14">
+      <c r="Y36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="14">
+      <c r="Z36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="14" t="str">
+      <c r="AA36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AB36" s="14" t="str">
+      <c r="AB36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AC36" s="14">
+      <c r="AC36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="14">
+      <c r="AD36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="14" t="str">
+      <c r="AE36" s="16" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AF36" s="14">
+      <c r="AF36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="14">
+      <c r="AG36" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="14">
+      <c r="AH36" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="14">
+      <c r="AI36" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="14" t="str">
+      <c r="AJ36" s="16" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AK36" s="14">
+      <c r="AK36" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="14">
+      <c r="AL36" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="14" t="str">
+      <c r="AM36" s="16" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AO36" s="14" t="str">
+      <c r="AO36" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP36" s="14" t="str">
+      <c r="AP36" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR36" s="41" t="s">
+      <c r="AR36" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26895,155 +26898,155 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="M37" s="14">
+      <c r="M37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N37" s="14">
+      <c r="N37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="O37" s="14">
+      <c r="O37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P37" s="14">
+      <c r="P37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="14">
+      <c r="Q37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R37" s="14">
+      <c r="R37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="S37" s="14">
+      <c r="S37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T37" s="14">
+      <c r="T37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="U37" s="14">
+      <c r="U37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="V37" s="14">
+      <c r="V37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="W37" s="14">
+      <c r="W37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X37" s="14">
+      <c r="X37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y37" s="14">
+      <c r="Y37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="14">
+      <c r="Z37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="14">
+      <c r="AA37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="14">
+      <c r="AB37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC37" s="14">
+      <c r="AC37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AD37" s="14">
+      <c r="AD37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AE37" s="14">
+      <c r="AE37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF37" s="14">
+      <c r="AF37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG37" s="14">
+      <c r="AG37" s="16">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="14">
+      <c r="AH37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AI37" s="14">
+      <c r="AI37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AJ37" s="14">
+      <c r="AJ37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AK37" s="14">
+      <c r="AK37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AL37" s="14">
+      <c r="AL37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM37" s="14">
+      <c r="AM37" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AO37" s="14" t="str">
+      <c r="AO37" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP37" s="14" t="str">
+      <c r="AP37" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR37" s="41" t="s">
+      <c r="AR37" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27060,155 +27063,155 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="19">
         <f>IF(E12="","",-E12)</f>
         <v>-0.057</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f t="shared" ref="F38:AM39" si="19">IF(F12="","",-F12)</f>
         <v>-0.287</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="19">
         <f t="shared" si="19"/>
         <v>-0.506</v>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="19">
         <f t="shared" si="19"/>
         <v>-0.564</v>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="19">
         <f t="shared" si="19"/>
         <v>-0.842</v>
       </c>
-      <c r="J38" s="17">
+      <c r="J38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="K38" s="17">
+      <c r="K38" s="19">
         <f t="shared" si="19"/>
         <v>-0.436</v>
       </c>
-      <c r="L38" s="17">
+      <c r="L38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="M38" s="17">
+      <c r="M38" s="19">
         <f t="shared" si="19"/>
         <v>-0.711</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="19">
         <f t="shared" si="19"/>
         <v>-0.77</v>
       </c>
-      <c r="O38" s="17">
+      <c r="O38" s="19">
         <f t="shared" si="19"/>
         <v>-0.834</v>
       </c>
-      <c r="P38" s="17">
+      <c r="P38" s="19">
         <f t="shared" si="19"/>
         <v>-0.769</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="19">
         <f t="shared" si="19"/>
         <v>-0.587</v>
       </c>
-      <c r="R38" s="17">
+      <c r="R38" s="19">
         <f t="shared" si="19"/>
         <v>-0.879</v>
       </c>
-      <c r="S38" s="17" t="str">
+      <c r="S38" s="19" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="T38" s="17">
+      <c r="T38" s="19">
         <f t="shared" si="19"/>
         <v>-0.655</v>
       </c>
-      <c r="U38" s="17">
+      <c r="U38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="V38" s="17">
+      <c r="V38" s="19">
         <f t="shared" si="19"/>
         <v>-0.751</v>
       </c>
-      <c r="W38" s="17">
+      <c r="W38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="X38" s="17">
+      <c r="X38" s="19">
         <f t="shared" si="19"/>
         <v>-0.462</v>
       </c>
-      <c r="Y38" s="17">
+      <c r="Y38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="Z38" s="19">
         <f t="shared" si="19"/>
         <v>-0.644</v>
       </c>
-      <c r="AA38" s="17">
+      <c r="AA38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AB38" s="17">
+      <c r="AB38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AC38" s="17">
+      <c r="AC38" s="19">
         <f t="shared" si="19"/>
         <v>-0.564</v>
       </c>
-      <c r="AD38" s="17">
+      <c r="AD38" s="19">
         <f t="shared" si="19"/>
         <v>-0.107</v>
       </c>
-      <c r="AE38" s="17" t="str">
+      <c r="AE38" s="19" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AF38" s="17">
+      <c r="AF38" s="19">
         <f t="shared" si="19"/>
         <v>-0.189</v>
       </c>
-      <c r="AG38" s="17">
+      <c r="AG38" s="19">
         <f t="shared" si="19"/>
         <v>-0.727</v>
       </c>
-      <c r="AH38" s="17">
+      <c r="AH38" s="19">
         <f t="shared" si="19"/>
         <v>-0.476</v>
       </c>
-      <c r="AI38" s="17">
+      <c r="AI38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AJ38" s="17">
+      <c r="AJ38" s="19">
         <f t="shared" si="19"/>
         <v>-0.56</v>
       </c>
-      <c r="AK38" s="17">
+      <c r="AK38" s="19">
         <f t="shared" si="19"/>
         <v>-0.77</v>
       </c>
-      <c r="AL38" s="17">
+      <c r="AL38" s="19">
         <f t="shared" si="19"/>
         <v>-0.41</v>
       </c>
-      <c r="AM38" s="17">
+      <c r="AM38" s="19">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AO38" s="14" t="str">
+      <c r="AO38" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP38" s="14" t="str">
+      <c r="AP38" s="16" t="str">
         <f t="shared" si="14"/>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR38" s="41" t="s">
+      <c r="AR38" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27225,155 +27228,155 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="19">
         <f t="shared" ref="E39:AG39" si="20">IF(E13="","",-E13)</f>
         <v>-0.777</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f t="shared" si="20"/>
         <v>-0.47</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="19">
         <f t="shared" si="20"/>
         <v>-0.724</v>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="19">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="19">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="J39" s="17">
+      <c r="J39" s="19">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K39" s="19">
         <f t="shared" si="20"/>
         <v>-0.922</v>
       </c>
-      <c r="L39" s="17">
+      <c r="L39" s="19">
         <f t="shared" si="20"/>
         <v>-0.587</v>
       </c>
-      <c r="M39" s="17">
+      <c r="M39" s="19">
         <f t="shared" si="20"/>
         <v>-0.578</v>
       </c>
-      <c r="N39" s="17">
+      <c r="N39" s="19">
         <f t="shared" si="20"/>
         <v>-0.544</v>
       </c>
-      <c r="O39" s="17">
+      <c r="O39" s="19">
         <f t="shared" si="20"/>
         <v>-0.391</v>
       </c>
-      <c r="P39" s="17">
+      <c r="P39" s="19">
         <f t="shared" si="20"/>
         <v>-0.625</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="Q39" s="19">
         <f t="shared" si="20"/>
         <v>-0.597</v>
       </c>
-      <c r="R39" s="17">
+      <c r="R39" s="19">
         <f t="shared" si="20"/>
         <v>-0.431</v>
       </c>
-      <c r="S39" s="17" t="str">
+      <c r="S39" s="19" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="T39" s="17">
+      <c r="T39" s="19">
         <f t="shared" si="20"/>
         <v>-0.707</v>
       </c>
-      <c r="U39" s="17">
+      <c r="U39" s="19">
         <f t="shared" si="20"/>
         <v>-0.604</v>
       </c>
-      <c r="V39" s="17">
+      <c r="V39" s="19">
         <f t="shared" si="20"/>
         <v>-0.509</v>
       </c>
-      <c r="W39" s="17">
+      <c r="W39" s="19">
         <f t="shared" si="20"/>
         <v>-0.9</v>
       </c>
-      <c r="X39" s="17">
+      <c r="X39" s="19">
         <f t="shared" si="20"/>
         <v>-0.777</v>
       </c>
-      <c r="Y39" s="17">
+      <c r="Y39" s="19">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="Z39" s="17">
+      <c r="Z39" s="19">
         <f t="shared" si="20"/>
         <v>-0.568</v>
       </c>
-      <c r="AA39" s="17">
+      <c r="AA39" s="19">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="AB39" s="17">
+      <c r="AB39" s="19">
         <f t="shared" si="20"/>
         <v>-0.522</v>
       </c>
-      <c r="AC39" s="17">
+      <c r="AC39" s="19">
         <f t="shared" si="20"/>
         <v>-0.7</v>
       </c>
-      <c r="AD39" s="17">
+      <c r="AD39" s="19">
         <f t="shared" si="20"/>
         <v>-0.637</v>
       </c>
-      <c r="AE39" s="17" t="str">
+      <c r="AE39" s="19" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AF39" s="17">
+      <c r="AF39" s="19">
         <f t="shared" si="20"/>
         <v>-0.671</v>
       </c>
-      <c r="AG39" s="17">
+      <c r="AG39" s="19">
         <f t="shared" si="20"/>
         <v>-0.575</v>
       </c>
-      <c r="AH39" s="17">
+      <c r="AH39" s="19">
         <f t="shared" si="19"/>
         <v>-0.351</v>
       </c>
-      <c r="AI39" s="17" t="str">
+      <c r="AI39" s="19" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AJ39" s="17">
+      <c r="AJ39" s="19">
         <f t="shared" si="19"/>
         <v>-0.679</v>
       </c>
-      <c r="AK39" s="17">
+      <c r="AK39" s="19">
         <f t="shared" si="19"/>
         <v>-0.539</v>
       </c>
-      <c r="AL39" s="17">
+      <c r="AL39" s="19">
         <f t="shared" si="19"/>
         <v>-0.319</v>
       </c>
-      <c r="AM39" s="17">
+      <c r="AM39" s="19">
         <f t="shared" si="19"/>
         <v>-0.695</v>
       </c>
-      <c r="AO39" s="14" t="str">
+      <c r="AO39" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP39" s="14" t="str">
+      <c r="AP39" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR39" s="41" t="s">
+      <c r="AR39" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27533,15 +27536,15 @@
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="AO40" s="14" t="str">
+      <c r="AO40" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP40" s="14" t="str">
+      <c r="AP40" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR40" s="41" t="s">
+      <c r="AR40" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27701,15 +27704,15 @@
         <f t="shared" si="23"/>
         <v>-0.95</v>
       </c>
-      <c r="AO41" s="14" t="str">
+      <c r="AO41" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP41" s="14" t="str">
+      <c r="AP41" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR41" s="41" t="s">
+      <c r="AR41" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27869,15 +27872,15 @@
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="AO42" s="14" t="str">
+      <c r="AO42" s="16" t="str">
         <f t="shared" si="18"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP42" s="14" t="str">
+      <c r="AP42" s="16" t="str">
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR42" s="41" t="s">
+      <c r="AR42" s="42" t="s">
         <v>341</v>
       </c>
     </row>
@@ -28902,8 +28905,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:39">
-      <c r="A14" t="s">
+    <row r="13" spans="1:39">
+      <c r="A13" s="2" t="s">
         <v>354</v>
       </c>
     </row>
@@ -30232,170 +30235,170 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:41">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1"/>
     <row r="27" s="1" customFormat="1"/>
     <row r="28" s="1" customFormat="1" spans="1:41">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
-      <c r="AC28" s="2"/>
-      <c r="AD28" s="2"/>
-      <c r="AE28" s="2"/>
-      <c r="AF28" s="2"/>
-      <c r="AG28" s="2"/>
-      <c r="AH28" s="2"/>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:41">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="K29" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L29" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="O29" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="P29" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="Q29" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="R29" s="2" t="s">
+      <c r="R29" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="S29" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="T29" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="U29" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="V29" s="2" t="s">
+      <c r="V29" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="X29" s="2" t="s">
+      <c r="X29" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="Y29" s="2" t="s">
+      <c r="Y29" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="Z29" s="2" t="s">
+      <c r="Z29" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AA29" s="2" t="s">
+      <c r="AA29" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AB29" s="2" t="s">
+      <c r="AB29" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="AC29" s="2" t="s">
+      <c r="AC29" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AD29" s="2" t="s">
+      <c r="AD29" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AE29" s="2" t="s">
+      <c r="AE29" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="AF29" s="2" t="s">
+      <c r="AF29" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="AG29" s="2" t="s">
+      <c r="AG29" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AH29" s="2" t="s">
+      <c r="AH29" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AI29" s="2" t="s">
+      <c r="AI29" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AJ29" s="2" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AK29" s="2" t="s">
+      <c r="AK29" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AL29" s="4" t="s">
         <v>284</v>
       </c>
       <c r="AM29" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AN29" s="2" t="s">
+      <c r="AN29" s="3" t="s">
         <v>356</v>
       </c>
       <c r="AO29" s="1">
@@ -30406,112 +30409,112 @@
       <c r="A30" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>2030</v>
       </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
         <v>3</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>4</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>1.5</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="3">
         <v>0.3</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="3">
         <v>0.2</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="3">
         <v>0.5</v>
       </c>
-      <c r="K30" s="2">
-        <v>2</v>
-      </c>
-      <c r="L30" s="2">
+      <c r="K30" s="3">
+        <v>2</v>
+      </c>
+      <c r="L30" s="3">
         <v>12</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="3">
         <v>0.2</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="3">
         <v>0.3</v>
       </c>
-      <c r="O30" s="2">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="2">
+      <c r="O30" s="3">
+        <v>1</v>
+      </c>
+      <c r="P30" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3">
         <v>0.4</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" s="3">
         <v>0.6</v>
       </c>
-      <c r="S30" s="2">
-        <v>2</v>
-      </c>
-      <c r="T30" s="2">
+      <c r="S30" s="3">
+        <v>2</v>
+      </c>
+      <c r="T30" s="3">
         <v>0.3</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="3">
         <v>1.2</v>
       </c>
-      <c r="V30" s="2">
-        <v>2</v>
-      </c>
-      <c r="W30" s="2">
+      <c r="V30" s="3">
+        <v>2</v>
+      </c>
+      <c r="W30" s="3">
         <v>5</v>
       </c>
-      <c r="X30" s="2">
+      <c r="X30" s="3">
         <v>8</v>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y30" s="3">
         <v>10</v>
       </c>
-      <c r="Z30" s="2">
+      <c r="Z30" s="3">
         <v>0.1</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AA30" s="3">
         <v>0.8</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AB30" s="3">
         <v>10</v>
       </c>
-      <c r="AC30" s="2">
+      <c r="AC30" s="3">
         <v>4</v>
       </c>
-      <c r="AD30" s="2">
+      <c r="AD30" s="3">
         <v>3</v>
       </c>
-      <c r="AE30" s="2">
+      <c r="AE30" s="3">
         <v>1.5</v>
       </c>
-      <c r="AF30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="2">
+      <c r="AF30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="3">
         <v>0.4</v>
       </c>
-      <c r="AH30" s="2">
+      <c r="AH30" s="3">
         <v>0.1</v>
       </c>
-      <c r="AI30" s="2">
+      <c r="AI30" s="3">
         <v>2.5</v>
       </c>
-      <c r="AJ30" s="2">
+      <c r="AJ30" s="3">
         <v>1.5</v>
       </c>
-      <c r="AK30" s="2">
+      <c r="AK30" s="3">
         <v>0.3</v>
       </c>
       <c r="AL30" s="1">
@@ -30531,112 +30534,112 @@
       <c r="A31" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>2040</v>
       </c>
-      <c r="D31" s="2">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
         <v>2.4</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>3.2</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>1.2</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="3">
         <v>0.24</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="3">
         <v>0.16</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="3">
         <v>0.4</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>1.6</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="3">
         <v>9.6</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="3">
         <v>0.16</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="3">
         <v>0.24</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31" s="3">
         <v>0.8</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="3">
         <v>1.6</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="3">
         <v>0.32</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="3">
         <v>0.48</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <v>1.6</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" s="3">
         <v>0.24</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="3">
         <v>0.96</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="3">
         <v>1.6</v>
       </c>
-      <c r="W31" s="2">
+      <c r="W31" s="3">
         <v>4</v>
       </c>
-      <c r="X31" s="2">
+      <c r="X31" s="3">
         <v>6.4</v>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y31" s="3">
         <v>8</v>
       </c>
-      <c r="Z31" s="2">
+      <c r="Z31" s="3">
         <v>0.08</v>
       </c>
-      <c r="AA31" s="2">
+      <c r="AA31" s="3">
         <v>0.64</v>
       </c>
-      <c r="AB31" s="2">
+      <c r="AB31" s="3">
         <v>8</v>
       </c>
-      <c r="AC31" s="2">
+      <c r="AC31" s="3">
         <v>3.2</v>
       </c>
-      <c r="AD31" s="2">
+      <c r="AD31" s="3">
         <v>2.4</v>
       </c>
-      <c r="AE31" s="2">
+      <c r="AE31" s="3">
         <v>1.2</v>
       </c>
-      <c r="AF31" s="2">
+      <c r="AF31" s="3">
         <v>0.8</v>
       </c>
-      <c r="AG31" s="2">
+      <c r="AG31" s="3">
         <v>0.32</v>
       </c>
-      <c r="AH31" s="2">
+      <c r="AH31" s="3">
         <v>0.08</v>
       </c>
-      <c r="AI31" s="2">
-        <v>2</v>
-      </c>
-      <c r="AJ31" s="2">
+      <c r="AI31" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="3">
         <v>1.2</v>
       </c>
-      <c r="AK31" s="2">
+      <c r="AK31" s="3">
         <v>0.24</v>
       </c>
       <c r="AL31" s="1">
@@ -30656,112 +30659,112 @@
       <c r="A32" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>2030</v>
       </c>
-      <c r="D32" s="2">
-        <v>1</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2">
-        <v>0</v>
-      </c>
-      <c r="U32" s="2">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2">
-        <v>0</v>
-      </c>
-      <c r="W32" s="2">
-        <v>0</v>
-      </c>
-      <c r="X32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="2">
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
       <c r="AL32" s="1">
@@ -30778,238 +30781,237 @@
       </c>
     </row>
     <row r="33" spans="1:41">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="4"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="4"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="4"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AC33" s="5"/>
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="5"/>
+      <c r="AF33" s="5"/>
+      <c r="AG33" s="5"/>
+      <c r="AH33" s="5"/>
+      <c r="AI33" s="5"/>
+      <c r="AJ33" s="5"/>
+      <c r="AK33" s="5"/>
     </row>
     <row r="34" spans="1:41">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="5"/>
+      <c r="AB34" s="5"/>
+      <c r="AC34" s="5"/>
+      <c r="AD34" s="5"/>
+      <c r="AE34" s="5"/>
+      <c r="AF34" s="5"/>
+      <c r="AG34" s="5"/>
+      <c r="AH34" s="5"/>
+      <c r="AI34" s="5"/>
+      <c r="AJ34" s="5"/>
+      <c r="AK34" s="5"/>
     </row>
     <row r="35" spans="1:41">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+      <c r="AA35" s="5"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="5"/>
+      <c r="AF35" s="5"/>
+      <c r="AG35" s="5"/>
+      <c r="AH35" s="5"/>
+      <c r="AI35" s="5"/>
+      <c r="AJ35" s="5"/>
+      <c r="AK35" s="5"/>
     </row>
     <row r="36" spans="1:41">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C36" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J36" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="L36" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="M36" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="N36" s="4" t="s">
+      <c r="N36" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="O36" s="4" t="s">
+      <c r="O36" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="P36" s="4" t="s">
+      <c r="P36" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="Q36" s="4" t="s">
+      <c r="Q36" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="R36" s="4" t="s">
+      <c r="R36" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="S36" s="4" t="s">
+      <c r="S36" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="T36" s="4" t="s">
+      <c r="T36" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="U36" s="4" t="s">
+      <c r="U36" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="V36" s="4" t="s">
+      <c r="V36" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="W36" s="4" t="s">
+      <c r="W36" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="X36" s="4" t="s">
+      <c r="X36" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="Y36" s="4" t="s">
+      <c r="Y36" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="Z36" s="4" t="s">
+      <c r="Z36" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="AA36" s="4" t="s">
+      <c r="AA36" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="AB36" s="4" t="s">
+      <c r="AB36" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="AC36" s="4" t="s">
+      <c r="AC36" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="AD36" s="4" t="s">
+      <c r="AD36" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="AE36" s="4" t="s">
+      <c r="AE36" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="AF36" s="4" t="s">
+      <c r="AF36" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="AG36" s="4" t="s">
+      <c r="AG36" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="AH36" s="4" t="s">
+      <c r="AH36" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="AI36" s="4" t="s">
+      <c r="AI36" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="AJ36" s="4" t="s">
+      <c r="AJ36" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="AK36" s="4" t="s">
+      <c r="AK36" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AL36" s="4" t="s">
+      <c r="AL36" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="AM36" s="5" t="s">
+      <c r="AM36" s="7" t="s">
         <v>284</v>
       </c>
       <c r="AN36" t="s">
@@ -31020,19 +31022,19 @@
       </c>
     </row>
     <row r="37" ht="16" spans="1:41">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="8">
         <v>2030</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="8">
         <v>1</v>
       </c>
       <c r="F37">
@@ -31175,12 +31177,12 @@
         <f t="shared" si="5"/>
         <v>1.66666666666667</v>
       </c>
-      <c r="AO37" s="6">
+      <c r="AO37" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:41">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="8" t="s">
         <v>373</v>
       </c>
       <c r="B38" t="s">
@@ -31305,7 +31307,7 @@
       </c>
     </row>
     <row r="39" spans="1:41">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="8" t="s">
         <v>376</v>
       </c>
       <c r="B39" t="s">
@@ -31430,13 +31432,13 @@
       </c>
     </row>
     <row r="40" ht="16" spans="1:41">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="8" t="s">
         <v>378</v>
       </c>
       <c r="B40" t="s">
         <v>369</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="10" t="s">
         <v>379</v>
       </c>
       <c r="D40">
@@ -31555,7 +31557,7 @@
       </c>
     </row>
     <row r="41" spans="1:41">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="8" t="s">
         <v>370</v>
       </c>
       <c r="D41">
@@ -31703,7 +31705,7 @@
       </c>
     </row>
     <row r="42" spans="1:41">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="8" t="s">
         <v>373</v>
       </c>
       <c r="D42">
@@ -31851,7 +31853,7 @@
       </c>
     </row>
     <row r="43" spans="1:41">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="8" t="s">
         <v>376</v>
       </c>
       <c r="D43">
@@ -31999,7 +32001,7 @@
       </c>
     </row>
     <row r="44" spans="1:41">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="8" t="s">
         <v>378</v>
       </c>
       <c r="D44">
@@ -32147,109 +32149,109 @@
       </c>
     </row>
     <row r="47" spans="1:41">
-      <c r="F47" s="6">
+      <c r="F47" s="8">
         <v>5</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="8">
         <v>30</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="8">
         <v>10</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="8">
         <v>3</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47" s="8">
         <v>4</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="8">
         <v>5</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="8">
         <v>50</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="8">
         <v>150</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47" s="8">
         <v>3</v>
       </c>
-      <c r="O47" s="6">
+      <c r="O47" s="8">
         <v>5</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="8">
         <v>15</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="Q47" s="8">
         <v>25</v>
       </c>
-      <c r="R47" s="6">
+      <c r="R47" s="8">
         <v>3</v>
       </c>
-      <c r="S47" s="6">
+      <c r="S47" s="8">
         <v>8</v>
       </c>
-      <c r="T47" s="6">
+      <c r="T47" s="8">
         <v>80</v>
       </c>
-      <c r="U47" s="6">
-        <v>2</v>
-      </c>
-      <c r="V47" s="6">
+      <c r="U47" s="8">
+        <v>2</v>
+      </c>
+      <c r="V47" s="8">
         <v>10</v>
       </c>
-      <c r="W47" s="6">
+      <c r="W47" s="8">
         <v>15</v>
       </c>
-      <c r="X47" s="6">
+      <c r="X47" s="8">
         <v>30</v>
       </c>
-      <c r="Y47" s="6">
+      <c r="Y47" s="8">
         <v>10</v>
       </c>
-      <c r="Z47" s="6">
+      <c r="Z47" s="8">
         <v>120</v>
       </c>
-      <c r="AA47" s="6">
+      <c r="AA47" s="8">
         <v>3</v>
       </c>
-      <c r="AB47" s="6">
+      <c r="AB47" s="8">
         <v>10</v>
       </c>
-      <c r="AC47" s="6">
+      <c r="AC47" s="8">
         <v>100</v>
       </c>
-      <c r="AD47" s="6">
+      <c r="AD47" s="8">
         <v>25</v>
       </c>
-      <c r="AE47" s="6">
+      <c r="AE47" s="8">
         <v>3</v>
       </c>
-      <c r="AF47" s="6">
+      <c r="AF47" s="8">
         <v>12</v>
       </c>
-      <c r="AG47" s="6">
+      <c r="AG47" s="8">
         <v>12</v>
       </c>
-      <c r="AH47" s="6">
+      <c r="AH47" s="8">
         <v>15</v>
       </c>
-      <c r="AI47" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ47" s="6">
+      <c r="AI47" s="8">
+        <v>2</v>
+      </c>
+      <c r="AJ47" s="8">
         <v>12</v>
       </c>
-      <c r="AK47" s="6">
+      <c r="AK47" s="8">
         <v>15</v>
       </c>
-      <c r="AL47" s="6">
+      <c r="AL47" s="8">
         <v>8</v>
       </c>
-      <c r="AM47" s="6">
+      <c r="AM47" s="8">
         <v>0.5</v>
       </c>
-      <c r="AN47" s="6">
+      <c r="AN47" s="8">
         <v>5</v>
       </c>
     </row>

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -1562,12 +1562,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -5112,8 +5112,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:13">
-      <c r="H20" s="24" t="s">
+    <row r="18" spans="2:13">
+      <c r="H18" s="2" t="s">
         <v>55</v>
       </c>
     </row>

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -5112,8 +5112,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:13">
-      <c r="H18" s="2" t="s">
+    <row r="20" spans="2:13">
+      <c r="H20" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5191,8 +5191,8 @@
       <c r="G23" t="s">
         <v>71</v>
       </c>
-      <c r="J23">
-        <v>-1</v>
+      <c r="J23" s="23">
+        <v>-2</v>
       </c>
     </row>
     <row r="24" spans="2:13">

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -90,6 +90,38 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>xli9</author>
+  </authors>
+  <commentList>
+    <comment ref="A36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+original Amit’s version is vacant/empty, then some nclear can have ca[acity but zero activity, that is not reasonable so we set as 0.1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>xli9</author>
@@ -1562,12 +1594,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -26721,6 +26753,9 @@
       </c>
     </row>
     <row r="36" spans="1:46">
+      <c r="A36" s="2">
+        <v>0.1</v>
+      </c>
       <c r="B36" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_nuclear_LO</v>
@@ -26755,31 +26790,31 @@
       </c>
       <c r="J36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0537</v>
       </c>
       <c r="K36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="L36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.072</v>
       </c>
       <c r="M36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="N36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0712</v>
       </c>
       <c r="O36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0548</v>
       </c>
       <c r="P36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="Q36" s="16" t="str">
         <f t="shared" si="17"/>
@@ -26787,7 +26822,7 @@
       </c>
       <c r="R36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="S36" s="16" t="str">
         <f t="shared" si="17"/>
@@ -26795,7 +26830,7 @@
       </c>
       <c r="T36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="U36" s="16" t="str">
         <f t="shared" si="17"/>
@@ -26811,15 +26846,15 @@
       </c>
       <c r="X36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0397</v>
       </c>
       <c r="Y36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0377</v>
       </c>
       <c r="Z36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AA36" s="16" t="str">
         <f t="shared" si="17"/>
@@ -26831,11 +26866,11 @@
       </c>
       <c r="AC36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0705</v>
       </c>
       <c r="AD36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0786</v>
       </c>
       <c r="AE36" s="16" t="str">
         <f t="shared" si="17"/>
@@ -26843,19 +26878,19 @@
       </c>
       <c r="AF36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0526</v>
       </c>
       <c r="AG36" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH36" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.073</v>
       </c>
       <c r="AI36" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.0699</v>
       </c>
       <c r="AJ36" s="16" t="str">
         <f t="shared" si="13"/>
@@ -26863,11 +26898,11 @@
       </c>
       <c r="AK36" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="AL36" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.0512</v>
       </c>
       <c r="AM36" s="16" t="str">
         <f t="shared" si="13"/>
@@ -26886,6 +26921,9 @@
       </c>
     </row>
     <row r="37" spans="1:46">
+      <c r="A37" s="2">
+        <v>0.1</v>
+      </c>
       <c r="B37" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_oil_\I: LO</v>
@@ -26900,59 +26938,59 @@
       </c>
       <c r="E37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0367</v>
       </c>
       <c r="F37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0146</v>
       </c>
       <c r="G37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="H37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0463</v>
       </c>
       <c r="I37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="J37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="K37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="L37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="M37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="N37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="O37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0571</v>
       </c>
       <c r="P37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="Q37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0301</v>
       </c>
       <c r="R37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="S37" s="16">
         <f t="shared" si="17"/>
@@ -26960,83 +26998,83 @@
       </c>
       <c r="T37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0021</v>
       </c>
       <c r="U37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0111</v>
       </c>
       <c r="V37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0782</v>
       </c>
       <c r="W37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0089</v>
       </c>
       <c r="X37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0221</v>
       </c>
       <c r="Y37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0616</v>
       </c>
       <c r="Z37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0117</v>
       </c>
       <c r="AA37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0632</v>
       </c>
       <c r="AB37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AC37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AD37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AE37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0629</v>
       </c>
       <c r="AF37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="AG37" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-0.0374</v>
       </c>
       <c r="AH37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="AJ37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.0059</v>
       </c>
       <c r="AK37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="AL37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AM37" s="16">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-0.0103</v>
       </c>
       <c r="AO37" s="16" t="str">
         <f t="shared" si="18"/>
@@ -27051,6 +27089,9 @@
       </c>
     </row>
     <row r="38" spans="1:46">
+      <c r="A38" s="2">
+        <v>0.1</v>
+      </c>
       <c r="B38" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_bioenergy_UP</v>
@@ -27216,6 +27257,9 @@
       </c>
     </row>
     <row r="39" spans="1:46">
+      <c r="A39" s="2">
+        <v>0.1</v>
+      </c>
       <c r="B39" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_coal_UP</v>
@@ -27887,6 +27931,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -127,7 +127,7 @@
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="C34" authorId="0">
+    <comment ref="C35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1597,18 +1597,18 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1631,12 +1631,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1644,6 +1638,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2009,7 +2009,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2104,7 +2104,7 @@
     <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2113,10 +2113,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2124,7 +2124,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2135,18 +2135,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="49"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="13"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="14"/>
@@ -2173,7 +2174,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="54"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="16" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="16" applyFont="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="54" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="53" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="24"/>
@@ -2543,2385 +2544,2385 @@
   <dimension ref="B2:AE92"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.13636363636364" style="33" customWidth="1"/>
-    <col min="2" max="2" width="9.86363636363636" style="33" customWidth="1"/>
-    <col min="3" max="3" width="8.46363636363636" style="33" customWidth="1"/>
-    <col min="4" max="4" width="12.8" style="33" customWidth="1"/>
-    <col min="5" max="5" width="5" style="33" customWidth="1"/>
-    <col min="6" max="6" width="14.2" style="33" customWidth="1"/>
-    <col min="7" max="7" width="6.86363636363636" style="33" customWidth="1"/>
-    <col min="8" max="8" width="10.4636363636364" style="33" customWidth="1"/>
-    <col min="9" max="9" width="8.46363636363636" style="33" customWidth="1"/>
-    <col min="10" max="10" width="5.13636363636364" style="33" customWidth="1"/>
-    <col min="11" max="12" width="5" style="33" customWidth="1"/>
-    <col min="13" max="256" width="11.4636363636364" style="33" customWidth="1"/>
-    <col min="257" max="16384" width="9.13636363636364" style="33"/>
+    <col min="1" max="1" width="9.13636363636364" style="34" customWidth="1"/>
+    <col min="2" max="2" width="9.86363636363636" style="34" customWidth="1"/>
+    <col min="3" max="3" width="8.46363636363636" style="34" customWidth="1"/>
+    <col min="4" max="4" width="12.8" style="34" customWidth="1"/>
+    <col min="5" max="5" width="5" style="34" customWidth="1"/>
+    <col min="6" max="6" width="14.2" style="34" customWidth="1"/>
+    <col min="7" max="7" width="6.86363636363636" style="34" customWidth="1"/>
+    <col min="8" max="8" width="10.4636363636364" style="34" customWidth="1"/>
+    <col min="9" max="9" width="8.46363636363636" style="34" customWidth="1"/>
+    <col min="10" max="10" width="5.13636363636364" style="34" customWidth="1"/>
+    <col min="11" max="12" width="5" style="34" customWidth="1"/>
+    <col min="13" max="256" width="11.4636363636364" style="34" customWidth="1"/>
+    <col min="257" max="16384" width="9.13636363636364" style="34"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:31">
-      <c r="B2" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="B2" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="34" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="14.5" spans="2:31">
-      <c r="B3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="34" t="s">
+      <c r="B3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="35" t="s">
         <v>8</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
-      <c r="Y3" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="Y3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="AB3" s="33" t="s">
+      <c r="AB3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="33" t="s">
+      <c r="AC3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="33" t="s">
+      <c r="AD3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AE3" s="33" t="s">
+      <c r="AE3" s="34" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="14.5" spans="2:31">
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="34" t="s">
         <v>9</v>
       </c>
       <c r="H4">
         <v>0.1</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="34" t="s">
         <v>10</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
-      <c r="T4" s="36" t="s">
+      <c r="T4" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="U4" s="36" t="s">
+      <c r="U4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="36" t="s">
+      <c r="V4" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="36" t="s">
+      <c r="W4" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AA4" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AC4" s="33" t="s">
+      <c r="AC4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AD4" s="33" t="s">
+      <c r="AD4" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AE4" s="33">
+      <c r="AE4" s="34">
         <f>1.10926234054354*H39</f>
         <v>1.20144204104271</v>
       </c>
     </row>
     <row r="5" ht="14.5" spans="2:31">
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="34">
         <v>2020</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
-      <c r="T5" s="36" t="s">
+      <c r="T5" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U5" s="36" t="s">
+      <c r="U5" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V5" s="36">
+      <c r="V5" s="37">
         <v>2001</v>
       </c>
-      <c r="W5" s="36">
+      <c r="W5" s="37">
         <v>0.762827515602112</v>
       </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AA5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AD5" s="33" t="s">
+      <c r="AD5" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AE5" s="33">
+      <c r="AE5" s="34">
         <f>O6</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="2:31">
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="34">
         <v>1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="O6" s="37">
+      <c r="O6" s="38">
         <v>0.07</v>
       </c>
-      <c r="P6" s="33" t="s">
+      <c r="P6" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="36" t="s">
+      <c r="T6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="36" t="s">
+      <c r="U6" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V6" s="36">
+      <c r="V6" s="37">
         <v>2002</v>
       </c>
-      <c r="W6" s="36">
+      <c r="W6" s="37">
         <v>0.774460315704346</v>
       </c>
-      <c r="AA6" s="36" t="s">
+      <c r="AA6" s="37" t="s">
         <v>15</v>
       </c>
       <c r="AB6"/>
-      <c r="AC6" s="36" t="s">
+      <c r="AC6" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="AD6" s="36" t="s">
+      <c r="AD6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AE6" s="38">
+      <c r="AE6" s="39">
         <f>H45</f>
         <v>0.9896</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:31">
-      <c r="D7" s="33" t="str">
+      <c r="D7" s="34" t="str">
         <f>IF(F7=G7,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="33" t="str">
+      <c r="G7" s="34" t="str">
         <f>"USD"&amp;RIGHT(O9,2)</f>
         <v>USD83</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="40">
         <f>ROUND($P$46/P9,4)</f>
         <v>2.2201</v>
       </c>
-      <c r="T7" s="36" t="s">
+      <c r="T7" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U7" s="36" t="s">
+      <c r="U7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V7" s="36">
+      <c r="V7" s="37">
         <v>2003</v>
       </c>
-      <c r="W7" s="36">
+      <c r="W7" s="37">
         <v>0.789065361022949</v>
       </c>
-      <c r="AA7" s="36" t="s">
+      <c r="AA7" s="37" t="s">
         <v>21</v>
       </c>
       <c r="AB7"/>
       <c r="AC7"/>
-      <c r="AD7" s="36" t="s">
+      <c r="AD7" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AE7" s="36">
+      <c r="AE7" s="37">
         <f>AE5</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:31">
-      <c r="D8" s="33" t="str">
+      <c r="D8" s="34" t="str">
         <f t="shared" ref="D8:D42" si="0">IF(F8=G8,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="33" t="str">
+      <c r="G8" s="34" t="str">
         <f t="shared" ref="G8:G42" si="1">"USD"&amp;RIGHT(O10,2)</f>
         <v>USD84</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="40">
         <f t="shared" ref="H8:H49" si="2">ROUND($P$46/P10,4)</f>
         <v>2.1427</v>
       </c>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40" t="s">
+      <c r="O8" s="41"/>
+      <c r="P8" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="T8" s="36" t="s">
+      <c r="T8" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U8" s="36" t="s">
+      <c r="U8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V8" s="36">
+      <c r="V8" s="37">
         <v>2004</v>
       </c>
-      <c r="W8" s="36">
+      <c r="W8" s="37">
         <v>0.810197472572327</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:31">
-      <c r="D9" s="33" t="str">
+      <c r="D9" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="33" t="str">
+      <c r="G9" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD85</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="40">
         <f t="shared" si="2"/>
         <v>2.077</v>
       </c>
-      <c r="O9" s="40">
+      <c r="O9" s="41">
         <v>1983</v>
       </c>
-      <c r="P9" s="41">
+      <c r="P9" s="42">
         <f>VLOOKUP(O9,$V$5:$W$99,2,FALSE)</f>
         <v>0.487872630357742</v>
       </c>
-      <c r="T9" s="36" t="s">
+      <c r="T9" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U9" s="36" t="s">
+      <c r="U9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V9" s="36">
+      <c r="V9" s="37">
         <v>2005</v>
       </c>
-      <c r="W9" s="36">
+      <c r="W9" s="37">
         <v>0.835319578647614</v>
       </c>
     </row>
     <row r="10" ht="14.5" spans="2:31">
-      <c r="D10" s="33" t="str">
+      <c r="D10" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="33" t="str">
+      <c r="G10" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD86</v>
       </c>
-      <c r="H10" s="39">
+      <c r="H10" s="40">
         <f t="shared" si="2"/>
         <v>2.0358</v>
       </c>
-      <c r="O10" s="40">
+      <c r="O10" s="41">
         <v>1984</v>
       </c>
-      <c r="P10" s="41">
+      <c r="P10" s="42">
         <f t="shared" ref="P10:P51" si="3">VLOOKUP(O10,$V$5:$W$99,2,FALSE)</f>
         <v>0.505495131015778</v>
       </c>
-      <c r="T10" s="36" t="s">
+      <c r="T10" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U10" s="36" t="s">
+      <c r="U10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V10" s="36">
+      <c r="V10" s="37">
         <v>2006</v>
       </c>
-      <c r="W10" s="36">
+      <c r="W10" s="37">
         <v>0.860807240009308</v>
       </c>
     </row>
     <row r="11" ht="14.5" spans="2:31">
-      <c r="D11" s="33" t="str">
+      <c r="D11" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="33" t="str">
+      <c r="G11" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD87</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="40">
         <f t="shared" si="2"/>
         <v>1.987</v>
       </c>
-      <c r="O11" s="40">
+      <c r="O11" s="41">
         <v>1985</v>
       </c>
-      <c r="P11" s="41">
+      <c r="P11" s="42">
         <f t="shared" si="3"/>
         <v>0.521485805511475</v>
       </c>
-      <c r="T11" s="36" t="s">
+      <c r="T11" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U11" s="36" t="s">
+      <c r="U11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V11" s="36">
+      <c r="V11" s="37">
         <v>2007</v>
       </c>
-      <c r="W11" s="36">
+      <c r="W11" s="37">
         <v>0.883970141410828</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="2:31">
-      <c r="D12" s="33" t="str">
+      <c r="D12" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="33" t="str">
+      <c r="G12" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD88</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="40">
         <f t="shared" si="2"/>
         <v>1.9192</v>
       </c>
-      <c r="O12" s="40">
+      <c r="O12" s="41">
         <v>1986</v>
       </c>
-      <c r="P12" s="41">
+      <c r="P12" s="42">
         <f t="shared" si="3"/>
         <v>0.532050728797913</v>
       </c>
-      <c r="T12" s="36" t="s">
+      <c r="T12" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U12" s="36" t="s">
+      <c r="U12" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V12" s="36">
+      <c r="V12" s="37">
         <v>2008</v>
       </c>
-      <c r="W12" s="36">
+      <c r="W12" s="37">
         <v>0.900844812393188</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="2:31">
-      <c r="D13" s="33" t="str">
+      <c r="D13" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="33" t="str">
+      <c r="G13" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD89</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="40">
         <f t="shared" si="2"/>
         <v>1.8468</v>
       </c>
-      <c r="O13" s="40">
+      <c r="O13" s="41">
         <v>1987</v>
       </c>
-      <c r="P13" s="41">
+      <c r="P13" s="42">
         <f t="shared" si="3"/>
         <v>0.54511946439743</v>
       </c>
-      <c r="T13" s="36" t="s">
+      <c r="T13" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U13" s="36" t="s">
+      <c r="U13" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V13" s="36">
+      <c r="V13" s="37">
         <v>2009</v>
       </c>
-      <c r="W13" s="36">
+      <c r="W13" s="37">
         <v>0.907873749732971</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="2:31">
-      <c r="D14" s="33" t="str">
+      <c r="D14" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="33" t="str">
+      <c r="G14" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD90</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="40">
         <f t="shared" si="2"/>
         <v>1.7799</v>
       </c>
-      <c r="O14" s="40">
+      <c r="O14" s="41">
         <v>1988</v>
       </c>
-      <c r="P14" s="41">
+      <c r="P14" s="42">
         <f t="shared" si="3"/>
         <v>0.564371347427368</v>
       </c>
-      <c r="T14" s="36" t="s">
+      <c r="T14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="36" t="s">
+      <c r="U14" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V14" s="36">
+      <c r="V14" s="37">
         <v>2010</v>
       </c>
-      <c r="W14" s="36">
+      <c r="W14" s="37">
         <v>0.918479204177856</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="2:31">
-      <c r="D15" s="33" t="str">
+      <c r="D15" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="33" t="str">
+      <c r="G15" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD91</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="40">
         <f t="shared" si="2"/>
         <v>1.722</v>
       </c>
-      <c r="O15" s="40">
+      <c r="O15" s="41">
         <v>1989</v>
       </c>
-      <c r="P15" s="41">
+      <c r="P15" s="42">
         <f t="shared" si="3"/>
         <v>0.58649742603302</v>
       </c>
-      <c r="T15" s="36" t="s">
+      <c r="T15" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U15" s="36" t="s">
+      <c r="U15" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V15" s="36">
+      <c r="V15" s="37">
         <v>2011</v>
       </c>
-      <c r="W15" s="36">
+      <c r="W15" s="37">
         <v>0.937618970870972</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:31">
-      <c r="D16" s="33" t="str">
+      <c r="D16" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="33" t="str">
+      <c r="G16" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD92</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="40">
         <f t="shared" si="2"/>
         <v>1.6836</v>
       </c>
-      <c r="O16" s="40">
+      <c r="O16" s="41">
         <v>1990</v>
       </c>
-      <c r="P16" s="41">
+      <c r="P16" s="42">
         <f t="shared" si="3"/>
         <v>0.608532726764679</v>
       </c>
-      <c r="T16" s="36" t="s">
+      <c r="T16" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="36" t="s">
+      <c r="U16" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="36">
+      <c r="V16" s="37">
         <v>2012</v>
       </c>
-      <c r="W16" s="36">
+      <c r="W16" s="37">
         <v>0.955666601657867</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="4:23">
-      <c r="D17" s="33" t="str">
+      <c r="D17" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="33" t="str">
+      <c r="G17" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD93</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="40">
         <f t="shared" si="2"/>
         <v>1.6446</v>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="41">
         <v>1991</v>
       </c>
-      <c r="P17" s="41">
+      <c r="P17" s="42">
         <f t="shared" si="3"/>
         <v>0.629012584686279</v>
       </c>
-      <c r="T17" s="36" t="s">
+      <c r="T17" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="36" t="s">
+      <c r="U17" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="36">
+      <c r="V17" s="37">
         <v>2013</v>
       </c>
-      <c r="W17" s="36">
+      <c r="W17" s="37">
         <v>0.972605764865875</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="4:23">
-      <c r="D18" s="33" t="str">
+      <c r="D18" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="33" t="str">
+      <c r="G18" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD94</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="40">
         <f t="shared" si="2"/>
         <v>1.6102</v>
       </c>
-      <c r="O18" s="40">
+      <c r="O18" s="41">
         <v>1992</v>
       </c>
-      <c r="P18" s="41">
+      <c r="P18" s="42">
         <f t="shared" si="3"/>
         <v>0.643362104892731</v>
       </c>
-      <c r="T18" s="36" t="s">
+      <c r="T18" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U18" s="36" t="s">
+      <c r="U18" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="36">
+      <c r="V18" s="37">
         <v>2014</v>
       </c>
-      <c r="W18" s="36">
+      <c r="W18" s="37">
         <v>0.990517318248749</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="4:23">
-      <c r="D19" s="33" t="str">
+      <c r="D19" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="33" t="str">
+      <c r="G19" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD95</v>
       </c>
-      <c r="H19" s="39">
+      <c r="H19" s="40">
         <f t="shared" si="2"/>
         <v>1.5771</v>
       </c>
-      <c r="O19" s="40">
+      <c r="O19" s="41">
         <v>1993</v>
       </c>
-      <c r="P19" s="41">
+      <c r="P19" s="42">
         <f t="shared" si="3"/>
         <v>0.658619225025177</v>
       </c>
-      <c r="T19" s="36" t="s">
+      <c r="T19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="36" t="s">
+      <c r="U19" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="36">
+      <c r="V19" s="37">
         <v>2015</v>
       </c>
-      <c r="W19" s="36">
+      <c r="W19" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="4:23">
-      <c r="D20" s="33" t="str">
+      <c r="D20" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="33" t="str">
+      <c r="G20" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD96</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="40">
         <f t="shared" si="2"/>
         <v>1.5488</v>
       </c>
-      <c r="O20" s="40">
+      <c r="O20" s="41">
         <v>1994</v>
       </c>
-      <c r="P20" s="41">
+      <c r="P20" s="42">
         <f t="shared" si="3"/>
         <v>0.67265796661377</v>
       </c>
-      <c r="T20" s="36" t="s">
+      <c r="T20" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U20" s="36" t="s">
+      <c r="U20" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V20" s="36">
+      <c r="V20" s="37">
         <v>2016</v>
       </c>
-      <c r="W20" s="36">
+      <c r="W20" s="37">
         <v>1.01048374176025</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="4:23">
-      <c r="D21" s="33" t="str">
+      <c r="D21" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F21" s="33" t="s">
+      <c r="F21" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="33" t="str">
+      <c r="G21" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD97</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="40">
         <f t="shared" si="2"/>
         <v>1.5224</v>
       </c>
-      <c r="O21" s="40">
+      <c r="O21" s="41">
         <v>1995</v>
       </c>
-      <c r="P21" s="41">
+      <c r="P21" s="42">
         <f t="shared" si="3"/>
         <v>0.686780393123627</v>
       </c>
-      <c r="T21" s="36" t="s">
+      <c r="T21" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U21" s="36" t="s">
+      <c r="U21" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V21" s="36">
+      <c r="V21" s="37">
         <v>2017</v>
       </c>
-      <c r="W21" s="36">
+      <c r="W21" s="37">
         <v>1.02974033355713</v>
       </c>
     </row>
     <row r="22" ht="14.5" spans="4:23">
-      <c r="D22" s="33" t="str">
+      <c r="D22" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="F22" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="33" t="str">
+      <c r="G22" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD98</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="40">
         <f t="shared" si="2"/>
         <v>1.5058</v>
       </c>
-      <c r="O22" s="40">
+      <c r="O22" s="41">
         <v>1996</v>
       </c>
-      <c r="P22" s="41">
+      <c r="P22" s="42">
         <f t="shared" si="3"/>
         <v>0.699335396289825</v>
       </c>
-      <c r="T22" s="36" t="s">
+      <c r="T22" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U22" s="36" t="s">
+      <c r="U22" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V22" s="36">
+      <c r="V22" s="37">
         <v>2018</v>
       </c>
-      <c r="W22" s="36">
+      <c r="W22" s="37">
         <v>1.05430805683136</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="4:23">
-      <c r="D23" s="33" t="str">
+      <c r="D23" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="33" t="str">
+      <c r="G23" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD99</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="40">
         <f t="shared" si="2"/>
         <v>1.4845</v>
       </c>
-      <c r="O23" s="40">
+      <c r="O23" s="41">
         <v>1997</v>
       </c>
-      <c r="P23" s="41">
+      <c r="P23" s="42">
         <f t="shared" si="3"/>
         <v>0.71145087480545</v>
       </c>
-      <c r="T23" s="36" t="s">
+      <c r="T23" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U23" s="36" t="s">
+      <c r="U23" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V23" s="36">
+      <c r="V23" s="37">
         <v>2019</v>
       </c>
-      <c r="W23" s="36">
+      <c r="W23" s="37">
         <v>1.07337832450867</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="4:23">
-      <c r="D24" s="33" t="str">
+      <c r="D24" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="33" t="str">
+      <c r="G24" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD00</v>
       </c>
-      <c r="H24" s="39">
+      <c r="H24" s="40">
         <f t="shared" si="2"/>
         <v>1.4518</v>
       </c>
-      <c r="O24" s="40">
+      <c r="O24" s="41">
         <v>1998</v>
       </c>
-      <c r="P24" s="41">
+      <c r="P24" s="42">
         <f t="shared" si="3"/>
         <v>0.719296872615814</v>
       </c>
-      <c r="T24" s="36" t="s">
+      <c r="T24" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U24" s="36" t="s">
+      <c r="U24" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="36">
+      <c r="V24" s="37">
         <v>2020</v>
       </c>
-      <c r="W24" s="36">
+      <c r="W24" s="37">
         <v>1.08314538002014</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="4:23">
-      <c r="D25" s="33" t="str">
+      <c r="D25" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="33" t="str">
+      <c r="G25" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD01</v>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="40">
         <f t="shared" si="2"/>
         <v>1.4199</v>
       </c>
-      <c r="O25" s="40">
+      <c r="O25" s="41">
         <v>1999</v>
       </c>
-      <c r="P25" s="41">
+      <c r="P25" s="42">
         <f t="shared" si="3"/>
         <v>0.729613304138184</v>
       </c>
-      <c r="T25" s="36" t="s">
+      <c r="T25" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U25" s="36" t="s">
+      <c r="U25" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V25" s="36">
+      <c r="V25" s="37">
         <v>2021</v>
       </c>
-      <c r="W25" s="36">
+      <c r="W25" s="37">
         <v>1.09456992149353</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="4:23">
-      <c r="D26" s="33" t="str">
+      <c r="D26" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="33" t="str">
+      <c r="G26" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD02</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="40">
         <f t="shared" si="2"/>
         <v>1.3986</v>
       </c>
-      <c r="O26" s="40">
+      <c r="O26" s="41">
         <v>2000</v>
       </c>
-      <c r="P26" s="41">
+      <c r="P26" s="42">
         <f t="shared" si="3"/>
         <v>0.746074616909027</v>
       </c>
-      <c r="T26" s="36" t="s">
+      <c r="T26" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U26" s="36" t="s">
+      <c r="U26" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V26" s="36">
+      <c r="V26" s="37">
         <v>2022</v>
       </c>
-      <c r="W26" s="36">
+      <c r="W26" s="37">
         <v>1.1073887348175</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="4:23">
-      <c r="D27" s="33" t="str">
+      <c r="D27" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="33" t="str">
+      <c r="G27" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD03</v>
       </c>
-      <c r="H27" s="39">
+      <c r="H27" s="40">
         <f t="shared" si="2"/>
         <v>1.3727</v>
       </c>
-      <c r="O27" s="40">
+      <c r="O27" s="41">
         <v>2001</v>
       </c>
-      <c r="P27" s="41">
+      <c r="P27" s="42">
         <f t="shared" si="3"/>
         <v>0.762827515602112</v>
       </c>
-      <c r="T27" s="36" t="s">
+      <c r="T27" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="36" t="s">
+      <c r="U27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V27" s="36">
+      <c r="V27" s="37">
         <v>2023</v>
       </c>
-      <c r="W27" s="36">
+      <c r="W27" s="37">
         <v>1.1224308013916</v>
       </c>
     </row>
     <row r="28" ht="14.5" spans="4:23">
-      <c r="D28" s="33" t="str">
+      <c r="D28" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="33" t="str">
+      <c r="G28" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD04</v>
       </c>
-      <c r="H28" s="39">
+      <c r="H28" s="40">
         <f t="shared" si="2"/>
         <v>1.3369</v>
       </c>
-      <c r="O28" s="40">
+      <c r="O28" s="41">
         <v>2002</v>
       </c>
-      <c r="P28" s="41">
+      <c r="P28" s="42">
         <f t="shared" si="3"/>
         <v>0.774460315704346</v>
       </c>
-      <c r="T28" s="36" t="s">
+      <c r="T28" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U28" s="36" t="s">
+      <c r="U28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V28" s="36">
+      <c r="V28" s="37">
         <v>2024</v>
       </c>
-      <c r="W28" s="36">
+      <c r="W28" s="37">
         <v>1.14128732681274</v>
       </c>
     </row>
     <row r="29" ht="14.5" spans="4:23">
-      <c r="D29" s="33" t="str">
+      <c r="D29" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="33" t="str">
+      <c r="G29" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD05</v>
       </c>
-      <c r="H29" s="39">
+      <c r="H29" s="40">
         <f t="shared" si="2"/>
         <v>1.2967</v>
       </c>
-      <c r="O29" s="40">
+      <c r="O29" s="41">
         <v>2003</v>
       </c>
-      <c r="P29" s="41">
+      <c r="P29" s="42">
         <f t="shared" si="3"/>
         <v>0.789065361022949</v>
       </c>
-      <c r="T29" s="36" t="s">
+      <c r="T29" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U29" s="36" t="s">
+      <c r="U29" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V29" s="36">
+      <c r="V29" s="37">
         <v>2025</v>
       </c>
-      <c r="W29" s="36">
+      <c r="W29" s="37">
         <v>1.16506481170654</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="4:23">
-      <c r="D30" s="33" t="str">
+      <c r="D30" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="33" t="str">
+      <c r="G30" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD06</v>
       </c>
-      <c r="H30" s="39">
+      <c r="H30" s="40">
         <f t="shared" si="2"/>
         <v>1.2583</v>
       </c>
-      <c r="O30" s="40">
+      <c r="O30" s="41">
         <v>2004</v>
       </c>
-      <c r="P30" s="41">
+      <c r="P30" s="42">
         <f t="shared" si="3"/>
         <v>0.810197472572327</v>
       </c>
-      <c r="T30" s="36" t="s">
+      <c r="T30" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U30" s="36" t="s">
+      <c r="U30" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>2026</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>1.19280254840851</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="4:23">
-      <c r="D31" s="33" t="str">
+      <c r="D31" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="33" t="str">
+      <c r="G31" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD07</v>
       </c>
-      <c r="H31" s="39">
+      <c r="H31" s="40">
         <f t="shared" si="2"/>
         <v>1.2253</v>
       </c>
-      <c r="O31" s="40">
+      <c r="O31" s="41">
         <v>2005</v>
       </c>
-      <c r="P31" s="41">
+      <c r="P31" s="42">
         <f t="shared" si="3"/>
         <v>0.835319578647614</v>
       </c>
-      <c r="T31" s="36" t="s">
+      <c r="T31" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U31" s="36" t="s">
+      <c r="U31" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V31" s="36">
+      <c r="V31" s="37">
         <v>2027</v>
       </c>
-      <c r="W31" s="36">
+      <c r="W31" s="37">
         <v>1.22309768199921</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="4:23">
-      <c r="D32" s="33" t="str">
+      <c r="D32" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F32" s="33" t="s">
+      <c r="F32" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="33" t="str">
+      <c r="G32" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD08</v>
       </c>
-      <c r="H32" s="39">
+      <c r="H32" s="40">
         <f t="shared" si="2"/>
         <v>1.2024</v>
       </c>
-      <c r="O32" s="40">
+      <c r="O32" s="41">
         <v>2006</v>
       </c>
-      <c r="P32" s="41">
+      <c r="P32" s="42">
         <f t="shared" si="3"/>
         <v>0.860807240009308</v>
       </c>
-      <c r="T32" s="36" t="s">
+      <c r="T32" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U32" s="36" t="s">
+      <c r="U32" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V32" s="36">
+      <c r="V32" s="37">
         <v>2028</v>
       </c>
-      <c r="W32" s="36">
+      <c r="W32" s="37">
         <v>1.25531399250031</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="4:23">
-      <c r="D33" s="33" t="str">
+      <c r="D33" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="33" t="str">
+      <c r="G33" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD09</v>
       </c>
-      <c r="H33" s="39">
+      <c r="H33" s="40">
         <f t="shared" si="2"/>
         <v>1.1931</v>
       </c>
-      <c r="O33" s="40">
+      <c r="O33" s="41">
         <v>2007</v>
       </c>
-      <c r="P33" s="41">
+      <c r="P33" s="42">
         <f t="shared" si="3"/>
         <v>0.883970141410828</v>
       </c>
-      <c r="T33" s="36" t="s">
+      <c r="T33" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U33" s="36" t="s">
+      <c r="U33" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V33" s="36">
+      <c r="V33" s="37">
         <v>2029</v>
       </c>
-      <c r="W33" s="36">
+      <c r="W33" s="37">
         <v>1.28839552402496</v>
       </c>
     </row>
     <row r="34" ht="14.5" spans="4:23">
-      <c r="D34" s="33" t="str">
+      <c r="D34" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F34" s="33" t="s">
+      <c r="F34" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="33" t="str">
+      <c r="G34" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD10</v>
       </c>
-      <c r="H34" s="39">
+      <c r="H34" s="40">
         <f t="shared" si="2"/>
         <v>1.1793</v>
       </c>
-      <c r="O34" s="40">
+      <c r="O34" s="41">
         <v>2008</v>
       </c>
-      <c r="P34" s="41">
+      <c r="P34" s="42">
         <f t="shared" si="3"/>
         <v>0.900844812393188</v>
       </c>
-      <c r="T34" s="36" t="s">
+      <c r="T34" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U34" s="36" t="s">
+      <c r="U34" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V34" s="36">
+      <c r="V34" s="37">
         <v>2030</v>
       </c>
-      <c r="W34" s="36">
+      <c r="W34" s="37">
         <v>1.32175171375275</v>
       </c>
     </row>
     <row r="35" ht="14.5" spans="4:23">
-      <c r="D35" s="33" t="str">
+      <c r="D35" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="F35" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="str">
+      <c r="G35" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD11</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="40">
         <f t="shared" si="2"/>
         <v>1.1552</v>
       </c>
-      <c r="O35" s="40">
+      <c r="O35" s="41">
         <v>2009</v>
       </c>
-      <c r="P35" s="41">
+      <c r="P35" s="42">
         <f t="shared" si="3"/>
         <v>0.907873749732971</v>
       </c>
-      <c r="T35" s="36" t="s">
+      <c r="T35" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U35" s="36" t="s">
+      <c r="U35" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>1980</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>0.404039144515991</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="4:23">
-      <c r="D36" s="33" t="str">
+      <c r="D36" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="F36" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="33" t="str">
+      <c r="G36" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD12</v>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="40">
         <f t="shared" si="2"/>
         <v>1.1334</v>
       </c>
-      <c r="O36" s="40">
+      <c r="O36" s="41">
         <v>2010</v>
       </c>
-      <c r="P36" s="41">
+      <c r="P36" s="42">
         <f t="shared" si="3"/>
         <v>0.918479204177856</v>
       </c>
-      <c r="T36" s="36" t="s">
+      <c r="T36" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U36" s="36" t="s">
+      <c r="U36" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>1981</v>
       </c>
-      <c r="W36" s="36">
+      <c r="W36" s="37">
         <v>0.442179799079895</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="4:23">
-      <c r="D37" s="33" t="str">
+      <c r="D37" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="F37" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="33" t="str">
+      <c r="G37" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD13</v>
       </c>
-      <c r="H37" s="39">
+      <c r="H37" s="40">
         <f t="shared" si="2"/>
         <v>1.1137</v>
       </c>
-      <c r="O37" s="40">
+      <c r="O37" s="41">
         <v>2011</v>
       </c>
-      <c r="P37" s="41">
+      <c r="P37" s="42">
         <f t="shared" si="3"/>
         <v>0.937618970870972</v>
       </c>
-      <c r="T37" s="36" t="s">
+      <c r="T37" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U37" s="36" t="s">
+      <c r="U37" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V37" s="36">
+      <c r="V37" s="37">
         <v>1982</v>
       </c>
-      <c r="W37" s="36">
+      <c r="W37" s="37">
         <v>0.469521433115005</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="4:23">
-      <c r="D38" s="33" t="str">
+      <c r="D38" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F38" s="33" t="s">
+      <c r="F38" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="33" t="str">
+      <c r="G38" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD14</v>
       </c>
-      <c r="H38" s="39">
+      <c r="H38" s="40">
         <f t="shared" si="2"/>
         <v>1.0935</v>
       </c>
-      <c r="O38" s="40">
+      <c r="O38" s="41">
         <v>2012</v>
       </c>
-      <c r="P38" s="41">
+      <c r="P38" s="42">
         <f t="shared" si="3"/>
         <v>0.955666601657867</v>
       </c>
-      <c r="T38" s="36" t="s">
+      <c r="T38" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U38" s="36" t="s">
+      <c r="U38" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V38" s="36">
+      <c r="V38" s="37">
         <v>1983</v>
       </c>
-      <c r="W38" s="36">
+      <c r="W38" s="37">
         <v>0.487872630357742</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="4:23">
-      <c r="D39" s="33" t="str">
+      <c r="D39" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="33" t="str">
+      <c r="G39" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD15</v>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="40">
         <f t="shared" si="2"/>
         <v>1.0831</v>
       </c>
-      <c r="O39" s="40">
+      <c r="O39" s="41">
         <v>2013</v>
       </c>
-      <c r="P39" s="41">
+      <c r="P39" s="42">
         <f t="shared" si="3"/>
         <v>0.972605764865875</v>
       </c>
-      <c r="T39" s="36" t="s">
+      <c r="T39" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U39" s="36" t="s">
+      <c r="U39" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V39" s="36">
+      <c r="V39" s="37">
         <v>1984</v>
       </c>
-      <c r="W39" s="36">
+      <c r="W39" s="37">
         <v>0.505495131015778</v>
       </c>
     </row>
     <row r="40" ht="14.5" spans="4:23">
-      <c r="D40" s="33" t="str">
+      <c r="D40" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="33" t="str">
+      <c r="G40" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD16</v>
       </c>
-      <c r="H40" s="39">
+      <c r="H40" s="40">
         <f t="shared" si="2"/>
         <v>1.0719</v>
       </c>
-      <c r="O40" s="40">
+      <c r="O40" s="41">
         <v>2014</v>
       </c>
-      <c r="P40" s="41">
+      <c r="P40" s="42">
         <f t="shared" si="3"/>
         <v>0.990517318248749</v>
       </c>
-      <c r="T40" s="36" t="s">
+      <c r="T40" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U40" s="36" t="s">
+      <c r="U40" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V40" s="36">
+      <c r="V40" s="37">
         <v>1985</v>
       </c>
-      <c r="W40" s="36">
+      <c r="W40" s="37">
         <v>0.521485805511475</v>
       </c>
     </row>
     <row r="41" ht="14.5" spans="4:23">
-      <c r="D41" s="33" t="str">
+      <c r="D41" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G41" s="33" t="str">
+      <c r="G41" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD17</v>
       </c>
-      <c r="H41" s="39">
+      <c r="H41" s="40">
         <f t="shared" si="2"/>
         <v>1.0519</v>
       </c>
-      <c r="O41" s="40">
+      <c r="O41" s="41">
         <v>2015</v>
       </c>
-      <c r="P41" s="41">
+      <c r="P41" s="42">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T41" s="36" t="s">
+      <c r="T41" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U41" s="36" t="s">
+      <c r="U41" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V41" s="36">
+      <c r="V41" s="37">
         <v>1986</v>
       </c>
-      <c r="W41" s="36">
+      <c r="W41" s="37">
         <v>0.532050728797913</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="4:23">
-      <c r="D42" s="33" t="str">
+      <c r="D42" s="34" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="str">
+      <c r="G42" s="34" t="str">
         <f t="shared" si="1"/>
         <v>USD18</v>
       </c>
-      <c r="H42" s="39">
+      <c r="H42" s="40">
         <f t="shared" si="2"/>
         <v>1.0274</v>
       </c>
-      <c r="O42" s="40">
+      <c r="O42" s="41">
         <v>2016</v>
       </c>
-      <c r="P42" s="41">
+      <c r="P42" s="42">
         <f t="shared" si="3"/>
         <v>1.01048374176025</v>
       </c>
-      <c r="T42" s="36" t="s">
+      <c r="T42" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U42" s="36" t="s">
+      <c r="U42" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V42" s="36">
+      <c r="V42" s="37">
         <v>1987</v>
       </c>
-      <c r="W42" s="36">
+      <c r="W42" s="37">
         <v>0.54511946439743</v>
       </c>
     </row>
     <row r="43" ht="14.5" spans="4:23">
-      <c r="D43" s="33" t="str">
+      <c r="D43" s="34" t="str">
         <f t="shared" ref="D43:D49" si="4">IF(F43=G43,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="33" t="str">
+      <c r="G43" s="34" t="str">
         <f t="shared" ref="G43:G49" si="5">"USD"&amp;RIGHT(O45,2)</f>
         <v>USD19</v>
       </c>
-      <c r="H43" s="39">
+      <c r="H43" s="40">
         <f t="shared" si="2"/>
         <v>1.0091</v>
       </c>
-      <c r="O43" s="40">
+      <c r="O43" s="41">
         <v>2017</v>
       </c>
-      <c r="P43" s="41">
+      <c r="P43" s="42">
         <f t="shared" si="3"/>
         <v>1.02974033355713</v>
       </c>
-      <c r="T43" s="36" t="s">
+      <c r="T43" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U43" s="36" t="s">
+      <c r="U43" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V43" s="36">
+      <c r="V43" s="37">
         <v>1988</v>
       </c>
-      <c r="W43" s="36">
+      <c r="W43" s="37">
         <v>0.564371347427368</v>
       </c>
     </row>
     <row r="44" ht="14.5" spans="4:23">
-      <c r="D44" s="33" t="str">
+      <c r="D44" s="34" t="str">
         <f t="shared" si="4"/>
         <v>*G_CUREX</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="33" t="str">
+      <c r="G44" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD20</v>
       </c>
-      <c r="H44" s="39">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O44" s="40">
+      <c r="H44" s="40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O44" s="41">
         <v>2018</v>
       </c>
-      <c r="P44" s="41">
+      <c r="P44" s="42">
         <f t="shared" si="3"/>
         <v>1.05430805683136</v>
       </c>
-      <c r="T44" s="36" t="s">
+      <c r="T44" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U44" s="36" t="s">
+      <c r="U44" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V44" s="36">
+      <c r="V44" s="37">
         <v>1989</v>
       </c>
-      <c r="W44" s="36">
+      <c r="W44" s="37">
         <v>0.58649742603302</v>
       </c>
     </row>
     <row r="45" ht="14.5" spans="4:23">
-      <c r="D45" s="33" t="str">
+      <c r="D45" s="34" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="33" t="str">
+      <c r="G45" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD21</v>
       </c>
-      <c r="H45" s="39">
+      <c r="H45" s="40">
         <f t="shared" si="2"/>
         <v>0.9896</v>
       </c>
-      <c r="O45" s="40">
+      <c r="O45" s="41">
         <v>2019</v>
       </c>
-      <c r="P45" s="41">
+      <c r="P45" s="42">
         <f t="shared" si="3"/>
         <v>1.07337832450867</v>
       </c>
-      <c r="T45" s="36" t="s">
+      <c r="T45" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U45" s="36" t="s">
+      <c r="U45" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V45" s="36">
+      <c r="V45" s="37">
         <v>1990</v>
       </c>
-      <c r="W45" s="36">
+      <c r="W45" s="37">
         <v>0.608532726764679</v>
       </c>
     </row>
     <row r="46" ht="14.5" spans="4:23">
-      <c r="D46" s="33" t="str">
+      <c r="D46" s="34" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F46" s="33" t="s">
+      <c r="F46" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="33" t="str">
+      <c r="G46" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD22</v>
       </c>
-      <c r="H46" s="39">
+      <c r="H46" s="40">
         <f t="shared" si="2"/>
         <v>0.9781</v>
       </c>
-      <c r="O46" s="40">
+      <c r="O46" s="41">
         <v>2020</v>
       </c>
-      <c r="P46" s="41">
+      <c r="P46" s="42">
         <f t="shared" si="3"/>
         <v>1.08314538002014</v>
       </c>
-      <c r="T46" s="36" t="s">
+      <c r="T46" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U46" s="36" t="s">
+      <c r="U46" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V46" s="36">
+      <c r="V46" s="37">
         <v>1991</v>
       </c>
-      <c r="W46" s="36">
+      <c r="W46" s="37">
         <v>0.629012584686279</v>
       </c>
     </row>
     <row r="47" ht="14.5" spans="4:23">
-      <c r="D47" s="33" t="str">
+      <c r="D47" s="34" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F47" s="33" t="s">
+      <c r="F47" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="33" t="str">
+      <c r="G47" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD23</v>
       </c>
-      <c r="H47" s="39">
+      <c r="H47" s="40">
         <f t="shared" si="2"/>
         <v>0.965</v>
       </c>
-      <c r="O47" s="40">
+      <c r="O47" s="41">
         <v>2021</v>
       </c>
-      <c r="P47" s="41">
+      <c r="P47" s="42">
         <f t="shared" si="3"/>
         <v>1.09456992149353</v>
       </c>
-      <c r="T47" s="36" t="s">
+      <c r="T47" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U47" s="36" t="s">
+      <c r="U47" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V47" s="36">
+      <c r="V47" s="37">
         <v>1992</v>
       </c>
-      <c r="W47" s="36">
+      <c r="W47" s="37">
         <v>0.643362104892731</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="4:23">
-      <c r="D48" s="33" t="str">
+      <c r="D48" s="34" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F48" s="33" t="s">
+      <c r="F48" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="33" t="str">
+      <c r="G48" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD24</v>
       </c>
-      <c r="H48" s="39">
+      <c r="H48" s="40">
         <f t="shared" si="2"/>
         <v>0.9491</v>
       </c>
-      <c r="O48" s="40">
+      <c r="O48" s="41">
         <v>2022</v>
       </c>
-      <c r="P48" s="41">
+      <c r="P48" s="42">
         <f t="shared" si="3"/>
         <v>1.1073887348175</v>
       </c>
-      <c r="T48" s="36" t="s">
+      <c r="T48" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U48" s="36" t="s">
+      <c r="U48" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V48" s="36">
+      <c r="V48" s="37">
         <v>1993</v>
       </c>
-      <c r="W48" s="36">
+      <c r="W48" s="37">
         <v>0.658619225025177</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="4:23">
-      <c r="D49" s="33" t="str">
+      <c r="D49" s="34" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F49" s="33" t="s">
+      <c r="F49" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="33" t="str">
+      <c r="G49" s="34" t="str">
         <f t="shared" si="5"/>
         <v>USD25</v>
       </c>
-      <c r="H49" s="39">
+      <c r="H49" s="40">
         <f t="shared" si="2"/>
         <v>0.9297</v>
       </c>
-      <c r="O49" s="40">
+      <c r="O49" s="41">
         <v>2023</v>
       </c>
-      <c r="P49" s="41">
+      <c r="P49" s="42">
         <f t="shared" si="3"/>
         <v>1.1224308013916</v>
       </c>
-      <c r="T49" s="36" t="s">
+      <c r="T49" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U49" s="36" t="s">
+      <c r="U49" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V49" s="36">
+      <c r="V49" s="37">
         <v>1994</v>
       </c>
-      <c r="W49" s="36">
+      <c r="W49" s="37">
         <v>0.67265796661377</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="4:23">
-      <c r="D50" s="33" t="s">
+      <c r="D50" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="33" t="str">
+      <c r="G50" s="34" t="str">
         <f t="shared" ref="G50:G85" si="6">G7</f>
         <v>USD83</v>
       </c>
-      <c r="H50" s="39">
+      <c r="H50" s="40">
         <f>$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O50" s="40">
+      <c r="O50" s="41">
         <v>2024</v>
       </c>
-      <c r="P50" s="41">
+      <c r="P50" s="42">
         <f t="shared" si="3"/>
         <v>1.14128732681274</v>
       </c>
-      <c r="T50" s="36" t="s">
+      <c r="T50" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U50" s="36" t="s">
+      <c r="U50" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V50" s="36">
+      <c r="V50" s="37">
         <v>1995</v>
       </c>
-      <c r="W50" s="36">
+      <c r="W50" s="37">
         <v>0.686780393123627</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="4:23">
-      <c r="D51" s="33" t="s">
+      <c r="D51" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="33" t="str">
+      <c r="G51" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD84</v>
       </c>
-      <c r="H51" s="39">
+      <c r="H51" s="40">
         <f t="shared" ref="H51:H92" si="7">$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O51" s="40">
+      <c r="O51" s="41">
         <v>2025</v>
       </c>
-      <c r="P51" s="41">
+      <c r="P51" s="42">
         <f t="shared" si="3"/>
         <v>1.16506481170654</v>
       </c>
-      <c r="T51" s="36" t="s">
+      <c r="T51" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U51" s="36" t="s">
+      <c r="U51" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V51" s="36">
+      <c r="V51" s="37">
         <v>1996</v>
       </c>
-      <c r="W51" s="36">
+      <c r="W51" s="37">
         <v>0.699335396289825</v>
       </c>
     </row>
     <row r="52" spans="4:23">
-      <c r="D52" s="33" t="s">
+      <c r="D52" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="33" t="str">
+      <c r="G52" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD85</v>
       </c>
-      <c r="H52" s="39">
+      <c r="H52" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T52" s="36" t="s">
+      <c r="T52" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U52" s="36" t="s">
+      <c r="U52" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V52" s="36">
+      <c r="V52" s="37">
         <v>1997</v>
       </c>
-      <c r="W52" s="36">
+      <c r="W52" s="37">
         <v>0.71145087480545</v>
       </c>
     </row>
     <row r="53" spans="4:23">
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="33" t="str">
+      <c r="G53" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD86</v>
       </c>
-      <c r="H53" s="39">
+      <c r="H53" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T53" s="36" t="s">
+      <c r="T53" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U53" s="36" t="s">
+      <c r="U53" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V53" s="36">
+      <c r="V53" s="37">
         <v>1998</v>
       </c>
-      <c r="W53" s="36">
+      <c r="W53" s="37">
         <v>0.719296872615814</v>
       </c>
     </row>
     <row r="54" spans="4:23">
-      <c r="D54" s="33" t="s">
+      <c r="D54" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="33" t="str">
+      <c r="G54" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD87</v>
       </c>
-      <c r="H54" s="39">
+      <c r="H54" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T54" s="36" t="s">
+      <c r="T54" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U54" s="36" t="s">
+      <c r="U54" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V54" s="36">
+      <c r="V54" s="37">
         <v>1999</v>
       </c>
-      <c r="W54" s="36">
+      <c r="W54" s="37">
         <v>0.729613304138184</v>
       </c>
     </row>
     <row r="55" spans="4:23">
-      <c r="D55" s="33" t="s">
+      <c r="D55" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="33" t="str">
+      <c r="G55" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD88</v>
       </c>
-      <c r="H55" s="39">
+      <c r="H55" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T55" s="36" t="s">
+      <c r="T55" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U55" s="36" t="s">
+      <c r="U55" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="V55" s="36">
+      <c r="V55" s="37">
         <v>2000</v>
       </c>
-      <c r="W55" s="36">
+      <c r="W55" s="37">
         <v>0.746074616909027</v>
       </c>
     </row>
     <row r="56" spans="4:23">
-      <c r="D56" s="33" t="s">
+      <c r="D56" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="33" t="str">
+      <c r="G56" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD89</v>
       </c>
-      <c r="H56" s="39">
+      <c r="H56" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="57" spans="4:23">
-      <c r="D57" s="33" t="s">
+      <c r="D57" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="33" t="str">
+      <c r="G57" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD90</v>
       </c>
-      <c r="H57" s="39">
+      <c r="H57" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="58" spans="4:23">
-      <c r="D58" s="33" t="s">
+      <c r="D58" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="33" t="str">
+      <c r="G58" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD91</v>
       </c>
-      <c r="H58" s="39">
+      <c r="H58" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="59" spans="4:23">
-      <c r="D59" s="33" t="s">
+      <c r="D59" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="33" t="str">
+      <c r="G59" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD92</v>
       </c>
-      <c r="H59" s="39">
+      <c r="H59" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="60" spans="4:23">
-      <c r="D60" s="33" t="s">
+      <c r="D60" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="33" t="str">
+      <c r="G60" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD93</v>
       </c>
-      <c r="H60" s="39">
+      <c r="H60" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="61" spans="4:23">
-      <c r="D61" s="33" t="s">
+      <c r="D61" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G61" s="33" t="str">
+      <c r="G61" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD94</v>
       </c>
-      <c r="H61" s="39">
+      <c r="H61" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="62" spans="4:23">
-      <c r="D62" s="33" t="s">
+      <c r="D62" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G62" s="33" t="str">
+      <c r="G62" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD95</v>
       </c>
-      <c r="H62" s="39">
+      <c r="H62" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="63" spans="4:23">
-      <c r="D63" s="33" t="s">
+      <c r="D63" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="33" t="str">
+      <c r="G63" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD96</v>
       </c>
-      <c r="H63" s="39">
+      <c r="H63" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="64" spans="4:23">
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="33" t="str">
+      <c r="G64" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD97</v>
       </c>
-      <c r="H64" s="39">
+      <c r="H64" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="65" spans="4:8">
-      <c r="D65" s="33" t="s">
+      <c r="D65" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="33" t="str">
+      <c r="G65" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD98</v>
       </c>
-      <c r="H65" s="39">
+      <c r="H65" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="66" spans="4:8">
-      <c r="D66" s="33" t="s">
+      <c r="D66" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G66" s="33" t="str">
+      <c r="G66" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD99</v>
       </c>
-      <c r="H66" s="39">
+      <c r="H66" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="67" spans="4:8">
-      <c r="D67" s="33" t="s">
+      <c r="D67" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="33" t="str">
+      <c r="G67" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD00</v>
       </c>
-      <c r="H67" s="39">
+      <c r="H67" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="68" spans="4:8">
-      <c r="D68" s="33" t="s">
+      <c r="D68" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="33" t="str">
+      <c r="G68" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD01</v>
       </c>
-      <c r="H68" s="39">
+      <c r="H68" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="69" spans="4:8">
-      <c r="D69" s="33" t="s">
+      <c r="D69" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="33" t="str">
+      <c r="G69" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD02</v>
       </c>
-      <c r="H69" s="39">
+      <c r="H69" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="70" spans="4:8">
-      <c r="D70" s="33" t="s">
+      <c r="D70" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="33" t="str">
+      <c r="G70" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD03</v>
       </c>
-      <c r="H70" s="39">
+      <c r="H70" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="71" spans="4:8">
-      <c r="D71" s="33" t="s">
+      <c r="D71" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G71" s="33" t="str">
+      <c r="G71" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD04</v>
       </c>
-      <c r="H71" s="39">
+      <c r="H71" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="72" spans="4:8">
-      <c r="D72" s="33" t="s">
+      <c r="D72" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="33" t="str">
+      <c r="G72" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD05</v>
       </c>
-      <c r="H72" s="39">
+      <c r="H72" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="73" spans="4:8">
-      <c r="D73" s="33" t="s">
+      <c r="D73" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G73" s="33" t="str">
+      <c r="G73" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD06</v>
       </c>
-      <c r="H73" s="39">
+      <c r="H73" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="74" spans="4:8">
-      <c r="D74" s="33" t="s">
+      <c r="D74" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="33" t="str">
+      <c r="G74" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD07</v>
       </c>
-      <c r="H74" s="39">
+      <c r="H74" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="75" spans="4:8">
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G75" s="33" t="str">
+      <c r="G75" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD08</v>
       </c>
-      <c r="H75" s="39">
+      <c r="H75" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="76" spans="4:8">
-      <c r="D76" s="33" t="s">
+      <c r="D76" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G76" s="33" t="str">
+      <c r="G76" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD09</v>
       </c>
-      <c r="H76" s="39">
+      <c r="H76" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="77" spans="4:8">
-      <c r="D77" s="33" t="s">
+      <c r="D77" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G77" s="33" t="str">
+      <c r="G77" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD10</v>
       </c>
-      <c r="H77" s="39">
+      <c r="H77" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="78" spans="4:8">
-      <c r="D78" s="33" t="s">
+      <c r="D78" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G78" s="33" t="str">
+      <c r="G78" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD11</v>
       </c>
-      <c r="H78" s="39">
+      <c r="H78" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="79" spans="4:8">
-      <c r="D79" s="33" t="s">
+      <c r="D79" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="33" t="str">
+      <c r="G79" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD12</v>
       </c>
-      <c r="H79" s="39">
+      <c r="H79" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="80" spans="4:8">
-      <c r="D80" s="33" t="s">
+      <c r="D80" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G80" s="33" t="str">
+      <c r="G80" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD13</v>
       </c>
-      <c r="H80" s="39">
+      <c r="H80" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="81" spans="4:8">
-      <c r="D81" s="33" t="s">
+      <c r="D81" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="33" t="str">
+      <c r="G81" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD14</v>
       </c>
-      <c r="H81" s="39">
+      <c r="H81" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="82" spans="4:8">
-      <c r="D82" s="33" t="s">
+      <c r="D82" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G82" s="33" t="str">
+      <c r="G82" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD15</v>
       </c>
-      <c r="H82" s="39">
+      <c r="H82" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="83" spans="4:8">
-      <c r="D83" s="33" t="s">
+      <c r="D83" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G83" s="33" t="str">
+      <c r="G83" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD16</v>
       </c>
-      <c r="H83" s="39">
+      <c r="H83" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="84" spans="4:8">
-      <c r="D84" s="33" t="s">
+      <c r="D84" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="33" t="str">
+      <c r="G84" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD17</v>
       </c>
-      <c r="H84" s="39">
+      <c r="H84" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="85" spans="4:8">
-      <c r="D85" s="33" t="s">
+      <c r="D85" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G85" s="33" t="str">
+      <c r="G85" s="34" t="str">
         <f t="shared" si="6"/>
         <v>USD18</v>
       </c>
-      <c r="H85" s="39">
+      <c r="H85" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="86" spans="4:8">
-      <c r="D86" s="33" t="s">
+      <c r="D86" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G86" s="33" t="str">
+      <c r="G86" s="34" t="str">
         <f t="shared" ref="G86:G92" si="8">G43</f>
         <v>USD19</v>
       </c>
-      <c r="H86" s="39">
+      <c r="H86" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="87" spans="4:8">
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G87" s="33" t="str">
+      <c r="G87" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD20</v>
       </c>
-      <c r="H87" s="39">
+      <c r="H87" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="88" spans="4:8">
-      <c r="D88" s="33" t="s">
+      <c r="D88" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G88" s="33" t="str">
+      <c r="G88" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD21</v>
       </c>
-      <c r="H88" s="39">
+      <c r="H88" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="89" spans="4:8">
-      <c r="D89" s="33" t="s">
+      <c r="D89" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="33" t="str">
+      <c r="G89" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD22</v>
       </c>
-      <c r="H89" s="39">
+      <c r="H89" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="90" spans="4:8">
-      <c r="D90" s="33" t="s">
+      <c r="D90" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G90" s="33" t="str">
+      <c r="G90" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD23</v>
       </c>
-      <c r="H90" s="39">
+      <c r="H90" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="91" spans="4:8">
-      <c r="D91" s="33" t="s">
+      <c r="D91" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G91" s="33" t="str">
+      <c r="G91" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD24</v>
       </c>
-      <c r="H91" s="39">
+      <c r="H91" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="92" spans="4:8">
-      <c r="D92" s="33" t="s">
+      <c r="D92" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G92" s="33" t="str">
+      <c r="G92" s="34" t="str">
         <f t="shared" si="8"/>
         <v>USD25</v>
       </c>
-      <c r="H92" s="39">
+      <c r="H92" s="40">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
@@ -5010,11 +5011,11 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="25" t="str">
+      <c r="F11" s="26" t="str">
         <f>F10</f>
         <v>Trd*</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="26" t="s">
         <v>37</v>
       </c>
       <c r="H11" s="12">
@@ -5023,26 +5024,26 @@
       </c>
     </row>
     <row r="12" spans="4:8">
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="4:8">
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29"/>
     </row>
     <row r="14" spans="4:8">
-      <c r="G14" s="29"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="17" spans="6:10">
-      <c r="H17" s="30"/>
+      <c r="H17" s="31"/>
     </row>
     <row r="18" spans="6:10">
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5064,7 +5065,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5113,7 +5114,7 @@
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="25" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5132,10 +5133,10 @@
       <c r="B13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <v>2150</v>
       </c>
     </row>
@@ -5145,7 +5146,7 @@
       </c>
     </row>
     <row r="20" spans="2:13">
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="19" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5223,8 +5224,8 @@
       <c r="G23" t="s">
         <v>71</v>
       </c>
-      <c r="J23" s="23">
-        <v>-2</v>
+      <c r="J23" s="24">
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -5237,7 +5238,7 @@
       <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="19">
         <v>0.5</v>
       </c>
     </row>
@@ -5252,7 +5253,7 @@
         <f>F24</f>
         <v>AuxStoOUT</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="19">
         <f>I24/4</f>
         <v>0.125</v>
       </c>
@@ -17982,7 +17983,7 @@
         <f t="shared" ref="U6:U28" si="0">L6</f>
         <v>Africa_North</v>
       </c>
-      <c r="V6" s="23"/>
+      <c r="V6" s="24"/>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
@@ -18029,7 +18030,7 @@
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="V7" s="23"/>
+      <c r="V7" s="24"/>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
@@ -18076,7 +18077,7 @@
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="V8" s="23"/>
+      <c r="V8" s="24"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
@@ -18123,7 +18124,7 @@
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="V9" s="23"/>
+      <c r="V9" s="24"/>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
@@ -18170,7 +18171,7 @@
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="V10" s="23"/>
+      <c r="V10" s="24"/>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
@@ -18217,7 +18218,7 @@
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="V11" s="23"/>
+      <c r="V11" s="24"/>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
@@ -18264,7 +18265,7 @@
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="V12" s="23"/>
+      <c r="V12" s="24"/>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
@@ -18311,7 +18312,7 @@
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="V13" s="23"/>
+      <c r="V13" s="24"/>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
@@ -18358,7 +18359,7 @@
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="V14" s="23"/>
+      <c r="V14" s="24"/>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
@@ -18405,7 +18406,7 @@
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="V15" s="23"/>
+      <c r="V15" s="24"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
@@ -18452,7 +18453,7 @@
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
@@ -18499,7 +18500,7 @@
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="V17" s="23"/>
+      <c r="V17" s="24"/>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
@@ -18546,7 +18547,7 @@
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="V18" s="23"/>
+      <c r="V18" s="24"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
@@ -18593,7 +18594,7 @@
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="V19" s="23"/>
+      <c r="V19" s="24"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
@@ -18640,7 +18641,7 @@
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="V20" s="23"/>
+      <c r="V20" s="24"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
@@ -18687,7 +18688,7 @@
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="V21" s="23"/>
+      <c r="V21" s="24"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
@@ -18734,7 +18735,7 @@
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="V22" s="23"/>
+      <c r="V22" s="24"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
@@ -18781,7 +18782,7 @@
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="V23" s="23"/>
+      <c r="V23" s="24"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
@@ -18828,7 +18829,7 @@
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="V24" s="23"/>
+      <c r="V24" s="24"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
@@ -18875,7 +18876,7 @@
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="V25" s="23"/>
+      <c r="V25" s="24"/>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
@@ -18922,7 +18923,7 @@
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="V26" s="23"/>
+      <c r="V26" s="24"/>
     </row>
     <row r="27" spans="1:22">
       <c r="E27" t="s">
@@ -18960,7 +18961,7 @@
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="V27" s="23"/>
+      <c r="V27" s="24"/>
     </row>
     <row r="28" spans="1:22">
       <c r="E28" t="s">
@@ -18998,7 +18999,7 @@
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="V28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22">
       <c r="E29" t="s">
@@ -19024,7 +19025,7 @@
       <c r="U29" t="s">
         <v>251</v>
       </c>
-      <c r="V29" s="23">
+      <c r="V29" s="24">
         <v>0.33</v>
       </c>
     </row>
@@ -19050,7 +19051,7 @@
       <c r="U30" t="s">
         <v>253</v>
       </c>
-      <c r="V30" s="23">
+      <c r="V30" s="24">
         <v>0.33</v>
       </c>
     </row>
@@ -21800,164 +21801,164 @@
       </c>
     </row>
     <row r="36" ht="17.75" spans="1:40">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="21" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="37" ht="16" spans="1:40">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="21" t="str">
+      <c r="C37" s="22" t="str">
         <f t="shared" ref="C37:AK37" si="0">B18</f>
         <v>Africa_North</v>
       </c>
-      <c r="D37" s="21" t="str">
+      <c r="D37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Africa_Other</v>
       </c>
-      <c r="E37" s="21" t="str">
+      <c r="E37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Australia</v>
       </c>
-      <c r="F37" s="21" t="str">
+      <c r="F37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Austria</v>
       </c>
-      <c r="G37" s="21" t="str">
+      <c r="G37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Baltics</v>
       </c>
-      <c r="H37" s="21" t="str">
+      <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="I37" s="21" t="str">
+      <c r="I37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="J37" s="21" t="str">
+      <c r="J37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="K37" s="21" t="str">
+      <c r="K37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="L37" s="21" t="str">
+      <c r="L37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="M37" s="21" t="str">
+      <c r="M37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="N37" s="21" t="str">
+      <c r="N37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="O37" s="21" t="str">
+      <c r="O37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>GreeceCyp</v>
       </c>
-      <c r="P37" s="21" t="str">
+      <c r="P37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="Q37" s="21" t="str">
+      <c r="Q37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Iceland</v>
       </c>
-      <c r="R37" s="21" t="str">
+      <c r="R37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="S37" s="21" t="str">
+      <c r="S37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Ireland</v>
       </c>
-      <c r="T37" s="21" t="str">
+      <c r="T37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ItalyMal</v>
       </c>
-      <c r="U37" s="21" t="str">
+      <c r="U37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V37" s="21" t="str">
+      <c r="V37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="W37" s="21" t="str">
+      <c r="W37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="X37" s="21" t="str">
+      <c r="X37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="Y37" s="21" t="str">
+      <c r="Y37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Norway</v>
       </c>
-      <c r="Z37" s="21" t="str">
+      <c r="Z37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Poland</v>
       </c>
-      <c r="AA37" s="21" t="str">
+      <c r="AA37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="AB37" s="21" t="str">
+      <c r="AB37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="AC37" s="21" t="str">
+      <c r="AC37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>SaudiArabia</v>
       </c>
-      <c r="AD37" s="21" t="str">
+      <c r="AD37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="AE37" s="21" t="str">
+      <c r="AE37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="AF37" s="21" t="str">
+      <c r="AF37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="AG37" s="21" t="str">
+      <c r="AG37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="AH37" s="21" t="str">
+      <c r="AH37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="AI37" s="21" t="str">
+      <c r="AI37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="AJ37" s="21" t="str">
+      <c r="AJ37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="AK37" s="21" t="str">
+      <c r="AK37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>WestBalkans</v>
       </c>
-      <c r="AL37" s="21" t="s">
+      <c r="AL37" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="AM37" s="21" t="s">
+      <c r="AM37" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AN37" s="21" t="s">
+      <c r="AN37" s="22" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22269,143 +22270,143 @@
       <c r="A41" t="s">
         <v>318</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="23">
         <f>1-B25/100</f>
         <v>0.781</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <f t="shared" ref="D41:AK41" si="4">1-C25/100</f>
         <v>0.8018</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <f t="shared" si="4"/>
         <v>0.9012</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="23">
         <f t="shared" si="4"/>
         <v>0.9157</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <f t="shared" si="4"/>
         <v>0.7593</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="23">
         <f t="shared" si="4"/>
         <v>0.9248</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="23">
         <f t="shared" si="4"/>
         <v>0.8378</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41" s="23">
         <f t="shared" si="4"/>
         <v>0.9004</v>
       </c>
-      <c r="K41" s="22">
+      <c r="K41" s="23">
         <f t="shared" si="4"/>
         <v>0.8597</v>
       </c>
-      <c r="L41" s="22">
+      <c r="L41" s="23">
         <f t="shared" si="4"/>
         <v>0.8738</v>
       </c>
-      <c r="M41" s="22">
+      <c r="M41" s="23">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="23">
         <f t="shared" si="4"/>
         <v>0.9038</v>
       </c>
-      <c r="O41" s="22">
+      <c r="O41" s="23">
         <f t="shared" si="4"/>
         <v>0.8756</v>
       </c>
-      <c r="P41" s="22">
+      <c r="P41" s="23">
         <f t="shared" si="4"/>
         <v>0.8429</v>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41" s="23">
         <f t="shared" si="4"/>
         <v>0.9532</v>
       </c>
-      <c r="R41" s="22">
+      <c r="R41" s="23">
         <f t="shared" si="4"/>
         <v>0.7732</v>
       </c>
-      <c r="S41" s="22">
+      <c r="S41" s="23">
         <f t="shared" si="4"/>
         <v>0.8973</v>
       </c>
-      <c r="T41" s="22">
+      <c r="T41" s="23">
         <f t="shared" si="4"/>
         <v>0.899</v>
       </c>
-      <c r="U41" s="22">
+      <c r="U41" s="23">
         <f t="shared" si="4"/>
         <v>0.9173</v>
       </c>
-      <c r="V41" s="22">
+      <c r="V41" s="23">
         <f t="shared" si="4"/>
         <v>0.8421</v>
       </c>
-      <c r="W41" s="22">
+      <c r="W41" s="23">
         <f t="shared" si="4"/>
         <v>0.8113</v>
       </c>
-      <c r="X41" s="22">
+      <c r="X41" s="23">
         <f t="shared" si="4"/>
         <v>0.9117</v>
       </c>
-      <c r="Y41" s="22">
+      <c r="Y41" s="23">
         <f t="shared" si="4"/>
         <v>0.9496</v>
       </c>
-      <c r="Z41" s="22">
+      <c r="Z41" s="23">
         <f t="shared" si="4"/>
         <v>0.8708</v>
       </c>
-      <c r="AA41" s="22">
+      <c r="AA41" s="23">
         <f t="shared" si="4"/>
         <v>0.895</v>
       </c>
-      <c r="AB41" s="22">
+      <c r="AB41" s="23">
         <f t="shared" si="4"/>
         <v>0.8521</v>
       </c>
-      <c r="AC41" s="22">
+      <c r="AC41" s="23">
         <f t="shared" si="4"/>
         <v>0.8649</v>
       </c>
-      <c r="AD41" s="22">
+      <c r="AD41" s="23">
         <f t="shared" si="4"/>
         <v>0.844</v>
       </c>
-      <c r="AE41" s="22">
+      <c r="AE41" s="23">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="AF41" s="22">
+      <c r="AF41" s="23">
         <f t="shared" si="4"/>
         <v>0.9225</v>
       </c>
-      <c r="AG41" s="22">
+      <c r="AG41" s="23">
         <f t="shared" si="4"/>
         <v>0.8956</v>
       </c>
-      <c r="AH41" s="22">
+      <c r="AH41" s="23">
         <f t="shared" si="4"/>
         <v>0.8644</v>
       </c>
-      <c r="AI41" s="22">
+      <c r="AI41" s="23">
         <f t="shared" si="4"/>
         <v>0.8994</v>
       </c>
-      <c r="AJ41" s="22">
+      <c r="AJ41" s="23">
         <f t="shared" si="4"/>
         <v>0.827</v>
       </c>
-      <c r="AK41" s="22">
+      <c r="AK41" s="23">
         <f t="shared" si="4"/>
         <v>0.8198</v>
       </c>
@@ -24670,7 +24671,7 @@
       <c r="AQ22">
         <v>2</v>
       </c>
-      <c r="AR22" s="42" t="s">
+      <c r="AR22" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -24843,7 +24844,7 @@
       <c r="AQ23">
         <v>2</v>
       </c>
-      <c r="AR23" s="42" t="s">
+      <c r="AR23" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -25016,10 +25017,10 @@
       <c r="AQ24">
         <v>2</v>
       </c>
-      <c r="AR24" s="42" t="s">
+      <c r="AR24" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="AS24" s="42" t="s">
+      <c r="AS24" s="43" t="s">
         <v>342</v>
       </c>
       <c r="AT24" t="s">
@@ -25195,7 +25196,7 @@
       <c r="AQ25">
         <v>2</v>
       </c>
-      <c r="AR25" s="42" t="s">
+      <c r="AR25" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -25368,7 +25369,7 @@
       <c r="AQ26">
         <v>2</v>
       </c>
-      <c r="AR26" s="42" t="s">
+      <c r="AR26" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -25541,7 +25542,7 @@
       <c r="AQ27">
         <v>2</v>
       </c>
-      <c r="AR27" s="42" t="s">
+      <c r="AR27" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -25714,7 +25715,7 @@
       <c r="AQ28">
         <v>2</v>
       </c>
-      <c r="AR28" s="42" t="s">
+      <c r="AR28" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -25887,7 +25888,7 @@
       <c r="AQ29">
         <v>2</v>
       </c>
-      <c r="AR29" s="42" t="s">
+      <c r="AR29" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26060,7 +26061,7 @@
       <c r="AQ30">
         <v>2</v>
       </c>
-      <c r="AR30" s="42" t="s">
+      <c r="AR30" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26233,7 +26234,7 @@
       <c r="AQ31">
         <v>2</v>
       </c>
-      <c r="AR31" s="42" t="s">
+      <c r="AR31" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26406,7 +26407,7 @@
         <f t="shared" ref="AP33:AP42" si="14">AP22</f>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR33" s="42" t="s">
+      <c r="AR33" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26574,7 +26575,7 @@
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR34" s="42" t="s">
+      <c r="AR34" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26742,10 +26743,10 @@
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR35" s="42" t="s">
+      <c r="AR35" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="AS35" s="42" t="s">
+      <c r="AS35" s="43" t="s">
         <v>342</v>
       </c>
       <c r="AT35" t="s">
@@ -26753,7 +26754,7 @@
       </c>
     </row>
     <row r="36" spans="1:46">
-      <c r="A36" s="2">
+      <c r="A36" s="19">
         <v>0.1</v>
       </c>
       <c r="B36" t="str">
@@ -26916,12 +26917,12 @@
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR36" s="42" t="s">
+      <c r="AR36" s="43" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:46">
-      <c r="A37" s="2">
+      <c r="A37" s="19">
         <v>0.1</v>
       </c>
       <c r="B37" t="str">
@@ -27084,12 +27085,12 @@
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR37" s="42" t="s">
+      <c r="AR37" s="43" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:46">
-      <c r="A38" s="2">
+      <c r="A38" s="19">
         <v>0.1</v>
       </c>
       <c r="B38" t="str">
@@ -27104,143 +27105,143 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <f>IF(E12="","",-E12)</f>
         <v>-0.057</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <f t="shared" ref="F38:AM39" si="19">IF(F12="","",-F12)</f>
         <v>-0.287</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="20">
         <f t="shared" si="19"/>
         <v>-0.506</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="20">
         <f t="shared" si="19"/>
         <v>-0.564</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <f t="shared" si="19"/>
         <v>-0.842</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="20">
         <f t="shared" si="19"/>
         <v>-0.436</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="M38" s="19">
+      <c r="M38" s="20">
         <f t="shared" si="19"/>
         <v>-0.711</v>
       </c>
-      <c r="N38" s="19">
+      <c r="N38" s="20">
         <f t="shared" si="19"/>
         <v>-0.77</v>
       </c>
-      <c r="O38" s="19">
+      <c r="O38" s="20">
         <f t="shared" si="19"/>
         <v>-0.834</v>
       </c>
-      <c r="P38" s="19">
+      <c r="P38" s="20">
         <f t="shared" si="19"/>
         <v>-0.769</v>
       </c>
-      <c r="Q38" s="19">
+      <c r="Q38" s="20">
         <f t="shared" si="19"/>
         <v>-0.587</v>
       </c>
-      <c r="R38" s="19">
+      <c r="R38" s="20">
         <f t="shared" si="19"/>
         <v>-0.879</v>
       </c>
-      <c r="S38" s="19" t="str">
+      <c r="S38" s="20" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="T38" s="19">
+      <c r="T38" s="20">
         <f t="shared" si="19"/>
         <v>-0.655</v>
       </c>
-      <c r="U38" s="19">
+      <c r="U38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="V38" s="19">
+      <c r="V38" s="20">
         <f t="shared" si="19"/>
         <v>-0.751</v>
       </c>
-      <c r="W38" s="19">
+      <c r="W38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="X38" s="19">
+      <c r="X38" s="20">
         <f t="shared" si="19"/>
         <v>-0.462</v>
       </c>
-      <c r="Y38" s="19">
+      <c r="Y38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="Z38" s="19">
+      <c r="Z38" s="20">
         <f t="shared" si="19"/>
         <v>-0.644</v>
       </c>
-      <c r="AA38" s="19">
+      <c r="AA38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AB38" s="19">
+      <c r="AB38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AC38" s="19">
+      <c r="AC38" s="20">
         <f t="shared" si="19"/>
         <v>-0.564</v>
       </c>
-      <c r="AD38" s="19">
+      <c r="AD38" s="20">
         <f t="shared" si="19"/>
         <v>-0.107</v>
       </c>
-      <c r="AE38" s="19" t="str">
+      <c r="AE38" s="20" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AF38" s="19">
+      <c r="AF38" s="20">
         <f t="shared" si="19"/>
         <v>-0.189</v>
       </c>
-      <c r="AG38" s="19">
+      <c r="AG38" s="20">
         <f t="shared" si="19"/>
         <v>-0.727</v>
       </c>
-      <c r="AH38" s="19">
+      <c r="AH38" s="20">
         <f t="shared" si="19"/>
         <v>-0.476</v>
       </c>
-      <c r="AI38" s="19">
+      <c r="AI38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="AJ38" s="19">
+      <c r="AJ38" s="20">
         <f t="shared" si="19"/>
         <v>-0.56</v>
       </c>
-      <c r="AK38" s="19">
+      <c r="AK38" s="20">
         <f t="shared" si="19"/>
         <v>-0.77</v>
       </c>
-      <c r="AL38" s="19">
+      <c r="AL38" s="20">
         <f t="shared" si="19"/>
         <v>-0.41</v>
       </c>
-      <c r="AM38" s="19">
+      <c r="AM38" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
@@ -27252,12 +27253,12 @@
         <f t="shared" si="14"/>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR38" s="42" t="s">
+      <c r="AR38" s="43" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:46">
-      <c r="A39" s="2">
+      <c r="A39" s="19">
         <v>0.1</v>
       </c>
       <c r="B39" t="str">
@@ -27272,143 +27273,143 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <f t="shared" ref="E39:AG39" si="20">IF(E13="","",-E13)</f>
         <v>-0.777</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <f t="shared" si="20"/>
         <v>-0.47</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="20">
         <f t="shared" si="20"/>
         <v>-0.724</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="20">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="20">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="20">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="20">
         <f t="shared" si="20"/>
         <v>-0.922</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="20">
         <f t="shared" si="20"/>
         <v>-0.587</v>
       </c>
-      <c r="M39" s="19">
+      <c r="M39" s="20">
         <f t="shared" si="20"/>
         <v>-0.578</v>
       </c>
-      <c r="N39" s="19">
+      <c r="N39" s="20">
         <f t="shared" si="20"/>
         <v>-0.544</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="20">
         <f t="shared" si="20"/>
         <v>-0.391</v>
       </c>
-      <c r="P39" s="19">
+      <c r="P39" s="20">
         <f t="shared" si="20"/>
         <v>-0.625</v>
       </c>
-      <c r="Q39" s="19">
+      <c r="Q39" s="20">
         <f t="shared" si="20"/>
         <v>-0.597</v>
       </c>
-      <c r="R39" s="19">
+      <c r="R39" s="20">
         <f t="shared" si="20"/>
         <v>-0.431</v>
       </c>
-      <c r="S39" s="19" t="str">
+      <c r="S39" s="20" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="T39" s="19">
+      <c r="T39" s="20">
         <f t="shared" si="20"/>
         <v>-0.707</v>
       </c>
-      <c r="U39" s="19">
+      <c r="U39" s="20">
         <f t="shared" si="20"/>
         <v>-0.604</v>
       </c>
-      <c r="V39" s="19">
+      <c r="V39" s="20">
         <f t="shared" si="20"/>
         <v>-0.509</v>
       </c>
-      <c r="W39" s="19">
+      <c r="W39" s="20">
         <f t="shared" si="20"/>
         <v>-0.9</v>
       </c>
-      <c r="X39" s="19">
+      <c r="X39" s="20">
         <f t="shared" si="20"/>
         <v>-0.777</v>
       </c>
-      <c r="Y39" s="19">
+      <c r="Y39" s="20">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="Z39" s="19">
+      <c r="Z39" s="20">
         <f t="shared" si="20"/>
         <v>-0.568</v>
       </c>
-      <c r="AA39" s="19">
+      <c r="AA39" s="20">
         <f t="shared" si="20"/>
         <v>-0.95</v>
       </c>
-      <c r="AB39" s="19">
+      <c r="AB39" s="20">
         <f t="shared" si="20"/>
         <v>-0.522</v>
       </c>
-      <c r="AC39" s="19">
+      <c r="AC39" s="20">
         <f t="shared" si="20"/>
         <v>-0.7</v>
       </c>
-      <c r="AD39" s="19">
+      <c r="AD39" s="20">
         <f t="shared" si="20"/>
         <v>-0.637</v>
       </c>
-      <c r="AE39" s="19" t="str">
+      <c r="AE39" s="20" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AF39" s="19">
+      <c r="AF39" s="20">
         <f t="shared" si="20"/>
         <v>-0.671</v>
       </c>
-      <c r="AG39" s="19">
+      <c r="AG39" s="20">
         <f t="shared" si="20"/>
         <v>-0.575</v>
       </c>
-      <c r="AH39" s="19">
+      <c r="AH39" s="20">
         <f t="shared" si="19"/>
         <v>-0.351</v>
       </c>
-      <c r="AI39" s="19" t="str">
+      <c r="AI39" s="20" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AJ39" s="19">
+      <c r="AJ39" s="20">
         <f t="shared" si="19"/>
         <v>-0.679</v>
       </c>
-      <c r="AK39" s="19">
+      <c r="AK39" s="20">
         <f t="shared" si="19"/>
         <v>-0.539</v>
       </c>
-      <c r="AL39" s="19">
+      <c r="AL39" s="20">
         <f t="shared" si="19"/>
         <v>-0.319</v>
       </c>
-      <c r="AM39" s="19">
+      <c r="AM39" s="20">
         <f t="shared" si="19"/>
         <v>-0.695</v>
       </c>
@@ -27420,7 +27421,7 @@
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR39" s="42" t="s">
+      <c r="AR39" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27588,7 +27589,7 @@
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR40" s="42" t="s">
+      <c r="AR40" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27756,7 +27757,7 @@
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR41" s="42" t="s">
+      <c r="AR41" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27924,7 +27925,7 @@
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR42" s="42" t="s">
+      <c r="AR42" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -28950,8 +28951,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:39">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:39">
+      <c r="A14" s="2" t="s">
         <v>354</v>
       </c>
     </row>
@@ -30866,9 +30867,6 @@
     <row r="34" spans="1:41">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -30906,6 +30904,9 @@
     </row>
     <row r="35" spans="1:41">
       <c r="B35" s="5"/>
+      <c r="C35" s="6" t="s">
+        <v>354</v>
+      </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -90,38 +90,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>xli9</author>
-  </authors>
-  <commentList>
-    <comment ref="A36" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>xli9:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-original Amit’s version is vacant/empty, then some nclear can have ca[acity but zero activity, that is not reasonable so we set as 0.1</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>xli9</author>
@@ -1597,18 +1565,18 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -26264,139 +26232,139 @@
         <v>-0.0042</v>
       </c>
       <c r="F33" s="16">
-        <f t="shared" ref="F33:AM37" si="13">IF(F7="","",-MIN(F7,F2,0.8)*$A33)</f>
+        <f>IF(F7="","",-MIN(F7,F2,0.8)*$A33)</f>
         <v>-0.0525</v>
       </c>
       <c r="G33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(G7="","",-MIN(G7,G2,0.8)*$A33)</f>
         <v>-0.1218</v>
       </c>
       <c r="H33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(H7="","",-MIN(H7,H2,0.8)*$A33)</f>
         <v>-0.1287</v>
       </c>
       <c r="I33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(I7="","",-MIN(I7,I2,0.8)*$A33)</f>
         <v>-0.1668</v>
       </c>
       <c r="J33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(J7="","",-MIN(J7,J2,0.8)*$A33)</f>
         <v>-0.24</v>
       </c>
       <c r="K33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(K7="","",-MIN(K7,K2,0.8)*$A33)</f>
         <v>-0.1089</v>
       </c>
       <c r="L33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(L7="","",-MIN(L7,L2,0.8)*$A33)</f>
         <v>-0.24</v>
       </c>
       <c r="M33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(M7="","",-MIN(M7,M2,0.8)*$A33)</f>
         <v>-0.165</v>
       </c>
       <c r="N33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(N7="","",-MIN(N7,N2,0.8)*$A33)</f>
         <v>-0.2106</v>
       </c>
       <c r="O33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(O7="","",-MIN(O7,O2,0.8)*$A33)</f>
         <v>-0.2085</v>
       </c>
       <c r="P33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(P7="","",-MIN(P7,P2,0.8)*$A33)</f>
         <v>-0.1767</v>
       </c>
       <c r="Q33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(Q7="","",-MIN(Q7,Q2,0.8)*$A33)</f>
         <v>-0.1407</v>
       </c>
       <c r="R33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(R7="","",-MIN(R7,R2,0.8)*$A33)</f>
         <v>-0.1467</v>
       </c>
       <c r="S33" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f>IF(S7="","",-MIN(S7,S2,0.8)*$A33)</f>
         <v/>
       </c>
       <c r="T33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(T7="","",-MIN(T7,T2,0.8)*$A33)</f>
         <v>-0.0921</v>
       </c>
       <c r="U33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(U7="","",-MIN(U7,U2,0.8)*$A33)</f>
         <v>-0.24</v>
       </c>
       <c r="V33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(V7="","",-MIN(V7,V2,0.8)*$A33)</f>
         <v>-0.1872</v>
       </c>
       <c r="W33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(W7="","",-MIN(W7,W2,0.8)*$A33)</f>
         <v>-0.24</v>
       </c>
       <c r="X33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(X7="","",-MIN(X7,X2,0.8)*$A33)</f>
         <v>-0.1044</v>
       </c>
       <c r="Y33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(Y7="","",-MIN(Y7,Y2,0.8)*$A33)</f>
         <v>-0.0882</v>
       </c>
       <c r="Z33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(Z7="","",-MIN(Z7,Z2,0.8)*$A33)</f>
         <v>-0.1641</v>
       </c>
       <c r="AA33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AA7="","",-MIN(AA7,AA2,0.8)*$A33)</f>
         <v>-0.0855</v>
       </c>
       <c r="AB33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AB7="","",-MIN(AB7,AB2,0.8)*$A33)</f>
         <v>-0.2232</v>
       </c>
       <c r="AC33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AC7="","",-MIN(AC7,AC2,0.8)*$A33)</f>
         <v>-0.1248</v>
       </c>
       <c r="AD33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AD7="","",-MIN(AD7,AD2,0.8)*$A33)</f>
         <v>-0.0153</v>
       </c>
       <c r="AE33" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f>IF(AE7="","",-MIN(AE7,AE2,0.8)*$A33)</f>
         <v/>
       </c>
       <c r="AF33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AF7="","",-MIN(AF7,AF2,0.8)*$A33)</f>
         <v>-0.0435</v>
       </c>
       <c r="AG33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AG7="","",-MIN(AG7,AG2,0.8)*$A33)</f>
         <v>-0.1812</v>
       </c>
       <c r="AH33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AH7="","",-MIN(AH7,AH2,0.8)*$A33)</f>
         <v>-0.1155</v>
       </c>
       <c r="AI33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AI7="","",-MIN(AI7,AI2,0.8)*$A33)</f>
         <v>-0.24</v>
       </c>
       <c r="AJ33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AJ7="","",-MIN(AJ7,AJ2,0.8)*$A33)</f>
         <v>-0.135</v>
       </c>
       <c r="AK33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AK7="","",-MIN(AK7,AK2,0.8)*$A33)</f>
         <v>-0.1737</v>
       </c>
       <c r="AL33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AL7="","",-MIN(AL7,AL2,0.8)*$A33)</f>
         <v>-0.0513</v>
       </c>
       <c r="AM33" s="16">
-        <f t="shared" si="13"/>
+        <f>IF(AM7="","",-MIN(AM7,AM2,0.8)*$A33)</f>
         <v>-0.0684</v>
       </c>
       <c r="AO33" s="16" t="str">
@@ -26404,7 +26372,7 @@
         <v>ELE,CHP</v>
       </c>
       <c r="AP33" s="16" t="str">
-        <f t="shared" ref="AP33:AP42" si="14">AP22</f>
+        <f t="shared" ref="AP33:AP42" si="13">AP22</f>
         <v>elcbsl,indbio</v>
       </c>
       <c r="AR33" s="43" t="s">
@@ -26416,163 +26384,163 @@
         <v>0.3</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" ref="B34:C42" si="15">B23</f>
+        <f t="shared" ref="B34:C42" si="14">B23</f>
         <v>UCE_utilization_coal_LO</v>
       </c>
       <c r="C34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>LO</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:D42" si="16">D23+7</f>
+        <f t="shared" ref="D34:D42" si="15">D23+7</f>
         <v>2030</v>
       </c>
       <c r="E34" s="16">
-        <f t="shared" ref="E34:AG37" si="17">IF(E8="","",-MIN(E8,E3,0.8)*$A34)</f>
+        <f t="shared" ref="E34:AG37" si="16">IF(E8="","",-MIN(E8,E3,0.8)*$A34)</f>
         <v>-0.171</v>
       </c>
       <c r="F34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1815</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0831</v>
       </c>
       <c r="I34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.24</v>
       </c>
       <c r="J34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0753</v>
       </c>
       <c r="K34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1527</v>
       </c>
       <c r="L34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1545</v>
       </c>
       <c r="M34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1104</v>
       </c>
       <c r="N34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1284</v>
       </c>
       <c r="O34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0282</v>
       </c>
       <c r="P34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0984</v>
       </c>
       <c r="Q34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0561</v>
       </c>
       <c r="R34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0804</v>
       </c>
       <c r="S34" s="16" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="T34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1734</v>
       </c>
       <c r="U34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0189</v>
       </c>
       <c r="V34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0591</v>
       </c>
       <c r="W34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.2022</v>
       </c>
       <c r="X34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1494</v>
       </c>
       <c r="Y34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1155</v>
       </c>
       <c r="Z34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1152</v>
       </c>
       <c r="AA34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.24</v>
       </c>
       <c r="AB34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1236</v>
       </c>
       <c r="AC34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1671</v>
       </c>
       <c r="AD34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.126</v>
       </c>
       <c r="AE34" s="16" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AF34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.1422</v>
       </c>
       <c r="AG34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.0375</v>
       </c>
       <c r="AH34" s="16">
+        <f>IF(AH8="","",-MIN(AH8,AH3,0.8)*$A34)</f>
+        <v>-0.0498</v>
+      </c>
+      <c r="AI34" s="16" t="str">
+        <f>IF(AI8="","",-MIN(AI8,AI3,0.8)*$A34)</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="16">
+        <f>IF(AJ8="","",-MIN(AJ8,AJ3,0.8)*$A34)</f>
+        <v>-0.1704</v>
+      </c>
+      <c r="AK34" s="16">
+        <f>IF(AK8="","",-MIN(AK8,AK3,0.8)*$A34)</f>
+        <v>-0.0246</v>
+      </c>
+      <c r="AL34" s="16">
+        <f>IF(AL8="","",-MIN(AL8,AL3,0.8)*$A34)</f>
+        <v>0</v>
+      </c>
+      <c r="AM34" s="16">
+        <f>IF(AM8="","",-MIN(AM8,AM3,0.8)*$A34)</f>
+        <v>-0.177</v>
+      </c>
+      <c r="AO34" s="16" t="str">
+        <f t="shared" ref="AO34:AO42" si="17">AO23</f>
+        <v>ELE,CHP</v>
+      </c>
+      <c r="AP34" s="16" t="str">
         <f t="shared" si="13"/>
-        <v>-0.0498</v>
-      </c>
-      <c r="AI34" s="16" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AJ34" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.1704</v>
-      </c>
-      <c r="AK34" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0246</v>
-      </c>
-      <c r="AL34" s="16">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AM34" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.177</v>
-      </c>
-      <c r="AO34" s="16" t="str">
-        <f t="shared" ref="AO34:AO42" si="18">AO23</f>
-        <v>ELE,CHP</v>
-      </c>
-      <c r="AP34" s="16" t="str">
-        <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
       <c r="AR34" s="43" t="s">
@@ -26584,163 +26552,163 @@
         <v>0.3</v>
       </c>
       <c r="B35" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_gas_LO</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="14"/>
+        <v>LO</v>
+      </c>
+      <c r="D35">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_gas_LO</v>
-      </c>
-      <c r="C35" t="str">
-        <f t="shared" si="15"/>
-        <v>LO</v>
-      </c>
-      <c r="D35">
+        <v>2030</v>
+      </c>
+      <c r="E35" s="16">
         <f t="shared" si="16"/>
-        <v>2030</v>
-      </c>
-      <c r="E35" s="16">
+        <v>-0.1119</v>
+      </c>
+      <c r="F35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0954</v>
+      </c>
+      <c r="G35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0591</v>
+      </c>
+      <c r="H35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0381</v>
+      </c>
+      <c r="I35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0189</v>
+      </c>
+      <c r="J35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0936</v>
+      </c>
+      <c r="K35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0696</v>
+      </c>
+      <c r="L35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0777</v>
+      </c>
+      <c r="M35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.087</v>
+      </c>
+      <c r="N35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0264</v>
+      </c>
+      <c r="O35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0189</v>
+      </c>
+      <c r="P35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0762</v>
+      </c>
+      <c r="Q35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0462</v>
+      </c>
+      <c r="R35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0492</v>
+      </c>
+      <c r="S35" s="16" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="T35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0495</v>
+      </c>
+      <c r="U35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0966</v>
+      </c>
+      <c r="V35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0474</v>
+      </c>
+      <c r="W35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1395</v>
+      </c>
+      <c r="X35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1056</v>
+      </c>
+      <c r="Y35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1167</v>
+      </c>
+      <c r="Z35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0942</v>
+      </c>
+      <c r="AA35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0138</v>
+      </c>
+      <c r="AB35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1116</v>
+      </c>
+      <c r="AC35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1371</v>
+      </c>
+      <c r="AD35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1425</v>
+      </c>
+      <c r="AE35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.1158</v>
+      </c>
+      <c r="AF35" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG35" s="16">
+        <f t="shared" si="16"/>
+        <v>-0.0585</v>
+      </c>
+      <c r="AH35" s="16">
+        <f>IF(AH9="","",-MIN(AH9,AH4,0.8)*$A35)</f>
+        <v>-0.0144</v>
+      </c>
+      <c r="AI35" s="16">
+        <f>IF(AI9="","",-MIN(AI9,AI4,0.8)*$A35)</f>
+        <v>-0.0714</v>
+      </c>
+      <c r="AJ35" s="16">
+        <f>IF(AJ9="","",-MIN(AJ9,AJ4,0.8)*$A35)</f>
+        <v>-0.0681</v>
+      </c>
+      <c r="AK35" s="16">
+        <f>IF(AK9="","",-MIN(AK9,AK4,0.8)*$A35)</f>
+        <v>-0.0903</v>
+      </c>
+      <c r="AL35" s="16">
+        <f>IF(AL9="","",-MIN(AL9,AL4,0.8)*$A35)</f>
+        <v>-0.042</v>
+      </c>
+      <c r="AM35" s="16">
+        <f>IF(AM9="","",-MIN(AM9,AM4,0.8)*$A35)</f>
+        <v>-0.0186</v>
+      </c>
+      <c r="AO35" s="16" t="str">
         <f t="shared" si="17"/>
-        <v>-0.1119</v>
-      </c>
-      <c r="F35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0954</v>
-      </c>
-      <c r="G35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0591</v>
-      </c>
-      <c r="H35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0381</v>
-      </c>
-      <c r="I35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0189</v>
-      </c>
-      <c r="J35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0936</v>
-      </c>
-      <c r="K35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0696</v>
-      </c>
-      <c r="L35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0777</v>
-      </c>
-      <c r="M35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.087</v>
-      </c>
-      <c r="N35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0264</v>
-      </c>
-      <c r="O35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0189</v>
-      </c>
-      <c r="P35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0762</v>
-      </c>
-      <c r="Q35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0462</v>
-      </c>
-      <c r="R35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0492</v>
-      </c>
-      <c r="S35" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="T35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0495</v>
-      </c>
-      <c r="U35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0966</v>
-      </c>
-      <c r="V35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0474</v>
-      </c>
-      <c r="W35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1395</v>
-      </c>
-      <c r="X35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1056</v>
-      </c>
-      <c r="Y35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1167</v>
-      </c>
-      <c r="Z35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0942</v>
-      </c>
-      <c r="AA35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0138</v>
-      </c>
-      <c r="AB35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1116</v>
-      </c>
-      <c r="AC35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1371</v>
-      </c>
-      <c r="AD35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1425</v>
-      </c>
-      <c r="AE35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.1158</v>
-      </c>
-      <c r="AF35" s="16">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AG35" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0585</v>
-      </c>
-      <c r="AH35" s="16">
+        <v>ELE,CHP</v>
+      </c>
+      <c r="AP35" s="16" t="str">
         <f t="shared" si="13"/>
-        <v>-0.0144</v>
-      </c>
-      <c r="AI35" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0714</v>
-      </c>
-      <c r="AJ35" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0681</v>
-      </c>
-      <c r="AK35" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0903</v>
-      </c>
-      <c r="AL35" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.042</v>
-      </c>
-      <c r="AM35" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0186</v>
-      </c>
-      <c r="AO35" s="16" t="str">
-        <f t="shared" si="18"/>
-        <v>ELE,CHP</v>
-      </c>
-      <c r="AP35" s="16" t="str">
-        <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
       <c r="AR35" s="43" t="s">
@@ -26754,167 +26722,60 @@
       </c>
     </row>
     <row r="36" spans="1:46">
-      <c r="A36" s="19">
-        <v>0.1</v>
-      </c>
+      <c r="A36" s="19"/>
       <c r="B36" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_nuclear_LO</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="14"/>
+        <v>LO</v>
+      </c>
+      <c r="D36">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_nuclear_LO</v>
-      </c>
-      <c r="C36" t="str">
-        <f t="shared" si="15"/>
-        <v>LO</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E36" s="16" t="str">
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="16"/>
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="16"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="16"/>
+      <c r="AI36" s="16"/>
+      <c r="AJ36" s="16"/>
+      <c r="AK36" s="16"/>
+      <c r="AL36" s="16"/>
+      <c r="AM36" s="16"/>
+      <c r="AO36" s="16" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="G36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="H36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="I36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="J36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0537</v>
-      </c>
-      <c r="K36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="L36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.072</v>
-      </c>
-      <c r="M36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="N36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0712</v>
-      </c>
-      <c r="O36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0548</v>
-      </c>
-      <c r="P36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="Q36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="R36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="S36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="T36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.063</v>
-      </c>
-      <c r="U36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="V36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="W36" s="16">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0397</v>
-      </c>
-      <c r="Y36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0377</v>
-      </c>
-      <c r="Z36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="AA36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AB36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AC36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0705</v>
-      </c>
-      <c r="AD36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0786</v>
-      </c>
-      <c r="AE36" s="16" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AF36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0526</v>
-      </c>
-      <c r="AG36" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="AH36" s="16">
+        <v>ELE,CHP</v>
+      </c>
+      <c r="AP36" s="16" t="str">
         <f t="shared" si="13"/>
-        <v>-0.073</v>
-      </c>
-      <c r="AI36" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0699</v>
-      </c>
-      <c r="AJ36" s="16" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AK36" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.062</v>
-      </c>
-      <c r="AL36" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0512</v>
-      </c>
-      <c r="AM36" s="16" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AO36" s="16" t="str">
-        <f t="shared" si="18"/>
-        <v>ELE,CHP</v>
-      </c>
-      <c r="AP36" s="16" t="str">
-        <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
       <c r="AR36" s="43" t="s">
@@ -26922,167 +26783,60 @@
       </c>
     </row>
     <row r="37" spans="1:46">
-      <c r="A37" s="19">
-        <v>0.1</v>
-      </c>
+      <c r="A37" s="19"/>
       <c r="B37" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_oil_\I: LO</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="14"/>
+        <v>\I: LO</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_oil_\I: LO</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="15"/>
-        <v>\I: LO</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="16"/>
+      <c r="AK37" s="16"/>
+      <c r="AL37" s="16"/>
+      <c r="AM37" s="16"/>
+      <c r="AO37" s="16" t="str">
         <f t="shared" si="17"/>
-        <v>-0.0367</v>
-      </c>
-      <c r="F37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0146</v>
-      </c>
-      <c r="G37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.021</v>
-      </c>
-      <c r="H37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0463</v>
-      </c>
-      <c r="I37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.021</v>
-      </c>
-      <c r="J37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="K37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.016</v>
-      </c>
-      <c r="L37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.052</v>
-      </c>
-      <c r="M37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0003</v>
-      </c>
-      <c r="N37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="O37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0571</v>
-      </c>
-      <c r="P37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="Q37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0301</v>
-      </c>
-      <c r="R37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.007</v>
-      </c>
-      <c r="S37" s="16">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="T37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0021</v>
-      </c>
-      <c r="U37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0111</v>
-      </c>
-      <c r="V37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0782</v>
-      </c>
-      <c r="W37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0089</v>
-      </c>
-      <c r="X37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0221</v>
-      </c>
-      <c r="Y37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0616</v>
-      </c>
-      <c r="Z37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0117</v>
-      </c>
-      <c r="AA37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0632</v>
-      </c>
-      <c r="AB37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="AC37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.02</v>
-      </c>
-      <c r="AD37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.08</v>
-      </c>
-      <c r="AE37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0629</v>
-      </c>
-      <c r="AF37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0001</v>
-      </c>
-      <c r="AG37" s="16">
-        <f t="shared" si="17"/>
-        <v>-0.0374</v>
-      </c>
-      <c r="AH37" s="16">
+        <v>ELE,CHP</v>
+      </c>
+      <c r="AP37" s="16" t="str">
         <f t="shared" si="13"/>
-        <v>-0.01</v>
-      </c>
-      <c r="AI37" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.026</v>
-      </c>
-      <c r="AJ37" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0059</v>
-      </c>
-      <c r="AK37" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.022</v>
-      </c>
-      <c r="AL37" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.08</v>
-      </c>
-      <c r="AM37" s="16">
-        <f t="shared" si="13"/>
-        <v>-0.0103</v>
-      </c>
-      <c r="AO37" s="16" t="str">
-        <f t="shared" si="18"/>
-        <v>ELE,CHP</v>
-      </c>
-      <c r="AP37" s="16" t="str">
-        <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
       <c r="AR37" s="43" t="s">
@@ -27090,19 +26844,17 @@
       </c>
     </row>
     <row r="38" spans="1:46">
-      <c r="A38" s="19">
-        <v>0.1</v>
-      </c>
+      <c r="A38" s="19"/>
       <c r="B38" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_bioenergy_UP</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="14"/>
+        <v>UP</v>
+      </c>
+      <c r="D38">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_bioenergy_UP</v>
-      </c>
-      <c r="C38" t="str">
-        <f t="shared" si="15"/>
-        <v>UP</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
       <c r="E38" s="20">
@@ -27110,315 +26862,313 @@
         <v>-0.057</v>
       </c>
       <c r="F38" s="20">
-        <f t="shared" ref="F38:AM39" si="19">IF(F12="","",-F12)</f>
+        <f t="shared" ref="F38:AM39" si="18">IF(F12="","",-F12)</f>
         <v>-0.287</v>
       </c>
       <c r="G38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.506</v>
+      </c>
+      <c r="H38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.564</v>
+      </c>
+      <c r="I38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.842</v>
+      </c>
+      <c r="J38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="K38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.436</v>
+      </c>
+      <c r="L38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="M38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.711</v>
+      </c>
+      <c r="N38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.77</v>
+      </c>
+      <c r="O38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.834</v>
+      </c>
+      <c r="P38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.769</v>
+      </c>
+      <c r="Q38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.587</v>
+      </c>
+      <c r="R38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.879</v>
+      </c>
+      <c r="S38" s="20" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="T38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.655</v>
+      </c>
+      <c r="U38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="V38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.751</v>
+      </c>
+      <c r="W38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="X38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.462</v>
+      </c>
+      <c r="Y38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="Z38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.644</v>
+      </c>
+      <c r="AA38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="AB38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="AC38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.564</v>
+      </c>
+      <c r="AD38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.107</v>
+      </c>
+      <c r="AE38" s="20" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AF38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.189</v>
+      </c>
+      <c r="AG38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.727</v>
+      </c>
+      <c r="AH38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.476</v>
+      </c>
+      <c r="AI38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="AJ38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.56</v>
+      </c>
+      <c r="AK38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.77</v>
+      </c>
+      <c r="AL38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.41</v>
+      </c>
+      <c r="AM38" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.95</v>
+      </c>
+      <c r="AO38" s="16" t="str">
+        <f t="shared" si="17"/>
+        <v>ELE,CHP</v>
+      </c>
+      <c r="AP38" s="16" t="str">
+        <f t="shared" si="13"/>
+        <v>elcbsl,indbio</v>
+      </c>
+      <c r="AR38" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:46">
+      <c r="A39" s="19"/>
+      <c r="B39" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_coal_UP</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="14"/>
+        <v>UP</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="15"/>
+        <v>2030</v>
+      </c>
+      <c r="E39" s="20">
+        <f t="shared" ref="E39:AG39" si="19">IF(E13="","",-E13)</f>
+        <v>-0.777</v>
+      </c>
+      <c r="F39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.506</v>
-      </c>
-      <c r="H38" s="20">
+        <v>-0.47</v>
+      </c>
+      <c r="G39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.564</v>
-      </c>
-      <c r="I38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.842</v>
-      </c>
-      <c r="J38" s="20">
+        <v>-0.724</v>
+      </c>
+      <c r="H39" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="K38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.436</v>
-      </c>
-      <c r="L38" s="20">
+      <c r="I39" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="M38" s="20">
+      <c r="J39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.711</v>
-      </c>
-      <c r="N38" s="20">
+        <v>-0.95</v>
+      </c>
+      <c r="K39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.77</v>
-      </c>
-      <c r="O38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.834</v>
-      </c>
-      <c r="P38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.769</v>
-      </c>
-      <c r="Q38" s="20">
+        <v>-0.922</v>
+      </c>
+      <c r="L39" s="20">
         <f t="shared" si="19"/>
         <v>-0.587</v>
       </c>
-      <c r="R38" s="20">
+      <c r="M39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.879</v>
-      </c>
-      <c r="S38" s="20" t="str">
+        <v>-0.578</v>
+      </c>
+      <c r="N39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.544</v>
+      </c>
+      <c r="O39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.391</v>
+      </c>
+      <c r="P39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.625</v>
+      </c>
+      <c r="Q39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.597</v>
+      </c>
+      <c r="R39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.431</v>
+      </c>
+      <c r="S39" s="20" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="T38" s="20">
+      <c r="T39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.655</v>
-      </c>
-      <c r="U38" s="20">
+        <v>-0.707</v>
+      </c>
+      <c r="U39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.604</v>
+      </c>
+      <c r="V39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.509</v>
+      </c>
+      <c r="W39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.9</v>
+      </c>
+      <c r="X39" s="20">
+        <f t="shared" si="19"/>
+        <v>-0.777</v>
+      </c>
+      <c r="Y39" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="V38" s="20">
+      <c r="Z39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.751</v>
-      </c>
-      <c r="W38" s="20">
+        <v>-0.568</v>
+      </c>
+      <c r="AA39" s="20">
         <f t="shared" si="19"/>
         <v>-0.95</v>
       </c>
-      <c r="X38" s="20">
+      <c r="AB39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.462</v>
-      </c>
-      <c r="Y38" s="20">
+        <v>-0.522</v>
+      </c>
+      <c r="AC39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.95</v>
-      </c>
-      <c r="Z38" s="20">
+        <v>-0.7</v>
+      </c>
+      <c r="AD39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.644</v>
-      </c>
-      <c r="AA38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AB38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AC38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.564</v>
-      </c>
-      <c r="AD38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.107</v>
-      </c>
-      <c r="AE38" s="20" t="str">
+        <v>-0.637</v>
+      </c>
+      <c r="AE39" s="20" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AF38" s="20">
+      <c r="AF39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.189</v>
-      </c>
-      <c r="AG38" s="20">
+        <v>-0.671</v>
+      </c>
+      <c r="AG39" s="20">
         <f t="shared" si="19"/>
-        <v>-0.727</v>
-      </c>
-      <c r="AH38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.476</v>
-      </c>
-      <c r="AI38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AJ38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.56</v>
-      </c>
-      <c r="AK38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.77</v>
-      </c>
-      <c r="AL38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.41</v>
-      </c>
-      <c r="AM38" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AO38" s="16" t="str">
+        <v>-0.575</v>
+      </c>
+      <c r="AH39" s="20">
         <f t="shared" si="18"/>
+        <v>-0.351</v>
+      </c>
+      <c r="AI39" s="20" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AJ39" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.679</v>
+      </c>
+      <c r="AK39" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.539</v>
+      </c>
+      <c r="AL39" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.319</v>
+      </c>
+      <c r="AM39" s="20">
+        <f t="shared" si="18"/>
+        <v>-0.695</v>
+      </c>
+      <c r="AO39" s="16" t="str">
+        <f t="shared" si="17"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP38" s="16" t="str">
-        <f t="shared" si="14"/>
-        <v>elcbsl,indbio</v>
-      </c>
-      <c r="AR38" s="43" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:46">
-      <c r="A39" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="B39" t="str">
-        <f t="shared" si="15"/>
-        <v>UCE_utilization_coal_UP</v>
-      </c>
-      <c r="C39" t="str">
-        <f t="shared" si="15"/>
-        <v>UP</v>
-      </c>
-      <c r="D39">
-        <f t="shared" si="16"/>
-        <v>2030</v>
-      </c>
-      <c r="E39" s="20">
-        <f t="shared" ref="E39:AG39" si="20">IF(E13="","",-E13)</f>
-        <v>-0.777</v>
-      </c>
-      <c r="F39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.47</v>
-      </c>
-      <c r="G39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.724</v>
-      </c>
-      <c r="H39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.95</v>
-      </c>
-      <c r="I39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.95</v>
-      </c>
-      <c r="J39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.95</v>
-      </c>
-      <c r="K39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.922</v>
-      </c>
-      <c r="L39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.587</v>
-      </c>
-      <c r="M39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.578</v>
-      </c>
-      <c r="N39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.544</v>
-      </c>
-      <c r="O39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.391</v>
-      </c>
-      <c r="P39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.625</v>
-      </c>
-      <c r="Q39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.597</v>
-      </c>
-      <c r="R39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.431</v>
-      </c>
-      <c r="S39" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="T39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.707</v>
-      </c>
-      <c r="U39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.604</v>
-      </c>
-      <c r="V39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.509</v>
-      </c>
-      <c r="W39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.9</v>
-      </c>
-      <c r="X39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.777</v>
-      </c>
-      <c r="Y39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.95</v>
-      </c>
-      <c r="Z39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.568</v>
-      </c>
-      <c r="AA39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AB39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.522</v>
-      </c>
-      <c r="AC39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.7</v>
-      </c>
-      <c r="AD39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.637</v>
-      </c>
-      <c r="AE39" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="AF39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.671</v>
-      </c>
-      <c r="AG39" s="20">
-        <f t="shared" si="20"/>
-        <v>-0.575</v>
-      </c>
-      <c r="AH39" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.351</v>
-      </c>
-      <c r="AI39" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AJ39" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.679</v>
-      </c>
-      <c r="AK39" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.539</v>
-      </c>
-      <c r="AL39" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.319</v>
-      </c>
-      <c r="AM39" s="20">
-        <f t="shared" si="19"/>
-        <v>-0.695</v>
-      </c>
-      <c r="AO39" s="16" t="str">
-        <f t="shared" si="18"/>
-        <v>ELE,CHP</v>
-      </c>
       <c r="AP39" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>???coa,elccob</v>
       </c>
       <c r="AR39" s="43" t="s">
@@ -27430,15 +27180,15 @@
         <v>0.8</v>
       </c>
       <c r="B40" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_gas_UP</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="14"/>
+        <v>UP</v>
+      </c>
+      <c r="D40">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_gas_UP</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="15"/>
-        <v>UP</v>
-      </c>
-      <c r="D40">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
       <c r="E40">
@@ -27446,147 +27196,147 @@
         <v>-0.8</v>
       </c>
       <c r="F40">
-        <f t="shared" ref="F40:U42" si="21">-$A40</f>
+        <f t="shared" ref="F40:U42" si="20">-$A40</f>
         <v>-0.8</v>
       </c>
       <c r="G40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="V40">
+        <f t="shared" ref="V40:AK42" si="21">-$A40</f>
+        <v>-0.8</v>
+      </c>
+      <c r="W40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="H40">
+      <c r="X40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="I40">
+      <c r="Y40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="J40">
+      <c r="Z40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="K40">
+      <c r="AA40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="L40">
+      <c r="AB40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="M40">
+      <c r="AC40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="N40">
+      <c r="AD40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="O40">
+      <c r="AE40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="P40">
+      <c r="AF40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="Q40">
+      <c r="AG40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="R40">
+      <c r="AH40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="S40">
+      <c r="AI40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="T40">
+      <c r="AJ40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="U40">
+      <c r="AK40">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="V40">
-        <f t="shared" ref="V40:AK42" si="22">-$A40</f>
+      <c r="AL40">
+        <f t="shared" ref="AL40:AM42" si="22">-$A40</f>
         <v>-0.8</v>
       </c>
-      <c r="W40">
+      <c r="AM40">
         <f t="shared" si="22"/>
         <v>-0.8</v>
       </c>
-      <c r="X40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="Y40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="Z40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AA40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AB40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AC40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AD40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AE40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AF40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AG40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AH40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AI40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AJ40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AK40">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AL40">
-        <f t="shared" ref="AL40:AM42" si="23">-$A40</f>
-        <v>-0.8</v>
-      </c>
-      <c r="AM40">
-        <f t="shared" si="23"/>
-        <v>-0.8</v>
-      </c>
       <c r="AO40" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>ELE,CHP</v>
       </c>
       <c r="AP40" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>???nga</v>
       </c>
       <c r="AR40" s="43" t="s">
@@ -27598,163 +27348,163 @@
         <v>0.95</v>
       </c>
       <c r="B41" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_nuclear_UP</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="14"/>
+        <v>UP</v>
+      </c>
+      <c r="D41">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_nuclear_UP</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="15"/>
-        <v>UP</v>
-      </c>
-      <c r="D41">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
       <c r="E41">
-        <f t="shared" ref="E41:E42" si="24">-$A41</f>
+        <f t="shared" ref="E41:E42" si="23">-$A41</f>
         <v>-0.95</v>
       </c>
       <c r="F41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="20"/>
+        <v>-0.95</v>
+      </c>
+      <c r="V41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="G41">
+      <c r="W41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="H41">
+      <c r="X41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="I41">
+      <c r="Y41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="J41">
+      <c r="Z41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="K41">
+      <c r="AA41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="L41">
+      <c r="AB41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="M41">
+      <c r="AC41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="N41">
+      <c r="AD41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="O41">
+      <c r="AE41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="P41">
+      <c r="AF41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="Q41">
+      <c r="AG41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="R41">
+      <c r="AH41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="S41">
+      <c r="AI41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="T41">
+      <c r="AJ41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="U41">
+      <c r="AK41">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="V41">
+      <c r="AL41">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="W41">
+      <c r="AM41">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="X41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="Y41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="Z41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AA41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AB41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AC41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AD41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AE41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AF41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AG41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AH41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AI41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AJ41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AK41">
-        <f t="shared" si="22"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AL41">
-        <f t="shared" si="23"/>
-        <v>-0.95</v>
-      </c>
-      <c r="AM41">
-        <f t="shared" si="23"/>
-        <v>-0.95</v>
-      </c>
       <c r="AO41" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>ELE,CHP</v>
       </c>
       <c r="AP41" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>???nuc</v>
       </c>
       <c r="AR41" s="43" t="s">
@@ -27766,163 +27516,163 @@
         <v>0.8</v>
       </c>
       <c r="B42" t="str">
+        <f t="shared" si="14"/>
+        <v>UCE_utilization_oil_UP</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="14"/>
+        <v>UP</v>
+      </c>
+      <c r="D42">
         <f t="shared" si="15"/>
-        <v>UCE_utilization_oil_UP</v>
-      </c>
-      <c r="C42" t="str">
-        <f t="shared" si="15"/>
-        <v>UP</v>
-      </c>
-      <c r="D42">
-        <f t="shared" si="16"/>
         <v>2030</v>
       </c>
       <c r="E42">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
       <c r="F42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="20"/>
+        <v>-0.8</v>
+      </c>
+      <c r="V42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="G42">
+      <c r="W42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="H42">
+      <c r="X42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="I42">
+      <c r="Y42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="J42">
+      <c r="Z42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="K42">
+      <c r="AA42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="L42">
+      <c r="AB42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="M42">
+      <c r="AC42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="N42">
+      <c r="AD42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="O42">
+      <c r="AE42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="P42">
+      <c r="AF42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="Q42">
+      <c r="AG42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="R42">
+      <c r="AH42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="S42">
+      <c r="AI42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="T42">
+      <c r="AJ42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="U42">
+      <c r="AK42">
         <f t="shared" si="21"/>
         <v>-0.8</v>
       </c>
-      <c r="V42">
+      <c r="AL42">
         <f t="shared" si="22"/>
         <v>-0.8</v>
       </c>
-      <c r="W42">
+      <c r="AM42">
         <f t="shared" si="22"/>
         <v>-0.8</v>
       </c>
-      <c r="X42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="Y42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="Z42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AA42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AB42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AC42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AD42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AE42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AF42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AG42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AH42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AI42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AJ42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AK42">
-        <f t="shared" si="22"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AL42">
-        <f t="shared" si="23"/>
-        <v>-0.8</v>
-      </c>
-      <c r="AM42">
-        <f t="shared" si="23"/>
-        <v>-0.8</v>
-      </c>
       <c r="AO42" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>ELE,CHP</v>
       </c>
       <c r="AP42" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>???oil*</v>
       </c>
       <c r="AR42" s="43" t="s">
@@ -27932,7 +27682,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/SuppXLS/Scen_dem-Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_dem-Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="3" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="12" r:id="rId1"/>
@@ -1561,11 +1561,6 @@
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1574,8 +1569,13 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1596,6 +1596,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1609,12 +1621,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1954,7 +1960,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1974,14 +1980,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1990,87 +1996,87 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
@@ -2078,11 +2084,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2103,25 +2110,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="49"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="49" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="13"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="14"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2139,15 +2153,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="53"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="54"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="16" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="16" applyFont="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="54" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="53" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="24"/>
-    <xf numFmtId="2" fontId="16" fillId="11" borderId="0" xfId="24" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="24"/>
+    <xf numFmtId="2" fontId="16" fillId="12" borderId="0" xfId="24" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="57">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2512,2385 +2527,2385 @@
   <dimension ref="B2:AE92"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.13636363636364" style="35" customWidth="1"/>
-    <col min="2" max="2" width="9.86363636363636" style="35" customWidth="1"/>
-    <col min="3" max="3" width="8.46363636363636" style="35" customWidth="1"/>
-    <col min="4" max="4" width="12.8" style="35" customWidth="1"/>
-    <col min="5" max="5" width="5" style="35" customWidth="1"/>
-    <col min="6" max="6" width="14.2" style="35" customWidth="1"/>
-    <col min="7" max="7" width="6.86363636363636" style="35" customWidth="1"/>
-    <col min="8" max="8" width="10.4636363636364" style="35" customWidth="1"/>
-    <col min="9" max="9" width="8.46363636363636" style="35" customWidth="1"/>
-    <col min="10" max="10" width="5.13636363636364" style="35" customWidth="1"/>
-    <col min="11" max="12" width="5" style="35" customWidth="1"/>
-    <col min="13" max="256" width="11.4636363636364" style="35" customWidth="1"/>
-    <col min="257" max="16384" width="9.13636363636364" style="35"/>
+    <col min="1" max="1" width="9.13636363636364" style="41" customWidth="1"/>
+    <col min="2" max="2" width="9.86363636363636" style="41" customWidth="1"/>
+    <col min="3" max="3" width="8.46363636363636" style="41" customWidth="1"/>
+    <col min="4" max="4" width="12.8" style="41" customWidth="1"/>
+    <col min="5" max="5" width="5" style="41" customWidth="1"/>
+    <col min="6" max="6" width="14.2" style="41" customWidth="1"/>
+    <col min="7" max="7" width="6.86363636363636" style="41" customWidth="1"/>
+    <col min="8" max="8" width="10.4636363636364" style="41" customWidth="1"/>
+    <col min="9" max="9" width="8.46363636363636" style="41" customWidth="1"/>
+    <col min="10" max="10" width="5.13636363636364" style="41" customWidth="1"/>
+    <col min="11" max="12" width="5" style="41" customWidth="1"/>
+    <col min="13" max="256" width="11.4636363636364" style="41" customWidth="1"/>
+    <col min="257" max="16384" width="9.13636363636364" style="41"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:31">
-      <c r="B2" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="35" t="s">
+      <c r="B2" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="14.5" spans="2:31">
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="36" t="s">
+      <c r="B3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="42" t="s">
         <v>8</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
-      <c r="Y3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="35" t="s">
+      <c r="Y3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="AB3" s="35" t="s">
+      <c r="AB3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="35" t="s">
+      <c r="AC3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="35" t="s">
+      <c r="AD3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AE3" s="35" t="s">
+      <c r="AE3" s="41" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="14.5" spans="2:31">
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="41" t="s">
         <v>9</v>
       </c>
       <c r="H4">
         <v>0.1</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="41" t="s">
         <v>10</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
-      <c r="T4" s="38" t="s">
+      <c r="T4" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="U4" s="38" t="s">
+      <c r="U4" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="38" t="s">
+      <c r="V4" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="38" t="s">
+      <c r="W4" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="35" t="s">
+      <c r="AA4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AC4" s="35" t="s">
+      <c r="AC4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="AD4" s="35" t="s">
+      <c r="AD4" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="AE4" s="35">
+      <c r="AE4" s="41">
         <f xml:space="preserve">1.10926234054354*H39</f>
         <v>1.20144204104271</v>
       </c>
     </row>
     <row r="5" ht="14.5" spans="2:31">
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="41">
         <v>2020</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
-      <c r="T5" s="38" t="s">
+      <c r="T5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U5" s="38" t="s">
+      <c r="U5" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V5" s="38">
+      <c r="V5" s="44">
         <v>2001</v>
       </c>
-      <c r="W5" s="38">
+      <c r="W5" s="44">
         <v>0.762827515602112</v>
       </c>
-      <c r="AA5" s="35" t="s">
+      <c r="AA5" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AD5" s="35" t="s">
+      <c r="AD5" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="AE5" s="35">
+      <c r="AE5" s="41">
         <f xml:space="preserve">O6</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="2:31">
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="41">
         <v>1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="O6" s="39">
+      <c r="O6" s="45">
         <v>0.07</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="P6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="38" t="s">
+      <c r="T6" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="38" t="s">
+      <c r="U6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V6" s="38">
+      <c r="V6" s="44">
         <v>2002</v>
       </c>
-      <c r="W6" s="38">
+      <c r="W6" s="44">
         <v>0.774460315704346</v>
       </c>
-      <c r="AA6" s="38" t="s">
+      <c r="AA6" s="44" t="s">
         <v>15</v>
       </c>
       <c r="AB6"/>
-      <c r="AC6" s="38" t="s">
+      <c r="AC6" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="AD6" s="38" t="s">
+      <c r="AD6" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="AE6" s="40">
+      <c r="AE6" s="46">
         <f xml:space="preserve">H45</f>
         <v>0.9896</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="2:31">
-      <c r="D7" s="35" t="str">
+      <c r="D7" s="41" t="str">
         <f xml:space="preserve">IF(F7=G7,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="35" t="str">
+      <c r="G7" s="41" t="str">
         <f xml:space="preserve">"USD"&amp;RIGHT(O9,2)</f>
         <v>USD83</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="47">
         <f xml:space="preserve">ROUND($P$46/P9,4)</f>
         <v>2.2201</v>
       </c>
-      <c r="T7" s="38" t="s">
+      <c r="T7" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U7" s="38" t="s">
+      <c r="U7" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V7" s="38">
+      <c r="V7" s="44">
         <v>2003</v>
       </c>
-      <c r="W7" s="38">
+      <c r="W7" s="44">
         <v>0.789065361022949</v>
       </c>
-      <c r="AA7" s="38" t="s">
+      <c r="AA7" s="44" t="s">
         <v>21</v>
       </c>
       <c r="AB7"/>
       <c r="AC7"/>
-      <c r="AD7" s="38" t="s">
+      <c r="AD7" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="AE7" s="38">
+      <c r="AE7" s="44">
         <f xml:space="preserve">AE5</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="2:31">
-      <c r="D8" s="35" t="str">
+      <c r="D8" s="41" t="str">
         <f t="shared" ref="D8:D42" si="0" xml:space="preserve">IF(F8=G8,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="35" t="str">
+      <c r="G8" s="41" t="str">
         <f t="shared" ref="G8:G42" si="1" xml:space="preserve">"USD"&amp;RIGHT(O10,2)</f>
         <v>USD84</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="47">
         <f t="shared" ref="H8:H49" si="2" xml:space="preserve">ROUND($P$46/P10,4)</f>
         <v>2.1427</v>
       </c>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42" t="s">
+      <c r="O8" s="48"/>
+      <c r="P8" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="T8" s="38" t="s">
+      <c r="T8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U8" s="38" t="s">
+      <c r="U8" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V8" s="38">
+      <c r="V8" s="44">
         <v>2004</v>
       </c>
-      <c r="W8" s="38">
+      <c r="W8" s="44">
         <v>0.810197472572327</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="2:31">
-      <c r="D9" s="35" t="str">
+      <c r="D9" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="35" t="str">
+      <c r="G9" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD85</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="47">
         <f t="shared" si="2"/>
         <v>2.077</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="48">
         <v>1983</v>
       </c>
-      <c r="P9" s="43">
+      <c r="P9" s="49">
         <f xml:space="preserve">VLOOKUP(O9,$V$5:$W$99,2,FALSE)</f>
         <v>0.487872630357742</v>
       </c>
-      <c r="T9" s="38" t="s">
+      <c r="T9" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U9" s="38" t="s">
+      <c r="U9" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V9" s="38">
+      <c r="V9" s="44">
         <v>2005</v>
       </c>
-      <c r="W9" s="38">
+      <c r="W9" s="44">
         <v>0.835319578647614</v>
       </c>
     </row>
     <row r="10" ht="14.5" spans="2:31">
-      <c r="D10" s="35" t="str">
+      <c r="D10" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="35" t="str">
+      <c r="G10" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD86</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="47">
         <f t="shared" si="2"/>
         <v>2.0358</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="48">
         <v>1984</v>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="49">
         <f t="shared" ref="P10:P51" si="3" xml:space="preserve">VLOOKUP(O10,$V$5:$W$99,2,FALSE)</f>
         <v>0.505495131015778</v>
       </c>
-      <c r="T10" s="38" t="s">
+      <c r="T10" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U10" s="38" t="s">
+      <c r="U10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V10" s="38">
+      <c r="V10" s="44">
         <v>2006</v>
       </c>
-      <c r="W10" s="38">
+      <c r="W10" s="44">
         <v>0.860807240009308</v>
       </c>
     </row>
     <row r="11" ht="14.5" spans="2:31">
-      <c r="D11" s="35" t="str">
+      <c r="D11" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="35" t="str">
+      <c r="G11" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD87</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="47">
         <f t="shared" si="2"/>
         <v>1.987</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="48">
         <v>1985</v>
       </c>
-      <c r="P11" s="43">
+      <c r="P11" s="49">
         <f t="shared" si="3"/>
         <v>0.521485805511475</v>
       </c>
-      <c r="T11" s="38" t="s">
+      <c r="T11" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U11" s="38" t="s">
+      <c r="U11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V11" s="38">
+      <c r="V11" s="44">
         <v>2007</v>
       </c>
-      <c r="W11" s="38">
+      <c r="W11" s="44">
         <v>0.883970141410828</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="2:31">
-      <c r="D12" s="35" t="str">
+      <c r="D12" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="35" t="str">
+      <c r="G12" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD88</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="47">
         <f t="shared" si="2"/>
         <v>1.9192</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="48">
         <v>1986</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="49">
         <f t="shared" si="3"/>
         <v>0.532050728797913</v>
       </c>
-      <c r="T12" s="38" t="s">
+      <c r="T12" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U12" s="38" t="s">
+      <c r="U12" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V12" s="38">
+      <c r="V12" s="44">
         <v>2008</v>
       </c>
-      <c r="W12" s="38">
+      <c r="W12" s="44">
         <v>0.900844812393188</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="2:31">
-      <c r="D13" s="35" t="str">
+      <c r="D13" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="35" t="str">
+      <c r="G13" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD89</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="47">
         <f t="shared" si="2"/>
         <v>1.8468</v>
       </c>
-      <c r="O13" s="42">
+      <c r="O13" s="48">
         <v>1987</v>
       </c>
-      <c r="P13" s="43">
+      <c r="P13" s="49">
         <f t="shared" si="3"/>
         <v>0.54511946439743</v>
       </c>
-      <c r="T13" s="38" t="s">
+      <c r="T13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U13" s="38" t="s">
+      <c r="U13" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V13" s="38">
+      <c r="V13" s="44">
         <v>2009</v>
       </c>
-      <c r="W13" s="38">
+      <c r="W13" s="44">
         <v>0.907873749732971</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="2:31">
-      <c r="D14" s="35" t="str">
+      <c r="D14" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="35" t="str">
+      <c r="G14" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD90</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="47">
         <f t="shared" si="2"/>
         <v>1.7799</v>
       </c>
-      <c r="O14" s="42">
+      <c r="O14" s="48">
         <v>1988</v>
       </c>
-      <c r="P14" s="43">
+      <c r="P14" s="49">
         <f t="shared" si="3"/>
         <v>0.564371347427368</v>
       </c>
-      <c r="T14" s="38" t="s">
+      <c r="T14" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="38" t="s">
+      <c r="U14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V14" s="38">
+      <c r="V14" s="44">
         <v>2010</v>
       </c>
-      <c r="W14" s="38">
+      <c r="W14" s="44">
         <v>0.918479204177856</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="2:31">
-      <c r="D15" s="35" t="str">
+      <c r="D15" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="35" t="str">
+      <c r="G15" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD91</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="47">
         <f t="shared" si="2"/>
         <v>1.722</v>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="48">
         <v>1989</v>
       </c>
-      <c r="P15" s="43">
+      <c r="P15" s="49">
         <f t="shared" si="3"/>
         <v>0.58649742603302</v>
       </c>
-      <c r="T15" s="38" t="s">
+      <c r="T15" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U15" s="38" t="s">
+      <c r="U15" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V15" s="38">
+      <c r="V15" s="44">
         <v>2011</v>
       </c>
-      <c r="W15" s="38">
+      <c r="W15" s="44">
         <v>0.937618970870972</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:31">
-      <c r="D16" s="35" t="str">
+      <c r="D16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="35" t="str">
+      <c r="G16" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD92</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="47">
         <f t="shared" si="2"/>
         <v>1.6836</v>
       </c>
-      <c r="O16" s="42">
+      <c r="O16" s="48">
         <v>1990</v>
       </c>
-      <c r="P16" s="43">
+      <c r="P16" s="49">
         <f t="shared" si="3"/>
         <v>0.608532726764679</v>
       </c>
-      <c r="T16" s="38" t="s">
+      <c r="T16" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="38" t="s">
+      <c r="U16" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="38">
+      <c r="V16" s="44">
         <v>2012</v>
       </c>
-      <c r="W16" s="38">
+      <c r="W16" s="44">
         <v>0.955666601657867</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="4:23">
-      <c r="D17" s="35" t="str">
+      <c r="D17" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="35" t="str">
+      <c r="G17" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD93</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="47">
         <f t="shared" si="2"/>
         <v>1.6446</v>
       </c>
-      <c r="O17" s="42">
+      <c r="O17" s="48">
         <v>1991</v>
       </c>
-      <c r="P17" s="43">
+      <c r="P17" s="49">
         <f t="shared" si="3"/>
         <v>0.629012584686279</v>
       </c>
-      <c r="T17" s="38" t="s">
+      <c r="T17" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="38" t="s">
+      <c r="U17" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="38">
+      <c r="V17" s="44">
         <v>2013</v>
       </c>
-      <c r="W17" s="38">
+      <c r="W17" s="44">
         <v>0.972605764865875</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="4:23">
-      <c r="D18" s="35" t="str">
+      <c r="D18" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="35" t="str">
+      <c r="G18" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD94</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="47">
         <f t="shared" si="2"/>
         <v>1.6102</v>
       </c>
-      <c r="O18" s="42">
+      <c r="O18" s="48">
         <v>1992</v>
       </c>
-      <c r="P18" s="43">
+      <c r="P18" s="49">
         <f t="shared" si="3"/>
         <v>0.643362104892731</v>
       </c>
-      <c r="T18" s="38" t="s">
+      <c r="T18" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U18" s="38" t="s">
+      <c r="U18" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="38">
+      <c r="V18" s="44">
         <v>2014</v>
       </c>
-      <c r="W18" s="38">
+      <c r="W18" s="44">
         <v>0.990517318248749</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="4:23">
-      <c r="D19" s="35" t="str">
+      <c r="D19" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="35" t="str">
+      <c r="G19" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD95</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="47">
         <f t="shared" si="2"/>
         <v>1.5771</v>
       </c>
-      <c r="O19" s="42">
+      <c r="O19" s="48">
         <v>1993</v>
       </c>
-      <c r="P19" s="43">
+      <c r="P19" s="49">
         <f t="shared" si="3"/>
         <v>0.658619225025177</v>
       </c>
-      <c r="T19" s="38" t="s">
+      <c r="T19" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="38" t="s">
+      <c r="U19" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="38">
+      <c r="V19" s="44">
         <v>2015</v>
       </c>
-      <c r="W19" s="38">
+      <c r="W19" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="4:23">
-      <c r="D20" s="35" t="str">
+      <c r="D20" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="35" t="str">
+      <c r="G20" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD96</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="47">
         <f t="shared" si="2"/>
         <v>1.5488</v>
       </c>
-      <c r="O20" s="42">
+      <c r="O20" s="48">
         <v>1994</v>
       </c>
-      <c r="P20" s="43">
+      <c r="P20" s="49">
         <f t="shared" si="3"/>
         <v>0.67265796661377</v>
       </c>
-      <c r="T20" s="38" t="s">
+      <c r="T20" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U20" s="38" t="s">
+      <c r="U20" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V20" s="38">
+      <c r="V20" s="44">
         <v>2016</v>
       </c>
-      <c r="W20" s="38">
+      <c r="W20" s="44">
         <v>1.01048374176025</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="4:23">
-      <c r="D21" s="35" t="str">
+      <c r="D21" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="35" t="str">
+      <c r="G21" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD97</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="47">
         <f t="shared" si="2"/>
         <v>1.5224</v>
       </c>
-      <c r="O21" s="42">
+      <c r="O21" s="48">
         <v>1995</v>
       </c>
-      <c r="P21" s="43">
+      <c r="P21" s="49">
         <f t="shared" si="3"/>
         <v>0.686780393123627</v>
       </c>
-      <c r="T21" s="38" t="s">
+      <c r="T21" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U21" s="38" t="s">
+      <c r="U21" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V21" s="38">
+      <c r="V21" s="44">
         <v>2017</v>
       </c>
-      <c r="W21" s="38">
+      <c r="W21" s="44">
         <v>1.02974033355713</v>
       </c>
     </row>
     <row r="22" ht="14.5" spans="4:23">
-      <c r="D22" s="35" t="str">
+      <c r="D22" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="35" t="str">
+      <c r="G22" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD98</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="47">
         <f t="shared" si="2"/>
         <v>1.5058</v>
       </c>
-      <c r="O22" s="42">
+      <c r="O22" s="48">
         <v>1996</v>
       </c>
-      <c r="P22" s="43">
+      <c r="P22" s="49">
         <f t="shared" si="3"/>
         <v>0.699335396289825</v>
       </c>
-      <c r="T22" s="38" t="s">
+      <c r="T22" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U22" s="38" t="s">
+      <c r="U22" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V22" s="38">
+      <c r="V22" s="44">
         <v>2018</v>
       </c>
-      <c r="W22" s="38">
+      <c r="W22" s="44">
         <v>1.05430805683136</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="4:23">
-      <c r="D23" s="35" t="str">
+      <c r="D23" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="35" t="str">
+      <c r="G23" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD99</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="47">
         <f t="shared" si="2"/>
         <v>1.4845</v>
       </c>
-      <c r="O23" s="42">
+      <c r="O23" s="48">
         <v>1997</v>
       </c>
-      <c r="P23" s="43">
+      <c r="P23" s="49">
         <f t="shared" si="3"/>
         <v>0.71145087480545</v>
       </c>
-      <c r="T23" s="38" t="s">
+      <c r="T23" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U23" s="38" t="s">
+      <c r="U23" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V23" s="38">
+      <c r="V23" s="44">
         <v>2019</v>
       </c>
-      <c r="W23" s="38">
+      <c r="W23" s="44">
         <v>1.07337832450867</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="4:23">
-      <c r="D24" s="35" t="str">
+      <c r="D24" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="35" t="str">
+      <c r="G24" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD00</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="47">
         <f t="shared" si="2"/>
         <v>1.4518</v>
       </c>
-      <c r="O24" s="42">
+      <c r="O24" s="48">
         <v>1998</v>
       </c>
-      <c r="P24" s="43">
+      <c r="P24" s="49">
         <f t="shared" si="3"/>
         <v>0.719296872615814</v>
       </c>
-      <c r="T24" s="38" t="s">
+      <c r="T24" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U24" s="38" t="s">
+      <c r="U24" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="38">
+      <c r="V24" s="44">
         <v>2020</v>
       </c>
-      <c r="W24" s="38">
+      <c r="W24" s="44">
         <v>1.08314538002014</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="4:23">
-      <c r="D25" s="35" t="str">
+      <c r="D25" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="35" t="str">
+      <c r="G25" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD01</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="47">
         <f t="shared" si="2"/>
         <v>1.4199</v>
       </c>
-      <c r="O25" s="42">
+      <c r="O25" s="48">
         <v>1999</v>
       </c>
-      <c r="P25" s="43">
+      <c r="P25" s="49">
         <f t="shared" si="3"/>
         <v>0.729613304138184</v>
       </c>
-      <c r="T25" s="38" t="s">
+      <c r="T25" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U25" s="38" t="s">
+      <c r="U25" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V25" s="38">
+      <c r="V25" s="44">
         <v>2021</v>
       </c>
-      <c r="W25" s="38">
+      <c r="W25" s="44">
         <v>1.09456992149353</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="4:23">
-      <c r="D26" s="35" t="str">
+      <c r="D26" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="35" t="str">
+      <c r="G26" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD02</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="47">
         <f t="shared" si="2"/>
         <v>1.3986</v>
       </c>
-      <c r="O26" s="42">
+      <c r="O26" s="48">
         <v>2000</v>
       </c>
-      <c r="P26" s="43">
+      <c r="P26" s="49">
         <f t="shared" si="3"/>
         <v>0.746074616909027</v>
       </c>
-      <c r="T26" s="38" t="s">
+      <c r="T26" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U26" s="38" t="s">
+      <c r="U26" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V26" s="38">
+      <c r="V26" s="44">
         <v>2022</v>
       </c>
-      <c r="W26" s="38">
+      <c r="W26" s="44">
         <v>1.1073887348175</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="4:23">
-      <c r="D27" s="35" t="str">
+      <c r="D27" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="35" t="str">
+      <c r="G27" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD03</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="47">
         <f t="shared" si="2"/>
         <v>1.3727</v>
       </c>
-      <c r="O27" s="42">
+      <c r="O27" s="48">
         <v>2001</v>
       </c>
-      <c r="P27" s="43">
+      <c r="P27" s="49">
         <f t="shared" si="3"/>
         <v>0.762827515602112</v>
       </c>
-      <c r="T27" s="38" t="s">
+      <c r="T27" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="38" t="s">
+      <c r="U27" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V27" s="38">
+      <c r="V27" s="44">
         <v>2023</v>
       </c>
-      <c r="W27" s="38">
+      <c r="W27" s="44">
         <v>1.1224308013916</v>
       </c>
     </row>
     <row r="28" ht="14.5" spans="4:23">
-      <c r="D28" s="35" t="str">
+      <c r="D28" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="35" t="str">
+      <c r="G28" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD04</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="47">
         <f t="shared" si="2"/>
         <v>1.3369</v>
       </c>
-      <c r="O28" s="42">
+      <c r="O28" s="48">
         <v>2002</v>
       </c>
-      <c r="P28" s="43">
+      <c r="P28" s="49">
         <f t="shared" si="3"/>
         <v>0.774460315704346</v>
       </c>
-      <c r="T28" s="38" t="s">
+      <c r="T28" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U28" s="38" t="s">
+      <c r="U28" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V28" s="38">
+      <c r="V28" s="44">
         <v>2024</v>
       </c>
-      <c r="W28" s="38">
+      <c r="W28" s="44">
         <v>1.14128732681274</v>
       </c>
     </row>
     <row r="29" ht="14.5" spans="4:23">
-      <c r="D29" s="35" t="str">
+      <c r="D29" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="35" t="str">
+      <c r="G29" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD05</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="47">
         <f t="shared" si="2"/>
         <v>1.2967</v>
       </c>
-      <c r="O29" s="42">
+      <c r="O29" s="48">
         <v>2003</v>
       </c>
-      <c r="P29" s="43">
+      <c r="P29" s="49">
         <f t="shared" si="3"/>
         <v>0.789065361022949</v>
       </c>
-      <c r="T29" s="38" t="s">
+      <c r="T29" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U29" s="38" t="s">
+      <c r="U29" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V29" s="38">
+      <c r="V29" s="44">
         <v>2025</v>
       </c>
-      <c r="W29" s="38">
+      <c r="W29" s="44">
         <v>1.16506481170654</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="4:23">
-      <c r="D30" s="35" t="str">
+      <c r="D30" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="35" t="str">
+      <c r="G30" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD06</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="47">
         <f t="shared" si="2"/>
         <v>1.2583</v>
       </c>
-      <c r="O30" s="42">
+      <c r="O30" s="48">
         <v>2004</v>
       </c>
-      <c r="P30" s="43">
+      <c r="P30" s="49">
         <f t="shared" si="3"/>
         <v>0.810197472572327</v>
       </c>
-      <c r="T30" s="38" t="s">
+      <c r="T30" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U30" s="38" t="s">
+      <c r="U30" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V30" s="38">
+      <c r="V30" s="44">
         <v>2026</v>
       </c>
-      <c r="W30" s="38">
+      <c r="W30" s="44">
         <v>1.19280254840851</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="4:23">
-      <c r="D31" s="35" t="str">
+      <c r="D31" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="35" t="str">
+      <c r="G31" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD07</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="47">
         <f t="shared" si="2"/>
         <v>1.2253</v>
       </c>
-      <c r="O31" s="42">
+      <c r="O31" s="48">
         <v>2005</v>
       </c>
-      <c r="P31" s="43">
+      <c r="P31" s="49">
         <f t="shared" si="3"/>
         <v>0.835319578647614</v>
       </c>
-      <c r="T31" s="38" t="s">
+      <c r="T31" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U31" s="38" t="s">
+      <c r="U31" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V31" s="38">
+      <c r="V31" s="44">
         <v>2027</v>
       </c>
-      <c r="W31" s="38">
+      <c r="W31" s="44">
         <v>1.22309768199921</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="4:23">
-      <c r="D32" s="35" t="str">
+      <c r="D32" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="35" t="str">
+      <c r="G32" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD08</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="47">
         <f t="shared" si="2"/>
         <v>1.2024</v>
       </c>
-      <c r="O32" s="42">
+      <c r="O32" s="48">
         <v>2006</v>
       </c>
-      <c r="P32" s="43">
+      <c r="P32" s="49">
         <f t="shared" si="3"/>
         <v>0.860807240009308</v>
       </c>
-      <c r="T32" s="38" t="s">
+      <c r="T32" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U32" s="38" t="s">
+      <c r="U32" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V32" s="38">
+      <c r="V32" s="44">
         <v>2028</v>
       </c>
-      <c r="W32" s="38">
+      <c r="W32" s="44">
         <v>1.25531399250031</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="4:23">
-      <c r="D33" s="35" t="str">
+      <c r="D33" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="35" t="str">
+      <c r="G33" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD09</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="47">
         <f t="shared" si="2"/>
         <v>1.1931</v>
       </c>
-      <c r="O33" s="42">
+      <c r="O33" s="48">
         <v>2007</v>
       </c>
-      <c r="P33" s="43">
+      <c r="P33" s="49">
         <f t="shared" si="3"/>
         <v>0.883970141410828</v>
       </c>
-      <c r="T33" s="38" t="s">
+      <c r="T33" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U33" s="38" t="s">
+      <c r="U33" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V33" s="38">
+      <c r="V33" s="44">
         <v>2029</v>
       </c>
-      <c r="W33" s="38">
+      <c r="W33" s="44">
         <v>1.28839552402496</v>
       </c>
     </row>
     <row r="34" ht="14.5" spans="4:23">
-      <c r="D34" s="35" t="str">
+      <c r="D34" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="35" t="str">
+      <c r="G34" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD10</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="47">
         <f t="shared" si="2"/>
         <v>1.1793</v>
       </c>
-      <c r="O34" s="42">
+      <c r="O34" s="48">
         <v>2008</v>
       </c>
-      <c r="P34" s="43">
+      <c r="P34" s="49">
         <f t="shared" si="3"/>
         <v>0.900844812393188</v>
       </c>
-      <c r="T34" s="38" t="s">
+      <c r="T34" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U34" s="38" t="s">
+      <c r="U34" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V34" s="38">
+      <c r="V34" s="44">
         <v>2030</v>
       </c>
-      <c r="W34" s="38">
+      <c r="W34" s="44">
         <v>1.32175171375275</v>
       </c>
     </row>
     <row r="35" ht="14.5" spans="4:23">
-      <c r="D35" s="35" t="str">
+      <c r="D35" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="35" t="str">
+      <c r="G35" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD11</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="47">
         <f t="shared" si="2"/>
         <v>1.1552</v>
       </c>
-      <c r="O35" s="42">
+      <c r="O35" s="48">
         <v>2009</v>
       </c>
-      <c r="P35" s="43">
+      <c r="P35" s="49">
         <f t="shared" si="3"/>
         <v>0.907873749732971</v>
       </c>
-      <c r="T35" s="38" t="s">
+      <c r="T35" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U35" s="38" t="s">
+      <c r="U35" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V35" s="38">
+      <c r="V35" s="44">
         <v>1980</v>
       </c>
-      <c r="W35" s="38">
+      <c r="W35" s="44">
         <v>0.404039144515991</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="4:23">
-      <c r="D36" s="35" t="str">
+      <c r="D36" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F36" s="35" t="s">
+      <c r="F36" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="35" t="str">
+      <c r="G36" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD12</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="47">
         <f t="shared" si="2"/>
         <v>1.1334</v>
       </c>
-      <c r="O36" s="42">
+      <c r="O36" s="48">
         <v>2010</v>
       </c>
-      <c r="P36" s="43">
+      <c r="P36" s="49">
         <f t="shared" si="3"/>
         <v>0.918479204177856</v>
       </c>
-      <c r="T36" s="38" t="s">
+      <c r="T36" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U36" s="38" t="s">
+      <c r="U36" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V36" s="38">
+      <c r="V36" s="44">
         <v>1981</v>
       </c>
-      <c r="W36" s="38">
+      <c r="W36" s="44">
         <v>0.442179799079895</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="4:23">
-      <c r="D37" s="35" t="str">
+      <c r="D37" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="F37" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="35" t="str">
+      <c r="G37" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD13</v>
       </c>
-      <c r="H37" s="41">
+      <c r="H37" s="47">
         <f t="shared" si="2"/>
         <v>1.1137</v>
       </c>
-      <c r="O37" s="42">
+      <c r="O37" s="48">
         <v>2011</v>
       </c>
-      <c r="P37" s="43">
+      <c r="P37" s="49">
         <f t="shared" si="3"/>
         <v>0.937618970870972</v>
       </c>
-      <c r="T37" s="38" t="s">
+      <c r="T37" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U37" s="38" t="s">
+      <c r="U37" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V37" s="38">
+      <c r="V37" s="44">
         <v>1982</v>
       </c>
-      <c r="W37" s="38">
+      <c r="W37" s="44">
         <v>0.469521433115005</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="4:23">
-      <c r="D38" s="35" t="str">
+      <c r="D38" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="35" t="str">
+      <c r="G38" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD14</v>
       </c>
-      <c r="H38" s="41">
+      <c r="H38" s="47">
         <f t="shared" si="2"/>
         <v>1.0935</v>
       </c>
-      <c r="O38" s="42">
+      <c r="O38" s="48">
         <v>2012</v>
       </c>
-      <c r="P38" s="43">
+      <c r="P38" s="49">
         <f t="shared" si="3"/>
         <v>0.955666601657867</v>
       </c>
-      <c r="T38" s="38" t="s">
+      <c r="T38" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U38" s="38" t="s">
+      <c r="U38" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V38" s="38">
+      <c r="V38" s="44">
         <v>1983</v>
       </c>
-      <c r="W38" s="38">
+      <c r="W38" s="44">
         <v>0.487872630357742</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="4:23">
-      <c r="D39" s="35" t="str">
+      <c r="D39" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="F39" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="35" t="str">
+      <c r="G39" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD15</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="47">
         <f t="shared" si="2"/>
         <v>1.0831</v>
       </c>
-      <c r="O39" s="42">
+      <c r="O39" s="48">
         <v>2013</v>
       </c>
-      <c r="P39" s="43">
+      <c r="P39" s="49">
         <f t="shared" si="3"/>
         <v>0.972605764865875</v>
       </c>
-      <c r="T39" s="38" t="s">
+      <c r="T39" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U39" s="38" t="s">
+      <c r="U39" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V39" s="38">
+      <c r="V39" s="44">
         <v>1984</v>
       </c>
-      <c r="W39" s="38">
+      <c r="W39" s="44">
         <v>0.505495131015778</v>
       </c>
     </row>
     <row r="40" ht="14.5" spans="4:23">
-      <c r="D40" s="35" t="str">
+      <c r="D40" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F40" s="35" t="s">
+      <c r="F40" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="35" t="str">
+      <c r="G40" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD16</v>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="47">
         <f t="shared" si="2"/>
         <v>1.0719</v>
       </c>
-      <c r="O40" s="42">
+      <c r="O40" s="48">
         <v>2014</v>
       </c>
-      <c r="P40" s="43">
+      <c r="P40" s="49">
         <f t="shared" si="3"/>
         <v>0.990517318248749</v>
       </c>
-      <c r="T40" s="38" t="s">
+      <c r="T40" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U40" s="38" t="s">
+      <c r="U40" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V40" s="38">
+      <c r="V40" s="44">
         <v>1985</v>
       </c>
-      <c r="W40" s="38">
+      <c r="W40" s="44">
         <v>0.521485805511475</v>
       </c>
     </row>
     <row r="41" ht="14.5" spans="4:23">
-      <c r="D41" s="35" t="str">
+      <c r="D41" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F41" s="35" t="s">
+      <c r="F41" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G41" s="35" t="str">
+      <c r="G41" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD17</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="47">
         <f t="shared" si="2"/>
         <v>1.0519</v>
       </c>
-      <c r="O41" s="42">
+      <c r="O41" s="48">
         <v>2015</v>
       </c>
-      <c r="P41" s="43">
+      <c r="P41" s="49">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="T41" s="38" t="s">
+      <c r="T41" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U41" s="38" t="s">
+      <c r="U41" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V41" s="38">
+      <c r="V41" s="44">
         <v>1986</v>
       </c>
-      <c r="W41" s="38">
+      <c r="W41" s="44">
         <v>0.532050728797913</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="4:23">
-      <c r="D42" s="35" t="str">
+      <c r="D42" s="41" t="str">
         <f t="shared" si="0"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F42" s="35" t="s">
+      <c r="F42" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="35" t="str">
+      <c r="G42" s="41" t="str">
         <f t="shared" si="1"/>
         <v>USD18</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="47">
         <f t="shared" si="2"/>
         <v>1.0274</v>
       </c>
-      <c r="O42" s="42">
+      <c r="O42" s="48">
         <v>2016</v>
       </c>
-      <c r="P42" s="43">
+      <c r="P42" s="49">
         <f t="shared" si="3"/>
         <v>1.01048374176025</v>
       </c>
-      <c r="T42" s="38" t="s">
+      <c r="T42" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U42" s="38" t="s">
+      <c r="U42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V42" s="38">
+      <c r="V42" s="44">
         <v>1987</v>
       </c>
-      <c r="W42" s="38">
+      <c r="W42" s="44">
         <v>0.54511946439743</v>
       </c>
     </row>
     <row r="43" ht="14.5" spans="4:23">
-      <c r="D43" s="35" t="str">
+      <c r="D43" s="41" t="str">
         <f t="shared" ref="D43:D49" si="4" xml:space="preserve">IF(F43=G43,"*","")&amp;"G_CUREX"</f>
         <v>G_CUREX</v>
       </c>
-      <c r="F43" s="35" t="s">
+      <c r="F43" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="35" t="str">
+      <c r="G43" s="41" t="str">
         <f t="shared" ref="G43:G49" si="5" xml:space="preserve">"USD"&amp;RIGHT(O45,2)</f>
         <v>USD19</v>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="47">
         <f t="shared" si="2"/>
         <v>1.0091</v>
       </c>
-      <c r="O43" s="42">
+      <c r="O43" s="48">
         <v>2017</v>
       </c>
-      <c r="P43" s="43">
+      <c r="P43" s="49">
         <f t="shared" si="3"/>
         <v>1.02974033355713</v>
       </c>
-      <c r="T43" s="38" t="s">
+      <c r="T43" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U43" s="38" t="s">
+      <c r="U43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V43" s="38">
+      <c r="V43" s="44">
         <v>1988</v>
       </c>
-      <c r="W43" s="38">
+      <c r="W43" s="44">
         <v>0.564371347427368</v>
       </c>
     </row>
     <row r="44" ht="14.5" spans="4:23">
-      <c r="D44" s="35" t="str">
+      <c r="D44" s="41" t="str">
         <f t="shared" si="4"/>
         <v>*G_CUREX</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F44" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="35" t="str">
+      <c r="G44" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD20</v>
       </c>
-      <c r="H44" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O44" s="42">
+      <c r="H44" s="47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O44" s="48">
         <v>2018</v>
       </c>
-      <c r="P44" s="43">
+      <c r="P44" s="49">
         <f t="shared" si="3"/>
         <v>1.05430805683136</v>
       </c>
-      <c r="T44" s="38" t="s">
+      <c r="T44" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U44" s="38" t="s">
+      <c r="U44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V44" s="38">
+      <c r="V44" s="44">
         <v>1989</v>
       </c>
-      <c r="W44" s="38">
+      <c r="W44" s="44">
         <v>0.58649742603302</v>
       </c>
     </row>
     <row r="45" ht="14.5" spans="4:23">
-      <c r="D45" s="35" t="str">
+      <c r="D45" s="41" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="35" t="str">
+      <c r="G45" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD21</v>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="47">
         <f t="shared" si="2"/>
         <v>0.9896</v>
       </c>
-      <c r="O45" s="42">
+      <c r="O45" s="48">
         <v>2019</v>
       </c>
-      <c r="P45" s="43">
+      <c r="P45" s="49">
         <f t="shared" si="3"/>
         <v>1.07337832450867</v>
       </c>
-      <c r="T45" s="38" t="s">
+      <c r="T45" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U45" s="38" t="s">
+      <c r="U45" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V45" s="38">
+      <c r="V45" s="44">
         <v>1990</v>
       </c>
-      <c r="W45" s="38">
+      <c r="W45" s="44">
         <v>0.608532726764679</v>
       </c>
     </row>
     <row r="46" ht="14.5" spans="4:23">
-      <c r="D46" s="35" t="str">
+      <c r="D46" s="41" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="35" t="str">
+      <c r="G46" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD22</v>
       </c>
-      <c r="H46" s="41">
+      <c r="H46" s="47">
         <f t="shared" si="2"/>
         <v>0.9781</v>
       </c>
-      <c r="O46" s="42">
+      <c r="O46" s="48">
         <v>2020</v>
       </c>
-      <c r="P46" s="43">
+      <c r="P46" s="49">
         <f t="shared" si="3"/>
         <v>1.08314538002014</v>
       </c>
-      <c r="T46" s="38" t="s">
+      <c r="T46" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U46" s="38" t="s">
+      <c r="U46" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V46" s="38">
+      <c r="V46" s="44">
         <v>1991</v>
       </c>
-      <c r="W46" s="38">
+      <c r="W46" s="44">
         <v>0.629012584686279</v>
       </c>
     </row>
     <row r="47" ht="14.5" spans="4:23">
-      <c r="D47" s="35" t="str">
+      <c r="D47" s="41" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="35" t="str">
+      <c r="G47" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD23</v>
       </c>
-      <c r="H47" s="41">
+      <c r="H47" s="47">
         <f t="shared" si="2"/>
         <v>0.965</v>
       </c>
-      <c r="O47" s="42">
+      <c r="O47" s="48">
         <v>2021</v>
       </c>
-      <c r="P47" s="43">
+      <c r="P47" s="49">
         <f t="shared" si="3"/>
         <v>1.09456992149353</v>
       </c>
-      <c r="T47" s="38" t="s">
+      <c r="T47" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U47" s="38" t="s">
+      <c r="U47" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V47" s="38">
+      <c r="V47" s="44">
         <v>1992</v>
       </c>
-      <c r="W47" s="38">
+      <c r="W47" s="44">
         <v>0.643362104892731</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="4:23">
-      <c r="D48" s="35" t="str">
+      <c r="D48" s="41" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F48" s="35" t="s">
+      <c r="F48" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="35" t="str">
+      <c r="G48" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD24</v>
       </c>
-      <c r="H48" s="41">
+      <c r="H48" s="47">
         <f t="shared" si="2"/>
         <v>0.9491</v>
       </c>
-      <c r="O48" s="42">
+      <c r="O48" s="48">
         <v>2022</v>
       </c>
-      <c r="P48" s="43">
+      <c r="P48" s="49">
         <f t="shared" si="3"/>
         <v>1.1073887348175</v>
       </c>
-      <c r="T48" s="38" t="s">
+      <c r="T48" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U48" s="38" t="s">
+      <c r="U48" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V48" s="38">
+      <c r="V48" s="44">
         <v>1993</v>
       </c>
-      <c r="W48" s="38">
+      <c r="W48" s="44">
         <v>0.658619225025177</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="4:23">
-      <c r="D49" s="35" t="str">
+      <c r="D49" s="41" t="str">
         <f t="shared" si="4"/>
         <v>G_CUREX</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="35" t="str">
+      <c r="G49" s="41" t="str">
         <f t="shared" si="5"/>
         <v>USD25</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="47">
         <f t="shared" si="2"/>
         <v>0.9297</v>
       </c>
-      <c r="O49" s="42">
+      <c r="O49" s="48">
         <v>2023</v>
       </c>
-      <c r="P49" s="43">
+      <c r="P49" s="49">
         <f t="shared" si="3"/>
         <v>1.1224308013916</v>
       </c>
-      <c r="T49" s="38" t="s">
+      <c r="T49" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U49" s="38" t="s">
+      <c r="U49" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V49" s="38">
+      <c r="V49" s="44">
         <v>1994</v>
       </c>
-      <c r="W49" s="38">
+      <c r="W49" s="44">
         <v>0.67265796661377</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="4:23">
-      <c r="D50" s="35" t="s">
+      <c r="D50" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="35" t="str">
+      <c r="G50" s="41" t="str">
         <f t="shared" ref="G50:G85" si="6" xml:space="preserve">G7</f>
         <v>USD83</v>
       </c>
-      <c r="H50" s="41">
+      <c r="H50" s="47">
         <f xml:space="preserve">$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O50" s="42">
+      <c r="O50" s="48">
         <v>2024</v>
       </c>
-      <c r="P50" s="43">
+      <c r="P50" s="49">
         <f t="shared" si="3"/>
         <v>1.14128732681274</v>
       </c>
-      <c r="T50" s="38" t="s">
+      <c r="T50" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U50" s="38" t="s">
+      <c r="U50" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V50" s="38">
+      <c r="V50" s="44">
         <v>1995</v>
       </c>
-      <c r="W50" s="38">
+      <c r="W50" s="44">
         <v>0.686780393123627</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="4:23">
-      <c r="D51" s="35" t="s">
+      <c r="D51" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="35" t="str">
+      <c r="G51" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD84</v>
       </c>
-      <c r="H51" s="41">
+      <c r="H51" s="47">
         <f t="shared" ref="H51:H92" si="7" xml:space="preserve">$O$6</f>
         <v>0.07</v>
       </c>
-      <c r="O51" s="42">
+      <c r="O51" s="48">
         <v>2025</v>
       </c>
-      <c r="P51" s="43">
+      <c r="P51" s="49">
         <f t="shared" si="3"/>
         <v>1.16506481170654</v>
       </c>
-      <c r="T51" s="38" t="s">
+      <c r="T51" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U51" s="38" t="s">
+      <c r="U51" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V51" s="38">
+      <c r="V51" s="44">
         <v>1996</v>
       </c>
-      <c r="W51" s="38">
+      <c r="W51" s="44">
         <v>0.699335396289825</v>
       </c>
     </row>
     <row r="52" spans="4:23">
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="35" t="str">
+      <c r="G52" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD85</v>
       </c>
-      <c r="H52" s="41">
+      <c r="H52" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T52" s="38" t="s">
+      <c r="T52" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U52" s="38" t="s">
+      <c r="U52" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V52" s="38">
+      <c r="V52" s="44">
         <v>1997</v>
       </c>
-      <c r="W52" s="38">
+      <c r="W52" s="44">
         <v>0.71145087480545</v>
       </c>
     </row>
     <row r="53" spans="4:23">
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="35" t="str">
+      <c r="G53" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD86</v>
       </c>
-      <c r="H53" s="41">
+      <c r="H53" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T53" s="38" t="s">
+      <c r="T53" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U53" s="38" t="s">
+      <c r="U53" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V53" s="38">
+      <c r="V53" s="44">
         <v>1998</v>
       </c>
-      <c r="W53" s="38">
+      <c r="W53" s="44">
         <v>0.719296872615814</v>
       </c>
     </row>
     <row r="54" spans="4:23">
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="35" t="str">
+      <c r="G54" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD87</v>
       </c>
-      <c r="H54" s="41">
+      <c r="H54" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T54" s="38" t="s">
+      <c r="T54" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U54" s="38" t="s">
+      <c r="U54" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V54" s="38">
+      <c r="V54" s="44">
         <v>1999</v>
       </c>
-      <c r="W54" s="38">
+      <c r="W54" s="44">
         <v>0.729613304138184</v>
       </c>
     </row>
     <row r="55" spans="4:23">
-      <c r="D55" s="35" t="s">
+      <c r="D55" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="35" t="str">
+      <c r="G55" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD88</v>
       </c>
-      <c r="H55" s="41">
+      <c r="H55" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="T55" s="38" t="s">
+      <c r="T55" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U55" s="38" t="s">
+      <c r="U55" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="V55" s="38">
+      <c r="V55" s="44">
         <v>2000</v>
       </c>
-      <c r="W55" s="38">
+      <c r="W55" s="44">
         <v>0.746074616909027</v>
       </c>
     </row>
     <row r="56" spans="4:23">
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="35" t="str">
+      <c r="G56" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD89</v>
       </c>
-      <c r="H56" s="41">
+      <c r="H56" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="57" spans="4:23">
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="35" t="str">
+      <c r="G57" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD90</v>
       </c>
-      <c r="H57" s="41">
+      <c r="H57" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="58" spans="4:23">
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="35" t="str">
+      <c r="G58" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD91</v>
       </c>
-      <c r="H58" s="41">
+      <c r="H58" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="59" spans="4:23">
-      <c r="D59" s="35" t="s">
+      <c r="D59" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="35" t="str">
+      <c r="G59" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD92</v>
       </c>
-      <c r="H59" s="41">
+      <c r="H59" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="60" spans="4:23">
-      <c r="D60" s="35" t="s">
+      <c r="D60" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="35" t="str">
+      <c r="G60" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD93</v>
       </c>
-      <c r="H60" s="41">
+      <c r="H60" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="61" spans="4:23">
-      <c r="D61" s="35" t="s">
+      <c r="D61" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G61" s="35" t="str">
+      <c r="G61" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD94</v>
       </c>
-      <c r="H61" s="41">
+      <c r="H61" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="62" spans="4:23">
-      <c r="D62" s="35" t="s">
+      <c r="D62" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G62" s="35" t="str">
+      <c r="G62" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD95</v>
       </c>
-      <c r="H62" s="41">
+      <c r="H62" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="63" spans="4:23">
-      <c r="D63" s="35" t="s">
+      <c r="D63" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="35" t="str">
+      <c r="G63" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD96</v>
       </c>
-      <c r="H63" s="41">
+      <c r="H63" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="64" spans="4:23">
-      <c r="D64" s="35" t="s">
+      <c r="D64" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="35" t="str">
+      <c r="G64" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD97</v>
       </c>
-      <c r="H64" s="41">
+      <c r="H64" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="65" spans="4:8">
-      <c r="D65" s="35" t="s">
+      <c r="D65" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="35" t="str">
+      <c r="G65" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD98</v>
       </c>
-      <c r="H65" s="41">
+      <c r="H65" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="66" spans="4:8">
-      <c r="D66" s="35" t="s">
+      <c r="D66" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G66" s="35" t="str">
+      <c r="G66" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD99</v>
       </c>
-      <c r="H66" s="41">
+      <c r="H66" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="67" spans="4:8">
-      <c r="D67" s="35" t="s">
+      <c r="D67" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="35" t="str">
+      <c r="G67" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD00</v>
       </c>
-      <c r="H67" s="41">
+      <c r="H67" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="68" spans="4:8">
-      <c r="D68" s="35" t="s">
+      <c r="D68" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="35" t="str">
+      <c r="G68" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD01</v>
       </c>
-      <c r="H68" s="41">
+      <c r="H68" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="69" spans="4:8">
-      <c r="D69" s="35" t="s">
+      <c r="D69" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="35" t="str">
+      <c r="G69" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD02</v>
       </c>
-      <c r="H69" s="41">
+      <c r="H69" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="70" spans="4:8">
-      <c r="D70" s="35" t="s">
+      <c r="D70" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="35" t="str">
+      <c r="G70" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD03</v>
       </c>
-      <c r="H70" s="41">
+      <c r="H70" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="71" spans="4:8">
-      <c r="D71" s="35" t="s">
+      <c r="D71" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G71" s="35" t="str">
+      <c r="G71" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD04</v>
       </c>
-      <c r="H71" s="41">
+      <c r="H71" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="72" spans="4:8">
-      <c r="D72" s="35" t="s">
+      <c r="D72" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="35" t="str">
+      <c r="G72" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD05</v>
       </c>
-      <c r="H72" s="41">
+      <c r="H72" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="73" spans="4:8">
-      <c r="D73" s="35" t="s">
+      <c r="D73" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G73" s="35" t="str">
+      <c r="G73" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD06</v>
       </c>
-      <c r="H73" s="41">
+      <c r="H73" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="74" spans="4:8">
-      <c r="D74" s="35" t="s">
+      <c r="D74" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="35" t="str">
+      <c r="G74" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD07</v>
       </c>
-      <c r="H74" s="41">
+      <c r="H74" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="75" spans="4:8">
-      <c r="D75" s="35" t="s">
+      <c r="D75" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G75" s="35" t="str">
+      <c r="G75" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD08</v>
       </c>
-      <c r="H75" s="41">
+      <c r="H75" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="76" spans="4:8">
-      <c r="D76" s="35" t="s">
+      <c r="D76" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G76" s="35" t="str">
+      <c r="G76" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD09</v>
       </c>
-      <c r="H76" s="41">
+      <c r="H76" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="77" spans="4:8">
-      <c r="D77" s="35" t="s">
+      <c r="D77" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G77" s="35" t="str">
+      <c r="G77" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD10</v>
       </c>
-      <c r="H77" s="41">
+      <c r="H77" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="78" spans="4:8">
-      <c r="D78" s="35" t="s">
+      <c r="D78" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G78" s="35" t="str">
+      <c r="G78" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD11</v>
       </c>
-      <c r="H78" s="41">
+      <c r="H78" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="79" spans="4:8">
-      <c r="D79" s="35" t="s">
+      <c r="D79" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="35" t="str">
+      <c r="G79" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD12</v>
       </c>
-      <c r="H79" s="41">
+      <c r="H79" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="80" spans="4:8">
-      <c r="D80" s="35" t="s">
+      <c r="D80" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G80" s="35" t="str">
+      <c r="G80" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD13</v>
       </c>
-      <c r="H80" s="41">
+      <c r="H80" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="81" spans="4:8">
-      <c r="D81" s="35" t="s">
+      <c r="D81" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="35" t="str">
+      <c r="G81" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD14</v>
       </c>
-      <c r="H81" s="41">
+      <c r="H81" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="82" spans="4:8">
-      <c r="D82" s="35" t="s">
+      <c r="D82" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G82" s="35" t="str">
+      <c r="G82" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD15</v>
       </c>
-      <c r="H82" s="41">
+      <c r="H82" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="83" spans="4:8">
-      <c r="D83" s="35" t="s">
+      <c r="D83" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G83" s="35" t="str">
+      <c r="G83" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD16</v>
       </c>
-      <c r="H83" s="41">
+      <c r="H83" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="84" spans="4:8">
-      <c r="D84" s="35" t="s">
+      <c r="D84" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="35" t="str">
+      <c r="G84" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD17</v>
       </c>
-      <c r="H84" s="41">
+      <c r="H84" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="85" spans="4:8">
-      <c r="D85" s="35" t="s">
+      <c r="D85" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G85" s="35" t="str">
+      <c r="G85" s="41" t="str">
         <f t="shared" si="6"/>
         <v>USD18</v>
       </c>
-      <c r="H85" s="41">
+      <c r="H85" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="86" spans="4:8">
-      <c r="D86" s="35" t="s">
+      <c r="D86" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G86" s="35" t="str">
+      <c r="G86" s="41" t="str">
         <f t="shared" ref="G86:G92" si="8" xml:space="preserve">G43</f>
         <v>USD19</v>
       </c>
-      <c r="H86" s="41">
+      <c r="H86" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="87" spans="4:8">
-      <c r="D87" s="35" t="s">
+      <c r="D87" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G87" s="35" t="str">
+      <c r="G87" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD20</v>
       </c>
-      <c r="H87" s="41">
+      <c r="H87" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="88" spans="4:8">
-      <c r="D88" s="35" t="s">
+      <c r="D88" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G88" s="35" t="str">
+      <c r="G88" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD21</v>
       </c>
-      <c r="H88" s="41">
+      <c r="H88" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="89" spans="4:8">
-      <c r="D89" s="35" t="s">
+      <c r="D89" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="35" t="str">
+      <c r="G89" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD22</v>
       </c>
-      <c r="H89" s="41">
+      <c r="H89" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="90" spans="4:8">
-      <c r="D90" s="35" t="s">
+      <c r="D90" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G90" s="35" t="str">
+      <c r="G90" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD23</v>
       </c>
-      <c r="H90" s="41">
+      <c r="H90" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="91" spans="4:8">
-      <c r="D91" s="35" t="s">
+      <c r="D91" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G91" s="35" t="str">
+      <c r="G91" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD24</v>
       </c>
-      <c r="H91" s="41">
+      <c r="H91" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
     </row>
     <row r="92" spans="4:8">
-      <c r="D92" s="35" t="s">
+      <c r="D92" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G92" s="35" t="str">
+      <c r="G92" s="41" t="str">
         <f t="shared" si="8"/>
         <v>USD25</v>
       </c>
-      <c r="H92" s="41">
+      <c r="H92" s="47">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
@@ -4949,7 +4964,7 @@
       <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="15">
         <v>0.1</v>
       </c>
     </row>
@@ -4967,7 +4982,7 @@
       <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="15">
         <f xml:space="preserve">H9</f>
         <v>0.1</v>
       </c>
@@ -4979,39 +4994,39 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="27" t="str">
+      <c r="F11" s="33" t="str">
         <f xml:space="preserve">F10</f>
         <v>Trd*</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="15">
         <f xml:space="preserve">H10</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="4:8">
-      <c r="G12" s="28"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" spans="4:8">
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="4:8">
-      <c r="G14" s="31"/>
+      <c r="G14" s="37"/>
     </row>
     <row r="17" spans="6:10">
-      <c r="H17" s="32"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="6:10">
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="34"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5030,10 +5045,12 @@
     <col min="4" max="4" width="28.5454545454545" customWidth="1"/>
     <col min="5" max="5" width="43.7272727272727" customWidth="1"/>
     <col min="8" max="8" width="10.1818181818182" customWidth="1"/>
+    <col min="11" max="11" width="10.3636363636364" customWidth="1"/>
+    <col min="12" max="12" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="32" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5082,7 +5099,7 @@
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="32" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5101,10 +5118,10 @@
       <c r="B13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="4">
         <v>2150</v>
       </c>
     </row>
@@ -5114,7 +5131,7 @@
       </c>
     </row>
     <row r="20" spans="2:13">
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="26" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5192,7 +5209,7 @@
       <c r="G23" t="s">
         <v>71</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="4">
         <v>-1</v>
       </c>
     </row>
@@ -5206,7 +5223,7 @@
       <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="26">
         <v>0.5</v>
       </c>
     </row>
@@ -5221,7 +5238,7 @@
         <f xml:space="preserve">F24</f>
         <v>AuxStoOUT</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="26">
         <f xml:space="preserve">I24/4</f>
         <v>0.125</v>
       </c>
@@ -17786,13 +17803,13 @@
       <c r="E3" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>0.5</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="15">
         <v>0.25</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="15">
         <v>0.1</v>
       </c>
       <c r="L3" t="s">
@@ -17932,11 +17949,11 @@
         <f xml:space="preserve">IF(A4="","\I:",A4)</f>
         <v>Africa_North</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="19">
         <f xml:space="preserve">B4*1.1</f>
         <v>0</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="19">
         <f xml:space="preserve">MAX(VLOOKUP(L6,$E$4:$G$40,3,FALSE),M6*1.5)</f>
         <v>41.3</v>
       </c>
@@ -17951,7 +17968,7 @@
         <f t="shared" ref="U6:U28" si="0" xml:space="preserve">L6</f>
         <v>Africa_North</v>
       </c>
-      <c r="V6" s="25"/>
+      <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
@@ -17979,11 +17996,11 @@
         <f t="shared" ref="L7:L27" si="1" xml:space="preserve">IF(A5="","\I:",A5)</f>
         <v>BeNeLux</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="19">
         <f t="shared" ref="M7:M27" si="2" xml:space="preserve">B5*1.1</f>
         <v>5.885</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="19">
         <f t="shared" ref="N7:N27" si="3" xml:space="preserve">MAX(VLOOKUP(L7,$E$4:$G$40,3,FALSE),M7*1.5)</f>
         <v>8.8275</v>
       </c>
@@ -17998,7 +18015,7 @@
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="V7" s="25"/>
+      <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
@@ -18026,11 +18043,11 @@
         <f t="shared" si="1"/>
         <v>Brazil</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="19">
         <f t="shared" si="2"/>
         <v>2.189</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="19">
         <f t="shared" si="3"/>
         <v>29.2</v>
       </c>
@@ -18045,7 +18062,7 @@
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="V8" s="25"/>
+      <c r="V8" s="4"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
@@ -18073,11 +18090,11 @@
         <f t="shared" si="1"/>
         <v>China</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="19">
         <f t="shared" si="2"/>
         <v>61.083</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="19">
         <f t="shared" si="3"/>
         <v>628.9</v>
       </c>
@@ -18092,7 +18109,7 @@
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="V9" s="25"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
@@ -18120,11 +18137,11 @@
         <f t="shared" si="1"/>
         <v>CroSloven</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="19">
         <f t="shared" si="2"/>
         <v>0.759</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="19">
         <f t="shared" si="3"/>
         <v>1.1385</v>
       </c>
@@ -18139,7 +18156,7 @@
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="V10" s="25"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
@@ -18167,11 +18184,11 @@
         <f t="shared" si="1"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="19">
         <f t="shared" si="2"/>
         <v>6.919</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="19">
         <f t="shared" si="3"/>
         <v>10.3785</v>
       </c>
@@ -18186,7 +18203,7 @@
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="V11" s="25"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
@@ -18214,11 +18231,11 @@
         <f t="shared" si="1"/>
         <v>France</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="19">
         <f t="shared" si="2"/>
         <v>67.54</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="19">
         <f t="shared" si="3"/>
         <v>101.31</v>
       </c>
@@ -18233,7 +18250,7 @@
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="V12" s="25"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
@@ -18261,11 +18278,11 @@
         <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="19">
         <f t="shared" si="2"/>
         <v>4.62</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="19">
         <f t="shared" si="3"/>
         <v>19.3</v>
       </c>
@@ -18280,7 +18297,7 @@
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="V13" s="25"/>
+      <c r="V13" s="4"/>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
@@ -18308,11 +18325,11 @@
         <f t="shared" si="1"/>
         <v>HunRomBul</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="19">
         <f t="shared" si="2"/>
         <v>5.874</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="19">
         <f t="shared" si="3"/>
         <v>8.811</v>
       </c>
@@ -18327,7 +18344,7 @@
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="V14" s="25"/>
+      <c r="V14" s="4"/>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
@@ -18355,11 +18372,11 @@
         <f t="shared" si="1"/>
         <v>India</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="19">
         <f t="shared" si="2"/>
         <v>7.458</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="19">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
@@ -18374,7 +18391,7 @@
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="V15" s="25"/>
+      <c r="V15" s="4"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
@@ -18402,11 +18419,11 @@
         <f t="shared" si="1"/>
         <v>Japan</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="19">
         <f t="shared" si="2"/>
         <v>36.388</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="19">
         <f t="shared" si="3"/>
         <v>54.582</v>
       </c>
@@ -18421,7 +18438,7 @@
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V16" s="25"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
@@ -18449,11 +18466,11 @@
         <f t="shared" si="1"/>
         <v>LatAm</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="19">
         <f t="shared" si="2"/>
         <v>1.925</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="19">
         <f t="shared" si="3"/>
         <v>46.1</v>
       </c>
@@ -18468,7 +18485,7 @@
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="V17" s="25"/>
+      <c r="V17" s="4"/>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
@@ -18496,11 +18513,11 @@
         <f t="shared" si="1"/>
         <v>MidEast</v>
       </c>
-      <c r="M18" s="17">
+      <c r="M18" s="19">
         <f t="shared" si="2"/>
         <v>4.18</v>
       </c>
-      <c r="N18" s="17">
+      <c r="N18" s="19">
         <f t="shared" si="3"/>
         <v>51.6</v>
       </c>
@@ -18515,7 +18532,7 @@
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="V18" s="25"/>
+      <c r="V18" s="4"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
@@ -18543,11 +18560,11 @@
         <f t="shared" si="1"/>
         <v>NorthAm</v>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="19">
         <f t="shared" si="2"/>
         <v>120.571</v>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="19">
         <f t="shared" si="3"/>
         <v>201.3</v>
       </c>
@@ -18562,7 +18579,7 @@
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="V19" s="25"/>
+      <c r="V19" s="4"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
@@ -18590,11 +18607,11 @@
         <f t="shared" si="1"/>
         <v>ROW</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="19">
         <f t="shared" si="2"/>
         <v>34.771</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="19">
         <f t="shared" si="3"/>
         <v>160.1</v>
       </c>
@@ -18609,7 +18626,7 @@
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="V20" s="25"/>
+      <c r="V20" s="4"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
@@ -18637,11 +18654,11 @@
         <f t="shared" si="1"/>
         <v>Russia</v>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="19">
         <f t="shared" si="2"/>
         <v>33.781</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="19">
         <f t="shared" si="3"/>
         <v>50.6715</v>
       </c>
@@ -18656,7 +18673,7 @@
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="V21" s="25"/>
+      <c r="V21" s="4"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
@@ -18684,11 +18701,11 @@
         <f t="shared" si="1"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="M22" s="17">
+      <c r="M22" s="19">
         <f t="shared" si="2"/>
         <v>2.134</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="19">
         <f t="shared" si="3"/>
         <v>10.3</v>
       </c>
@@ -18703,7 +18720,7 @@
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="V22" s="25"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
@@ -18731,11 +18748,11 @@
         <f t="shared" si="1"/>
         <v>SpainPor</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="19">
         <f t="shared" si="2"/>
         <v>7.832</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="19">
         <f t="shared" si="3"/>
         <v>11.748</v>
       </c>
@@ -18750,7 +18767,7 @@
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="V23" s="25"/>
+      <c r="V23" s="4"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
@@ -18778,11 +18795,11 @@
         <f t="shared" si="1"/>
         <v>SweFinDen</v>
       </c>
-      <c r="M24" s="17">
+      <c r="M24" s="19">
         <f t="shared" si="2"/>
         <v>10.659</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="19">
         <f t="shared" si="3"/>
         <v>15.9885</v>
       </c>
@@ -18797,7 +18814,7 @@
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="V24" s="25"/>
+      <c r="V24" s="4"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
@@ -18825,11 +18842,11 @@
         <f t="shared" si="1"/>
         <v>Switzerland</v>
       </c>
-      <c r="M25" s="17">
+      <c r="M25" s="19">
         <f t="shared" si="2"/>
         <v>3.256</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="19">
         <f t="shared" si="3"/>
         <v>4.884</v>
       </c>
@@ -18844,7 +18861,7 @@
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="V25" s="25"/>
+      <c r="V25" s="4"/>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
@@ -18872,11 +18889,11 @@
         <f t="shared" si="1"/>
         <v>Turkey</v>
       </c>
-      <c r="M26" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="17">
+      <c r="M26" s="19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
         <f t="shared" si="3"/>
         <v>16.4</v>
       </c>
@@ -18891,7 +18908,7 @@
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="V26" s="25"/>
+      <c r="V26" s="4"/>
     </row>
     <row r="27" spans="1:22">
       <c r="E27" t="s">
@@ -18910,11 +18927,11 @@
         <f t="shared" si="1"/>
         <v>UK</v>
       </c>
-      <c r="M27" s="17">
+      <c r="M27" s="19">
         <f t="shared" si="2"/>
         <v>8.613</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="19">
         <f t="shared" si="3"/>
         <v>13.2</v>
       </c>
@@ -18929,7 +18946,7 @@
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="V27" s="25"/>
+      <c r="V27" s="4"/>
     </row>
     <row r="28" spans="1:22">
       <c r="E28" t="s">
@@ -18948,11 +18965,11 @@
         <f t="shared" ref="L28" si="5" xml:space="preserve">IF(A26="","\I:",A26)</f>
         <v>Ukraine</v>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="19">
         <f t="shared" ref="M28" si="6" xml:space="preserve">B26*1.1</f>
         <v>15.224</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="19">
         <f t="shared" ref="N28" si="7" xml:space="preserve">MAX(VLOOKUP(L28,$E$4:$G$40,3,FALSE),M28*1.5)</f>
         <v>22.836</v>
       </c>
@@ -18967,7 +18984,7 @@
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="V28" s="25"/>
+      <c r="V28" s="4"/>
     </row>
     <row r="29" spans="1:22">
       <c r="E29" t="s">
@@ -18982,8 +18999,8 @@
       <c r="H29">
         <v>9.3</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
       <c r="S29" t="s">
         <v>287</v>
       </c>
@@ -18993,7 +19010,7 @@
       <c r="U29" t="s">
         <v>251</v>
       </c>
-      <c r="V29" s="25">
+      <c r="V29" s="4">
         <v>0.33</v>
       </c>
     </row>
@@ -19019,7 +19036,7 @@
       <c r="U30" t="s">
         <v>253</v>
       </c>
-      <c r="V30" s="25">
+      <c r="V30" s="4">
         <v>0.33</v>
       </c>
     </row>
@@ -19062,11 +19079,11 @@
       <c r="H32">
         <v>3.8</v>
       </c>
-      <c r="M32" s="17">
+      <c r="M32" s="19">
         <f xml:space="preserve">SUM(M6:M29)</f>
         <v>441.661</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="19">
         <f xml:space="preserve">SUM(N6:N29)</f>
         <v>1704.8755</v>
       </c>
@@ -21769,164 +21786,164 @@
       </c>
     </row>
     <row r="36" ht="17.75" spans="1:40">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="29" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="37" ht="16" spans="1:40">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="23" t="str">
+      <c r="C37" s="30" t="str">
         <f t="shared" ref="C37:AK37" si="0" xml:space="preserve">B18</f>
         <v>Africa_North</v>
       </c>
-      <c r="D37" s="23" t="str">
+      <c r="D37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Africa_Other</v>
       </c>
-      <c r="E37" s="23" t="str">
+      <c r="E37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Australia</v>
       </c>
-      <c r="F37" s="23" t="str">
+      <c r="F37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Austria</v>
       </c>
-      <c r="G37" s="23" t="str">
+      <c r="G37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Baltics</v>
       </c>
-      <c r="H37" s="23" t="str">
+      <c r="H37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>BeNeLux</v>
       </c>
-      <c r="I37" s="23" t="str">
+      <c r="I37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Brazil</v>
       </c>
-      <c r="J37" s="23" t="str">
+      <c r="J37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>China</v>
       </c>
-      <c r="K37" s="23" t="str">
+      <c r="K37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>CroSloven</v>
       </c>
-      <c r="L37" s="23" t="str">
+      <c r="L37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="M37" s="23" t="str">
+      <c r="M37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>France</v>
       </c>
-      <c r="N37" s="23" t="str">
+      <c r="N37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Germany</v>
       </c>
-      <c r="O37" s="23" t="str">
+      <c r="O37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>GreeceCyp</v>
       </c>
-      <c r="P37" s="23" t="str">
+      <c r="P37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>HunRomBul</v>
       </c>
-      <c r="Q37" s="23" t="str">
+      <c r="Q37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Iceland</v>
       </c>
-      <c r="R37" s="23" t="str">
+      <c r="R37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>India</v>
       </c>
-      <c r="S37" s="23" t="str">
+      <c r="S37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Ireland</v>
       </c>
-      <c r="T37" s="23" t="str">
+      <c r="T37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>ItalyMal</v>
       </c>
-      <c r="U37" s="23" t="str">
+      <c r="U37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Japan</v>
       </c>
-      <c r="V37" s="23" t="str">
+      <c r="V37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>LatAm</v>
       </c>
-      <c r="W37" s="23" t="str">
+      <c r="W37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>MidEast</v>
       </c>
-      <c r="X37" s="23" t="str">
+      <c r="X37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>NorthAm</v>
       </c>
-      <c r="Y37" s="23" t="str">
+      <c r="Y37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Norway</v>
       </c>
-      <c r="Z37" s="23" t="str">
+      <c r="Z37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Poland</v>
       </c>
-      <c r="AA37" s="23" t="str">
+      <c r="AA37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>ROW</v>
       </c>
-      <c r="AB37" s="23" t="str">
+      <c r="AB37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Russia</v>
       </c>
-      <c r="AC37" s="23" t="str">
+      <c r="AC37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>SaudiArabia</v>
       </c>
-      <c r="AD37" s="23" t="str">
+      <c r="AD37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="AE37" s="23" t="str">
+      <c r="AE37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>SpainPor</v>
       </c>
-      <c r="AF37" s="23" t="str">
+      <c r="AF37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>SweFinDen</v>
       </c>
-      <c r="AG37" s="23" t="str">
+      <c r="AG37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Switzerland</v>
       </c>
-      <c r="AH37" s="23" t="str">
+      <c r="AH37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Turkey</v>
       </c>
-      <c r="AI37" s="23" t="str">
+      <c r="AI37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>UK</v>
       </c>
-      <c r="AJ37" s="23" t="str">
+      <c r="AJ37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Ukraine</v>
       </c>
-      <c r="AK37" s="23" t="str">
+      <c r="AK37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>WestBalkans</v>
       </c>
-      <c r="AL37" s="23" t="s">
+      <c r="AL37" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AM37" s="23" t="s">
+      <c r="AM37" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="AN37" s="23" t="s">
+      <c r="AN37" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22238,143 +22255,143 @@
       <c r="A41" t="s">
         <v>318</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="31">
         <f xml:space="preserve">1-B25/100</f>
         <v>0.781</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="31">
         <f t="shared" ref="D41:AK41" si="4" xml:space="preserve">1-C25/100</f>
         <v>0.8018</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="31">
         <f t="shared" si="4"/>
         <v>0.9012</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="31">
         <f t="shared" si="4"/>
         <v>0.9157</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="31">
         <f t="shared" si="4"/>
         <v>0.7593</v>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="31">
         <f t="shared" si="4"/>
         <v>0.9248</v>
       </c>
-      <c r="I41" s="24">
+      <c r="I41" s="31">
         <f t="shared" si="4"/>
         <v>0.8378</v>
       </c>
-      <c r="J41" s="24">
+      <c r="J41" s="31">
         <f t="shared" si="4"/>
         <v>0.9004</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="31">
         <f t="shared" si="4"/>
         <v>0.8597</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L41" s="31">
         <f t="shared" si="4"/>
         <v>0.8738</v>
       </c>
-      <c r="M41" s="24">
+      <c r="M41" s="31">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="N41" s="24">
+      <c r="N41" s="31">
         <f t="shared" si="4"/>
         <v>0.9038</v>
       </c>
-      <c r="O41" s="24">
+      <c r="O41" s="31">
         <f t="shared" si="4"/>
         <v>0.8756</v>
       </c>
-      <c r="P41" s="24">
+      <c r="P41" s="31">
         <f t="shared" si="4"/>
         <v>0.8429</v>
       </c>
-      <c r="Q41" s="24">
+      <c r="Q41" s="31">
         <f t="shared" si="4"/>
         <v>0.9532</v>
       </c>
-      <c r="R41" s="24">
+      <c r="R41" s="31">
         <f t="shared" si="4"/>
         <v>0.7732</v>
       </c>
-      <c r="S41" s="24">
+      <c r="S41" s="31">
         <f t="shared" si="4"/>
         <v>0.8973</v>
       </c>
-      <c r="T41" s="24">
+      <c r="T41" s="31">
         <f t="shared" si="4"/>
         <v>0.899</v>
       </c>
-      <c r="U41" s="24">
+      <c r="U41" s="31">
         <f t="shared" si="4"/>
         <v>0.9173</v>
       </c>
-      <c r="V41" s="24">
+      <c r="V41" s="31">
         <f t="shared" si="4"/>
         <v>0.8421</v>
       </c>
-      <c r="W41" s="24">
+      <c r="W41" s="31">
         <f t="shared" si="4"/>
         <v>0.8113</v>
       </c>
-      <c r="X41" s="24">
+      <c r="X41" s="31">
         <f t="shared" si="4"/>
         <v>0.9117</v>
       </c>
-      <c r="Y41" s="24">
+      <c r="Y41" s="31">
         <f t="shared" si="4"/>
         <v>0.9496</v>
       </c>
-      <c r="Z41" s="24">
+      <c r="Z41" s="31">
         <f t="shared" si="4"/>
         <v>0.8708</v>
       </c>
-      <c r="AA41" s="24">
+      <c r="AA41" s="31">
         <f t="shared" si="4"/>
         <v>0.895</v>
       </c>
-      <c r="AB41" s="24">
+      <c r="AB41" s="31">
         <f t="shared" si="4"/>
         <v>0.8521</v>
       </c>
-      <c r="AC41" s="24">
+      <c r="AC41" s="31">
         <f t="shared" si="4"/>
         <v>0.8649</v>
       </c>
-      <c r="AD41" s="24">
+      <c r="AD41" s="31">
         <f t="shared" si="4"/>
         <v>0.844</v>
       </c>
-      <c r="AE41" s="24">
+      <c r="AE41" s="31">
         <f t="shared" si="4"/>
         <v>0.8802</v>
       </c>
-      <c r="AF41" s="24">
+      <c r="AF41" s="31">
         <f t="shared" si="4"/>
         <v>0.9225</v>
       </c>
-      <c r="AG41" s="24">
+      <c r="AG41" s="31">
         <f t="shared" si="4"/>
         <v>0.8956</v>
       </c>
-      <c r="AH41" s="24">
+      <c r="AH41" s="31">
         <f t="shared" si="4"/>
         <v>0.8644</v>
       </c>
-      <c r="AI41" s="24">
+      <c r="AI41" s="31">
         <f t="shared" si="4"/>
         <v>0.8994</v>
       </c>
-      <c r="AJ41" s="24">
+      <c r="AJ41" s="31">
         <f t="shared" si="4"/>
         <v>0.827</v>
       </c>
-      <c r="AK41" s="24">
+      <c r="AK41" s="31">
         <f t="shared" si="4"/>
         <v>0.8198</v>
       </c>
@@ -22389,143 +22406,143 @@
       <c r="A42" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="15">
         <f t="shared" ref="C42:AK42" si="5" xml:space="preserve">MAX($C$41:$AL$41)</f>
         <v>0.9532</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="I42" s="13">
+      <c r="I42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="J42" s="13">
+      <c r="J42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="K42" s="13">
+      <c r="K42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="M42" s="13">
+      <c r="M42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="N42" s="13">
+      <c r="N42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="O42" s="13">
+      <c r="O42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="P42" s="13">
+      <c r="P42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Q42" s="13">
+      <c r="Q42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="R42" s="13">
+      <c r="R42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="S42" s="13">
+      <c r="S42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="T42" s="13">
+      <c r="T42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="U42" s="13">
+      <c r="U42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="V42" s="13">
+      <c r="V42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="W42" s="13">
+      <c r="W42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="X42" s="13">
+      <c r="X42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Y42" s="13">
+      <c r="Y42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="Z42" s="13">
+      <c r="Z42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AA42" s="13">
+      <c r="AA42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AB42" s="13">
+      <c r="AB42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AC42" s="13">
+      <c r="AC42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AD42" s="13">
+      <c r="AD42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AE42" s="13">
+      <c r="AE42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AF42" s="13">
+      <c r="AF42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AG42" s="13">
+      <c r="AG42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AH42" s="13">
+      <c r="AH42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AI42" s="13">
+      <c r="AI42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AJ42" s="13">
+      <c r="AJ42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
-      <c r="AK42" s="13">
+      <c r="AK42" s="15">
         <f t="shared" si="5"/>
         <v>0.9532</v>
       </c>
@@ -22580,6 +22597,7 @@
     <col min="36" max="36" width="6.46363636363636" customWidth="1"/>
     <col min="37" max="37" width="7.46363636363636" customWidth="1"/>
     <col min="38" max="39" width="5.8" customWidth="1"/>
+    <col min="43" max="43" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:39">
@@ -24262,39 +24280,39 @@
       </c>
     </row>
     <row r="20" spans="1:46">
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="13"/>
-      <c r="AF20" s="13"/>
-      <c r="AG20" s="13"/>
-      <c r="AH20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="15"/>
+      <c r="AC20" s="15"/>
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="15"/>
+      <c r="AF20" s="15"/>
+      <c r="AG20" s="15"/>
+      <c r="AH20" s="15"/>
     </row>
     <row r="21" spans="1:46">
       <c r="A21" t="s">
@@ -24306,150 +24324,150 @@
       <c r="C21" t="s">
         <v>335</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="13" t="str">
+      <c r="E21" s="15" t="str">
         <f xml:space="preserve">E1</f>
         <v>Africa_North</v>
       </c>
-      <c r="F21" s="13" t="str">
+      <c r="F21" s="15" t="str">
         <f t="shared" ref="F21:AM21" si="1" xml:space="preserve">F1</f>
         <v>Africa_Other</v>
       </c>
-      <c r="G21" s="13" t="str">
+      <c r="G21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Australia</v>
       </c>
-      <c r="H21" s="13" t="str">
+      <c r="H21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Austria</v>
       </c>
-      <c r="I21" s="13" t="str">
+      <c r="I21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Baltics</v>
       </c>
-      <c r="J21" s="13" t="str">
+      <c r="J21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>BeNeLux</v>
       </c>
-      <c r="K21" s="13" t="str">
+      <c r="K21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Brazil</v>
       </c>
-      <c r="L21" s="13" t="str">
+      <c r="L21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>China</v>
       </c>
-      <c r="M21" s="13" t="str">
+      <c r="M21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>CroSloven</v>
       </c>
-      <c r="N21" s="13" t="str">
+      <c r="N21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>CzechSlovak</v>
       </c>
-      <c r="O21" s="13" t="str">
+      <c r="O21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>France</v>
       </c>
-      <c r="P21" s="13" t="str">
+      <c r="P21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
-      <c r="Q21" s="13" t="str">
+      <c r="Q21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>GreeceCyp</v>
       </c>
-      <c r="R21" s="13" t="str">
+      <c r="R21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>HunRomBul</v>
       </c>
-      <c r="S21" s="13" t="str">
+      <c r="S21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Iceland</v>
       </c>
-      <c r="T21" s="13" t="str">
+      <c r="T21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>India</v>
       </c>
-      <c r="U21" s="13" t="str">
+      <c r="U21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Ireland</v>
       </c>
-      <c r="V21" s="13" t="str">
+      <c r="V21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>ItalyMal</v>
       </c>
-      <c r="W21" s="13" t="str">
+      <c r="W21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Japan</v>
       </c>
-      <c r="X21" s="13" t="str">
+      <c r="X21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>LatAm</v>
       </c>
-      <c r="Y21" s="13" t="str">
+      <c r="Y21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>MidEast</v>
       </c>
-      <c r="Z21" s="13" t="str">
+      <c r="Z21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>NorthAm</v>
       </c>
-      <c r="AA21" s="13" t="str">
+      <c r="AA21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Norway</v>
       </c>
-      <c r="AB21" s="13" t="str">
+      <c r="AB21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Poland</v>
       </c>
-      <c r="AC21" s="13" t="str">
+      <c r="AC21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>ROW</v>
       </c>
-      <c r="AD21" s="13" t="str">
+      <c r="AD21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Russia</v>
       </c>
-      <c r="AE21" s="13" t="str">
+      <c r="AE21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>SaudiArabia</v>
       </c>
-      <c r="AF21" s="13" t="str">
+      <c r="AF21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>SouthAfrica</v>
       </c>
-      <c r="AG21" s="13" t="str">
+      <c r="AG21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>SpainPor</v>
       </c>
-      <c r="AH21" s="13" t="str">
+      <c r="AH21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>SweFinDen</v>
       </c>
-      <c r="AI21" s="13" t="str">
+      <c r="AI21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Switzerland</v>
       </c>
-      <c r="AJ21" s="13" t="str">
+      <c r="AJ21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Turkey</v>
       </c>
-      <c r="AK21" s="13" t="str">
+      <c r="AK21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>UK</v>
       </c>
-      <c r="AL21" s="13" t="str">
+      <c r="AL21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>Ukraine</v>
       </c>
-      <c r="AM21" s="13" t="str">
+      <c r="AM21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>WestBalkans</v>
       </c>
-      <c r="AN21" s="13" t="s">
+      <c r="AN21" s="15" t="s">
         <v>336</v>
       </c>
       <c r="AO21" t="s">
@@ -24458,21 +24476,21 @@
       <c r="AP21" t="s">
         <v>337</v>
       </c>
-      <c r="AQ21" s="13" t="s">
+      <c r="AQ21" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="AR21" s="13" t="s">
+      <c r="AR21" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="AS21" s="13" t="s">
+      <c r="AS21" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AT21" s="13" t="s">
+      <c r="AT21" s="15" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:46">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>0.95</v>
       </c>
       <c r="B22" t="str">
@@ -24482,150 +24500,150 @@
       <c r="C22" t="s">
         <v>340</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="18">
         <v>2023</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="15">
         <f xml:space="preserve">IF(E2="","",-MIN(E2,0.8)*$A22)</f>
         <v>-0.03135</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="15">
         <f t="shared" ref="F22:AM26" si="2" xml:space="preserve">IF(F2="","",-MIN(F2,0.8)*$A22)</f>
         <v>-0.2527</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="15">
         <f t="shared" si="2"/>
         <v>-0.3857</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="15">
         <f t="shared" si="2"/>
         <v>-0.40755</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="15">
         <f t="shared" si="2"/>
         <v>-0.5282</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="15">
         <f t="shared" si="2"/>
         <v>-0.34485</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="15">
         <f t="shared" si="2"/>
         <v>-0.5586</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="15">
         <f t="shared" si="2"/>
         <v>-0.6669</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="15">
         <f t="shared" si="2"/>
         <v>-0.66025</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="15">
         <f t="shared" si="2"/>
         <v>-0.55955</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="15">
         <f t="shared" si="2"/>
         <v>-0.4883</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="15">
         <f t="shared" si="2"/>
         <v>-0.64315</v>
       </c>
-      <c r="S22" s="13" t="str">
+      <c r="S22" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="15">
         <f t="shared" si="2"/>
         <v>-0.38665</v>
       </c>
-      <c r="U22" s="13">
+      <c r="U22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="V22" s="13">
+      <c r="V22" s="15">
         <f t="shared" si="2"/>
         <v>-0.5928</v>
       </c>
-      <c r="W22" s="13">
+      <c r="W22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="X22" s="13">
+      <c r="X22" s="15">
         <f t="shared" si="2"/>
         <v>-0.4389</v>
       </c>
-      <c r="Y22" s="13">
+      <c r="Y22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Z22" s="13">
+      <c r="Z22" s="15">
         <f t="shared" si="2"/>
         <v>-0.51965</v>
       </c>
-      <c r="AA22" s="13">
+      <c r="AA22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AB22" s="13">
+      <c r="AB22" s="15">
         <f t="shared" si="2"/>
         <v>-0.741</v>
       </c>
-      <c r="AC22" s="13">
+      <c r="AC22" s="15">
         <f t="shared" si="2"/>
         <v>-0.5358</v>
       </c>
-      <c r="AD22" s="13">
+      <c r="AD22" s="15">
         <f t="shared" si="2"/>
         <v>-0.06745</v>
       </c>
-      <c r="AE22" s="13" t="str">
+      <c r="AE22" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF22" s="13">
+      <c r="AF22" s="15">
         <f t="shared" si="2"/>
         <v>-0.171</v>
       </c>
-      <c r="AG22" s="13">
+      <c r="AG22" s="15">
         <f t="shared" si="2"/>
         <v>-0.5738</v>
       </c>
-      <c r="AH22" s="13">
+      <c r="AH22" s="15">
         <f t="shared" si="2"/>
         <v>-0.36575</v>
       </c>
-      <c r="AI22" s="13">
+      <c r="AI22" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AJ22" s="13">
+      <c r="AJ22" s="15">
         <f t="shared" si="2"/>
         <v>-0.45695</v>
       </c>
-      <c r="AK22" s="13">
+      <c r="AK22" s="15">
         <f t="shared" si="2"/>
         <v>-0.55005</v>
       </c>
-      <c r="AL22" s="13">
+      <c r="AL22" s="15">
         <f t="shared" si="2"/>
         <v>-0.16245</v>
       </c>
-      <c r="AM22" s="13">
+      <c r="AM22" s="15">
         <f t="shared" si="2"/>
         <v>-0.60705</v>
       </c>
-      <c r="AN22" s="17">
+      <c r="AN22" s="19">
         <f xml:space="preserve">1/31.536</f>
         <v>0.0317097919837646</v>
       </c>
@@ -24639,12 +24657,12 @@
       <c r="AQ22">
         <v>2</v>
       </c>
-      <c r="AR22" s="44" t="s">
+      <c r="AR22" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:46">
-      <c r="A23" s="18">
+      <c r="A23" s="20">
         <v>0.8</v>
       </c>
       <c r="B23" t="str">
@@ -24654,151 +24672,151 @@
       <c r="C23" t="s">
         <v>340</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="18">
         <f xml:space="preserve">D22</f>
         <v>2023</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="15">
         <f t="shared" ref="E23:T26" si="4" xml:space="preserve">IF(E3="","",-MIN(E3,0.8)*$A23)</f>
         <v>-0.5864</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="15">
         <f t="shared" si="4"/>
         <v>-0.5016</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="15">
         <f t="shared" si="4"/>
         <v>-0.64</v>
       </c>
-      <c r="I23" s="13" t="str">
+      <c r="I23" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="15">
         <f t="shared" si="4"/>
         <v>-0.2224</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="15">
         <f t="shared" si="4"/>
         <v>-0.4072</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="15">
         <f t="shared" si="4"/>
         <v>-0.4608</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="15">
         <f t="shared" si="4"/>
         <v>-0.2944</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="15">
         <f t="shared" si="4"/>
         <v>-0.3656</v>
       </c>
-      <c r="O23" s="13">
+      <c r="O23" s="15">
         <f t="shared" si="4"/>
         <v>-0.0784</v>
       </c>
-      <c r="P23" s="13">
+      <c r="P23" s="15">
         <f t="shared" si="4"/>
         <v>-0.3056</v>
       </c>
-      <c r="Q23" s="13">
+      <c r="Q23" s="15">
         <f t="shared" si="4"/>
         <v>-0.1496</v>
       </c>
-      <c r="R23" s="13">
+      <c r="R23" s="15">
         <f t="shared" si="4"/>
         <v>-0.2216</v>
       </c>
-      <c r="S23" s="13" t="str">
+      <c r="S23" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T23" s="13">
+      <c r="T23" s="15">
         <f t="shared" si="4"/>
         <v>-0.5656</v>
       </c>
-      <c r="U23" s="13">
+      <c r="U23" s="15">
         <f t="shared" si="2"/>
         <v>-0.1056</v>
       </c>
-      <c r="V23" s="13">
+      <c r="V23" s="15">
         <f t="shared" si="2"/>
         <v>-0.2056</v>
       </c>
-      <c r="W23" s="13">
+      <c r="W23" s="15">
         <f t="shared" si="2"/>
         <v>-0.5392</v>
       </c>
-      <c r="X23" s="13">
+      <c r="X23" s="15">
         <f t="shared" si="2"/>
         <v>-0.3984</v>
       </c>
-      <c r="Y23" s="13">
+      <c r="Y23" s="15">
         <f t="shared" si="2"/>
         <v>-0.64</v>
       </c>
-      <c r="Z23" s="13">
+      <c r="Z23" s="15">
         <f t="shared" si="2"/>
         <v>-0.316</v>
       </c>
-      <c r="AA23" s="13">
+      <c r="AA23" s="15">
         <f t="shared" si="2"/>
         <v>-0.64</v>
       </c>
-      <c r="AB23" s="13">
+      <c r="AB23" s="15">
         <f t="shared" si="2"/>
         <v>-0.3296</v>
       </c>
-      <c r="AC23" s="13">
+      <c r="AC23" s="15">
         <f t="shared" si="2"/>
         <v>-0.452</v>
       </c>
-      <c r="AD23" s="13">
+      <c r="AD23" s="15">
         <f t="shared" si="2"/>
         <v>-0.5096</v>
       </c>
-      <c r="AE23" s="13" t="str">
+      <c r="AE23" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF23" s="13">
+      <c r="AF23" s="15">
         <f t="shared" si="2"/>
         <v>-0.3792</v>
       </c>
-      <c r="AG23" s="13">
+      <c r="AG23" s="15">
         <f t="shared" si="2"/>
         <v>-0.1208</v>
       </c>
-      <c r="AH23" s="13">
+      <c r="AH23" s="15">
         <f t="shared" si="2"/>
         <v>-0.1328</v>
       </c>
-      <c r="AI23" s="13" t="str">
+      <c r="AI23" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AJ23" s="13">
+      <c r="AJ23" s="15">
         <f t="shared" si="2"/>
         <v>-0.5168</v>
       </c>
-      <c r="AK23" s="13">
+      <c r="AK23" s="15">
         <f t="shared" si="2"/>
         <v>-0.1472</v>
       </c>
-      <c r="AL23" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM23" s="13">
+      <c r="AL23" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="15">
         <f t="shared" si="2"/>
         <v>-0.472</v>
       </c>
-      <c r="AN23" s="17">
+      <c r="AN23" s="19">
         <f t="shared" ref="AN23:AN31" si="5" xml:space="preserve">1/31.536</f>
         <v>0.0317097919837646</v>
       </c>
@@ -24812,12 +24830,12 @@
       <c r="AQ23">
         <v>2</v>
       </c>
-      <c r="AR23" s="44" t="s">
+      <c r="AR23" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:46">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>0.95</v>
       </c>
       <c r="B24" t="str">
@@ -24827,151 +24845,151 @@
       <c r="C24" t="s">
         <v>340</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="18">
         <f t="shared" ref="D24:D31" si="6" xml:space="preserve">D23</f>
         <v>2023</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="15">
         <f t="shared" si="4"/>
         <v>-0.36765</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="15">
         <f t="shared" si="2"/>
         <v>-0.31065</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="15">
         <f t="shared" si="2"/>
         <v>-0.18715</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="15">
         <f t="shared" si="2"/>
         <v>-0.1501</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="15">
         <f t="shared" si="2"/>
         <v>-0.07315</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="15">
         <f t="shared" si="2"/>
         <v>-0.2964</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="15">
         <f t="shared" si="2"/>
         <v>-0.2204</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="15">
         <f t="shared" si="2"/>
         <v>-0.24605</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="15">
         <f t="shared" si="2"/>
         <v>-0.6536</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="15">
         <f t="shared" si="2"/>
         <v>-0.13775</v>
       </c>
-      <c r="O24" s="13">
+      <c r="O24" s="15">
         <f t="shared" si="2"/>
         <v>-0.1843</v>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="15">
         <f t="shared" si="2"/>
         <v>-0.24795</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="15">
         <f t="shared" si="2"/>
         <v>-0.26885</v>
       </c>
-      <c r="R24" s="13">
+      <c r="R24" s="15">
         <f t="shared" si="2"/>
         <v>-0.18905</v>
       </c>
-      <c r="S24" s="13" t="str">
+      <c r="S24" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T24" s="13">
+      <c r="T24" s="15">
         <f t="shared" si="2"/>
         <v>-0.17575</v>
       </c>
-      <c r="U24" s="13">
+      <c r="U24" s="15">
         <f t="shared" si="2"/>
         <v>-0.39045</v>
       </c>
-      <c r="V24" s="13">
+      <c r="V24" s="15">
         <f t="shared" si="2"/>
         <v>-0.2261</v>
       </c>
-      <c r="W24" s="13">
+      <c r="W24" s="15">
         <f t="shared" si="2"/>
         <v>-0.44175</v>
       </c>
-      <c r="X24" s="13">
+      <c r="X24" s="15">
         <f t="shared" si="2"/>
         <v>-0.38</v>
       </c>
-      <c r="Y24" s="13">
+      <c r="Y24" s="15">
         <f t="shared" si="2"/>
         <v>-0.41515</v>
       </c>
-      <c r="Z24" s="13">
+      <c r="Z24" s="15">
         <f t="shared" si="2"/>
         <v>-0.37335</v>
       </c>
-      <c r="AA24" s="13">
+      <c r="AA24" s="15">
         <f t="shared" si="2"/>
         <v>-0.24985</v>
       </c>
-      <c r="AB24" s="13">
+      <c r="AB24" s="15">
         <f t="shared" si="2"/>
         <v>-0.4579</v>
       </c>
-      <c r="AC24" s="13">
+      <c r="AC24" s="15">
         <f t="shared" si="2"/>
         <v>-0.43415</v>
       </c>
-      <c r="AD24" s="13">
+      <c r="AD24" s="15">
         <f t="shared" si="2"/>
         <v>-0.51015</v>
       </c>
-      <c r="AE24" s="13">
+      <c r="AE24" s="15">
         <f t="shared" si="2"/>
         <v>-0.4104</v>
       </c>
-      <c r="AF24" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="13">
+      <c r="AF24" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="15">
         <f t="shared" si="2"/>
         <v>-0.25555</v>
       </c>
-      <c r="AH24" s="13">
+      <c r="AH24" s="15">
         <f t="shared" si="2"/>
         <v>-0.0456</v>
       </c>
-      <c r="AI24" s="13">
+      <c r="AI24" s="15">
         <f t="shared" si="2"/>
         <v>-0.2356</v>
       </c>
-      <c r="AJ24" s="13">
+      <c r="AJ24" s="15">
         <f t="shared" si="2"/>
         <v>-0.26125</v>
       </c>
-      <c r="AK24" s="13">
+      <c r="AK24" s="15">
         <f t="shared" si="2"/>
         <v>-0.28595</v>
       </c>
-      <c r="AL24" s="13">
+      <c r="AL24" s="15">
         <f t="shared" si="2"/>
         <v>-0.47025</v>
       </c>
-      <c r="AM24" s="13">
+      <c r="AM24" s="15">
         <f t="shared" si="2"/>
         <v>-0.2489</v>
       </c>
-      <c r="AN24" s="17">
+      <c r="AN24" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -24985,10 +25003,10 @@
       <c r="AQ24">
         <v>2</v>
       </c>
-      <c r="AR24" s="44" t="s">
+      <c r="AR24" s="50" t="s">
         <v>341</v>
       </c>
-      <c r="AS24" s="44" t="s">
+      <c r="AS24" s="50" t="s">
         <v>342</v>
       </c>
       <c r="AT24" t="s">
@@ -24996,7 +25014,7 @@
       </c>
     </row>
     <row r="25" spans="1:46">
-      <c r="A25" s="15">
+      <c r="A25" s="17">
         <v>0.95</v>
       </c>
       <c r="B25" t="str">
@@ -25006,151 +25024,151 @@
       <c r="C25" t="s">
         <v>340</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="18">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E25" s="13" t="str">
+      <c r="E25" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F25" s="13" t="str">
+      <c r="F25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G25" s="13" t="str">
+      <c r="G25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H25" s="13" t="str">
+      <c r="H25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I25" s="13" t="str">
+      <c r="I25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="O25" s="13">
+      <c r="O25" s="15">
         <f t="shared" si="2"/>
         <v>-0.5928</v>
       </c>
-      <c r="P25" s="13">
+      <c r="P25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Q25" s="13" t="str">
+      <c r="Q25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R25" s="13">
+      <c r="R25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="S25" s="13" t="str">
+      <c r="S25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T25" s="13">
+      <c r="T25" s="15">
         <f t="shared" si="2"/>
         <v>-0.6992</v>
       </c>
-      <c r="U25" s="13" t="str">
+      <c r="U25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V25" s="13" t="str">
+      <c r="V25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="W25" s="13">
+      <c r="W25" s="15">
         <f t="shared" si="2"/>
         <v>-0.25365</v>
       </c>
-      <c r="X25" s="13">
+      <c r="X25" s="15">
         <f t="shared" si="2"/>
         <v>-0.5548</v>
       </c>
-      <c r="Y25" s="13">
+      <c r="Y25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Z25" s="13">
+      <c r="Z25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AA25" s="13" t="str">
+      <c r="AA25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB25" s="13" t="str">
+      <c r="AB25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AC25" s="13">
+      <c r="AC25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AD25" s="13">
+      <c r="AD25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AE25" s="13" t="str">
+      <c r="AE25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AF25" s="13">
+      <c r="AF25" s="15">
         <f t="shared" si="2"/>
         <v>-0.4997</v>
       </c>
-      <c r="AG25" s="13">
+      <c r="AG25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AH25" s="13">
+      <c r="AH25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AI25" s="13">
+      <c r="AI25" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="AJ25" s="13" t="str">
+      <c r="AJ25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AK25" s="13">
+      <c r="AK25" s="15">
         <f t="shared" si="2"/>
         <v>-0.75145</v>
       </c>
-      <c r="AL25" s="13" t="str">
+      <c r="AL25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AM25" s="13" t="str">
+      <c r="AM25" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AN25" s="17">
+      <c r="AN25" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25164,12 +25182,12 @@
       <c r="AQ25">
         <v>2</v>
       </c>
-      <c r="AR25" s="44" t="s">
+      <c r="AR25" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:46">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>0.95</v>
       </c>
       <c r="B26" t="str">
@@ -25179,151 +25197,151 @@
       <c r="C26" t="s">
         <v>344</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="18">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="15">
         <f t="shared" si="4"/>
         <v>-0.76</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="15">
         <f t="shared" si="2"/>
         <v>-0.1387</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="15">
         <f t="shared" si="2"/>
         <v>-0.2489</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="15">
         <f t="shared" si="2"/>
         <v>-0.54435</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="15">
         <f t="shared" si="2"/>
         <v>-0.35055</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="15">
         <f t="shared" si="2"/>
         <v>-0.1577</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="15">
         <f t="shared" si="2"/>
         <v>-0.5529</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="15">
         <f t="shared" si="2"/>
         <v>-0.01615</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="15">
         <f t="shared" si="2"/>
         <v>-0.54245</v>
       </c>
-      <c r="P26" s="13">
+      <c r="P26" s="15">
         <f t="shared" si="2"/>
         <v>-0.76</v>
       </c>
-      <c r="Q26" s="13">
+      <c r="Q26" s="15">
         <f t="shared" si="2"/>
         <v>-0.2964</v>
       </c>
-      <c r="R26" s="13">
+      <c r="R26" s="15">
         <f t="shared" si="2"/>
         <v>-0.0836</v>
       </c>
-      <c r="S26" s="13" t="str">
+      <c r="S26" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="15">
         <f t="shared" ref="T26:AM26" si="7" xml:space="preserve">IF(T6="","",-MIN(T6,0.8)*$A26)</f>
         <v>-0.0247</v>
       </c>
-      <c r="U26" s="13">
+      <c r="U26" s="15">
         <f t="shared" si="7"/>
         <v>-0.10545</v>
       </c>
-      <c r="V26" s="13">
+      <c r="V26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="W26" s="13">
+      <c r="W26" s="15">
         <f t="shared" si="7"/>
         <v>-0.1843</v>
       </c>
-      <c r="X26" s="13">
+      <c r="X26" s="15">
         <f t="shared" si="7"/>
         <v>-0.20995</v>
       </c>
-      <c r="Y26" s="13">
+      <c r="Y26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="Z26" s="13">
+      <c r="Z26" s="15">
         <f t="shared" si="7"/>
         <v>-0.12825</v>
       </c>
-      <c r="AA26" s="13">
+      <c r="AA26" s="15">
         <f t="shared" si="7"/>
         <v>-0.684</v>
       </c>
-      <c r="AB26" s="13">
+      <c r="AB26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AC26" s="13">
+      <c r="AC26" s="15">
         <f t="shared" si="7"/>
         <v>-0.19</v>
       </c>
-      <c r="AD26" s="13">
+      <c r="AD26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AE26" s="13">
+      <c r="AE26" s="15">
         <f t="shared" si="7"/>
         <v>-0.608</v>
       </c>
-      <c r="AF26" s="13">
+      <c r="AF26" s="15">
         <f t="shared" si="7"/>
         <v>-0.21945</v>
       </c>
-      <c r="AG26" s="13">
+      <c r="AG26" s="15">
         <f t="shared" si="7"/>
         <v>-0.3553</v>
       </c>
-      <c r="AH26" s="13">
+      <c r="AH26" s="15">
         <f t="shared" si="7"/>
         <v>-0.095</v>
       </c>
-      <c r="AI26" s="13">
+      <c r="AI26" s="15">
         <f t="shared" si="7"/>
         <v>-0.26505</v>
       </c>
-      <c r="AJ26" s="13">
+      <c r="AJ26" s="15">
         <f t="shared" si="7"/>
         <v>-0.15485</v>
       </c>
-      <c r="AK26" s="13">
+      <c r="AK26" s="15">
         <f t="shared" si="7"/>
         <v>-0.40375</v>
       </c>
-      <c r="AL26" s="13">
+      <c r="AL26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AM26" s="13">
+      <c r="AM26" s="15">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="AN26" s="17">
+      <c r="AN26" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25337,12 +25355,12 @@
       <c r="AQ26">
         <v>2</v>
       </c>
-      <c r="AR26" s="44" t="s">
+      <c r="AR26" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:46">
-      <c r="A27" s="15">
+      <c r="A27" s="17">
         <v>1.05</v>
       </c>
       <c r="B27" t="str">
@@ -25352,151 +25370,151 @@
       <c r="C27" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="18">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="15">
         <f xml:space="preserve">IF(E2="","",-E2*$A27)</f>
         <v>-0.03465</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="15">
         <f xml:space="preserve">IF(F2="","",-F2*$A27)</f>
         <v>-0.2793</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="15">
         <f t="shared" ref="G27:AM30" si="8" xml:space="preserve">IF(G2="","",-G2*$A27)</f>
         <v>-0.4263</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="15">
         <f t="shared" si="8"/>
         <v>-0.45045</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="15">
         <f t="shared" si="8"/>
         <v>-0.5838</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="15">
         <f t="shared" si="8"/>
         <v>-0.38115</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="15">
         <f t="shared" si="8"/>
         <v>-0.6174</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="15">
         <f t="shared" si="8"/>
         <v>-0.7371</v>
       </c>
-      <c r="O27" s="13">
+      <c r="O27" s="15">
         <f t="shared" si="8"/>
         <v>-0.72975</v>
       </c>
-      <c r="P27" s="13">
+      <c r="P27" s="15">
         <f t="shared" si="8"/>
         <v>-0.61845</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="15">
         <f t="shared" si="8"/>
         <v>-0.5397</v>
       </c>
-      <c r="R27" s="13">
+      <c r="R27" s="15">
         <f t="shared" si="8"/>
         <v>-0.71085</v>
       </c>
-      <c r="S27" s="13" t="str">
+      <c r="S27" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="15">
         <f t="shared" si="8"/>
         <v>-0.42735</v>
       </c>
-      <c r="U27" s="13">
+      <c r="U27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="V27" s="13">
+      <c r="V27" s="15">
         <f t="shared" si="8"/>
         <v>-0.6552</v>
       </c>
-      <c r="W27" s="13">
+      <c r="W27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9408</v>
       </c>
-      <c r="X27" s="13">
+      <c r="X27" s="15">
         <f t="shared" si="8"/>
         <v>-0.4851</v>
       </c>
-      <c r="Y27" s="13">
+      <c r="Y27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Z27" s="13">
+      <c r="Z27" s="15">
         <f t="shared" si="8"/>
         <v>-0.57435</v>
       </c>
-      <c r="AA27" s="13">
+      <c r="AA27" s="15">
         <f t="shared" si="8"/>
         <v>-0.95865</v>
       </c>
-      <c r="AB27" s="13">
+      <c r="AB27" s="15">
         <f t="shared" si="8"/>
         <v>-0.819</v>
       </c>
-      <c r="AC27" s="13">
+      <c r="AC27" s="15">
         <f t="shared" si="8"/>
         <v>-0.5922</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="AD27" s="15">
         <f t="shared" si="8"/>
         <v>-0.07455</v>
       </c>
-      <c r="AE27" s="13" t="str">
+      <c r="AE27" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF27" s="13">
+      <c r="AF27" s="15">
         <f t="shared" si="8"/>
         <v>-0.189</v>
       </c>
-      <c r="AG27" s="13">
+      <c r="AG27" s="15">
         <f t="shared" si="8"/>
         <v>-0.6342</v>
       </c>
-      <c r="AH27" s="13">
+      <c r="AH27" s="15">
         <f t="shared" si="8"/>
         <v>-0.40425</v>
       </c>
-      <c r="AI27" s="13">
+      <c r="AI27" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="AJ27" s="13">
+      <c r="AJ27" s="15">
         <f t="shared" si="8"/>
         <v>-0.50505</v>
       </c>
-      <c r="AK27" s="13">
+      <c r="AK27" s="15">
         <f t="shared" si="8"/>
         <v>-0.60795</v>
       </c>
-      <c r="AL27" s="13">
+      <c r="AL27" s="15">
         <f t="shared" si="8"/>
         <v>-0.17955</v>
       </c>
-      <c r="AM27" s="13">
+      <c r="AM27" s="15">
         <f t="shared" si="8"/>
         <v>-0.67095</v>
       </c>
-      <c r="AN27" s="17">
+      <c r="AN27" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -25510,358 +25528,358 @@
       <c r="AQ27">
         <v>2</v>
       </c>
-      <c r="AR27" s="44" t="s">
+      <c r="AR27" s="50" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="28" spans="1:46">
-      <c r="A28" s="15">
+    <row r="28" s="13" customFormat="1" spans="1:46">
+      <c r="A28" s="21">
         <v>1.05</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B28" s="13" t="str">
         <f t="shared" ref="B28:B31" si="9" xml:space="preserve">"UCE_utilization_"&amp;C3&amp;"_"&amp;C28</f>
         <v>UCE_utilization_coal_UP</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="22">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="23">
         <f t="shared" ref="E28:T31" si="10" xml:space="preserve">IF(E3="","",-E3*$A28)</f>
         <v>-0.76965</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="23">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="23">
         <f t="shared" si="8"/>
         <v>-0.65835</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="23">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="I28" s="13" t="str">
+      <c r="I28" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="23">
         <f t="shared" si="8"/>
         <v>-0.2919</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="23">
         <f t="shared" si="8"/>
         <v>-0.53445</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="23">
         <f t="shared" si="8"/>
         <v>-0.6048</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="23">
         <f t="shared" si="8"/>
         <v>-0.3864</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="23">
         <f t="shared" si="8"/>
         <v>-0.47985</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="23">
         <f t="shared" si="8"/>
         <v>-0.1029</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="23">
         <f t="shared" si="8"/>
         <v>-0.4011</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="23">
         <f t="shared" si="8"/>
         <v>-0.19635</v>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="23">
         <f t="shared" si="8"/>
         <v>-0.29085</v>
       </c>
-      <c r="S28" s="13" t="str">
+      <c r="S28" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="23">
         <f t="shared" si="8"/>
         <v>-0.74235</v>
       </c>
-      <c r="U28" s="13">
+      <c r="U28" s="23">
         <f t="shared" si="8"/>
         <v>-0.1386</v>
       </c>
-      <c r="V28" s="13">
+      <c r="V28" s="23">
         <f t="shared" si="8"/>
         <v>-0.26985</v>
       </c>
-      <c r="W28" s="13">
+      <c r="W28" s="23">
         <f t="shared" si="8"/>
         <v>-0.7077</v>
       </c>
-      <c r="X28" s="13">
+      <c r="X28" s="23">
         <f t="shared" si="8"/>
         <v>-0.5229</v>
       </c>
-      <c r="Y28" s="13">
+      <c r="Y28" s="23">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Z28" s="13">
+      <c r="Z28" s="23">
         <f t="shared" si="8"/>
         <v>-0.41475</v>
       </c>
-      <c r="AA28" s="13">
+      <c r="AA28" s="23">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="AB28" s="13">
+      <c r="AB28" s="23">
         <f t="shared" si="8"/>
         <v>-0.4326</v>
       </c>
-      <c r="AC28" s="13">
+      <c r="AC28" s="23">
         <f t="shared" si="8"/>
         <v>-0.59325</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AD28" s="23">
         <f t="shared" si="8"/>
         <v>-0.66885</v>
       </c>
-      <c r="AE28" s="13" t="str">
+      <c r="AE28" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF28" s="13">
+      <c r="AF28" s="23">
         <f t="shared" si="8"/>
         <v>-0.4977</v>
       </c>
-      <c r="AG28" s="13">
+      <c r="AG28" s="23">
         <f t="shared" si="8"/>
         <v>-0.15855</v>
       </c>
-      <c r="AH28" s="13">
+      <c r="AH28" s="23">
         <f t="shared" si="8"/>
         <v>-0.1743</v>
       </c>
-      <c r="AI28" s="13" t="str">
+      <c r="AI28" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AJ28" s="13">
+      <c r="AJ28" s="23">
         <f t="shared" si="8"/>
         <v>-0.6783</v>
       </c>
-      <c r="AK28" s="13">
+      <c r="AK28" s="23">
         <f t="shared" si="8"/>
         <v>-0.1932</v>
       </c>
-      <c r="AL28" s="13">
+      <c r="AL28" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM28" s="13">
+      <c r="AM28" s="23">
         <f t="shared" si="8"/>
         <v>-0.6195</v>
       </c>
-      <c r="AN28" s="17">
+      <c r="AN28" s="24">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
-      <c r="AO28" t="s">
+      <c r="AO28" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AP28" t="str">
+      <c r="AP28" s="13" t="str">
         <f t="shared" ref="AP28:AP31" si="11" xml:space="preserve">AP23</f>
         <v>???coa,elccob</v>
       </c>
-      <c r="AQ28">
-        <v>2</v>
-      </c>
-      <c r="AR28" s="44" t="s">
+      <c r="AQ28" s="13">
+        <v>4</v>
+      </c>
+      <c r="AR28" s="51" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:46">
-      <c r="A29" s="15">
+    <row r="29" s="13" customFormat="1" spans="1:46">
+      <c r="A29" s="21">
         <v>1.05</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B29" s="13" t="str">
         <f t="shared" si="9"/>
         <v>UCE_utilization_gas_UP</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="22">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="23">
         <f t="shared" si="10"/>
         <v>-0.40635</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="23">
         <f t="shared" si="10"/>
         <v>-0.34335</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="23">
         <f t="shared" si="8"/>
         <v>-0.20685</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="23">
         <f t="shared" si="8"/>
         <v>-0.1659</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="23">
         <f t="shared" si="8"/>
         <v>-0.08085</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="23">
         <f t="shared" si="8"/>
         <v>-0.3276</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="23">
         <f t="shared" si="8"/>
         <v>-0.2436</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="23">
         <f t="shared" si="8"/>
         <v>-0.27195</v>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="23">
         <f t="shared" si="8"/>
         <v>-0.7224</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="23">
         <f t="shared" si="8"/>
         <v>-0.15225</v>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="23">
         <f t="shared" si="8"/>
         <v>-0.2037</v>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="23">
         <f t="shared" si="8"/>
         <v>-0.27405</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="23">
         <f t="shared" si="8"/>
         <v>-0.29715</v>
       </c>
-      <c r="R29" s="13">
+      <c r="R29" s="23">
         <f t="shared" si="8"/>
         <v>-0.20895</v>
       </c>
-      <c r="S29" s="13" t="str">
+      <c r="S29" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T29" s="13">
+      <c r="T29" s="23">
         <f t="shared" si="8"/>
         <v>-0.19425</v>
       </c>
-      <c r="U29" s="13">
+      <c r="U29" s="23">
         <f t="shared" si="8"/>
         <v>-0.43155</v>
       </c>
-      <c r="V29" s="13">
+      <c r="V29" s="23">
         <f t="shared" si="8"/>
         <v>-0.2499</v>
       </c>
-      <c r="W29" s="13">
+      <c r="W29" s="23">
         <f t="shared" si="8"/>
         <v>-0.48825</v>
       </c>
-      <c r="X29" s="13">
+      <c r="X29" s="23">
         <f t="shared" si="8"/>
         <v>-0.42</v>
       </c>
-      <c r="Y29" s="13">
+      <c r="Y29" s="23">
         <f t="shared" si="8"/>
         <v>-0.45885</v>
       </c>
-      <c r="Z29" s="13">
+      <c r="Z29" s="23">
         <f t="shared" si="8"/>
         <v>-0.41265</v>
       </c>
-      <c r="AA29" s="13">
+      <c r="AA29" s="23">
         <f t="shared" si="8"/>
         <v>-0.27615</v>
       </c>
-      <c r="AB29" s="13">
+      <c r="AB29" s="23">
         <f t="shared" si="8"/>
         <v>-0.5061</v>
       </c>
-      <c r="AC29" s="13">
+      <c r="AC29" s="23">
         <f t="shared" si="8"/>
         <v>-0.47985</v>
       </c>
-      <c r="AD29" s="13">
+      <c r="AD29" s="23">
         <f t="shared" si="8"/>
         <v>-0.56385</v>
       </c>
-      <c r="AE29" s="13">
+      <c r="AE29" s="23">
         <f t="shared" si="8"/>
         <v>-0.4536</v>
       </c>
-      <c r="AF29" s="13">
+      <c r="AF29" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="13">
+      <c r="AG29" s="23">
         <f t="shared" si="8"/>
         <v>-0.28245</v>
       </c>
-      <c r="AH29" s="13">
+      <c r="AH29" s="23">
         <f t="shared" si="8"/>
         <v>-0.0504</v>
       </c>
-      <c r="AI29" s="13">
+      <c r="AI29" s="23">
         <f t="shared" si="8"/>
         <v>-0.2604</v>
       </c>
-      <c r="AJ29" s="13">
+      <c r="AJ29" s="23">
         <f t="shared" si="8"/>
         <v>-0.28875</v>
       </c>
-      <c r="AK29" s="13">
+      <c r="AK29" s="23">
         <f t="shared" si="8"/>
         <v>-0.31605</v>
       </c>
-      <c r="AL29" s="13">
+      <c r="AL29" s="23">
         <f t="shared" si="8"/>
         <v>-0.51975</v>
       </c>
-      <c r="AM29" s="13">
+      <c r="AM29" s="23">
         <f t="shared" si="8"/>
         <v>-0.2751</v>
       </c>
-      <c r="AN29" s="17">
+      <c r="AN29" s="24">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
-      <c r="AO29" t="s">
+      <c r="AO29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AP29" t="str">
+      <c r="AP29" s="13" t="str">
         <f t="shared" si="11"/>
         <v>???nga</v>
       </c>
-      <c r="AQ29">
-        <v>2</v>
-      </c>
-      <c r="AR29" s="44" t="s">
+      <c r="AQ29" s="13">
+        <v>4</v>
+      </c>
+      <c r="AR29" s="51" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:46">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>1.05</v>
       </c>
       <c r="B30" t="str">
@@ -25871,151 +25889,151 @@
       <c r="C30" t="s">
         <v>345</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="18">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E30" s="13" t="str">
+      <c r="E30" s="15" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F30" s="13" t="str">
+      <c r="F30" s="15" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G30" s="13" t="str">
+      <c r="G30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H30" s="13" t="str">
+      <c r="H30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I30" s="13" t="str">
+      <c r="I30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="K30" s="13">
+      <c r="K30" s="15">
         <f t="shared" si="8"/>
         <v>-0.8736</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="15">
         <f t="shared" si="8"/>
         <v>-0.9156</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30" s="15">
         <f t="shared" si="8"/>
         <v>-0.97965</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="15">
         <f t="shared" si="8"/>
         <v>-0.92925</v>
       </c>
-      <c r="O30" s="13">
+      <c r="O30" s="15">
         <f t="shared" si="8"/>
         <v>-0.6552</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="15">
         <f t="shared" si="8"/>
         <v>-0.9975</v>
       </c>
-      <c r="Q30" s="13" t="str">
+      <c r="Q30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R30" s="13">
+      <c r="R30" s="15">
         <f t="shared" si="8"/>
         <v>-0.97125</v>
       </c>
-      <c r="S30" s="13" t="str">
+      <c r="S30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="15">
         <f t="shared" si="8"/>
         <v>-0.7728</v>
       </c>
-      <c r="U30" s="13" t="str">
+      <c r="U30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="V30" s="13" t="str">
+      <c r="V30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="W30" s="13">
+      <c r="W30" s="15">
         <f t="shared" si="8"/>
         <v>-0.28035</v>
       </c>
-      <c r="X30" s="13">
+      <c r="X30" s="15">
         <f t="shared" si="8"/>
         <v>-0.6132</v>
       </c>
-      <c r="Y30" s="13">
+      <c r="Y30" s="15">
         <f t="shared" si="8"/>
         <v>-0.8988</v>
       </c>
-      <c r="Z30" s="13">
+      <c r="Z30" s="15">
         <f t="shared" si="8"/>
         <v>-0.94815</v>
       </c>
-      <c r="AA30" s="13" t="str">
+      <c r="AA30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB30" s="13" t="str">
+      <c r="AB30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AC30" s="13">
+      <c r="AC30" s="15">
         <f t="shared" si="8"/>
         <v>-0.87675</v>
       </c>
-      <c r="AD30" s="13">
+      <c r="AD30" s="15">
         <f t="shared" si="8"/>
         <v>-0.882</v>
       </c>
-      <c r="AE30" s="13" t="str">
+      <c r="AE30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AF30" s="13">
+      <c r="AF30" s="15">
         <f t="shared" si="8"/>
         <v>-0.5523</v>
       </c>
-      <c r="AG30" s="13">
+      <c r="AG30" s="15">
         <f t="shared" si="8"/>
         <v>-0.95655</v>
       </c>
-      <c r="AH30" s="13">
+      <c r="AH30" s="15">
         <f t="shared" si="8"/>
         <v>-0.8736</v>
       </c>
-      <c r="AI30" s="13">
+      <c r="AI30" s="15">
         <f t="shared" si="8"/>
         <v>-0.97965</v>
       </c>
-      <c r="AJ30" s="13" t="str">
+      <c r="AJ30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AK30" s="13">
+      <c r="AK30" s="15">
         <f t="shared" si="8"/>
         <v>-0.83055</v>
       </c>
-      <c r="AL30" s="13" t="str">
+      <c r="AL30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AM30" s="13" t="str">
+      <c r="AM30" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN30" s="17">
+      <c r="AN30" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -26029,12 +26047,12 @@
       <c r="AQ30">
         <v>2</v>
       </c>
-      <c r="AR30" s="44" t="s">
+      <c r="AR30" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:46">
-      <c r="A31" s="15">
+      <c r="A31" s="17">
         <v>1.05</v>
       </c>
       <c r="B31" t="str">
@@ -26044,151 +26062,151 @@
       <c r="C31" t="s">
         <v>345</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="18">
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="15">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="15">
         <f t="shared" si="10"/>
         <v>-0.1533</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="15">
         <f t="shared" si="10"/>
         <v>-0.2751</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="15">
         <f t="shared" si="10"/>
         <v>-0.60165</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="15">
         <f t="shared" si="10"/>
         <v>-0.38745</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="15">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="K31" s="13">
+      <c r="K31" s="15">
         <f t="shared" si="10"/>
         <v>-0.1743</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="15">
         <f t="shared" si="10"/>
         <v>-0.6111</v>
       </c>
-      <c r="M31" s="13">
+      <c r="M31" s="15">
         <f t="shared" si="10"/>
         <v>-0.01785</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="15">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="O31" s="13">
+      <c r="O31" s="15">
         <f t="shared" si="10"/>
         <v>-0.59955</v>
       </c>
-      <c r="P31" s="13">
+      <c r="P31" s="15">
         <f t="shared" si="10"/>
         <v>-0.9975</v>
       </c>
-      <c r="Q31" s="13">
+      <c r="Q31" s="15">
         <f t="shared" si="10"/>
         <v>-0.3276</v>
       </c>
-      <c r="R31" s="13">
+      <c r="R31" s="15">
         <f t="shared" si="10"/>
         <v>-0.0924</v>
       </c>
-      <c r="S31" s="13" t="str">
+      <c r="S31" s="15" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="T31" s="13">
+      <c r="T31" s="15">
         <f t="shared" si="10"/>
         <v>-0.0273</v>
       </c>
-      <c r="U31" s="13">
+      <c r="U31" s="15">
         <f t="shared" ref="U31:AM31" si="12" xml:space="preserve">IF(U6="","",-U6*$A31)</f>
         <v>-0.11655</v>
       </c>
-      <c r="V31" s="13">
+      <c r="V31" s="15">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="W31" s="13">
+      <c r="W31" s="15">
         <f t="shared" si="12"/>
         <v>-0.2037</v>
       </c>
-      <c r="X31" s="13">
+      <c r="X31" s="15">
         <f t="shared" si="12"/>
         <v>-0.23205</v>
       </c>
-      <c r="Y31" s="13">
+      <c r="Y31" s="15">
         <f t="shared" si="12"/>
         <v>-0.93975</v>
       </c>
-      <c r="Z31" s="13">
+      <c r="Z31" s="15">
         <f t="shared" si="12"/>
         <v>-0.14175</v>
       </c>
-      <c r="AA31" s="13">
+      <c r="AA31" s="15">
         <f t="shared" si="12"/>
         <v>-0.756</v>
       </c>
-      <c r="AB31" s="13">
+      <c r="AB31" s="15">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AC31" s="13">
+      <c r="AC31" s="15">
         <f t="shared" si="12"/>
         <v>-0.21</v>
       </c>
-      <c r="AD31" s="13">
+      <c r="AD31" s="15">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AE31" s="13">
+      <c r="AE31" s="15">
         <f t="shared" si="12"/>
         <v>-0.672</v>
       </c>
-      <c r="AF31" s="13">
+      <c r="AF31" s="15">
         <f t="shared" si="12"/>
         <v>-0.24255</v>
       </c>
-      <c r="AG31" s="13">
+      <c r="AG31" s="15">
         <f t="shared" si="12"/>
         <v>-0.3927</v>
       </c>
-      <c r="AH31" s="13">
+      <c r="AH31" s="15">
         <f t="shared" si="12"/>
         <v>-0.105</v>
       </c>
-      <c r="AI31" s="13">
+      <c r="AI31" s="15">
         <f t="shared" si="12"/>
         <v>-0.29295</v>
       </c>
-      <c r="AJ31" s="13">
+      <c r="AJ31" s="15">
         <f t="shared" si="12"/>
         <v>-0.17115</v>
       </c>
-      <c r="AK31" s="13">
+      <c r="AK31" s="15">
         <f t="shared" si="12"/>
         <v>-0.44625</v>
       </c>
-      <c r="AL31" s="13">
+      <c r="AL31" s="15">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AM31" s="13">
+      <c r="AM31" s="15">
         <f t="shared" si="12"/>
         <v>-0.9975</v>
       </c>
-      <c r="AN31" s="17">
+      <c r="AN31" s="19">
         <f t="shared" si="5"/>
         <v>0.0317097919837646</v>
       </c>
@@ -26200,9 +26218,9 @@
         <v>???oil*</v>
       </c>
       <c r="AQ31">
-        <v>2</v>
-      </c>
-      <c r="AR31" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR31" s="50" t="s">
         <v>341</v>
       </c>
     </row>
@@ -26212,7 +26230,7 @@
       </c>
     </row>
     <row r="33" spans="1:46">
-      <c r="A33" s="19">
+      <c r="A33" s="25">
         <v>0.3</v>
       </c>
       <c r="B33" t="str">
@@ -26227,160 +26245,160 @@
         <f xml:space="preserve">D22+7</f>
         <v>2030</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="19">
         <f t="shared" ref="E33:AM33" si="13" xml:space="preserve">IF(E7="","",-MIN(E7,E2,0.8)*$A33)</f>
         <v>-0.0042</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0525</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1218</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1287</v>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1668</v>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="19">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1089</v>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="19">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="M33" s="17">
+      <c r="M33" s="19">
         <f t="shared" si="13"/>
         <v>-0.165</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="19">
         <f t="shared" si="13"/>
         <v>-0.2106</v>
       </c>
-      <c r="O33" s="17">
+      <c r="O33" s="19">
         <f t="shared" si="13"/>
         <v>-0.2085</v>
       </c>
-      <c r="P33" s="17">
+      <c r="P33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1767</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1407</v>
       </c>
-      <c r="R33" s="17">
+      <c r="R33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1467</v>
       </c>
-      <c r="S33" s="17" t="str">
+      <c r="S33" s="19" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="T33" s="17">
+      <c r="T33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0921</v>
       </c>
-      <c r="U33" s="17">
+      <c r="U33" s="19">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="V33" s="17">
+      <c r="V33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1872</v>
       </c>
-      <c r="W33" s="17">
+      <c r="W33" s="19">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="X33" s="17">
+      <c r="X33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1044</v>
       </c>
-      <c r="Y33" s="17">
+      <c r="Y33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0882</v>
       </c>
-      <c r="Z33" s="17">
+      <c r="Z33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1641</v>
       </c>
-      <c r="AA33" s="17">
+      <c r="AA33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0855</v>
       </c>
-      <c r="AB33" s="17">
+      <c r="AB33" s="19">
         <f t="shared" si="13"/>
         <v>-0.2232</v>
       </c>
-      <c r="AC33" s="17">
+      <c r="AC33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1248</v>
       </c>
-      <c r="AD33" s="17">
+      <c r="AD33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0153</v>
       </c>
-      <c r="AE33" s="17" t="str">
+      <c r="AE33" s="19" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AF33" s="17">
+      <c r="AF33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0435</v>
       </c>
-      <c r="AG33" s="17">
+      <c r="AG33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1812</v>
       </c>
-      <c r="AH33" s="17">
+      <c r="AH33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1155</v>
       </c>
-      <c r="AI33" s="17">
+      <c r="AI33" s="19">
         <f t="shared" si="13"/>
         <v>-0.24</v>
       </c>
-      <c r="AJ33" s="17">
+      <c r="AJ33" s="19">
         <f t="shared" si="13"/>
         <v>-0.135</v>
       </c>
-      <c r="AK33" s="17">
+      <c r="AK33" s="19">
         <f t="shared" si="13"/>
         <v>-0.1737</v>
       </c>
-      <c r="AL33" s="17">
+      <c r="AL33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0513</v>
       </c>
-      <c r="AM33" s="17">
+      <c r="AM33" s="19">
         <f t="shared" si="13"/>
         <v>-0.0684</v>
       </c>
-      <c r="AO33" s="17" t="str">
+      <c r="AO33" s="19" t="str">
         <f xml:space="preserve">AO22</f>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP33" s="17" t="str">
+      <c r="AP33" s="19" t="str">
         <f t="shared" ref="AP33:AP42" si="14" xml:space="preserve">AP22</f>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR33" s="44" t="s">
+      <c r="AR33" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:46">
-      <c r="A34" s="19">
+      <c r="A34" s="25">
         <v>0.3</v>
       </c>
       <c r="B34" t="str">
@@ -26395,160 +26413,160 @@
         <f t="shared" ref="D34:D42" si="16" xml:space="preserve">D23+7</f>
         <v>2030</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f t="shared" ref="E34:AG37" si="17" xml:space="preserve">IF(E8="","",-MIN(E8,E3,0.8)*$A34)</f>
         <v>-0.171</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1815</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0831</v>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="19">
         <f t="shared" si="17"/>
         <v>-0.24</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0753</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1527</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1545</v>
       </c>
-      <c r="M34" s="17">
+      <c r="M34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1104</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1284</v>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0282</v>
       </c>
-      <c r="P34" s="17">
+      <c r="P34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0984</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0561</v>
       </c>
-      <c r="R34" s="17">
+      <c r="R34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0804</v>
       </c>
-      <c r="S34" s="17" t="str">
+      <c r="S34" s="19" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T34" s="17">
+      <c r="T34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1734</v>
       </c>
-      <c r="U34" s="17">
+      <c r="U34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="V34" s="17">
+      <c r="V34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0591</v>
       </c>
-      <c r="W34" s="17">
+      <c r="W34" s="19">
         <f t="shared" si="17"/>
         <v>-0.2022</v>
       </c>
-      <c r="X34" s="17">
+      <c r="X34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1494</v>
       </c>
-      <c r="Y34" s="17">
+      <c r="Y34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1155</v>
       </c>
-      <c r="Z34" s="17">
+      <c r="Z34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1152</v>
       </c>
-      <c r="AA34" s="17">
+      <c r="AA34" s="19">
         <f t="shared" si="17"/>
         <v>-0.24</v>
       </c>
-      <c r="AB34" s="17">
+      <c r="AB34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1236</v>
       </c>
-      <c r="AC34" s="17">
+      <c r="AC34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1671</v>
       </c>
-      <c r="AD34" s="17">
+      <c r="AD34" s="19">
         <f t="shared" si="17"/>
         <v>-0.126</v>
       </c>
-      <c r="AE34" s="17" t="str">
+      <c r="AE34" s="19" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AF34" s="17">
+      <c r="AF34" s="19">
         <f t="shared" si="17"/>
         <v>-0.1422</v>
       </c>
-      <c r="AG34" s="17">
+      <c r="AG34" s="19">
         <f t="shared" si="17"/>
         <v>-0.0375</v>
       </c>
-      <c r="AH34" s="17">
+      <c r="AH34" s="19">
         <f t="shared" ref="AH34:AM34" si="18" xml:space="preserve">IF(AH8="","",-MIN(AH8,AH3,0.8)*$A34)</f>
         <v>-0.0498</v>
       </c>
-      <c r="AI34" s="17" t="str">
+      <c r="AI34" s="19" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AJ34" s="17">
+      <c r="AJ34" s="19">
         <f t="shared" si="18"/>
         <v>-0.1704</v>
       </c>
-      <c r="AK34" s="17">
+      <c r="AK34" s="19">
         <f t="shared" si="18"/>
         <v>-0.0246</v>
       </c>
-      <c r="AL34" s="17">
+      <c r="AL34" s="19">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AM34" s="17">
+      <c r="AM34" s="19">
         <f t="shared" si="18"/>
         <v>-0.177</v>
       </c>
-      <c r="AO34" s="17" t="str">
+      <c r="AO34" s="19" t="str">
         <f t="shared" ref="AO34:AO42" si="19" xml:space="preserve">AO23</f>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP34" s="17" t="str">
+      <c r="AP34" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR34" s="44" t="s">
+      <c r="AR34" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:46">
-      <c r="A35" s="19">
+      <c r="A35" s="25">
         <v>0.3</v>
       </c>
       <c r="B35" t="str">
@@ -26563,158 +26581,158 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1119</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0954</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0591</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0381</v>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="J35" s="17">
+      <c r="J35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0936</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0696</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0777</v>
       </c>
-      <c r="M35" s="17">
+      <c r="M35" s="19">
         <f t="shared" si="17"/>
         <v>-0.087</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0264</v>
       </c>
-      <c r="O35" s="17">
+      <c r="O35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0189</v>
       </c>
-      <c r="P35" s="17">
+      <c r="P35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0762</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0462</v>
       </c>
-      <c r="R35" s="17">
+      <c r="R35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0492</v>
       </c>
-      <c r="S35" s="17" t="str">
+      <c r="S35" s="19" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T35" s="17">
+      <c r="T35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0495</v>
       </c>
-      <c r="U35" s="17">
+      <c r="U35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0966</v>
       </c>
-      <c r="V35" s="17">
+      <c r="V35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0474</v>
       </c>
-      <c r="W35" s="17">
+      <c r="W35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1395</v>
       </c>
-      <c r="X35" s="17">
+      <c r="X35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1056</v>
       </c>
-      <c r="Y35" s="17">
+      <c r="Y35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1167</v>
       </c>
-      <c r="Z35" s="17">
+      <c r="Z35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0942</v>
       </c>
-      <c r="AA35" s="17">
+      <c r="AA35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0138</v>
       </c>
-      <c r="AB35" s="17">
+      <c r="AB35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1116</v>
       </c>
-      <c r="AC35" s="17">
+      <c r="AC35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1371</v>
       </c>
-      <c r="AD35" s="17">
+      <c r="AD35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1425</v>
       </c>
-      <c r="AE35" s="17">
+      <c r="AE35" s="19">
         <f t="shared" si="17"/>
         <v>-0.1158</v>
       </c>
-      <c r="AF35" s="17">
+      <c r="AF35" s="19">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="17">
+      <c r="AG35" s="19">
         <f t="shared" si="17"/>
         <v>-0.0585</v>
       </c>
-      <c r="AH35" s="17">
+      <c r="AH35" s="19">
         <f t="shared" ref="AH35:AM35" si="20" xml:space="preserve">IF(AH9="","",-MIN(AH9,AH4,0.8)*$A35)</f>
         <v>-0.0144</v>
       </c>
-      <c r="AI35" s="17">
+      <c r="AI35" s="19">
         <f t="shared" si="20"/>
         <v>-0.0714</v>
       </c>
-      <c r="AJ35" s="17">
+      <c r="AJ35" s="19">
         <f t="shared" si="20"/>
         <v>-0.0681</v>
       </c>
-      <c r="AK35" s="17">
+      <c r="AK35" s="19">
         <f t="shared" si="20"/>
         <v>-0.0903</v>
       </c>
-      <c r="AL35" s="17">
+      <c r="AL35" s="19">
         <f t="shared" si="20"/>
         <v>-0.042</v>
       </c>
-      <c r="AM35" s="17">
+      <c r="AM35" s="19">
         <f t="shared" si="20"/>
         <v>-0.0186</v>
       </c>
-      <c r="AO35" s="17" t="str">
+      <c r="AO35" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP35" s="17" t="str">
+      <c r="AP35" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR35" s="44" t="s">
+      <c r="AR35" s="50" t="s">
         <v>341</v>
       </c>
-      <c r="AS35" s="44" t="s">
+      <c r="AS35" s="50" t="s">
         <v>342</v>
       </c>
       <c r="AT35" t="s">
@@ -26722,7 +26740,7 @@
       </c>
     </row>
     <row r="36" spans="1:46">
-      <c r="A36" s="20"/>
+      <c r="A36" s="26"/>
       <c r="B36" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_nuclear_LO</v>
@@ -26735,55 +26753,55 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
-      <c r="Z36" s="17"/>
-      <c r="AA36" s="17"/>
-      <c r="AB36" s="17"/>
-      <c r="AC36" s="17"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="17"/>
-      <c r="AF36" s="17"/>
-      <c r="AG36" s="17"/>
-      <c r="AH36" s="17"/>
-      <c r="AI36" s="17"/>
-      <c r="AJ36" s="17"/>
-      <c r="AK36" s="17"/>
-      <c r="AL36" s="17"/>
-      <c r="AM36" s="17"/>
-      <c r="AO36" s="17" t="str">
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="19"/>
+      <c r="AA36" s="19"/>
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="19"/>
+      <c r="AD36" s="19"/>
+      <c r="AE36" s="19"/>
+      <c r="AF36" s="19"/>
+      <c r="AG36" s="19"/>
+      <c r="AH36" s="19"/>
+      <c r="AI36" s="19"/>
+      <c r="AJ36" s="19"/>
+      <c r="AK36" s="19"/>
+      <c r="AL36" s="19"/>
+      <c r="AM36" s="19"/>
+      <c r="AO36" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP36" s="17" t="str">
+      <c r="AP36" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR36" s="44" t="s">
+      <c r="AR36" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:46">
-      <c r="A37" s="20"/>
+      <c r="A37" s="26"/>
       <c r="B37" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_oil_\I: LO</v>
@@ -26796,55 +26814,55 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
-      <c r="Z37" s="17"/>
-      <c r="AA37" s="17"/>
-      <c r="AB37" s="17"/>
-      <c r="AC37" s="17"/>
-      <c r="AD37" s="17"/>
-      <c r="AE37" s="17"/>
-      <c r="AF37" s="17"/>
-      <c r="AG37" s="17"/>
-      <c r="AH37" s="17"/>
-      <c r="AI37" s="17"/>
-      <c r="AJ37" s="17"/>
-      <c r="AK37" s="17"/>
-      <c r="AL37" s="17"/>
-      <c r="AM37" s="17"/>
-      <c r="AO37" s="17" t="str">
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="19"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="19"/>
+      <c r="AA37" s="19"/>
+      <c r="AB37" s="19"/>
+      <c r="AC37" s="19"/>
+      <c r="AD37" s="19"/>
+      <c r="AE37" s="19"/>
+      <c r="AF37" s="19"/>
+      <c r="AG37" s="19"/>
+      <c r="AH37" s="19"/>
+      <c r="AI37" s="19"/>
+      <c r="AJ37" s="19"/>
+      <c r="AK37" s="19"/>
+      <c r="AL37" s="19"/>
+      <c r="AM37" s="19"/>
+      <c r="AO37" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP37" s="17" t="str">
+      <c r="AP37" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR37" s="44" t="s">
+      <c r="AR37" s="50" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:46">
-      <c r="A38" s="20"/>
+      <c r="A38" s="26"/>
       <c r="B38" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_bioenergy_UP</v>
@@ -26857,489 +26875,489 @@
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="27">
         <f xml:space="preserve">IF(E12="","",-E12)</f>
         <v>-0.057</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="27">
         <f t="shared" ref="F38:AM39" si="21" xml:space="preserve">IF(F12="","",-F12)</f>
         <v>-0.287</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="27">
         <f t="shared" si="21"/>
         <v>-0.506</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="27">
         <f t="shared" si="21"/>
         <v>-0.564</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="27">
         <f t="shared" si="21"/>
         <v>-0.842</v>
       </c>
-      <c r="J38" s="21">
+      <c r="J38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="27">
         <f t="shared" si="21"/>
         <v>-0.436</v>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="M38" s="21">
+      <c r="M38" s="27">
         <f t="shared" si="21"/>
         <v>-0.711</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="27">
         <f t="shared" si="21"/>
         <v>-0.77</v>
       </c>
-      <c r="O38" s="21">
+      <c r="O38" s="27">
         <f t="shared" si="21"/>
         <v>-0.834</v>
       </c>
-      <c r="P38" s="21">
+      <c r="P38" s="27">
         <f t="shared" si="21"/>
         <v>-0.769</v>
       </c>
-      <c r="Q38" s="21">
+      <c r="Q38" s="27">
         <f t="shared" si="21"/>
         <v>-0.587</v>
       </c>
-      <c r="R38" s="21">
+      <c r="R38" s="27">
         <f t="shared" si="21"/>
         <v>-0.879</v>
       </c>
-      <c r="S38" s="21" t="str">
+      <c r="S38" s="27" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="T38" s="21">
+      <c r="T38" s="27">
         <f t="shared" si="21"/>
         <v>-0.655</v>
       </c>
-      <c r="U38" s="21">
+      <c r="U38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="V38" s="21">
+      <c r="V38" s="27">
         <f t="shared" si="21"/>
         <v>-0.751</v>
       </c>
-      <c r="W38" s="21">
+      <c r="W38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="X38" s="21">
+      <c r="X38" s="27">
         <f t="shared" si="21"/>
         <v>-0.462</v>
       </c>
-      <c r="Y38" s="21">
+      <c r="Y38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="Z38" s="21">
+      <c r="Z38" s="27">
         <f t="shared" si="21"/>
         <v>-0.644</v>
       </c>
-      <c r="AA38" s="21">
+      <c r="AA38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="AB38" s="21">
+      <c r="AB38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="AC38" s="21">
+      <c r="AC38" s="27">
         <f t="shared" si="21"/>
         <v>-0.564</v>
       </c>
-      <c r="AD38" s="21">
+      <c r="AD38" s="27">
         <f t="shared" si="21"/>
         <v>-0.107</v>
       </c>
-      <c r="AE38" s="21" t="str">
+      <c r="AE38" s="27" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AF38" s="21">
+      <c r="AF38" s="27">
         <f t="shared" si="21"/>
         <v>-0.189</v>
       </c>
-      <c r="AG38" s="21">
+      <c r="AG38" s="27">
         <f t="shared" si="21"/>
         <v>-0.727</v>
       </c>
-      <c r="AH38" s="21">
+      <c r="AH38" s="27">
         <f t="shared" si="21"/>
         <v>-0.476</v>
       </c>
-      <c r="AI38" s="21">
+      <c r="AI38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="AJ38" s="21">
+      <c r="AJ38" s="27">
         <f t="shared" si="21"/>
         <v>-0.56</v>
       </c>
-      <c r="AK38" s="21">
+      <c r="AK38" s="27">
         <f t="shared" si="21"/>
         <v>-0.77</v>
       </c>
-      <c r="AL38" s="21">
+      <c r="AL38" s="27">
         <f t="shared" si="21"/>
         <v>-0.41</v>
       </c>
-      <c r="AM38" s="21">
+      <c r="AM38" s="27">
         <f t="shared" si="21"/>
         <v>-0.95</v>
       </c>
-      <c r="AO38" s="17" t="str">
+      <c r="AO38" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP38" s="17" t="str">
+      <c r="AP38" s="19" t="str">
         <f t="shared" si="14"/>
         <v>elcbsl,indbio</v>
       </c>
-      <c r="AR38" s="44" t="s">
+      <c r="AR38" s="50" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:46">
-      <c r="A39" s="20"/>
-      <c r="B39" t="str">
+    <row r="39" s="13" customFormat="1" spans="1:46">
+      <c r="A39" s="4"/>
+      <c r="B39" s="13" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_coal_UP</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C39" s="13" t="str">
         <f t="shared" si="15"/>
         <v>UP</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="13">
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="28">
         <f t="shared" ref="E39:AG39" si="22" xml:space="preserve">IF(E13="","",-E13)</f>
         <v>-0.777</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="28">
         <f t="shared" si="22"/>
         <v>-0.47</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="28">
         <f t="shared" si="22"/>
         <v>-0.724</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="28">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="28">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="28">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="K39" s="21">
+      <c r="K39" s="28">
         <f t="shared" si="22"/>
         <v>-0.922</v>
       </c>
-      <c r="L39" s="21">
+      <c r="L39" s="28">
         <f t="shared" si="22"/>
         <v>-0.587</v>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="28">
         <f t="shared" si="22"/>
         <v>-0.578</v>
       </c>
-      <c r="N39" s="21">
+      <c r="N39" s="28">
         <f t="shared" si="22"/>
         <v>-0.544</v>
       </c>
-      <c r="O39" s="21">
+      <c r="O39" s="28">
         <f t="shared" si="22"/>
         <v>-0.391</v>
       </c>
-      <c r="P39" s="21">
+      <c r="P39" s="28">
         <f t="shared" si="22"/>
         <v>-0.625</v>
       </c>
-      <c r="Q39" s="21">
+      <c r="Q39" s="28">
         <f t="shared" si="22"/>
         <v>-0.597</v>
       </c>
-      <c r="R39" s="21">
+      <c r="R39" s="28">
         <f t="shared" si="22"/>
         <v>-0.431</v>
       </c>
-      <c r="S39" s="21" t="str">
+      <c r="S39" s="28" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="T39" s="21">
+      <c r="T39" s="28">
         <f t="shared" si="22"/>
         <v>-0.707</v>
       </c>
-      <c r="U39" s="21">
+      <c r="U39" s="28">
         <f t="shared" si="22"/>
         <v>-0.604</v>
       </c>
-      <c r="V39" s="21">
+      <c r="V39" s="28">
         <f t="shared" si="22"/>
         <v>-0.509</v>
       </c>
-      <c r="W39" s="21">
+      <c r="W39" s="28">
         <f t="shared" si="22"/>
         <v>-0.9</v>
       </c>
-      <c r="X39" s="21">
+      <c r="X39" s="28">
         <f t="shared" si="22"/>
         <v>-0.777</v>
       </c>
-      <c r="Y39" s="21">
+      <c r="Y39" s="28">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="Z39" s="21">
+      <c r="Z39" s="28">
         <f t="shared" si="22"/>
         <v>-0.568</v>
       </c>
-      <c r="AA39" s="21">
+      <c r="AA39" s="28">
         <f t="shared" si="22"/>
         <v>-0.95</v>
       </c>
-      <c r="AB39" s="21">
+      <c r="AB39" s="28">
         <f t="shared" si="22"/>
         <v>-0.522</v>
       </c>
-      <c r="AC39" s="21">
+      <c r="AC39" s="28">
         <f t="shared" si="22"/>
         <v>-0.7</v>
       </c>
-      <c r="AD39" s="21">
+      <c r="AD39" s="28">
         <f t="shared" si="22"/>
         <v>-0.637</v>
       </c>
-      <c r="AE39" s="21" t="str">
+      <c r="AE39" s="28" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AF39" s="21">
+      <c r="AF39" s="28">
         <f t="shared" si="22"/>
         <v>-0.671</v>
       </c>
-      <c r="AG39" s="21">
+      <c r="AG39" s="28">
         <f t="shared" si="22"/>
         <v>-0.575</v>
       </c>
-      <c r="AH39" s="21">
+      <c r="AH39" s="28">
         <f t="shared" si="21"/>
         <v>-0.351</v>
       </c>
-      <c r="AI39" s="21" t="str">
+      <c r="AI39" s="28" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AJ39" s="21">
+      <c r="AJ39" s="28">
         <f t="shared" si="21"/>
         <v>-0.679</v>
       </c>
-      <c r="AK39" s="21">
+      <c r="AK39" s="28">
         <f t="shared" si="21"/>
         <v>-0.539</v>
       </c>
-      <c r="AL39" s="21">
+      <c r="AL39" s="28">
         <f t="shared" si="21"/>
         <v>-0.319</v>
       </c>
-      <c r="AM39" s="21">
+      <c r="AM39" s="28">
         <f t="shared" si="21"/>
         <v>-0.695</v>
       </c>
-      <c r="AO39" s="17" t="str">
+      <c r="AO39" s="24" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP39" s="17" t="str">
+      <c r="AP39" s="24" t="str">
         <f t="shared" si="14"/>
         <v>???coa,elccob</v>
       </c>
-      <c r="AR39" s="44" t="s">
+      <c r="AR39" s="51" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="40" spans="1:46">
-      <c r="A40">
+    <row r="40" s="13" customFormat="1" spans="1:46">
+      <c r="A40" s="13">
         <v>0.8</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B40" s="13" t="str">
         <f t="shared" si="15"/>
         <v>UCE_utilization_gas_UP</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C40" s="13" t="str">
         <f t="shared" si="15"/>
         <v>UP</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="13">
         <f t="shared" si="16"/>
         <v>2030</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="13">
         <f xml:space="preserve">-$A40</f>
         <v>-0.8</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="13">
         <f t="shared" ref="F40:U42" si="23" xml:space="preserve">-$A40</f>
         <v>-0.8</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="13">
         <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="V40">
+      <c r="V40" s="13">
         <f t="shared" ref="V40:AK42" si="24" xml:space="preserve">-$A40</f>
         <v>-0.8</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="Z40">
+      <c r="Z40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AA40">
+      <c r="AA40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AB40">
+      <c r="AB40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AC40">
+      <c r="AC40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AD40">
+      <c r="AD40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AE40">
+      <c r="AE40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AF40">
+      <c r="AF40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AG40">
+      <c r="AG40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AH40">
+      <c r="AH40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AI40">
+      <c r="AI40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AJ40">
+      <c r="AJ40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AK40">
+      <c r="AK40" s="13">
         <f t="shared" si="24"/>
         <v>-0.8</v>
       </c>
-      <c r="AL40">
+      <c r="AL40" s="13">
         <f t="shared" ref="AL40:AM42" si="25" xml:space="preserve">-$A40</f>
         <v>-0.8</v>
       </c>
-      <c r="AM40">
+      <c r="AM40" s="13">
         <f t="shared" si="25"/>
         <v>-0.8</v>
       </c>
-      <c r="AO40" s="17" t="str">
+      <c r="AO40" s="24" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP40" s="17" t="str">
+      <c r="AP40" s="24" t="str">
         <f t="shared" si="14"/>
         <v>???nga</v>
       </c>
-      <c r="AR40" s="44" t="s">
+      <c r="AR40" s="51" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27499,15 +27517,15 @@
         <f t="shared" si="25"/>
         <v>-0.95</v>
       </c>
-      <c r="AO41" s="17" t="str">
+      <c r="AO41" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP41" s="17" t="str">
+      <c r="AP41" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???nuc</v>
       </c>
-      <c r="AR41" s="44" t="s">
+      <c r="AR41" s="50" t="s">
         <v>341</v>
       </c>
     </row>
@@ -27667,15 +27685,15 @@
         <f t="shared" si="25"/>
         <v>-0.8</v>
       </c>
-      <c r="AO42" s="17" t="str">
+      <c r="AO42" s="19" t="str">
         <f t="shared" si="19"/>
         <v>ELE,CHP</v>
       </c>
-      <c r="AP42" s="17" t="str">
+      <c r="AP42" s="19" t="str">
         <f t="shared" si="14"/>
         <v>???oil*</v>
       </c>
-      <c r="AR42" s="44" t="s">
+      <c r="AR42" s="50" t="s">
         <v>341</v>
       </c>
     </row>
@@ -29202,9 +29220,8 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>120</v>
+      <c r="L18" s="4">
+        <v>300</v>
       </c>
       <c r="M18">
         <f t="shared" si="0"/>
@@ -29354,9 +29371,8 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>60</v>
+      <c r="L19" s="4">
+        <v>100</v>
       </c>
       <c r="M19">
         <f t="shared" si="0"/>
@@ -29783,9 +29799,8 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="L22">
-        <f t="shared" si="2"/>
-        <v>250</v>
+      <c r="L22" s="4">
+        <v>400</v>
       </c>
       <c r="M22">
         <f t="shared" si="2"/>
@@ -29924,9 +29939,8 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="L23">
-        <f t="shared" si="2"/>
-        <v>100</v>
+      <c r="L23" s="4">
+        <v>150</v>
       </c>
       <c r="M23">
         <f t="shared" si="2"/>
@@ -30030,170 +30044,170 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:41">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1"/>
     <row r="27" s="1" customFormat="1"/>
     <row r="28" s="1" customFormat="1" spans="1:41">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="4"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5"/>
+      <c r="AI28" s="5"/>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="5"/>
+      <c r="AL28" s="5"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:41">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="M29" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="O29" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="P29" s="4" t="s">
+      <c r="P29" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="Q29" s="4" t="s">
+      <c r="Q29" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="R29" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="S29" s="4" t="s">
+      <c r="S29" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="T29" s="4" t="s">
+      <c r="T29" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="U29" s="4" t="s">
+      <c r="U29" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="V29" s="4" t="s">
+      <c r="V29" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="W29" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="X29" s="4" t="s">
+      <c r="X29" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="Y29" s="4" t="s">
+      <c r="Y29" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="Z29" s="4" t="s">
+      <c r="Z29" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="AA29" s="4" t="s">
+      <c r="AA29" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="AB29" s="4" t="s">
+      <c r="AB29" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="AC29" s="4" t="s">
+      <c r="AC29" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="AD29" s="4" t="s">
+      <c r="AD29" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="AE29" s="4" t="s">
+      <c r="AE29" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="AF29" s="4" t="s">
+      <c r="AF29" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="AG29" s="4" t="s">
+      <c r="AG29" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="AH29" s="4" t="s">
+      <c r="AH29" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="AI29" s="4" t="s">
+      <c r="AI29" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="AJ29" s="4" t="s">
+      <c r="AJ29" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AK29" s="4" t="s">
+      <c r="AK29" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="AL29" s="5" t="s">
+      <c r="AL29" s="6" t="s">
         <v>284</v>
       </c>
       <c r="AM29" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AN29" s="4" t="s">
+      <c r="AN29" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO29" s="1">
@@ -30204,112 +30218,112 @@
       <c r="A30" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>2030</v>
       </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5">
         <v>3</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>4</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>1.5</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="5">
         <v>0.3</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>0.2</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="5">
         <v>0.5</v>
       </c>
-      <c r="K30" s="4">
-        <v>2</v>
-      </c>
-      <c r="L30" s="4">
+      <c r="K30" s="5">
+        <v>2</v>
+      </c>
+      <c r="L30" s="5">
         <v>12</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M30" s="5">
         <v>0.2</v>
       </c>
-      <c r="N30" s="4">
+      <c r="N30" s="5">
         <v>0.3</v>
       </c>
-      <c r="O30" s="4">
-        <v>1</v>
-      </c>
-      <c r="P30" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="4">
+      <c r="O30" s="5">
+        <v>1</v>
+      </c>
+      <c r="P30" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="5">
         <v>0.4</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30" s="5">
         <v>0.6</v>
       </c>
-      <c r="S30" s="4">
-        <v>2</v>
-      </c>
-      <c r="T30" s="4">
+      <c r="S30" s="5">
+        <v>2</v>
+      </c>
+      <c r="T30" s="5">
         <v>0.3</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="5">
         <v>1.2</v>
       </c>
-      <c r="V30" s="4">
-        <v>2</v>
-      </c>
-      <c r="W30" s="4">
+      <c r="V30" s="5">
+        <v>2</v>
+      </c>
+      <c r="W30" s="5">
         <v>5</v>
       </c>
-      <c r="X30" s="4">
+      <c r="X30" s="5">
         <v>8</v>
       </c>
-      <c r="Y30" s="4">
+      <c r="Y30" s="5">
         <v>10</v>
       </c>
-      <c r="Z30" s="4">
+      <c r="Z30" s="5">
         <v>0.1</v>
       </c>
-      <c r="AA30" s="4">
+      <c r="AA30" s="5">
         <v>0.8</v>
       </c>
-      <c r="AB30" s="4">
+      <c r="AB30" s="5">
         <v>10</v>
       </c>
-      <c r="AC30" s="4">
+      <c r="AC30" s="5">
         <v>4</v>
       </c>
-      <c r="AD30" s="4">
+      <c r="AD30" s="5">
         <v>3</v>
       </c>
-      <c r="AE30" s="4">
+      <c r="AE30" s="5">
         <v>1.5</v>
       </c>
-      <c r="AF30" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="4">
+      <c r="AF30" s="5">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="5">
         <v>0.4</v>
       </c>
-      <c r="AH30" s="4">
+      <c r="AH30" s="5">
         <v>0.1</v>
       </c>
-      <c r="AI30" s="4">
+      <c r="AI30" s="5">
         <v>2.5</v>
       </c>
-      <c r="AJ30" s="4">
+      <c r="AJ30" s="5">
         <v>1.5</v>
       </c>
-      <c r="AK30" s="4">
+      <c r="AK30" s="5">
         <v>0.3</v>
       </c>
       <c r="AL30" s="1">
@@ -30329,112 +30343,112 @@
       <c r="A31" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>2040</v>
       </c>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="E31" s="4">
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
         <v>2.4</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>3.2</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="5">
         <v>1.2</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="5">
         <v>0.24</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="5">
         <v>0.16</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="5">
         <v>0.4</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="5">
         <v>1.6</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="5">
         <v>9.6</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M31" s="5">
         <v>0.16</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="5">
         <v>0.24</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="5">
         <v>0.8</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P31" s="5">
         <v>1.6</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="Q31" s="5">
         <v>0.32</v>
       </c>
-      <c r="R31" s="4">
+      <c r="R31" s="5">
         <v>0.48</v>
       </c>
-      <c r="S31" s="4">
+      <c r="S31" s="5">
         <v>1.6</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="5">
         <v>0.24</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="5">
         <v>0.96</v>
       </c>
-      <c r="V31" s="4">
+      <c r="V31" s="5">
         <v>1.6</v>
       </c>
-      <c r="W31" s="4">
+      <c r="W31" s="5">
         <v>4</v>
       </c>
-      <c r="X31" s="4">
+      <c r="X31" s="5">
         <v>6.4</v>
       </c>
-      <c r="Y31" s="4">
+      <c r="Y31" s="5">
         <v>8</v>
       </c>
-      <c r="Z31" s="4">
+      <c r="Z31" s="5">
         <v>0.08</v>
       </c>
-      <c r="AA31" s="4">
+      <c r="AA31" s="5">
         <v>0.64</v>
       </c>
-      <c r="AB31" s="4">
+      <c r="AB31" s="5">
         <v>8</v>
       </c>
-      <c r="AC31" s="4">
+      <c r="AC31" s="5">
         <v>3.2</v>
       </c>
-      <c r="AD31" s="4">
+      <c r="AD31" s="5">
         <v>2.4</v>
       </c>
-      <c r="AE31" s="4">
+      <c r="AE31" s="5">
         <v>1.2</v>
       </c>
-      <c r="AF31" s="4">
+      <c r="AF31" s="5">
         <v>0.8</v>
       </c>
-      <c r="AG31" s="4">
+      <c r="AG31" s="5">
         <v>0.32</v>
       </c>
-      <c r="AH31" s="4">
+      <c r="AH31" s="5">
         <v>0.08</v>
       </c>
-      <c r="AI31" s="4">
-        <v>2</v>
-      </c>
-      <c r="AJ31" s="4">
+      <c r="AI31" s="5">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="5">
         <v>1.2</v>
       </c>
-      <c r="AK31" s="4">
+      <c r="AK31" s="5">
         <v>0.24</v>
       </c>
       <c r="AL31" s="1">
@@ -30454,112 +30468,112 @@
       <c r="A32" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>2030</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4">
-        <v>0</v>
-      </c>
-      <c r="H32" s="4">
-        <v>0</v>
-      </c>
-      <c r="I32" s="4">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4">
-        <v>0</v>
-      </c>
-      <c r="N32" s="4">
-        <v>0</v>
-      </c>
-      <c r="O32" s="4">
-        <v>0</v>
-      </c>
-      <c r="P32" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="4">
-        <v>0</v>
-      </c>
-      <c r="R32" s="4">
-        <v>0</v>
-      </c>
-      <c r="S32" s="4">
-        <v>0</v>
-      </c>
-      <c r="T32" s="4">
-        <v>0</v>
-      </c>
-      <c r="U32" s="4">
-        <v>0</v>
-      </c>
-      <c r="V32" s="4">
-        <v>0</v>
-      </c>
-      <c r="W32" s="4">
-        <v>0</v>
-      </c>
-      <c r="X32" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="4">
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5">
+        <v>0</v>
+      </c>
+      <c r="W32" s="5">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="5">
         <v>0</v>
       </c>
       <c r="AL32" s="1">
@@ -30576,239 +30590,239 @@
       </c>
     </row>
     <row r="33" spans="1:41">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
+      <c r="AE33" s="7"/>
+      <c r="AF33" s="7"/>
+      <c r="AG33" s="7"/>
+      <c r="AH33" s="7"/>
+      <c r="AI33" s="7"/>
+      <c r="AJ33" s="7"/>
+      <c r="AK33" s="7"/>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:41">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
-      <c r="AD34" s="7"/>
-      <c r="AE34" s="7"/>
-      <c r="AF34" s="7"/>
-      <c r="AG34" s="7"/>
-      <c r="AH34" s="7"/>
-      <c r="AI34" s="7"/>
-      <c r="AJ34" s="7"/>
-      <c r="AK34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="8"/>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="8"/>
+      <c r="AB34" s="8"/>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="8"/>
+      <c r="AE34" s="8"/>
+      <c r="AF34" s="8"/>
+      <c r="AG34" s="8"/>
+      <c r="AH34" s="8"/>
+      <c r="AI34" s="8"/>
+      <c r="AJ34" s="8"/>
+      <c r="AK34" s="8"/>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:41">
-      <c r="B35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="7"/>
-      <c r="AC35" s="7"/>
-      <c r="AD35" s="7"/>
-      <c r="AE35" s="7"/>
-      <c r="AF35" s="7"/>
-      <c r="AG35" s="7"/>
-      <c r="AH35" s="7"/>
-      <c r="AI35" s="7"/>
-      <c r="AJ35" s="7"/>
-      <c r="AK35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="8"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="8"/>
+      <c r="AC35" s="8"/>
+      <c r="AD35" s="8"/>
+      <c r="AE35" s="8"/>
+      <c r="AF35" s="8"/>
+      <c r="AG35" s="8"/>
+      <c r="AH35" s="8"/>
+      <c r="AI35" s="8"/>
+      <c r="AJ35" s="8"/>
+      <c r="AK35" s="8"/>
     </row>
     <row r="36" s="2" customFormat="1" spans="1:41">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="K36" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="L36" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="M36" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="N36" s="7" t="s">
+      <c r="N36" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="O36" s="7" t="s">
+      <c r="O36" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="P36" s="7" t="s">
+      <c r="P36" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="Q36" s="7" t="s">
+      <c r="Q36" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="R36" s="7" t="s">
+      <c r="R36" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="S36" s="7" t="s">
+      <c r="S36" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="T36" s="7" t="s">
+      <c r="T36" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="U36" s="7" t="s">
+      <c r="U36" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="V36" s="7" t="s">
+      <c r="V36" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="W36" s="7" t="s">
+      <c r="W36" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="X36" s="7" t="s">
+      <c r="X36" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="Y36" s="7" t="s">
+      <c r="Y36" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="Z36" s="7" t="s">
+      <c r="Z36" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AA36" s="7" t="s">
+      <c r="AA36" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="AB36" s="7" t="s">
+      <c r="AB36" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="AC36" s="7" t="s">
+      <c r="AC36" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="AD36" s="7" t="s">
+      <c r="AD36" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="AE36" s="7" t="s">
+      <c r="AE36" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="AF36" s="7" t="s">
+      <c r="AF36" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="AG36" s="7" t="s">
+      <c r="AG36" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="AH36" s="7" t="s">
+      <c r="AH36" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="AI36" s="7" t="s">
+      <c r="AI36" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="AJ36" s="7" t="s">
+      <c r="AJ36" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="AK36" s="7" t="s">
+      <c r="AK36" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="AL36" s="7" t="s">
+      <c r="AL36" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="AM36" s="8" t="s">
+      <c r="AM36" s="9" t="s">
         <v>284</v>
       </c>
       <c r="AN36" s="2" t="s">
@@ -30819,17 +30833,17 @@
       </c>
     </row>
     <row r="37" s="2" customFormat="1" ht="16" spans="1:41">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="10">
         <v>2030</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="10">
         <v>1</v>
       </c>
       <c r="F37" s="2">
@@ -30972,12 +30986,12 @@
         <f t="shared" si="5"/>
         <v>1.66666666666667</v>
       </c>
-      <c r="AO37" s="9">
+      <c r="AO37" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:41">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="10" t="s">
         <v>373</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -31099,7 +31113,7 @@
       </c>
     </row>
     <row r="39" s="2" customFormat="1" spans="1:41">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="10" t="s">
         <v>375</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -31221,7 +31235,7 @@
       </c>
     </row>
     <row r="40" s="2" customFormat="1" spans="1:41">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="10" t="s">
         <v>371</v>
       </c>
       <c r="D40" s="2">
@@ -31369,7 +31383,7 @@
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:41">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="10" t="s">
         <v>373</v>
       </c>
       <c r="D41" s="2">
@@ -31517,7 +31531,7 @@
       </c>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:41">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="10" t="s">
         <v>375</v>
       </c>
       <c r="D42" s="2">
@@ -31665,112 +31679,112 @@
       </c>
     </row>
     <row r="44" spans="1:41">
-      <c r="A44" s="11"/>
+      <c r="A44" s="12"/>
     </row>
     <row r="47" spans="1:41">
-      <c r="F47" s="11">
+      <c r="F47" s="12">
         <v>5</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="12">
         <v>30</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="12">
         <v>10</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="12">
         <v>3</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="12">
         <v>4</v>
       </c>
-      <c r="K47" s="11">
+      <c r="K47" s="12">
         <v>5</v>
       </c>
-      <c r="L47" s="11">
+      <c r="L47" s="12">
         <v>50</v>
       </c>
-      <c r="M47" s="11">
+      <c r="M47" s="12">
         <v>150</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N47" s="12">
         <v>3</v>
       </c>
-      <c r="O47" s="11">
+      <c r="O47" s="12">
         <v>5</v>
       </c>
-      <c r="P47" s="11">
+      <c r="P47" s="12">
         <v>15</v>
       </c>
-      <c r="Q47" s="11">
+      <c r="Q47" s="12">
         <v>25</v>
       </c>
-      <c r="R47" s="11">
+      <c r="R47" s="12">
         <v>3</v>
       </c>
-      <c r="S47" s="11">
+      <c r="S47" s="12">
         <v>8</v>
       </c>
-      <c r="T47" s="11">
+      <c r="T47" s="12">
         <v>80</v>
       </c>
-      <c r="U47" s="11">
-        <v>2</v>
-      </c>
-      <c r="V47" s="11">
+      <c r="U47" s="12">
+        <v>2</v>
+      </c>
+      <c r="V47" s="12">
         <v>10</v>
       </c>
-      <c r="W47" s="11">
+      <c r="W47" s="12">
         <v>15</v>
       </c>
-      <c r="X47" s="11">
+      <c r="X47" s="12">
         <v>30</v>
       </c>
-      <c r="Y47" s="11">
+      <c r="Y47" s="12">
         <v>10</v>
       </c>
-      <c r="Z47" s="11">
+      <c r="Z47" s="12">
         <v>120</v>
       </c>
-      <c r="AA47" s="11">
+      <c r="AA47" s="12">
         <v>3</v>
       </c>
-      <c r="AB47" s="11">
+      <c r="AB47" s="12">
         <v>10</v>
       </c>
-      <c r="AC47" s="11">
+      <c r="AC47" s="12">
         <v>100</v>
       </c>
-      <c r="AD47" s="11">
+      <c r="AD47" s="12">
         <v>25</v>
       </c>
-      <c r="AE47" s="11">
+      <c r="AE47" s="12">
         <v>3</v>
       </c>
-      <c r="AF47" s="11">
+      <c r="AF47" s="12">
         <v>12</v>
       </c>
-      <c r="AG47" s="11">
+      <c r="AG47" s="12">
         <v>12</v>
       </c>
-      <c r="AH47" s="11">
+      <c r="AH47" s="12">
         <v>15</v>
       </c>
-      <c r="AI47" s="11">
-        <v>2</v>
-      </c>
-      <c r="AJ47" s="11">
+      <c r="AI47" s="12">
+        <v>2</v>
+      </c>
+      <c r="AJ47" s="12">
         <v>12</v>
       </c>
-      <c r="AK47" s="11">
+      <c r="AK47" s="12">
         <v>15</v>
       </c>
-      <c r="AL47" s="11">
+      <c r="AL47" s="12">
         <v>8</v>
       </c>
-      <c r="AM47" s="11">
+      <c r="AM47" s="12">
         <v>0.5</v>
       </c>
-      <c r="AN47" s="11">
+      <c r="AN47" s="12">
         <v>5</v>
       </c>
     </row>
